--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44089.49</v>
+        <v>44034.48</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43933.97</v>
+        <v>43878.95</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6194.44</v>
+        <v>6139.42</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1641366492905449</v>
+        <v>0.1626787615002095</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>155.52</v>
+        <v>155.53</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-04 20:54:30</t>
+          <t>2026-09-05 20:32:08</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -721,7 +721,7 @@
         <v>7054.08</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1606638205760327</v>
+        <v>0.1608648198968415</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1008.31</v>
@@ -778,7 +778,7 @@
         <v>4227.62</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09628832975294403</v>
+        <v>0.09640879177614729</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>796.91</v>
@@ -835,7 +835,7 @@
         <v>2787.37</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06348517645944139</v>
+        <v>0.06356459992456268</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1591.41</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27.43</v>
+        <v>27.19</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2333.81</v>
+        <v>2310.98</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05315488782357883</v>
+        <v>0.05270076062154141</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>408</v>
+        <v>385.17</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2118589061226185</v>
+        <v>0.2000041540961985</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-10.61</v>
+        <v>-12.6</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>109.28</v>
+        <v>109</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2005.59</v>
+        <v>1998.36</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04567934470676339</v>
+        <v>0.0455716155032339</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>359.02</v>
+        <v>351.79</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.218041140066927</v>
+        <v>0.2136501940397311</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-12.09</v>
+        <v>-13.8</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>230.04</v>
+        <v>229.5</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1859.56</v>
+        <v>1853.26</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04235336347055426</v>
+        <v>0.04226268147256914</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>606.88</v>
+        <v>600.58</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4844653063831146</v>
+        <v>0.4794360890251301</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-39.37</v>
+        <v>-40.64</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>509.97</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>476.31</v>
+        <v>476.25</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1761.98</v>
+        <v>1759.93</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04013088008337844</v>
+        <v>0.04013433679247305</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-136.57</v>
+        <v>-138.62</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.07193384424955887</v>
+        <v>-0.07301361565405178</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-12.05</v>
+        <v>-14.01</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>222.54</v>
+        <v>222.39</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1580.6</v>
+        <v>1577.89</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03599976677362283</v>
+        <v>0.03598300425668936</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-415.46</v>
+        <v>-418.17</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.2081400358706652</v>
+        <v>-0.2094977104896646</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-17.63</v>
+        <v>-19.69</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>154.51</v>
+        <v>154.5</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1438.33</v>
+        <v>1436.73</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03275942334778244</v>
+        <v>0.03276391998536863</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-433.51</v>
+        <v>-435.11</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2315956492007864</v>
+        <v>-0.2324504231130866</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-88.94</v>
+        <v>-90.8</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1231,19 +1231,19 @@
         <v>1228.34</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1432.35</v>
+        <v>1430.13</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03262322278767472</v>
+        <v>0.03261341023621365</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>204.01</v>
+        <v>201.79</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.1660859371183874</v>
+        <v>0.1642786199260791</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-44.04</v>
+        <v>-45.87</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
         <v>1343.79</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1404.05</v>
+        <v>1402.58</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03197866160856961</v>
+        <v>0.03198514605602885</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>60.26</v>
+        <v>58.79</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04484331629198014</v>
+        <v>0.04374939536683559</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-13.86</v>
+        <v>-15.25</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1247.31</v>
+        <v>1246.69</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02840874926888997</v>
+        <v>0.02843015139000314</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>332.82</v>
+        <v>332.2</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3639405570317882</v>
+        <v>0.3632625835164955</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.49</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>1142.17</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02601407922044084</v>
+        <v>0.02604662427156702</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>534.98</v>
@@ -1462,7 +1462,7 @@
         <v>1119.68</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02550184667916615</v>
+        <v>0.02553375089906771</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>366.22</v>
@@ -1485,17 +1485,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW_US_EQ</t>
+          <t>KOIDl_EQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>KraneShares Global Humanoid Robotics and Physical AI Index (Acc)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US8334451098</t>
+          <t>IE000O6Z73N7</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1504,55 +1504,55 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.3814255</v>
+        <v>52</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>187.8703632</v>
+        <v>28.53653846</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>339</v>
+        <v>28.552</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>641.99</v>
+        <v>1095.78</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1098.9</v>
+        <v>1097.31</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02502856112079851</v>
+        <v>0.02502361406746212</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>456.91</v>
+        <v>1.53</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.7117089051231328</v>
+        <v>0.001396265673766632</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-32.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KOIDl_EQ</t>
+          <t>SNOW_US_EQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KraneShares Global Humanoid Robotics and Physical AI Index (Acc)</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IE000O6Z73N7</t>
+          <t>US8334451098</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1561,38 +1561,38 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>52</v>
+        <v>4.3814255</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>28.53653846</v>
+        <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>28.552</v>
+        <v>338.16</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1095.78</v>
+        <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1098.45</v>
+        <v>1095.03</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02501831191477034</v>
+        <v>0.02497161979048131</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>2.67</v>
+        <v>453.04</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.002436620489514318</v>
+        <v>0.7056807738438293</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2.08</v>
+        <v>-33.63</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2024-11-21</t>
         </is>
       </c>
     </row>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>319.79</v>
+        <v>320.01</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>723.96</v>
+        <v>723.7</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01648892265812475</v>
+        <v>0.01650362203991792</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>232.91</v>
+        <v>232.65</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.4743101517157112</v>
+        <v>0.4737806740657774</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-20.46</v>
+        <v>-20.95</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1656,17 +1656,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US6701002056</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1675,55 +1675,55 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>57.84</v>
+        <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46.59</v>
+        <v>499.61</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>689.39</v>
+        <v>688.66</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01570155587502711</v>
+        <v>0.01570455209894967</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-178.19</v>
+        <v>154.28</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-0.2053873994329053</v>
+        <v>0.2887084097458738</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-11.72</v>
+        <v>-25.11</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>0.3650317</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US6701002056</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1732,38 +1732,38 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>20</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>369.46288902</v>
+        <v>57.84</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>499.57</v>
+        <v>46.54</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>534.38</v>
+        <v>867.58</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>689.33</v>
+        <v>687.9299999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01570018931422335</v>
+        <v>0.01568790480851283</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>154.95</v>
+        <v>-179.65</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2899621991841012</v>
+        <v>-0.2070702413610272</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-24.58</v>
+        <v>-12.62</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
         <v>666.25</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01517451892504505</v>
+        <v>0.01519350308704617</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>3.57</v>
@@ -1858,19 +1858,19 @@
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>663.35</v>
+        <v>662.66</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01510846848619683</v>
+        <v>0.01511163490530884</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>114.17</v>
+        <v>113.48</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.2078917659055319</v>
+        <v>0.2066353472449834</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-23.93</v>
+        <v>-24.47</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>326.16</v>
+        <v>326.73</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>562.26</v>
+        <v>562.66</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01280604129200125</v>
+        <v>0.01283118416053643</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>72.98999999999999</v>
+        <v>73.39</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1491814335642896</v>
+        <v>0.1499989780693687</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31.37</v>
+        <v>-31.84</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>531.86</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01211365048476467</v>
+        <v>0.01212880533114653</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>-6.51</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>338.8</v>
+        <v>338.79</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>501.32</v>
+        <v>500.78</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01141807103565266</v>
+        <v>0.01142004123967127</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>92.86</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2289664640125515</v>
+        <v>0.2276426750343205</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-9.25</v>
+        <v>-9.66</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>234.89</v>
+        <v>234.3</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>192.94</v>
+        <v>192.25</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004394404024612671</v>
+        <v>0.004384166556824955</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-3.58</v>
+        <v>-4.27</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.01821697537146346</v>
+        <v>-0.02172806838998575</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.95</v>
+        <v>-2.16</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>134</v>
+        <v>133.56</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>131.42</v>
+        <v>130.85</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.00299322368049444</v>
+        <v>0.002983969799534697</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>11.69</v>
+        <v>11.12</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.09763634845068069</v>
+        <v>0.09287563684957821</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.53</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2194,25 +2194,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>276.56</v>
+        <v>277.55</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>129.77</v>
+        <v>130.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002955643258391139</v>
+        <v>0.002966866418948903</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>29.92</v>
+        <v>30.25</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.299649474211317</v>
+        <v>0.3029544316474712</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2257,19 +2257,19 @@
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>126.16</v>
+        <v>126.02</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002873421850031796</v>
+        <v>0.002873824028562189</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>17</v>
+        <v>16.86</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.155734701355808</v>
+        <v>0.154452180285819</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.32</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2308,25 +2308,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>108.31</v>
+        <v>108.43</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.85</v>
+        <v>124.86</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002843585272483114</v>
+        <v>0.002847370799922829</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>19.57</v>
+        <v>19.58</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1858852583586626</v>
+        <v>0.1859802431610942</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>1.55804584</v>
@@ -2365,25 +2365,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>66.98</v>
+        <v>67</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>124.1</v>
+        <v>124</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002826503262436159</v>
+        <v>0.002827758923517787</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>17.29</v>
+        <v>17.19</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1618762288175264</v>
+        <v>0.160939986892613</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.27</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>2.50421091</v>
@@ -2422,25 +2422,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>50.55</v>
+        <v>50.7</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>123.74</v>
+        <v>123.98</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.00281830389761362</v>
+        <v>0.002827302833368832</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>11.03</v>
+        <v>11.27</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.09786176914204596</v>
+        <v>0.09999112767278857</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.39</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>3.30858696</v>
@@ -2479,25 +2479,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>208.5</v>
+        <v>208.63</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>121.95</v>
+        <v>121.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002777534833634888</v>
+        <v>0.002779869457877566</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>11.54</v>
+        <v>11.49</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.104519518159587</v>
+        <v>0.1040666606285663</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.37</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0.7905852</v>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>235.02053179</v>
+        <v>228.00445932</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>261.24</v>
+        <v>278.51</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>108.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>120.69</v>
+        <v>121.82</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002748837056756004</v>
+        <v>0.002778045097281748</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>11.92</v>
+        <v>21.97</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1095890410958904</v>
+        <v>0.2200300450676014</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.12</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.62445608</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>228.00445932</v>
+        <v>235.02053179</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>275.19</v>
+        <v>263.65</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>120.5</v>
+        <v>121.68</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002744509614210775</v>
+        <v>0.002774852466239067</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>20.65</v>
+        <v>12.91</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.2068102153229845</v>
+        <v>0.1186908154822102</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.3</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.62445608</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>579</v>
+        <v>579.72</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>120.11</v>
+        <v>120.13</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002735626968986358</v>
+        <v>0.002739505479695094</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>14.36</v>
+        <v>14.38</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1357919621749409</v>
+        <v>0.1359810874704492</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.24</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.28038062</v>
@@ -2707,25 +2707,25 @@
         <v>54.82621761</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>57.74</v>
+        <v>57</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>118.18</v>
+        <v>116.54</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002691669263132194</v>
+        <v>0.002657637297957765</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5.7</v>
+        <v>4.06</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.05067567567567568</v>
+        <v>0.03609530583214794</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.38</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>2.76637723</v>
@@ -2770,19 +2770,19 @@
         <v>108.23</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>116.31</v>
+        <v>116.19</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002649078118081786</v>
+        <v>0.002649655720351062</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>8.08</v>
+        <v>7.96</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.07465582555668483</v>
+        <v>0.07354707567217962</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.3</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>3.81488812</v>
@@ -2821,25 +2821,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>58</v>
+        <v>57.96</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>116.17</v>
+        <v>115.97</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002645889476206355</v>
+        <v>0.002644638728712562</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.07924563359345968</v>
+        <v>0.07738758825715347</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.28</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>2.70722512</v>
@@ -2878,25 +2878,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>88.15000000000001</v>
+        <v>88.14</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.09</v>
+        <v>112.96</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002575739354946859</v>
+        <v>0.002575997161294913</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>11.56</v>
+        <v>11.43</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1138579730129026</v>
+        <v>0.1125775632817886</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.73400968</v>
@@ -2935,25 +2935,25 @@
         <v>194.45976548</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>247.18</v>
+        <v>248.47</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>88.09</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.95</v>
+        <v>112.42</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002549774699675488</v>
+        <v>0.002563682727273142</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>23.86</v>
+        <v>24.33</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.2708593483936882</v>
+        <v>0.2761948007719378</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.61215748</v>
@@ -2992,25 +2992,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>215.75</v>
+        <v>215.25</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>111.74</v>
+        <v>111.36</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.00254499173686234</v>
+        <v>0.002539509949378554</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-7.02</v>
+        <v>-7.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.05911081172111821</v>
+        <v>-0.06231054227012462</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-1.9</v>
+        <v>-2.03</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>0</v>
@@ -3055,19 +3055,19 @@
         <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.58</v>
+        <v>110.46</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.00251857156132305</v>
+        <v>0.002518985892675602</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4.43</v>
+        <v>4.31</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.04173339613754121</v>
+        <v>0.04060292039566651</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.25</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>11.40066159</v>
@@ -3112,19 +3112,19 @@
         <v>89.66</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>110.37</v>
+        <v>110.26</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002513788598509903</v>
+        <v>0.002514424991186058</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20.71</v>
+        <v>20.6</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2309837162614321</v>
+        <v>0.2297568592460406</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>1.59010207</v>
@@ -3163,25 +3163,25 @@
         <v>306.99401668</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>358.99</v>
+        <v>358.69</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.54</v>
+        <v>108.34</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002472108493995332</v>
+        <v>0.002470640336886428</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>15.71</v>
+        <v>15.51</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1692340838091135</v>
+        <v>0.1670796078853819</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>0.40867246</v>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.5550481</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>322.35040597</v>
+        <v>221.99877812</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>332.99</v>
+        <v>262.92</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>104.04</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>107.37</v>
+        <v>107.86</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002445460558322082</v>
+        <v>0.00245969417331152</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3.33</v>
+        <v>16.68</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.03200692041522491</v>
+        <v>0.1829348541346786</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.5550481</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.42255419</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>324.07677699</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>1124.29</v>
+        <v>342.88</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>98.89</v>
+        <v>101.39</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>106.94</v>
+        <v>107.08</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002435666872561828</v>
+        <v>0.002441906657502295</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>5.69</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.08140357973505917</v>
+        <v>0.05611993293224184</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.42255419</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>176.50746647</v>
+        <v>322.35040597</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>210.75</v>
+        <v>332.39</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>106.8</v>
+        <v>107.07</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002432478230686396</v>
+        <v>0.002441678612427818</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>17.34</v>
+        <v>3.03</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1938296445338699</v>
+        <v>0.02912341407151095</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.2</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.68495686</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>324.07677699</v>
+        <v>176.50746647</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>341.58</v>
+        <v>210.59</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>101.39</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>106.79</v>
+        <v>106.61</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002432250470552437</v>
+        <v>0.002431188539001865</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>5.4</v>
+        <v>17.15</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.05325969030476379</v>
+        <v>0.1917057902973396</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.68495686</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>221.99877812</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>259</v>
+        <v>1121.73</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>106.36</v>
+        <v>106.59</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002422456784792183</v>
+        <v>0.00243073244885291</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>15.18</v>
+        <v>7.7</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1664838780434306</v>
+        <v>0.0778642936596218</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1.35094641</v>
+        <v>13.30225117</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.717382</v>
+        <v>10.85229847</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>105.25</v>
+        <v>10.77</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.96</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>105.2</v>
+        <v>105.88</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002396036609252892</v>
+        <v>0.002414541248565026</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>8.52</v>
+        <v>-1.08</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.08812577575506826</v>
+        <v>-0.01009723261032162</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.27</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>1.35094641</v>
+        <v>13.30225117</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>10.85229847</v>
+        <v>96.717382</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>10.67</v>
+        <v>105.14</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>105.01</v>
+        <v>104.98</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002391709166707664</v>
+        <v>0.002394017191862074</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>-1.95</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>-0.01823111443530292</v>
+        <v>0.08585022755482002</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.11</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.80409618</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>257.81779936</v>
+        <v>148.63893521</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>279.28</v>
+        <v>176.3</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>104.71</v>
+        <v>104.77</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002384876362688882</v>
+        <v>0.002389228245298052</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>16.33</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.08305750930906081</v>
+        <v>0.1846449570330167</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.80409618</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.50675322</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>148.63893521</v>
+        <v>257.81779936</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>175.4</v>
+        <v>279.28</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>88.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>104.35</v>
+        <v>104.6</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002376676997866343</v>
+        <v>0.002385351479031939</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>15.91</v>
+        <v>7.92</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1798959746720941</v>
+        <v>0.08191973520893669</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.12</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.50675322</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3739,19 +3739,19 @@
         <v>89.53</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>103.79</v>
+        <v>103.68</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002363922430364617</v>
+        <v>0.002364371332180034</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>14.26</v>
+        <v>14.15</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1592762202613649</v>
+        <v>0.158047581816151</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>1.1533463</v>
@@ -3796,19 +3796,19 @@
         <v>95.94</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>103.68</v>
+        <v>103.58</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002361417068891064</v>
+        <v>0.002362090881435261</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>7.74</v>
+        <v>7.64</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.08067542213883677</v>
+        <v>0.07963310402334793</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>0.51881442</v>
@@ -3847,25 +3847,25 @@
         <v>74.99726962</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>80.20999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>103.38</v>
+        <v>103.39</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002354584264872282</v>
+        <v>0.002357758025020193</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.06930078609846918</v>
+        <v>0.06940422010757137</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>1.74206342</v>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>62.95787236</v>
+        <v>113.12478542</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>61.35</v>
+        <v>118.6</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>103.3</v>
+        <v>103.39</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002352762183800606</v>
+        <v>0.002357758025020193</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-2.85</v>
+        <v>4.67</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.02684879886952426</v>
+        <v>0.04730551053484603</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>2.27580753</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>137.713206</v>
+        <v>62.95787236</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>152.82</v>
+        <v>61.35</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>102.37</v>
+        <v>103.19</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002331580491342382</v>
+        <v>0.002353197123530648</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>10.1</v>
+        <v>-2.96</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1094613633900509</v>
+        <v>-0.02788506829957607</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.26</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>2.27580753</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4024,19 +4024,19 @@
         <v>88.89</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>102.36</v>
+        <v>102.25</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002331352731208422</v>
+        <v>0.002331760886529788</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>13.47</v>
+        <v>13.36</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1515356058049274</v>
+        <v>0.1502981212734841</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>0.10445851</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>113.12478542</v>
+        <v>137.713206</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>117.21</v>
+        <v>152</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>98.72</v>
+        <v>92.27</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>102.28</v>
+        <v>101.72</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002329530650136747</v>
+        <v>0.002319674497582494</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>3.56</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.03606158833063209</v>
+        <v>0.1024168202015823</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4132,25 +4132,25 @@
         <v>105.04894536</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>24.18</v>
+        <v>24.1</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>101.82</v>
+        <v>101.37</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002319053683974615</v>
+        <v>0.002311692919975791</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-351.14</v>
+        <v>-351.59</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.7752119392440834</v>
+        <v>-0.7762054044507241</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-10.62</v>
+        <v>-11.09</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>0</v>
@@ -4189,25 +4189,25 @@
         <v>341.38450299</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>357.15</v>
+        <v>360.35</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>99.91</v>
+        <v>100.7</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002275551498388369</v>
+        <v>0.002296413899985816</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>4.4</v>
+        <v>5.19</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.04606847450528741</v>
+        <v>0.05433985970055492</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.11</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>0.37810738</v>
@@ -4246,25 +4246,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>72.62</v>
+        <v>72.91</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>99.88</v>
+        <v>100.18</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002274868217986491</v>
+        <v>0.002284555556112999</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.04858068203467326</v>
+        <v>-0.04572299485616307</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.22</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>1.85908491</v>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>127.23134407</v>
+        <v>147.21071381</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>120.15</v>
+        <v>147.35</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>105.36</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>99.38</v>
+        <v>99.8</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002263480211288521</v>
+        <v>0.002275889843282864</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-5.98</v>
+        <v>-0.05</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.0567577828397874</v>
+        <v>-0.0005007511266900351</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.11796351</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>147.21071381</v>
+        <v>127.23134407</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>146.54</v>
+        <v>120.38</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.36</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>99.34999999999999</v>
+        <v>99.47</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002262796930886643</v>
+        <v>0.002268364355825115</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-0.5</v>
+        <v>-5.89</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.005007511266900351</v>
+        <v>-0.05590356871678056</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.23</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.11796351</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>137.8</v>
+        <v>137.82</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>99.20999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002259608289011211</v>
+        <v>0.002260382778218412</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-12.23</v>
+        <v>-12.32</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1097451543431443</v>
+        <v>-0.1105527638190955</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.97307689</v>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>112.53</v>
+        <v>110.97</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>97.04000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002210184339942022</v>
+        <v>0.002180110912002423</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4.27</v>
+        <v>2.83</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.04602781071467069</v>
+        <v>0.03050555136358737</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4531,25 +4531,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>137.94</v>
+        <v>137.75</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>95.38</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002172376157704761</v>
+        <v>0.002169848883650947</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>7</v>
+        <v>6.77</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.07920343969223807</v>
+        <v>0.07660104095949309</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.11</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.93456659</v>
@@ -4588,25 +4588,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>204.26</v>
+        <v>204.44</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>93.92</v>
+        <v>93.91</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002139123178146689</v>
+        <v>0.002141571294415769</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-13.9</v>
+        <v>-13.91</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1289185679836765</v>
+        <v>-0.1290113151548878</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.28</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.6214908</v>
@@ -4645,25 +4645,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>107.17</v>
+        <v>107.15</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>93.01000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002118397005956383</v>
+        <v>0.002118538741893568</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.44</v>
+        <v>-17.55</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1578995020371209</v>
+        <v>-0.1588954277953825</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.34</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.17308322</v>
@@ -4708,19 +4708,19 @@
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>82.27</v>
+        <v>82.19</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001873782622083987</v>
+        <v>0.001874302467128442</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-28.26</v>
+        <v>-28.34</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2556771917126572</v>
+        <v>-0.2564009771102868</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.34</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>109.78</v>
+        <v>110.63</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>51.35</v>
+        <v>51.69</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001169548287881521</v>
+        <v>0.001178764989972858</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3.48</v>
+        <v>3.82</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.07269688740338417</v>
+        <v>0.0797994568623355</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>255.99</v>
+        <v>256.01</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.9</v>
+        <v>45.86</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001045419014873648</v>
+        <v>0.001045814711552627</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.21</v>
+        <v>-6.25</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1191709844559586</v>
+        <v>-0.1199385914411821</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-04 20:54:29</t>
+          <t>2026-09-05 20:32:08</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44089.49</v>
+        <v>44034.48</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43933.97</v>
+        <v>43878.95</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37739.53</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6194.44</v>
+        <v>6139.42</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1641366492905449</v>
+        <v>0.1626787615002095</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>183.49</v>
+        <v>183.5</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5076,7 +5076,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>27.43</v>
+        <v>27.19</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2333.81</v>
+        <v>2310.98</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>408</v>
+        <v>385.17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>109.28</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2005.59</v>
+        <v>1998.36</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>359.02</v>
+        <v>351.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D7" t="n">
-        <v>230.04</v>
+        <v>229.5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1859.56</v>
+        <v>1853.26</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>606.88</v>
+        <v>600.58</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>476.31</v>
+        <v>476.25</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1761.98</v>
+        <v>1759.93</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-136.57</v>
+        <v>-138.62</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>222.54</v>
+        <v>222.39</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1580.6</v>
+        <v>1577.89</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-415.46</v>
+        <v>-418.17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>154.51</v>
+        <v>154.5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1438.33</v>
+        <v>1436.73</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-433.51</v>
+        <v>-435.11</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5280,19 +5280,19 @@
         <v>44.81</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1432.35</v>
+        <v>1430.13</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>204.01</v>
+        <v>201.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5307,19 +5307,19 @@
         <v>119.34</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1404.05</v>
+        <v>1402.58</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>60.26</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5334,19 +5334,19 @@
         <v>450.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1247.31</v>
+        <v>1246.69</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>332.82</v>
+        <v>332.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5400,61 +5400,61 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SNOW_US_EQ</t>
+          <t>KOIDl_EQ</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.3814255</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>339</v>
+        <v>28.552</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1098.9</v>
+        <v>1097.31</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>641.99</v>
+        <v>1095.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>456.91</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KOIDl_EQ</t>
+          <t>SNOW_US_EQ</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>52</v>
+        <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>28.552</v>
+        <v>338.16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1098.45</v>
+        <v>1095.03</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1095.78</v>
+        <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>2.67</v>
+        <v>453.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,76 +5466,76 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>319.79</v>
+        <v>320.01</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>723.96</v>
+        <v>723.7</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>232.91</v>
+        <v>232.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>46.59</v>
+        <v>499.61</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>689.39</v>
+        <v>688.66</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-178.19</v>
+        <v>154.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>499.57</v>
+        <v>46.54</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>689.33</v>
+        <v>687.9299999999999</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>534.38</v>
+        <v>867.58</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>154.95</v>
+        <v>-179.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5562,7 +5562,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5577,19 +5577,19 @@
         <v>97.5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>663.35</v>
+        <v>662.66</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>114.17</v>
+        <v>113.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>326.16</v>
+        <v>326.73</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>562.26</v>
+        <v>562.66</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>72.98999999999999</v>
+        <v>73.39</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5643,7 +5643,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>338.8</v>
+        <v>338.79</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>501.32</v>
+        <v>500.78</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>93.40000000000001</v>
+        <v>92.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>234.89</v>
+        <v>234.3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>192.94</v>
+        <v>192.25</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-3.58</v>
+        <v>-4.27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,22 +5709,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>134</v>
+        <v>133.56</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>131.42</v>
+        <v>130.85</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>11.69</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5736,22 +5736,22 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>276.56</v>
+        <v>277.55</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>129.77</v>
+        <v>130.1</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>29.92</v>
+        <v>30.25</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5766,19 +5766,19 @@
         <v>405.89</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.16</v>
+        <v>126.02</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>17</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5790,22 +5790,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D30" t="n">
-        <v>108.31</v>
+        <v>108.43</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.85</v>
+        <v>124.86</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>19.57</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5817,22 +5817,22 @@
         <v>2.50421091</v>
       </c>
       <c r="D31" t="n">
-        <v>66.98</v>
+        <v>67</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>124.1</v>
+        <v>124</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>17.29</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5844,22 +5844,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D32" t="n">
-        <v>50.55</v>
+        <v>50.7</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>123.74</v>
+        <v>123.98</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.03</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5871,76 +5871,76 @@
         <v>0.7905852</v>
       </c>
       <c r="D33" t="n">
-        <v>208.5</v>
+        <v>208.63</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>121.95</v>
+        <v>121.9</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>11.54</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="D34" t="n">
-        <v>261.24</v>
+        <v>278.51</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>120.69</v>
+        <v>121.82</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>108.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11.92</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.62445608</v>
       </c>
       <c r="D35" t="n">
-        <v>275.19</v>
+        <v>263.65</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>120.5</v>
+        <v>121.68</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>20.65</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5952,22 +5952,22 @@
         <v>0.28038062</v>
       </c>
       <c r="D36" t="n">
-        <v>579</v>
+        <v>579.72</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>120.11</v>
+        <v>120.13</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>14.36</v>
+        <v>14.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,22 +5979,22 @@
         <v>2.76637723</v>
       </c>
       <c r="D37" t="n">
-        <v>57.74</v>
+        <v>57</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>118.18</v>
+        <v>116.54</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5.7</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6009,19 +6009,19 @@
         <v>41.21</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>116.31</v>
+        <v>116.19</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.08</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6033,22 +6033,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>58</v>
+        <v>57.96</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>116.17</v>
+        <v>115.97</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6060,22 +6060,22 @@
         <v>1.73400968</v>
       </c>
       <c r="D40" t="n">
-        <v>88.15000000000001</v>
+        <v>88.14</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.09</v>
+        <v>112.96</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>11.56</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,22 +6087,22 @@
         <v>0.61215748</v>
       </c>
       <c r="D41" t="n">
-        <v>247.18</v>
+        <v>248.47</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.95</v>
+        <v>112.42</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>88.09</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>23.86</v>
+        <v>24.33</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6114,22 +6114,22 @@
         <v>0.7</v>
       </c>
       <c r="D42" t="n">
-        <v>215.75</v>
+        <v>215.25</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>111.74</v>
+        <v>111.36</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-7.02</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6144,19 +6144,19 @@
         <v>13.11</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.58</v>
+        <v>110.46</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>4.43</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6171,19 +6171,19 @@
         <v>93.81999999999999</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>110.37</v>
+        <v>110.26</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20.71</v>
+        <v>20.6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6195,265 +6195,265 @@
         <v>0.40867246</v>
       </c>
       <c r="D45" t="n">
-        <v>358.99</v>
+        <v>358.69</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.54</v>
+        <v>108.34</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>15.71</v>
+        <v>15.51</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.5550481</v>
       </c>
       <c r="D46" t="n">
-        <v>332.99</v>
+        <v>262.92</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>107.37</v>
+        <v>107.86</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>104.04</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>3.33</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.42255419</v>
       </c>
       <c r="D47" t="n">
-        <v>1124.29</v>
+        <v>342.88</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>106.94</v>
+        <v>107.08</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>98.89</v>
+        <v>101.39</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>8.050000000000001</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="D48" t="n">
-        <v>210.75</v>
+        <v>332.39</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>106.8</v>
+        <v>107.07</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>17.34</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.68495686</v>
       </c>
       <c r="D49" t="n">
-        <v>341.58</v>
+        <v>210.59</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>106.79</v>
+        <v>106.61</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>101.39</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>5.4</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="D50" t="n">
-        <v>259</v>
+        <v>1121.73</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>106.36</v>
+        <v>106.59</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>15.18</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1.35094641</v>
+        <v>13.30225117</v>
       </c>
       <c r="D51" t="n">
-        <v>105.25</v>
+        <v>10.77</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>105.2</v>
+        <v>105.88</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.96</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>8.52</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="D52" t="n">
-        <v>10.67</v>
+        <v>105.14</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>105.01</v>
+        <v>104.98</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-1.95</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.80409618</v>
       </c>
       <c r="D53" t="n">
-        <v>279.28</v>
+        <v>176.3</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>104.71</v>
+        <v>104.77</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>8.029999999999999</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.50675322</v>
       </c>
       <c r="D54" t="n">
-        <v>175.4</v>
+        <v>279.28</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>104.35</v>
+        <v>104.6</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>88.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>15.91</v>
+        <v>7.92</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6468,19 +6468,19 @@
         <v>121.63</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>103.79</v>
+        <v>103.68</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>14.26</v>
+        <v>14.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6495,19 +6495,19 @@
         <v>270.12</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>103.68</v>
+        <v>103.58</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>7.74</v>
+        <v>7.64</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6519,76 +6519,76 @@
         <v>1.74206342</v>
       </c>
       <c r="D57" t="n">
-        <v>80.20999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>103.38</v>
+        <v>103.39</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6.7</v>
+        <v>6.71</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="D58" t="n">
-        <v>61.35</v>
+        <v>118.6</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>103.3</v>
+        <v>103.39</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-2.85</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>2.27580753</v>
       </c>
       <c r="D59" t="n">
-        <v>152.82</v>
+        <v>61.35</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>102.37</v>
+        <v>103.19</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>10.1</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6603,46 +6603,46 @@
         <v>1324.49</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>102.36</v>
+        <v>102.25</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>13.47</v>
+        <v>13.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="D61" t="n">
-        <v>117.21</v>
+        <v>152</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>102.28</v>
+        <v>101.72</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>98.72</v>
+        <v>92.27</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>3.56</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6654,22 +6654,22 @@
         <v>5.691347</v>
       </c>
       <c r="D62" t="n">
-        <v>24.18</v>
+        <v>24.1</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>101.82</v>
+        <v>101.37</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-351.14</v>
+        <v>-351.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6681,22 +6681,22 @@
         <v>0.37810738</v>
       </c>
       <c r="D63" t="n">
-        <v>357.15</v>
+        <v>360.35</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>99.91</v>
+        <v>100.7</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>4.4</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6708,76 +6708,76 @@
         <v>1.85908491</v>
       </c>
       <c r="D64" t="n">
-        <v>72.62</v>
+        <v>72.91</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>99.88</v>
+        <v>100.18</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-5.1</v>
+        <v>-4.8</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D65" t="n">
-        <v>120.15</v>
+        <v>147.35</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>99.38</v>
+        <v>99.8</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>105.36</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-5.98</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.11796351</v>
       </c>
       <c r="D66" t="n">
-        <v>146.54</v>
+        <v>120.38</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>99.34999999999999</v>
+        <v>99.47</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.36</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.5</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6789,22 +6789,22 @@
         <v>0.97307689</v>
       </c>
       <c r="D67" t="n">
-        <v>137.8</v>
+        <v>137.82</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>99.20999999999999</v>
+        <v>99.12</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-12.23</v>
+        <v>-12.32</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,22 +6816,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>112.53</v>
+        <v>110.97</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>97.04000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4.27</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6843,22 +6843,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>137.94</v>
+        <v>137.75</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>95.38</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>7</v>
+        <v>6.77</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6870,22 +6870,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D70" t="n">
-        <v>204.26</v>
+        <v>204.44</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>93.92</v>
+        <v>93.91</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-13.9</v>
+        <v>-13.91</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D71" t="n">
-        <v>107.17</v>
+        <v>107.15</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>93.01000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.44</v>
+        <v>-17.55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6927,19 +6927,19 @@
         <v>60.21</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>82.27</v>
+        <v>82.19</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-28.26</v>
+        <v>-28.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>109.78</v>
+        <v>110.63</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>51.35</v>
+        <v>51.69</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>3.48</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>255.99</v>
+        <v>256.01</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.9</v>
+        <v>45.86</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.21</v>
+        <v>-6.25</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44034.48</v>
+        <v>44034.5</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>155.53</v>
+        <v>155.55</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-05 20:32:08</t>
+          <t>2026-09-06 20:35:31</t>
         </is>
       </c>
     </row>
@@ -4926,16 +4926,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05 20:32:08</t>
+          <t>2026-09-06 20:35:31</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44034.48</v>
+        <v>44034.5</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>43878.95</v>
@@ -4953,7 +4953,7 @@
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>183.5</v>
+        <v>183.52</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5076,7 +5076,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5157,7 +5157,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5184,7 +5184,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5238,7 +5238,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5454,7 +5454,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5481,7 +5481,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5508,7 +5508,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5535,7 +5535,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5562,7 +5562,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5616,7 +5616,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5643,7 +5643,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5697,7 +5697,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5724,7 +5724,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5751,7 +5751,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5805,7 +5805,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5832,7 +5832,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5940,7 +5940,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5994,7 +5994,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6021,7 +6021,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6075,7 +6075,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6129,7 +6129,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6156,7 +6156,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6237,7 +6237,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6264,7 +6264,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6291,7 +6291,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6372,7 +6372,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6426,7 +6426,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6480,7 +6480,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6588,7 +6588,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6615,7 +6615,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6642,7 +6642,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6723,7 +6723,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6750,7 +6750,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6777,7 +6777,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6804,7 +6804,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6831,7 +6831,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6885,7 +6885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44034.5</v>
+        <v>44071.5</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43878.95</v>
+        <v>43915.93</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6139.42</v>
+        <v>6176.4</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1626787615002095</v>
+        <v>0.1636586359183593</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>155.55</v>
+        <v>155.57</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-06 20:35:31</t>
+          <t>2026-09-07 21:38:36</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>110.22</v>
+        <v>109.94</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7054.08</v>
+        <v>7036.16</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1608648198968415</v>
+        <v>0.1603200860367935</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1008.31</v>
+        <v>990.39</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1667794176754987</v>
+        <v>0.1638153618149549</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.578</v>
+        <v>14.93</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4227.62</v>
+        <v>4329.7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09640879177614729</v>
+        <v>0.0986529408816037</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>796.91</v>
+        <v>898.99</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2322871941959536</v>
+        <v>0.2620419679891334</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1580.2</v>
+        <v>1579</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2787.37</v>
+        <v>2785.25</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06356459992456268</v>
+        <v>0.0634623885235667</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1591.41</v>
+        <v>1589.29</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.330654871400381</v>
+        <v>1.328882236864109</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -889,19 +889,19 @@
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2310.98</v>
+        <v>2307.74</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05270076062154141</v>
+        <v>0.05258224306305567</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>385.17</v>
+        <v>381.93</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2000041540961985</v>
+        <v>0.198321745135813</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-12.6</v>
+        <v>-15.28</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -946,19 +946,19 @@
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1998.36</v>
+        <v>1995.56</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0455716155032339</v>
+        <v>0.04546916938949421</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>351.79</v>
+        <v>348.99</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2136501940397311</v>
+        <v>0.2119496893542334</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-13.8</v>
+        <v>-16.09</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -1003,19 +1003,19 @@
         <v>1252.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1853.26</v>
+        <v>1850.66</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04226268147256914</v>
+        <v>0.04216759858002835</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>600.58</v>
+        <v>597.98</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4794360890251301</v>
+        <v>0.4773605390043746</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-40.64</v>
+        <v>-42.34</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1060,19 +1060,19 @@
         <v>1898.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1759.93</v>
+        <v>1757.46</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04013433679247305</v>
+        <v>0.04004402094412621</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-138.62</v>
+        <v>-141.09</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.07301361565405178</v>
+        <v>-0.07431460851702615</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-14.01</v>
+        <v>-16.66</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1117,19 +1117,19 @@
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1577.89</v>
+        <v>1575.67</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03598300425668936</v>
+        <v>0.03590190529572869</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-418.17</v>
+        <v>-420.39</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.2094977104896646</v>
+        <v>-0.2106099015059668</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-19.69</v>
+        <v>-22.47</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1174,19 +1174,19 @@
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1436.73</v>
+        <v>1434.72</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03276391998536863</v>
+        <v>0.03269033589894322</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-435.11</v>
+        <v>-437.12</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2324504231130866</v>
+        <v>-0.2335242328404137</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-90.8</v>
+        <v>-93.3</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>37.05</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>44.81</v>
+        <v>44.36</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1430.13</v>
+        <v>1414.94</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03261341023621365</v>
+        <v>0.0322396452805082</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>201.79</v>
+        <v>186.6</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.1642786199260791</v>
+        <v>0.1519123369751046</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-45.87</v>
+        <v>-46.57</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
         <v>1343.79</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1402.58</v>
+        <v>1400.62</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03198514605602885</v>
+        <v>0.03191336167808203</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>58.79</v>
+        <v>56.83</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04374939536683559</v>
+        <v>0.04229083413330952</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-15.25</v>
+        <v>-17.11</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>450.6</v>
+        <v>447.4</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1246.69</v>
+        <v>1236.64</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02843015139000314</v>
+        <v>0.02817704986761817</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>332.2</v>
+        <v>322.15</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3632625835164955</v>
+        <v>0.3522728515347352</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0.49</v>
+        <v>-0.4</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>112.6</v>
+        <v>113.35</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1142.17</v>
+        <v>1149.78</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02604662427156702</v>
+        <v>0.02619793019536002</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>534.98</v>
+        <v>542.59</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8810751165203643</v>
+        <v>0.893608261005616</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>699.8</v>
+        <v>700</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1119.68</v>
+        <v>1120</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02553375089906771</v>
+        <v>0.0255193878992531</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>366.22</v>
+        <v>366.54</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4860510179704298</v>
+        <v>0.4864757253205214</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.552</v>
+        <v>28.795</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1097.31</v>
+        <v>1105.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02502361406746212</v>
+        <v>0.02517988889952196</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1.53</v>
+        <v>9.32</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.001396265673766632</v>
+        <v>0.008505356914709158</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.6</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1573,19 +1573,19 @@
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1095.03</v>
+        <v>1093.5</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02497161979048131</v>
+        <v>0.02491558095342256</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>453.04</v>
+        <v>451.51</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.7056807738438293</v>
+        <v>0.7032975591520116</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-33.63</v>
+        <v>-34.48</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1630,19 +1630,19 @@
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>723.7</v>
+        <v>722.6900000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01650362203991792</v>
+        <v>0.01646661289367074</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>232.65</v>
+        <v>231.64</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.4737806740657774</v>
+        <v>0.4717238570410345</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-20.95</v>
+        <v>-21.6</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1687,19 +1687,19 @@
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>688.66</v>
+        <v>687.7</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01570455209894967</v>
+        <v>0.01566935987349675</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>154.28</v>
+        <v>153.32</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2887084097458738</v>
+        <v>0.2869119353269209</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.11</v>
+        <v>-25.82</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1744,19 +1744,19 @@
         <v>867.58</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>687.9299999999999</v>
+        <v>686.97</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01568790480851283</v>
+        <v>0.0156527267010267</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-179.65</v>
+        <v>-180.61</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.2070702413610272</v>
+        <v>-0.2081767675603403</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-12.62</v>
+        <v>-13.81</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
         <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>666.25</v>
+        <v>663</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01519350308704617</v>
+        <v>0.01510656622964715</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3.57</v>
+        <v>0.32</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.005387215548982918</v>
+        <v>0.000482887668256172</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -1858,19 +1858,19 @@
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>662.66</v>
+        <v>661.73</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01511163490530884</v>
+        <v>0.01507762906658282</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>113.48</v>
+        <v>112.55</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.2066353472449834</v>
+        <v>0.2049419133981573</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-24.47</v>
+        <v>-25.21</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1915,19 +1915,19 @@
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>562.66</v>
+        <v>561.87</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01283118416053643</v>
+        <v>0.0128023022133512</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>73.39</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1499989780693687</v>
+        <v>0.1483843276718376</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31.84</v>
+        <v>-32.49</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.799</v>
+        <v>3.796</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>531.86</v>
+        <v>531.4400000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01212880533114653</v>
+        <v>0.0121089495581956</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-6.51</v>
+        <v>-6.93</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.01209205564946041</v>
+        <v>-0.01287218827200624</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2029,19 +2029,19 @@
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>500.78</v>
+        <v>500.08</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01142004123967127</v>
+        <v>0.01139440669701651</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>92.86</v>
+        <v>92.16</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2276426750343205</v>
+        <v>0.2259266522847617</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-9.66</v>
+        <v>-10.22</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2086,19 +2086,19 @@
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>192.25</v>
+        <v>191.98</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004384166556824955</v>
+        <v>0.004374296507945187</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-4.27</v>
+        <v>-4.54</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.02172806838998575</v>
+        <v>-0.02310197435375534</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-2.16</v>
+        <v>-2.43</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2143,19 +2143,19 @@
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.85</v>
+        <v>130.67</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002983969799534697</v>
+        <v>0.002977337872138752</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>11.12</v>
+        <v>10.94</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.09287563684957821</v>
+        <v>0.09137225423870374</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.7</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2200,19 +2200,19 @@
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>130.1</v>
+        <v>129.92</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002966866418948903</v>
+        <v>0.002960248996313359</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>30.25</v>
+        <v>30.07</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3029544316474712</v>
+        <v>0.3011517275913871</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.25</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2257,19 +2257,19 @@
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>126.02</v>
+        <v>125.85</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002873824028562189</v>
+        <v>0.002867513363500895</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>16.86</v>
+        <v>16.69</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.154452180285819</v>
+        <v>0.1528948332722609</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.47</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2314,19 +2314,19 @@
         <v>105.28</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.86</v>
+        <v>124.68</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002847370799922829</v>
+        <v>0.002840854717213283</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>19.58</v>
+        <v>19.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1859802431610942</v>
+        <v>0.1842705167173252</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.41</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>1.55804584</v>
@@ -2371,19 +2371,19 @@
         <v>106.81</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>124</v>
+        <v>123.83</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002827758923517787</v>
+        <v>0.002821487324611171</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>17.19</v>
+        <v>17.02</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.160939986892613</v>
+        <v>0.1593483756202603</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.41</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>2.50421091</v>
@@ -2428,19 +2428,19 @@
         <v>112.71</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>123.98</v>
+        <v>123.8</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002827302833368832</v>
+        <v>0.002820803769578155</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>11.27</v>
+        <v>11.09</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.09999112767278857</v>
+        <v>0.09839410877473162</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.55</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>3.30858696</v>
@@ -2485,19 +2485,19 @@
         <v>110.41</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>121.9</v>
+        <v>121.73</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002779869457877566</v>
+        <v>0.002773638472300071</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>11.49</v>
+        <v>11.32</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1040666606285663</v>
+        <v>0.1025269450230957</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.53</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0.7905852</v>
@@ -2542,19 +2542,19 @@
         <v>99.84999999999999</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>121.82</v>
+        <v>121.65</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002778045097281748</v>
+        <v>0.002771815658878696</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>21.97</v>
+        <v>21.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.2200300450676014</v>
+        <v>0.2183274912368553</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0.59183053</v>
@@ -2599,19 +2599,19 @@
         <v>108.77</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>121.68</v>
+        <v>121.51</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002774852466239067</v>
+        <v>0.002768625735391289</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.91</v>
+        <v>12.74</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1186908154822102</v>
+        <v>0.1171278845269836</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.45</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>0.62445608</v>
@@ -2656,19 +2656,19 @@
         <v>105.75</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>120.13</v>
+        <v>119.96</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002739505479695094</v>
+        <v>0.002733308725352144</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>14.38</v>
+        <v>14.21</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1359810874704492</v>
+        <v>0.1343735224586289</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.39</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.28038062</v>
@@ -2713,19 +2713,19 @@
         <v>112.48</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.54</v>
+        <v>116.38</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002657637297957765</v>
+        <v>0.002651737824745603</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.03609530583214794</v>
+        <v>0.0346728307254623</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.54</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>2.76637723</v>
@@ -2770,19 +2770,19 @@
         <v>108.23</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>116.19</v>
+        <v>116.03</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002649655720351062</v>
+        <v>0.002643763016027087</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>7.96</v>
+        <v>7.8</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.07354707567217962</v>
+        <v>0.07206874249283932</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.45</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>3.81488812</v>
@@ -2827,19 +2827,19 @@
         <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>115.97</v>
+        <v>115.81</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002644638728712562</v>
+        <v>0.002638750279118305</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>8.33</v>
+        <v>8.17</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.07738758825715347</v>
+        <v>0.07590115198810851</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.43</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>2.70722512</v>
@@ -2884,19 +2884,19 @@
         <v>101.53</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.96</v>
+        <v>112.8</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002575997161294913</v>
+        <v>0.002570166924139062</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1125775632817886</v>
+        <v>0.1110016743819561</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.29</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.73400968</v>
@@ -2941,19 +2941,19 @@
         <v>88.09</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>112.42</v>
+        <v>112.26</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002563682727273142</v>
+        <v>0.002557862933544779</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>24.33</v>
+        <v>24.17</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.2761948007719378</v>
+        <v>0.2743784765580656</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.23</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.61215748</v>
@@ -2998,19 +2998,19 @@
         <v>118.76</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>111.36</v>
+        <v>111.2</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002539509949378554</v>
+        <v>0.002533710655711558</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-7.4</v>
+        <v>-7.56</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.06231054227012462</v>
+        <v>-0.06365779723812731</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-2.03</v>
+        <v>-2.2</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>0</v>
@@ -3055,19 +3055,19 @@
         <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.46</v>
+        <v>110.31</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002518985892675602</v>
+        <v>0.002513431856398758</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4.31</v>
+        <v>4.16</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.04060292039566651</v>
+        <v>0.03918982571832313</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.4</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>11.40066159</v>
@@ -3112,19 +3112,19 @@
         <v>89.66</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>110.26</v>
+        <v>110.1</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002514424991186058</v>
+        <v>0.002508646971167648</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20.6</v>
+        <v>20.44</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2297568592460406</v>
+        <v>0.2279723399509258</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.24</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>1.59010207</v>
@@ -3169,19 +3169,19 @@
         <v>92.83</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.34</v>
+        <v>108.19</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002470640336886428</v>
+        <v>0.002465127300732315</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>15.51</v>
+        <v>15.36</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1670796078853819</v>
+        <v>0.1654637509425832</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.23</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>0.40867246</v>
@@ -3226,19 +3226,19 @@
         <v>91.18000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>107.86</v>
+        <v>107.7</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.00245969417331152</v>
+        <v>0.002453962568526392</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>16.68</v>
+        <v>16.52</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1829348541346786</v>
+        <v>0.1811800833516122</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.24</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0.5550481</v>
@@ -3283,19 +3283,19 @@
         <v>101.39</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>107.08</v>
+        <v>106.93</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002441906657502295</v>
+        <v>0.002436417989345655</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>5.69</v>
+        <v>5.54</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.05611993293224184</v>
+        <v>0.05464049709044284</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.32</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>0.42255419</v>
@@ -3340,19 +3340,19 @@
         <v>104.04</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>107.07</v>
+        <v>106.92</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002441678612427818</v>
+        <v>0.002436190137667983</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.02912341407151095</v>
+        <v>0.02768166089965398</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>0.43583007</v>
@@ -3397,19 +3397,19 @@
         <v>89.45999999999999</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>106.61</v>
+        <v>106.46</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002431188539001865</v>
+        <v>0.002425708960495076</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>17.15</v>
+        <v>17</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1917057902973396</v>
+        <v>0.1900290632684999</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.23</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>0.68495686</v>
@@ -3454,19 +3454,19 @@
         <v>98.89</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>106.59</v>
+        <v>106.44</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.00243073244885291</v>
+        <v>0.002425253257139732</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.0778642936596218</v>
+        <v>0.07634745677014865</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.25</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.1285649</v>
@@ -3511,19 +3511,19 @@
         <v>106.96</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>105.88</v>
+        <v>105.74</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002414541248565026</v>
+        <v>0.002409303639702699</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-1.08</v>
+        <v>-1.22</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.01009723261032162</v>
+        <v>-0.01140613313388182</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.41</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>13.30225117</v>
@@ -3568,19 +3568,19 @@
         <v>96.68000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>104.98</v>
+        <v>104.83</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002394017191862074</v>
+        <v>0.002388569137034556</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.15</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.08585022755482002</v>
+        <v>0.08429871741828714</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>1.35094641</v>
@@ -3625,19 +3625,19 @@
         <v>88.44</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>104.77</v>
+        <v>104.63</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002389228245298052</v>
+        <v>0.002384012103481118</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>16.33</v>
+        <v>16.19</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1846449570330167</v>
+        <v>0.1830619629127092</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.23</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0.80409618</v>
@@ -3682,19 +3682,19 @@
         <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>104.6</v>
+        <v>104.45</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002385351479031939</v>
+        <v>0.002379910773283023</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>7.92</v>
+        <v>7.77</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.08191973520893669</v>
+        <v>0.08036822507240379</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>0.50675322</v>
@@ -3739,19 +3739,19 @@
         <v>89.53</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>103.68</v>
+        <v>103.53</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002364371332180034</v>
+        <v>0.002358948418937208</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>14.15</v>
+        <v>14</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.158047581816151</v>
+        <v>0.1563721657544957</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.24</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>1.1533463</v>
@@ -3796,19 +3796,19 @@
         <v>95.94</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>103.58</v>
+        <v>103.43</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002362090881435261</v>
+        <v>0.00235666990216049</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>7.64</v>
+        <v>7.49</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.07963310402334793</v>
+        <v>0.07806962685011466</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>0.51881442</v>
@@ -3853,19 +3853,19 @@
         <v>96.68000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>103.39</v>
+        <v>103.24</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002357758025020193</v>
+        <v>0.002352340720284723</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>6.71</v>
+        <v>6.56</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.06940422010757137</v>
+        <v>0.06785270997103847</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>1.74206342</v>
@@ -3910,19 +3910,19 @@
         <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>103.39</v>
+        <v>103.24</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002357758025020193</v>
+        <v>0.002352340720284723</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4.67</v>
+        <v>4.52</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.04730551053484603</v>
+        <v>0.04578606158833063</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.25</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>1.17949395</v>
@@ -3967,19 +3967,19 @@
         <v>106.15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>103.19</v>
+        <v>103.05</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002353197123530648</v>
+        <v>0.002348011538408957</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-2.96</v>
+        <v>-3.1</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.02788506829957607</v>
+        <v>-0.02920395666509656</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.4</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>2.27580753</v>
@@ -4024,19 +4024,19 @@
         <v>88.89</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>102.25</v>
+        <v>102.11</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002331760886529788</v>
+        <v>0.002326593480707798</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>13.36</v>
+        <v>13.22</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1502981212734841</v>
+        <v>0.148723140960738</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.23</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>0.10445851</v>
@@ -4081,19 +4081,19 @@
         <v>92.27</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>101.72</v>
+        <v>101.57</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002319674497582494</v>
+        <v>0.002314289490113516</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1024168202015823</v>
+        <v>0.1007911563888588</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.25</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>0.90543241</v>
@@ -4138,19 +4138,19 @@
         <v>452.96</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>101.37</v>
+        <v>101.23</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002311692919975791</v>
+        <v>0.002306542533072671</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-351.59</v>
+        <v>-351.73</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.7762054044507241</v>
+        <v>-0.7765144825150124</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-11.09</v>
+        <v>-11.71</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>0</v>
@@ -4195,19 +4195,19 @@
         <v>95.51000000000001</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>100.7</v>
+        <v>100.56</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002296413899985816</v>
+        <v>0.002291276470668653</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>5.19</v>
+        <v>5.05</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.05433985970055492</v>
+        <v>0.0528740446026594</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.24</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>0.37810738</v>
@@ -4252,19 +4252,19 @@
         <v>104.98</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>100.18</v>
+        <v>100.04</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002284555556112999</v>
+        <v>0.002279428183429715</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-4.8</v>
+        <v>-4.94</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.04572299485616307</v>
+        <v>-0.0470565822061345</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.37</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>1.85908491</v>
@@ -4309,19 +4309,19 @@
         <v>99.84999999999999</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>99.8</v>
+        <v>99.66</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002275889843282864</v>
+        <v>0.002270769819678182</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.0005007511266900351</v>
+        <v>-0.001902854281422133</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4366,19 +4366,19 @@
         <v>105.36</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>99.47</v>
+        <v>99.33</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002268364355825115</v>
+        <v>0.002263250714315009</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-5.89</v>
+        <v>-6.03</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.05590356871678056</v>
+        <v>-0.05723234624145786</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.38</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>1.11796351</v>
@@ -4423,19 +4423,19 @@
         <v>111.44</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>99.12</v>
+        <v>98.98</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002260382778218412</v>
+        <v>0.002255275905596493</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-12.32</v>
+        <v>-12.46</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1105527638190955</v>
+        <v>-0.1118090452261307</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.52</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.97307689</v>
@@ -4480,19 +4480,19 @@
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002180110912002423</v>
+        <v>0.002175072115055983</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.03050555136358737</v>
+        <v>0.02899644281556538</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.24</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4537,19 +4537,19 @@
         <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>95.15000000000001</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002169848883650947</v>
+        <v>0.002164818789560747</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6.77</v>
+        <v>6.63</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.07660104095949309</v>
+        <v>0.07501697216564834</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.24</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.93456659</v>
@@ -4594,19 +4594,19 @@
         <v>107.82</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>93.91</v>
+        <v>93.77</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002141571294415769</v>
+        <v>0.002136565181529431</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-13.91</v>
+        <v>-14.05</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1290113151548878</v>
+        <v>-0.1303097755518457</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.44</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.6214908</v>
@@ -4651,19 +4651,19 @@
         <v>110.45</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>92.77</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002118538741893568</v>
+        <v>0.002113780013762241</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.55</v>
+        <v>-17.68</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1588954277953825</v>
+        <v>-0.1600724309642372</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.5</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.17308322</v>
@@ -4708,19 +4708,19 @@
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>82.19</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001874302467128442</v>
+        <v>0.001869978718653305</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-28.34</v>
+        <v>-28.46</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2564009771102868</v>
+        <v>-0.2574866552067312</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.5</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4765,19 +4765,19 @@
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>51.69</v>
+        <v>51.62</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001178764989972858</v>
+        <v>0.001176170360142361</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.0797994568623355</v>
+        <v>0.07833716315019845</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.13</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4822,19 +4822,19 @@
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.86</v>
+        <v>45.79</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001045814711552627</v>
+        <v>0.001043332832059642</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.25</v>
+        <v>-6.32</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1199385914411821</v>
+        <v>-0.1212819036653234</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.14</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06 20:35:31</t>
+          <t>2026-09-07 21:38:36</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44034.5</v>
+        <v>44071.5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43878.95</v>
+        <v>43915.93</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37739.53</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6139.42</v>
+        <v>6176.4</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1626787615002095</v>
+        <v>0.1636586359183593</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>183.52</v>
+        <v>183.54</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>110.22</v>
+        <v>109.94</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7054.08</v>
+        <v>7036.16</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1008.31</v>
+        <v>990.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.578</v>
+        <v>14.93</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4227.62</v>
+        <v>4329.7</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>796.91</v>
+        <v>898.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1580.2</v>
+        <v>1579</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2787.37</v>
+        <v>2785.25</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1591.41</v>
+        <v>1589.29</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5118,19 +5118,19 @@
         <v>27.19</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2310.98</v>
+        <v>2307.74</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>385.17</v>
+        <v>381.93</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5145,19 +5145,19 @@
         <v>109</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1998.36</v>
+        <v>1995.56</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>351.79</v>
+        <v>348.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5172,19 +5172,19 @@
         <v>229.5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1853.26</v>
+        <v>1850.66</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>600.58</v>
+        <v>597.98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5199,19 +5199,19 @@
         <v>476.25</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1759.93</v>
+        <v>1757.46</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-138.62</v>
+        <v>-141.09</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5226,19 +5226,19 @@
         <v>222.39</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1577.89</v>
+        <v>1575.67</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-418.17</v>
+        <v>-420.39</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5253,19 +5253,19 @@
         <v>154.5</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1436.73</v>
+        <v>1434.72</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-435.11</v>
+        <v>-437.12</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,22 +5277,22 @@
         <v>35</v>
       </c>
       <c r="D11" t="n">
-        <v>44.81</v>
+        <v>44.36</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1430.13</v>
+        <v>1414.94</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>201.79</v>
+        <v>186.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5307,19 +5307,19 @@
         <v>119.34</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1402.58</v>
+        <v>1400.62</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>58.79</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>450.6</v>
+        <v>447.4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1246.69</v>
+        <v>1236.64</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>332.2</v>
+        <v>322.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>112.6</v>
+        <v>113.35</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1142.17</v>
+        <v>1149.78</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>534.98</v>
+        <v>542.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>699.8</v>
+        <v>700</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1119.68</v>
+        <v>1120</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>366.22</v>
+        <v>366.54</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>28.552</v>
+        <v>28.795</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1097.31</v>
+        <v>1105.1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>1.53</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5442,19 +5442,19 @@
         <v>338.16</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1095.03</v>
+        <v>1093.5</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>453.04</v>
+        <v>451.51</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5469,19 +5469,19 @@
         <v>320.01</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>723.7</v>
+        <v>722.6900000000001</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>232.65</v>
+        <v>231.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5496,19 +5496,19 @@
         <v>499.61</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>688.66</v>
+        <v>687.7</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>154.28</v>
+        <v>153.32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5523,19 +5523,19 @@
         <v>46.54</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>687.9299999999999</v>
+        <v>686.97</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-179.65</v>
+        <v>-180.61</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>666.25</v>
+        <v>663</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>3.57</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5577,19 +5577,19 @@
         <v>97.5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>662.66</v>
+        <v>661.73</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>113.48</v>
+        <v>112.55</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5604,19 +5604,19 @@
         <v>326.73</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>562.66</v>
+        <v>561.87</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>73.39</v>
+        <v>72.59999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.799</v>
+        <v>3.796</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>531.86</v>
+        <v>531.4400000000001</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-6.51</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5658,19 +5658,19 @@
         <v>338.79</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>500.78</v>
+        <v>500.08</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>92.86</v>
+        <v>92.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5685,19 +5685,19 @@
         <v>234.3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>192.25</v>
+        <v>191.98</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-4.27</v>
+        <v>-4.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5712,19 +5712,19 @@
         <v>133.56</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.85</v>
+        <v>130.67</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>11.12</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5739,19 +5739,19 @@
         <v>277.55</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>130.1</v>
+        <v>129.92</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30.25</v>
+        <v>30.07</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5766,19 +5766,19 @@
         <v>405.89</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.02</v>
+        <v>125.85</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.86</v>
+        <v>16.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5793,19 +5793,19 @@
         <v>108.43</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.86</v>
+        <v>124.68</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>19.58</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5820,19 +5820,19 @@
         <v>67</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>124</v>
+        <v>123.83</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>17.19</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5847,19 +5847,19 @@
         <v>50.7</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>123.98</v>
+        <v>123.8</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.27</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5874,19 +5874,19 @@
         <v>208.63</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>121.9</v>
+        <v>121.73</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>11.49</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5901,19 +5901,19 @@
         <v>278.51</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>121.82</v>
+        <v>121.65</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>21.97</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5928,19 +5928,19 @@
         <v>263.65</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>121.68</v>
+        <v>121.51</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.91</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5955,19 +5955,19 @@
         <v>579.72</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>120.13</v>
+        <v>119.96</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>14.38</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5982,19 +5982,19 @@
         <v>57</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.54</v>
+        <v>116.38</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.06</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6009,19 +6009,19 @@
         <v>41.21</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>116.19</v>
+        <v>116.03</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7.96</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6036,19 +6036,19 @@
         <v>57.96</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>115.97</v>
+        <v>115.81</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>8.33</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6063,19 +6063,19 @@
         <v>88.14</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.96</v>
+        <v>112.8</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6090,19 +6090,19 @@
         <v>248.47</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>112.42</v>
+        <v>112.26</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>88.09</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>24.33</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6117,19 +6117,19 @@
         <v>215.25</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>111.36</v>
+        <v>111.2</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-7.4</v>
+        <v>-7.56</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6144,19 +6144,19 @@
         <v>13.11</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.46</v>
+        <v>110.31</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>4.31</v>
+        <v>4.16</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6171,19 +6171,19 @@
         <v>93.81999999999999</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>110.26</v>
+        <v>110.1</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20.6</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6198,19 +6198,19 @@
         <v>358.69</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.34</v>
+        <v>108.19</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>15.51</v>
+        <v>15.36</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6225,19 +6225,19 @@
         <v>262.92</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>107.86</v>
+        <v>107.7</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>16.68</v>
+        <v>16.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6252,19 +6252,19 @@
         <v>342.88</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>107.08</v>
+        <v>106.93</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>5.69</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6279,19 +6279,19 @@
         <v>332.39</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>107.07</v>
+        <v>106.92</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>3.03</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6306,19 +6306,19 @@
         <v>210.59</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>106.61</v>
+        <v>106.46</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>17.15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6333,19 +6333,19 @@
         <v>1121.73</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>106.59</v>
+        <v>106.44</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>98.89</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>7.7</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6360,19 +6360,19 @@
         <v>10.77</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>105.88</v>
+        <v>105.74</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-1.08</v>
+        <v>-1.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6387,19 +6387,19 @@
         <v>105.14</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>104.98</v>
+        <v>104.83</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6414,19 +6414,19 @@
         <v>176.3</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>104.77</v>
+        <v>104.63</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>16.33</v>
+        <v>16.19</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6441,19 +6441,19 @@
         <v>279.28</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>104.6</v>
+        <v>104.45</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>7.92</v>
+        <v>7.77</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6468,19 +6468,19 @@
         <v>121.63</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>103.68</v>
+        <v>103.53</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>14.15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6495,19 +6495,19 @@
         <v>270.12</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>103.58</v>
+        <v>103.43</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>7.64</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6522,19 +6522,19 @@
         <v>80.3</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>103.39</v>
+        <v>103.24</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6.71</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6549,19 +6549,19 @@
         <v>118.6</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>103.39</v>
+        <v>103.24</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.67</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6576,19 +6576,19 @@
         <v>61.35</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>103.19</v>
+        <v>103.05</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-2.96</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6603,19 +6603,19 @@
         <v>1324.49</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>102.25</v>
+        <v>102.11</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>13.36</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6630,19 +6630,19 @@
         <v>152</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>101.72</v>
+        <v>101.57</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9.449999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6657,19 +6657,19 @@
         <v>24.1</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>101.37</v>
+        <v>101.23</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-351.59</v>
+        <v>-351.73</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6684,19 +6684,19 @@
         <v>360.35</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>100.7</v>
+        <v>100.56</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>5.19</v>
+        <v>5.05</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6711,19 +6711,19 @@
         <v>72.91</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>100.18</v>
+        <v>100.04</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-4.8</v>
+        <v>-4.94</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6738,19 +6738,19 @@
         <v>147.35</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>99.8</v>
+        <v>99.66</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6765,19 +6765,19 @@
         <v>120.38</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>99.47</v>
+        <v>99.33</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-5.89</v>
+        <v>-6.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6792,19 +6792,19 @@
         <v>137.82</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>99.12</v>
+        <v>98.98</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-12.32</v>
+        <v>-12.46</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6819,19 +6819,19 @@
         <v>110.97</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>95.45999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6846,19 +6846,19 @@
         <v>137.75</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>95.15000000000001</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>6.77</v>
+        <v>6.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6873,19 +6873,19 @@
         <v>204.44</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>93.91</v>
+        <v>93.77</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-13.91</v>
+        <v>-14.05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6900,19 +6900,19 @@
         <v>107.15</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>92.90000000000001</v>
+        <v>92.77</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.55</v>
+        <v>-17.68</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6927,19 +6927,19 @@
         <v>60.21</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>82.19</v>
+        <v>82.06999999999999</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-28.34</v>
+        <v>-28.46</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6954,19 +6954,19 @@
         <v>110.63</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>51.69</v>
+        <v>51.62</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>3.82</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6981,13 +6981,13 @@
         <v>256.01</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.86</v>
+        <v>45.79</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.25</v>
+        <v>-6.32</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44071.5</v>
+        <v>44018.42</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43915.93</v>
+        <v>43862.83</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37739.53</v>
+        <v>37740.21</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6176.4</v>
+        <v>6122.62</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1636586359183593</v>
+        <v>0.1622306818112565</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>155.57</v>
+        <v>155.59</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>27.97</v>
+        <v>28.65</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-07 21:38:36</t>
+          <t>2026-09-08 21:17:55</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109.94</v>
+        <v>109.84</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7036.16</v>
+        <v>7029.76</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1603200860367935</v>
+        <v>0.1603706307777032</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>990.39</v>
+        <v>983.99</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1638153618149549</v>
+        <v>0.1627567704361892</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.93</v>
+        <v>15.064</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4329.7</v>
+        <v>4368.56</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0986529408816037</v>
+        <v>0.09966040416603741</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>898.99</v>
+        <v>937.85</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2620419679891334</v>
+        <v>0.2733690693763098</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1579</v>
+        <v>1574.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2785.25</v>
+        <v>2777.84</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.0634623885235667</v>
+        <v>0.06337114681006678</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1589.29</v>
+        <v>1581.88</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.328882236864109</v>
+        <v>1.322686377470818</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>27.19</v>
+        <v>26.9</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2307.74</v>
+        <v>2284.34</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05258224306305567</v>
+        <v>0.05211288105294328</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>381.93</v>
+        <v>358.53</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.198321745135813</v>
+        <v>0.186171013755251</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-15.28</v>
+        <v>-14.27</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>109</v>
+        <v>109.2</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1995.56</v>
+        <v>2000.29</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04546916938949421</v>
+        <v>0.0456328194758188</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>348.99</v>
+        <v>353.72</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2119496893542334</v>
+        <v>0.2148223276265206</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-16.09</v>
+        <v>-15.21</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -972,17 +972,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,55 +991,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>150.09436705</v>
+        <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>229.5</v>
+        <v>504.91</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1850.66</v>
+        <v>1864.21</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04216759858002835</v>
+        <v>0.04252841257768432</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>597.98</v>
+        <v>-34.34</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4773605390043746</v>
+        <v>-0.01808748781965184</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-42.34</v>
+        <v>-15.66</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,38 +1048,38 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>509.97</v>
+        <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>476.25</v>
+        <v>225.72</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1757.46</v>
+        <v>1821.14</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04004402094412621</v>
+        <v>0.04154585228151551</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-141.09</v>
+        <v>568.46</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.07431460851702615</v>
+        <v>0.4537950633841045</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-16.66</v>
+        <v>-41.7</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>222.39</v>
+        <v>225.7</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1575.67</v>
+        <v>1599.98</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03590190529572869</v>
+        <v>0.03650050667899182</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-420.39</v>
+        <v>-396.08</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.2106099015059668</v>
+        <v>-0.1984309088905143</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-22.47</v>
+        <v>-21.41</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1143,131 +1143,131 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US75734B1008</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>12.5822526</v>
+        <v>35</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>191.52532353</v>
+        <v>37.05</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>154.5</v>
+        <v>45</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1871.84</v>
+        <v>1228.34</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1434.72</v>
+        <v>1434.94</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03269033589894322</v>
+        <v>0.03273543235162473</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-437.12</v>
+        <v>206.6</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2335242328404137</v>
+        <v>0.1681944738427471</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-93.3</v>
+        <v>-46.91</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37.05</v>
+        <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>44.36</v>
+        <v>119.32</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1414.94</v>
+        <v>1401.13</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.0322396452805082</v>
+        <v>0.03196412137847712</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>186.6</v>
+        <v>57.34</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.1519123369751046</v>
+        <v>0.04267035771958416</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-46.57</v>
+        <v>-16.4</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>US75734B1008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1276,38 +1276,38 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>12.5822526</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>113.04005874</v>
+        <v>191.52532353</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>119.34</v>
+        <v>149.76</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1871.84</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1400.62</v>
+        <v>1391.44</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03191336167808203</v>
+        <v>0.03174306242166551</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>56.83</v>
+        <v>-480.4</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04229083413330952</v>
+        <v>-0.256645867168134</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-17.11</v>
+        <v>-92.34999999999999</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-03-22</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>447.4</v>
+        <v>445.4</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1236.64</v>
+        <v>1231.74</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02817704986761817</v>
+        <v>0.0280998100581141</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>322.15</v>
+        <v>317.25</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3522728515347352</v>
+        <v>0.3469146737525834</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>113.35</v>
+        <v>112.1</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1149.78</v>
+        <v>1137.1</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02619793019536002</v>
+        <v>0.02594077810015225</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>542.59</v>
+        <v>529.91</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.893608261005616</v>
+        <v>0.8727251766333436</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>700</v>
+        <v>696.4</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1120</v>
+        <v>1114.24</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0255193878992531</v>
+        <v>0.02541927059213231</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>366.54</v>
+        <v>360.78</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4864757253205214</v>
+        <v>0.4788309930188729</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.795</v>
+        <v>28.83</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1105.1</v>
+        <v>1107.03</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02517988889952196</v>
+        <v>0.0252547881278793</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>9.32</v>
+        <v>11.25</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.008505356914709158</v>
+        <v>0.01026665936593112</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.02</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>338.16</v>
+        <v>336</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1093.5</v>
+        <v>1087.09</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02491558095342256</v>
+        <v>0.02479989487722673</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>451.51</v>
+        <v>445.1</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.7032975591520116</v>
+        <v>0.6933129799529588</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-34.48</v>
+        <v>-34.16</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>320.01</v>
+        <v>316.3</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>722.6900000000001</v>
+        <v>714.6900000000001</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01646661289367074</v>
+        <v>0.01630429575270233</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>231.64</v>
+        <v>223.64</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.4717238570410345</v>
+        <v>0.455432237043071</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-21.6</v>
+        <v>-21.36</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>499.61</v>
+        <v>493.52</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>687.7</v>
+        <v>679.6799999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01566935987349675</v>
+        <v>0.01550560905734894</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>153.32</v>
+        <v>145.3</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2869119353269209</v>
+        <v>0.2719038886185861</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.82</v>
+        <v>-25.55</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,25 +1738,25 @@
         <v>57.84</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46.54</v>
+        <v>45.29</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>686.97</v>
+        <v>668.87</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.0156527267010267</v>
+        <v>0.01525899942647862</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-180.61</v>
+        <v>-198.71</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.2081767675603403</v>
+        <v>-0.2290393969432214</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-13.81</v>
+        <v>-13.36</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1770,114 +1770,114 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IE00B43HR379</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1019.5</v>
+        <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1020</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>663</v>
+        <v>651.9</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01510656622964715</v>
+        <v>0.01487186108828534</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.32</v>
+        <v>102.72</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.000482887668256172</v>
+        <v>0.1870424997268655</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>-24.93</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>IE00B43HR379</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>77.20222067</v>
+        <v>1019.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>97.5</v>
+        <v>995.5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>661.73</v>
+        <v>647.08</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01507762906658282</v>
+        <v>0.01476190193742549</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>112.55</v>
+        <v>-15.6</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.2049419133981573</v>
+        <v>-0.02354077382748838</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-25.21</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>326.73</v>
+        <v>326.4</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>561.87</v>
+        <v>561.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.0128023022133512</v>
+        <v>0.01281183799230104</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>72.33</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1483843276718376</v>
+        <v>0.1478324851309093</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-32.49</v>
+        <v>-32.24</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>531.4400000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.0121089495581956</v>
+        <v>0.01212379484086265</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>-6.93</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>338.79</v>
+        <v>338.58</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>500.08</v>
+        <v>500.04</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01139440669701651</v>
+        <v>0.01140746344314496</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>92.16</v>
+        <v>92.12</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2259266522847617</v>
+        <v>0.2258285938419298</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-10.22</v>
+        <v>-10.01</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>234.3</v>
+        <v>232.68</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>191.98</v>
+        <v>190.76</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004374296507945187</v>
+        <v>0.004351827306644134</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-4.54</v>
+        <v>-5.76</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.02310197435375534</v>
+        <v>-0.02930999389375127</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-2.43</v>
+        <v>-2.32</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>133.56</v>
+        <v>135.05</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.67</v>
+        <v>132.2</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002977337872138752</v>
+        <v>0.003015892063002487</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>10.94</v>
+        <v>12.47</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.09137225423870374</v>
+        <v>0.1041510064311367</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.7</v>
+        <v>-0.63</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2194,25 +2194,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>277.55</v>
+        <v>272</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>129.92</v>
+        <v>127.39</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002960248996313359</v>
+        <v>0.00290616104316102</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>30.07</v>
+        <v>27.54</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3011517275913871</v>
+        <v>0.2758137205808713</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>3.30858696</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>350.55601106</v>
+        <v>45.93199509</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>405.89</v>
+        <v>51.5</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>109.16</v>
+        <v>112.71</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.85</v>
+        <v>125.82</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002867513363500895</v>
+        <v>0.002870344473275136</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>16.69</v>
+        <v>13.11</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1528948332722609</v>
+        <v>0.1163162097418153</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>3.30858696</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>91.20399179</v>
+        <v>188.32884805</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>108.43</v>
+        <v>210.15</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>105.28</v>
+        <v>110.41</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.68</v>
+        <v>122.68</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002840854717213283</v>
+        <v>0.002798711333503367</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>19.4</v>
+        <v>12.27</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1842705167173252</v>
+        <v>0.1111312381124898</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.47</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.42010405</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>57.56703616</v>
+        <v>350.55601106</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>67</v>
+        <v>394.07</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>106.81</v>
+        <v>109.16</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>123.83</v>
+        <v>122.25</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002821487324611171</v>
+        <v>0.002788901699712965</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>17.02</v>
+        <v>13.09</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1593483756202603</v>
+        <v>0.1199157200439721</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>-0.41</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.42010405</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.55804584</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45.93199509</v>
+        <v>91.20399179</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>50.7</v>
+        <v>105.74</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>112.71</v>
+        <v>105.28</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>123.8</v>
+        <v>121.66</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002820803769578155</v>
+        <v>0.002775441969628461</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>11.09</v>
+        <v>16.38</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.09839410877473162</v>
+        <v>0.1555851063829787</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.34</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.55804584</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>188.32884805</v>
+        <v>235.02053179</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>208.63</v>
+        <v>262.16</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>110.41</v>
+        <v>108.77</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>121.73</v>
+        <v>120.89</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002773638472300071</v>
+        <v>0.002757875881213091</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>11.32</v>
+        <v>12.12</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1025269450230957</v>
+        <v>0.111427783396157</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.39</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.50421091</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>228.00445932</v>
+        <v>57.56703616</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>278.51</v>
+        <v>65</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>106.81</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>121.65</v>
+        <v>120.2</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002771815658878696</v>
+        <v>0.002742134840944773</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>21.8</v>
+        <v>13.39</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.2183274912368553</v>
+        <v>0.1253627937459039</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.35</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.50421091</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.28038062</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>235.02053179</v>
+        <v>509.16500577</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>263.65</v>
+        <v>571.5700000000001</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>108.77</v>
+        <v>105.75</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>121.51</v>
+        <v>118.34</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002768625735391289</v>
+        <v>0.002699702471525827</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.74</v>
+        <v>12.59</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1171278845269836</v>
+        <v>0.1190543735224586</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.33</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.28038062</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.81488812</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>509.16500577</v>
+        <v>38.28159448</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>579.72</v>
+        <v>42.01</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>105.75</v>
+        <v>108.23</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>119.96</v>
+        <v>118.34</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002733308725352144</v>
+        <v>0.002699702471525827</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>14.21</v>
+        <v>10.11</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1343735224586289</v>
+        <v>0.09341217776956481</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-0.39</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.81488812</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.59183053</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>54.82621761</v>
+        <v>228.00445932</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>57</v>
+        <v>269.25</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>112.48</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.38</v>
+        <v>117.67</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002651737824745603</v>
+        <v>0.002684417693294272</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3.9</v>
+        <v>17.82</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.0346728307254623</v>
+        <v>0.1784677015523285</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.59183053</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.76637723</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>38.28159448</v>
+        <v>54.82621761</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>41.21</v>
+        <v>57.44</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>108.23</v>
+        <v>112.48</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>116.03</v>
+        <v>117.34</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002643763016027087</v>
+        <v>0.002676889369687684</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>7.8</v>
+        <v>4.86</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.07206874249283932</v>
+        <v>0.0432076813655761</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.48</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.76637723</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2821,25 +2821,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>57.96</v>
+        <v>56.78</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>115.81</v>
+        <v>113.51</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002638750279118305</v>
+        <v>0.002589515189647597</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>8.17</v>
+        <v>5.87</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.07590115198810851</v>
+        <v>0.05453363062058714</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>2.70722512</v>
@@ -2878,25 +2878,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>88.14</v>
+        <v>88.45</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.8</v>
+        <v>113.26</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002570166924139062</v>
+        <v>0.002583811914188061</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>11.27</v>
+        <v>11.73</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1110016743819561</v>
+        <v>0.1155323549689747</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.23</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.73400968</v>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.7</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>194.45976548</v>
+        <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>248.47</v>
+        <v>213.4</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>88.09</v>
+        <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>112.26</v>
+        <v>110.31</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002557862933544779</v>
+        <v>0.00251651326376554</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>24.17</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.2743784765580656</v>
+        <v>-0.07115190299764229</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.23</v>
+        <v>-2.13</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,55 +2986,55 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.7</v>
+        <v>11.40066159</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>225.62857143</v>
+        <v>12.56856884</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>215.25</v>
+        <v>13.06</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>118.76</v>
+        <v>106.15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>111.2</v>
+        <v>109.95</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002533710655711558</v>
+        <v>0.002508300547103808</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-7.56</v>
+        <v>3.8</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.06365779723812731</v>
+        <v>0.03579839849269901</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-2.2</v>
+        <v>-0.34</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0</v>
+        <v>11.40066159</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>12.56856884</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>13.11</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.31</v>
+        <v>109.32</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002513431856398758</v>
+        <v>0.002493928292945778</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>4.16</v>
+        <v>19.66</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.03918982571832313</v>
+        <v>0.2192728083872407</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.19</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.61215748</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>194.45976548</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>93.81999999999999</v>
+        <v>240.49</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>89.66</v>
+        <v>88.09</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>110.1</v>
+        <v>108.71</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002508646971167648</v>
+        <v>0.002480012300824511</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20.44</v>
+        <v>20.62</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2279723399509258</v>
+        <v>0.2340787830627767</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.19</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.61215748</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
         <v>306.99401668</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>358.69</v>
+        <v>353.65</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.19</v>
+        <v>106.72</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002465127300732315</v>
+        <v>0.002434614228166607</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>15.36</v>
+        <v>13.89</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1654637509425832</v>
+        <v>0.1496283529031563</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>0.40867246</v>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.42255419</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>221.99877812</v>
+        <v>324.07677699</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>262.92</v>
+        <v>339.9</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>107.7</v>
+        <v>106.06</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002453962568526392</v>
+        <v>0.002419557580953433</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>16.52</v>
+        <v>4.67</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1811800833516122</v>
+        <v>0.04605976920800868</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.42255419</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.68495686</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>324.07677699</v>
+        <v>176.50746647</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>342.88</v>
+        <v>209.15</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>101.39</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>106.93</v>
+        <v>105.79</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002436417989345655</v>
+        <v>0.002413398043457134</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>5.54</v>
+        <v>16.33</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.05464049709044284</v>
+        <v>0.1825396825396825</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.18</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.68495686</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.5550481</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>322.35040597</v>
+        <v>221.99877812</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>332.39</v>
+        <v>256.6</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>104.04</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>106.92</v>
+        <v>105.17</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002436190137667983</v>
+        <v>0.002399253920317485</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.88</v>
+        <v>13.99</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.02768166089965398</v>
+        <v>0.1534327703443737</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.19</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.5550481</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>13.30225117</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>176.50746647</v>
+        <v>10.85229847</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>210.59</v>
+        <v>10.7</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>106.96</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>106.46</v>
+        <v>105.1</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002425708960495076</v>
+        <v>0.002397657003188815</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>17</v>
+        <v>-1.86</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1900290632684999</v>
+        <v>-0.01738967838444279</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.36</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>13.30225117</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.43583007</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>322.35040597</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1121.73</v>
+        <v>326.09</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>98.89</v>
+        <v>104.04</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>106.44</v>
+        <v>104.95</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002425253257139732</v>
+        <v>0.002394235037913094</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>7.55</v>
+        <v>0.91</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.07634745677014865</v>
+        <v>0.008746635909265667</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.29</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.43583007</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.1285649</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>10.85229847</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10.77</v>
+        <v>1102</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>106.96</v>
+        <v>98.89</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>105.74</v>
+        <v>104.62</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002409303639702699</v>
+        <v>0.002386706714306507</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-1.22</v>
+        <v>5.73</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.01140613313388182</v>
+        <v>0.05794316917787441</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.21</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.1285649</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.50675322</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.717382</v>
+        <v>257.81779936</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>105.14</v>
+        <v>278.11</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>104.83</v>
+        <v>104.07</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002388569137034556</v>
+        <v>0.002374159508295528</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>8.15</v>
+        <v>7.39</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.08429871741828714</v>
+        <v>0.07643773272652048</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.50675322</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
         <v>148.63893521</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>176.3</v>
+        <v>175.23</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>104.63</v>
+        <v>104.05</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002384012103481118</v>
+        <v>0.002373703246258766</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>16.19</v>
+        <v>15.61</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1830619629127092</v>
+        <v>0.1765038444142922</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.18</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0.80409618</v>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>257.81779936</v>
+        <v>104.90344487</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>279.28</v>
+        <v>121</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>104.45</v>
+        <v>103.05</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002379910773283023</v>
+        <v>0.002350890144420623</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>7.77</v>
+        <v>13.52</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.08036822507240379</v>
+        <v>0.1510108343571987</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.19</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.35094641</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>104.90344487</v>
+        <v>96.717382</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>121.63</v>
+        <v>103.2</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>103.53</v>
+        <v>102.95</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002358948418937208</v>
+        <v>0.002348608834236808</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>14</v>
+        <v>6.27</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1563721657544957</v>
+        <v>0.06485312370707488</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.2</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.35094641</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.74206342</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>249.91595261</v>
+        <v>74.99726962</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>270.12</v>
+        <v>79.84</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>95.94</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>103.43</v>
+        <v>102.71</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.00235666990216049</v>
+        <v>0.002343133689795654</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>7.49</v>
+        <v>6.03</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.07806962685011466</v>
+        <v>0.06237070748862226</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.74206342</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.51881442</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>74.99726962</v>
+        <v>249.91595261</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>80.3</v>
+        <v>268.05</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>103.24</v>
+        <v>102.69</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002352340720284723</v>
+        <v>0.002342677427758891</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>6.56</v>
+        <v>6.75</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.06785270997103847</v>
+        <v>0.07035647279549719</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.51881442</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>2.27580753</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>113.12478542</v>
+        <v>62.95787236</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>118.6</v>
+        <v>61.07</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>98.72</v>
+        <v>106.15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>103.24</v>
+        <v>102.63</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002352340720284723</v>
+        <v>0.002341308641648603</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4.52</v>
+        <v>-3.52</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.04578606158833063</v>
+        <v>-0.03316062176165803</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.35</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>2.27580753</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>62.95787236</v>
+        <v>137.713206</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>61.35</v>
+        <v>152.15</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>103.05</v>
+        <v>101.73</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002348011538408957</v>
+        <v>0.002320776849994274</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-3.1</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.02920395666509656</v>
+        <v>0.1025251977890972</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.19</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.17949395</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>113.12478542</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1324.49</v>
+        <v>116.44</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>88.89</v>
+        <v>98.72</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>102.11</v>
+        <v>101.42</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002326593480707798</v>
+        <v>0.00231370478842445</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>13.22</v>
+        <v>2.7</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.148723140960738</v>
+        <v>0.02735008103727715</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.19</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.17949395</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.85908491</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>137.713206</v>
+        <v>76.24181082</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>152</v>
+        <v>73.37</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>92.27</v>
+        <v>104.98</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>101.57</v>
+        <v>100.72</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002314289490113516</v>
+        <v>0.00229773561713775</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>-4.26</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1007911563888588</v>
+        <v>-0.04057915793484473</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.32</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.85908491</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,55 +4126,55 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.37810738</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>105.04894536</v>
+        <v>341.38450299</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>24.1</v>
+        <v>357</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>452.96</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>101.23</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002306542533072671</v>
+        <v>0.002274009991226081</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-351.73</v>
+        <v>4.17</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.7765144825150124</v>
+        <v>0.04366034970160192</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-11.71</v>
+        <v>-0.19</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0</v>
+        <v>0.37810738</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.11796351</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>341.38450299</v>
+        <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>360.35</v>
+        <v>120.72</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>100.56</v>
+        <v>99.66</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002291276470668653</v>
+        <v>0.002273553729189318</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>5.05</v>
+        <v>-5.7</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.0528740446026594</v>
+        <v>-0.0541002277904328</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.32</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.11796351</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.10445851</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>76.24181082</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>72.91</v>
+        <v>1289.17</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>104.98</v>
+        <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>100.04</v>
+        <v>99.44</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002279428183429715</v>
+        <v>0.002268534846784927</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-4.94</v>
+        <v>10.55</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.0470565822061345</v>
+        <v>0.1186860164247947</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.18</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.10445851</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>147.21071381</v>
+        <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>147.35</v>
+        <v>138.21</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>99.66</v>
+        <v>99.31</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002270769819678182</v>
+        <v>0.002265569143545968</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-0.19</v>
+        <v>-12.13</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.001902854281422133</v>
+        <v>-0.1088478104809763</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.46</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>127.23134407</v>
+        <v>147.21071381</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>120.38</v>
+        <v>145.51</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>105.36</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>99.33</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002263250714315009</v>
+        <v>0.002246178006983547</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-6.03</v>
+        <v>-1.39</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.05723234624145786</v>
+        <v>-0.01392088132198297</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.24</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,38 +4411,38 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>5.691347</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>154.44822659</v>
+        <v>105.04894536</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>137.82</v>
+        <v>22.81</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>111.44</v>
+        <v>452.96</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>98.98</v>
+        <v>95.86</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002255275905596493</v>
+        <v>0.002186863942204375</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-12.46</v>
+        <v>-357.1</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1118090452261307</v>
+        <v>-0.7883698339809255</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.52</v>
+        <v>-11.48</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>110.97</v>
+        <v>109.72</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>95.45999999999999</v>
+        <v>94.44</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002175072115055983</v>
+        <v>0.002154469337594213</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.69</v>
+        <v>1.67</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.02899644281556538</v>
+        <v>0.01800150910854802</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.18</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4531,25 +4531,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>137.75</v>
+        <v>136.74</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>95.01000000000001</v>
+        <v>94.37</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002164818789560747</v>
+        <v>0.002152872420465543</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6.63</v>
+        <v>5.99</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.07501697216564834</v>
+        <v>0.06777551482235801</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.19</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.93456659</v>
@@ -4588,25 +4588,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>204.44</v>
+        <v>201.08</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>93.77</v>
+        <v>92.28</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002136565181529431</v>
+        <v>0.002105193037623824</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-14.05</v>
+        <v>-15.54</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1303097755518457</v>
+        <v>-0.1441291040623261</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.38</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.6214908</v>
@@ -4645,25 +4645,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>107.15</v>
+        <v>105.95</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>92.77</v>
+        <v>91.78</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002113780013762241</v>
+        <v>0.002093786486704752</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.68</v>
+        <v>-18.67</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1600724309642372</v>
+        <v>-0.1690357627885921</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.44</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.17308322</v>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>60.21</v>
+        <v>59.48</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>82.06999999999999</v>
+        <v>81.12</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001869978718653305</v>
+        <v>0.001850598821110149</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-28.46</v>
+        <v>-29.41</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2574866552067312</v>
+        <v>-0.2660816068035827</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.44</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>110.63</v>
+        <v>109.42</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>51.62</v>
+        <v>51.08</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001176170360142361</v>
+        <v>0.001165293241892338</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.07833716315019845</v>
+        <v>0.06705661165656988</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>256.01</v>
+        <v>256</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.79</v>
+        <v>45.82</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001043332832059642</v>
+        <v>0.001045296326223706</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.32</v>
+        <v>-6.29</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1212819036653234</v>
+        <v>-0.1207061984264057</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,7 +4865,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-07 21:38:36</t>
+          <t>2026-09-08 21:17:55</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44071.5</v>
+        <v>44018.42</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43915.93</v>
+        <v>43862.83</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37739.53</v>
+        <v>37740.21</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6176.4</v>
+        <v>6122.62</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1636586359183593</v>
+        <v>0.1622306818112565</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>183.54</v>
+        <v>184.24</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109.94</v>
+        <v>109.84</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7036.16</v>
+        <v>7029.76</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>990.39</v>
+        <v>983.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.93</v>
+        <v>15.064</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4329.7</v>
+        <v>4368.56</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>898.99</v>
+        <v>937.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1579</v>
+        <v>1574.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2785.25</v>
+        <v>2777.84</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1589.29</v>
+        <v>1581.88</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>27.19</v>
+        <v>26.9</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2307.74</v>
+        <v>2284.34</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>381.93</v>
+        <v>358.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,76 +5142,76 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>109</v>
+        <v>109.2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1995.56</v>
+        <v>2000.29</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>348.99</v>
+        <v>353.72</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>229.5</v>
+        <v>504.91</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1850.66</v>
+        <v>1864.21</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>597.98</v>
+        <v>-34.34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>476.25</v>
+        <v>225.72</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1757.46</v>
+        <v>1821.14</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-141.09</v>
+        <v>568.46</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,103 +5223,103 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>222.39</v>
+        <v>225.7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1575.67</v>
+        <v>1599.98</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-420.39</v>
+        <v>-396.08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>12.5822526</v>
+        <v>35</v>
       </c>
       <c r="D10" t="n">
-        <v>154.5</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1434.72</v>
+        <v>1434.94</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1871.84</v>
+        <v>1228.34</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-437.12</v>
+        <v>206.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>44.36</v>
+        <v>119.32</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1414.94</v>
+        <v>1401.13</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>186.6</v>
+        <v>57.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>12.5822526</v>
       </c>
       <c r="D12" t="n">
-        <v>119.34</v>
+        <v>149.76</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1400.62</v>
+        <v>1391.44</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1871.84</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>56.83</v>
+        <v>-480.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>447.4</v>
+        <v>445.4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1236.64</v>
+        <v>1231.74</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>322.15</v>
+        <v>317.25</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>113.35</v>
+        <v>112.1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1149.78</v>
+        <v>1137.1</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>542.59</v>
+        <v>529.91</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>700</v>
+        <v>696.4</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1120</v>
+        <v>1114.24</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>366.54</v>
+        <v>360.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>28.795</v>
+        <v>28.83</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1105.1</v>
+        <v>1107.03</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>9.32</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>338.16</v>
+        <v>336</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1093.5</v>
+        <v>1087.09</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>451.51</v>
+        <v>445.1</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>320.01</v>
+        <v>316.3</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>722.6900000000001</v>
+        <v>714.6900000000001</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>231.64</v>
+        <v>223.64</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>499.61</v>
+        <v>493.52</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>687.7</v>
+        <v>679.6799999999999</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>153.32</v>
+        <v>145.3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,76 +5520,76 @@
         <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>46.54</v>
+        <v>45.29</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>686.97</v>
+        <v>668.87</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-180.61</v>
+        <v>-198.71</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>1020</v>
+        <v>96</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>663</v>
+        <v>651.9</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.32</v>
+        <v>102.72</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>97.5</v>
+        <v>995.5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>661.73</v>
+        <v>647.08</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>112.55</v>
+        <v>-15.6</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>326.73</v>
+        <v>326.4</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>561.87</v>
+        <v>561.6</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>72.59999999999999</v>
+        <v>72.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5643,7 +5643,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>338.79</v>
+        <v>338.58</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>500.08</v>
+        <v>500.04</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>92.16</v>
+        <v>92.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>234.3</v>
+        <v>232.68</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>191.98</v>
+        <v>190.76</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-4.54</v>
+        <v>-5.76</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,22 +5709,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>133.56</v>
+        <v>135.05</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.67</v>
+        <v>132.2</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>10.94</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5736,292 +5736,292 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>277.55</v>
+        <v>272</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>129.92</v>
+        <v>127.39</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30.07</v>
+        <v>27.54</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>3.30858696</v>
       </c>
       <c r="D29" t="n">
-        <v>405.89</v>
+        <v>51.5</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.85</v>
+        <v>125.82</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>109.16</v>
+        <v>112.71</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.69</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="D30" t="n">
-        <v>108.43</v>
+        <v>210.15</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.68</v>
+        <v>122.68</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>105.28</v>
+        <v>110.41</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>19.4</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.42010405</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>394.07</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>123.83</v>
+        <v>122.25</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>106.81</v>
+        <v>109.16</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>17.02</v>
+        <v>13.09</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.55804584</v>
       </c>
       <c r="D32" t="n">
-        <v>50.7</v>
+        <v>105.74</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>123.8</v>
+        <v>121.66</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>112.71</v>
+        <v>105.28</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.09</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="D33" t="n">
-        <v>208.63</v>
+        <v>262.16</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>121.73</v>
+        <v>120.89</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>110.41</v>
+        <v>108.77</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>11.32</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.50421091</v>
       </c>
       <c r="D34" t="n">
-        <v>278.51</v>
+        <v>65</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>121.65</v>
+        <v>120.2</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>106.81</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>21.8</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.28038062</v>
       </c>
       <c r="D35" t="n">
-        <v>263.65</v>
+        <v>571.5700000000001</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>121.51</v>
+        <v>118.34</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>108.77</v>
+        <v>105.75</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.74</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.81488812</v>
       </c>
       <c r="D36" t="n">
-        <v>579.72</v>
+        <v>42.01</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>119.96</v>
+        <v>118.34</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>105.75</v>
+        <v>108.23</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>14.21</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.59183053</v>
       </c>
       <c r="D37" t="n">
-        <v>57</v>
+        <v>269.25</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.38</v>
+        <v>117.67</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>112.48</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3.9</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.76637723</v>
       </c>
       <c r="D38" t="n">
-        <v>41.21</v>
+        <v>57.44</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>116.03</v>
+        <v>117.34</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>108.23</v>
+        <v>112.48</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7.8</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6033,22 +6033,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>57.96</v>
+        <v>56.78</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>115.81</v>
+        <v>113.51</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>8.17</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6060,130 +6060,130 @@
         <v>1.73400968</v>
       </c>
       <c r="D40" t="n">
-        <v>88.14</v>
+        <v>88.45</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.8</v>
+        <v>113.26</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>11.27</v>
+        <v>11.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>248.47</v>
+        <v>213.4</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>112.26</v>
+        <v>110.31</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>88.09</v>
+        <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>24.17</v>
+        <v>-8.449999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.7</v>
+        <v>11.40066159</v>
       </c>
       <c r="D42" t="n">
-        <v>215.25</v>
+        <v>13.06</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>111.2</v>
+        <v>109.95</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>118.76</v>
+        <v>106.15</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-7.56</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="D43" t="n">
-        <v>13.11</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.31</v>
+        <v>109.32</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>4.16</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.61215748</v>
       </c>
       <c r="D44" t="n">
-        <v>93.81999999999999</v>
+        <v>240.49</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>110.1</v>
+        <v>108.71</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>89.66</v>
+        <v>88.09</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20.44</v>
+        <v>20.62</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6195,211 +6195,211 @@
         <v>0.40867246</v>
       </c>
       <c r="D45" t="n">
-        <v>358.69</v>
+        <v>353.65</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.19</v>
+        <v>106.72</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>15.36</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.42255419</v>
       </c>
       <c r="D46" t="n">
-        <v>262.92</v>
+        <v>339.9</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>107.7</v>
+        <v>106.06</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>16.52</v>
+        <v>4.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.68495686</v>
       </c>
       <c r="D47" t="n">
-        <v>342.88</v>
+        <v>209.15</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>106.93</v>
+        <v>105.79</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>101.39</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>5.54</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.5550481</v>
       </c>
       <c r="D48" t="n">
-        <v>332.39</v>
+        <v>256.6</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>106.92</v>
+        <v>105.17</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>104.04</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2.88</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>13.30225117</v>
       </c>
       <c r="D49" t="n">
-        <v>210.59</v>
+        <v>10.7</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>106.46</v>
+        <v>105.1</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>106.96</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>17</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.43583007</v>
       </c>
       <c r="D50" t="n">
-        <v>1121.73</v>
+        <v>326.09</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>106.44</v>
+        <v>104.95</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>98.89</v>
+        <v>104.04</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>7.55</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.1285649</v>
       </c>
       <c r="D51" t="n">
-        <v>10.77</v>
+        <v>1102</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>105.74</v>
+        <v>104.62</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>106.96</v>
+        <v>98.89</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-1.22</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.50675322</v>
       </c>
       <c r="D52" t="n">
-        <v>105.14</v>
+        <v>278.11</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>104.83</v>
+        <v>104.07</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>8.15</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6411,400 +6411,400 @@
         <v>0.80409618</v>
       </c>
       <c r="D53" t="n">
-        <v>176.3</v>
+        <v>175.23</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>104.63</v>
+        <v>104.05</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>16.19</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="D54" t="n">
-        <v>279.28</v>
+        <v>121</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>104.45</v>
+        <v>103.05</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>7.77</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.35094641</v>
       </c>
       <c r="D55" t="n">
-        <v>121.63</v>
+        <v>103.2</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>103.53</v>
+        <v>102.95</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>14</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.74206342</v>
       </c>
       <c r="D56" t="n">
-        <v>270.12</v>
+        <v>79.84</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>103.43</v>
+        <v>102.71</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>95.94</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>7.49</v>
+        <v>6.03</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.51881442</v>
       </c>
       <c r="D57" t="n">
-        <v>80.3</v>
+        <v>268.05</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>103.24</v>
+        <v>102.69</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6.56</v>
+        <v>6.75</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>2.27580753</v>
       </c>
       <c r="D58" t="n">
-        <v>118.6</v>
+        <v>61.07</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>103.24</v>
+        <v>102.63</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>98.72</v>
+        <v>106.15</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.52</v>
+        <v>-3.52</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="D59" t="n">
-        <v>61.35</v>
+        <v>152.15</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>103.05</v>
+        <v>101.73</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-3.1</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.17949395</v>
       </c>
       <c r="D60" t="n">
-        <v>1324.49</v>
+        <v>116.44</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>102.11</v>
+        <v>101.42</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>88.89</v>
+        <v>98.72</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>13.22</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.85908491</v>
       </c>
       <c r="D61" t="n">
-        <v>152</v>
+        <v>73.37</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>101.57</v>
+        <v>100.72</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>92.27</v>
+        <v>104.98</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9.300000000000001</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.37810738</v>
       </c>
       <c r="D62" t="n">
-        <v>24.1</v>
+        <v>357</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>101.23</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>452.96</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-351.73</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>360.35</v>
+        <v>120.72</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>100.56</v>
+        <v>99.66</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>5.05</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>72.91</v>
+        <v>1289.17</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>100.04</v>
+        <v>99.44</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>104.98</v>
+        <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-4.94</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>147.35</v>
+        <v>138.21</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>99.66</v>
+        <v>99.31</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-0.19</v>
+        <v>-12.13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D66" t="n">
-        <v>120.38</v>
+        <v>145.51</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>99.33</v>
+        <v>98.45999999999999</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>105.36</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-6.03</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>5.691347</v>
       </c>
       <c r="D67" t="n">
-        <v>137.82</v>
+        <v>22.81</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>98.98</v>
+        <v>95.86</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>111.44</v>
+        <v>452.96</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-12.46</v>
+        <v>-357.1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,22 +6816,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>110.97</v>
+        <v>109.72</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>95.45999999999999</v>
+        <v>94.44</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>2.69</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6843,22 +6843,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>137.75</v>
+        <v>136.74</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>95.01000000000001</v>
+        <v>94.37</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>6.63</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6870,22 +6870,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D70" t="n">
-        <v>204.44</v>
+        <v>201.08</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>93.77</v>
+        <v>92.28</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-14.05</v>
+        <v>-15.54</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D71" t="n">
-        <v>107.15</v>
+        <v>105.95</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>92.77</v>
+        <v>91.78</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.68</v>
+        <v>-18.67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>60.21</v>
+        <v>59.48</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>82.06999999999999</v>
+        <v>81.12</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-28.46</v>
+        <v>-29.41</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>110.63</v>
+        <v>109.42</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>51.62</v>
+        <v>51.08</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>256.01</v>
+        <v>256</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.79</v>
+        <v>45.82</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.32</v>
+        <v>-6.29</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44018.42</v>
+        <v>43677.19</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43862.83</v>
+        <v>43521.58</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6122.62</v>
+        <v>5781.37</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1622306818112565</v>
+        <v>0.1531886017592377</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>155.59</v>
+        <v>155.61</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-08 21:17:55</t>
+          <t>2026-09-09 21:03:40</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109.84</v>
+        <v>109</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7029.76</v>
+        <v>6976</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1603706307777032</v>
+        <v>0.1603137148199182</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>983.99</v>
+        <v>930.23</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1627567704361892</v>
+        <v>0.1538646028545578</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.064</v>
+        <v>14.968</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4368.56</v>
+        <v>4340.72</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09966040416603741</v>
+        <v>0.09975300289465533</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>937.85</v>
+        <v>910.01</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2733690693763098</v>
+        <v>0.265254131069079</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1574.8</v>
+        <v>1549.2</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2777.84</v>
+        <v>2732.68</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06337114681006678</v>
+        <v>0.06279903701463506</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1581.88</v>
+        <v>1536.72</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.322686377470818</v>
+        <v>1.284925917254758</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.9</v>
+        <v>26.31</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2284.34</v>
+        <v>2230.75</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05211288105294328</v>
+        <v>0.0512643089642392</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>358.53</v>
+        <v>304.94</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.186171013755251</v>
+        <v>0.158343761845665</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-14.27</v>
+        <v>-17.25</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>109.2</v>
+        <v>109.58</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2000.29</v>
+        <v>2004.11</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0456328194758188</v>
+        <v>0.04605595169262418</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>353.72</v>
+        <v>357.54</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2148223276265206</v>
+        <v>0.2171423018760211</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-15.21</v>
+        <v>-17.77</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>504.91</v>
+        <v>521.3</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1864.21</v>
+        <v>1921.72</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04252841257768432</v>
+        <v>0.04416256766681956</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-34.34</v>
+        <v>23.17</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01808748781965184</v>
+        <v>0.01220405045956125</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-15.66</v>
+        <v>-18.6</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>225.72</v>
+        <v>223.68</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1821.14</v>
+        <v>1801.86</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04154585228151551</v>
+        <v>0.04140809492336839</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>568.46</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4537950633841045</v>
+        <v>0.4384040616917328</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-41.7</v>
+        <v>-43.59</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>225.7</v>
+        <v>235.21</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1599.98</v>
+        <v>1664.79</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03650050667899182</v>
+        <v>0.03825812346546039</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-396.08</v>
+        <v>-331.27</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1984309088905143</v>
+        <v>-0.1659619450317125</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-21.41</v>
+        <v>-24.5</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>37.05</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>45</v>
+        <v>44.57</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1434.94</v>
+        <v>1419.03</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03273543235162473</v>
+        <v>0.03261037424611648</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>206.6</v>
+        <v>190.69</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.1681944738427471</v>
+        <v>0.1552420339645375</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-46.91</v>
+        <v>-48.73</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.32</v>
+        <v>119.38</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1401.13</v>
+        <v>1399.64</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03196412137847712</v>
+        <v>0.03216477749577844</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>57.34</v>
+        <v>55.85</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04267035771958416</v>
+        <v>0.04156155351654649</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-16.4</v>
+        <v>-18.48</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>149.76</v>
+        <v>146.58</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1391.44</v>
+        <v>1359.77</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03174306242166551</v>
+        <v>0.03124853497716173</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-480.4</v>
+        <v>-512.0700000000001</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>-0.256645867168134</v>
+        <v>-0.2735650482947261</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-92.34999999999999</v>
+        <v>-95.13</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>445.4</v>
+        <v>437.1</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1231.74</v>
+        <v>1207.8</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.0280998100581141</v>
+        <v>0.02775615033823068</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>317.25</v>
+        <v>293.31</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3469146737525834</v>
+        <v>0.3207361480169275</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>112.1</v>
+        <v>109.65</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1137.1</v>
+        <v>1112.25</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02594077810015225</v>
+        <v>0.02556033963710637</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>529.91</v>
+        <v>505.06</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8727251766333436</v>
+        <v>0.8317989426703337</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>696.4</v>
+        <v>688</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1114.24</v>
+        <v>1100.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02541927059213231</v>
+        <v>0.02529721004497792</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>360.78</v>
+        <v>347.34</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4788309930188729</v>
+        <v>0.4609932843150266</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.83</v>
+        <v>28.215</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1107.03</v>
+        <v>1081.72</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.0252547881278793</v>
+        <v>0.02485873732726519</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>11.25</v>
+        <v>-14.06</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.01026665936593112</v>
+        <v>-0.0128310427275548</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-0.02</v>
+        <v>-1.73</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>336</v>
+        <v>331.89</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1087.09</v>
+        <v>1072.11</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02479989487722673</v>
+        <v>0.02463789231588052</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>445.1</v>
+        <v>430.12</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6933129799529588</v>
+        <v>0.6699792831664044</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-34.16</v>
+        <v>-35.11</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>316.3</v>
+        <v>315.95</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>714.6900000000001</v>
+        <v>712.78</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01630429575270233</v>
+        <v>0.01638021927312806</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>223.64</v>
+        <v>221.73</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.455432237043071</v>
+        <v>0.4515426127685571</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-21.36</v>
+        <v>-22.09</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>493.52</v>
+        <v>491.9</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>679.6799999999999</v>
+        <v>676.39</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01550560905734894</v>
+        <v>0.01554394976591808</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>145.3</v>
+        <v>142.01</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2719038886185861</v>
+        <v>0.2657472210786332</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.55</v>
+        <v>-26.35</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,25 +1738,25 @@
         <v>57.84</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>45.29</v>
+        <v>44.71</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>668.87</v>
+        <v>659.27</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01525899942647862</v>
+        <v>0.01515051931899764</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-198.71</v>
+        <v>-208.31</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.2290393969432214</v>
+        <v>-0.2401046589363517</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-13.36</v>
+        <v>-14.7</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1770,114 +1770,114 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>IE00B43HR379</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>77.20222067</v>
+        <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>96</v>
+        <v>993.75</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>651.9</v>
+        <v>645.9400000000001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01487186108828534</v>
+        <v>0.01484418591610923</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>102.72</v>
+        <v>-16.74</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1870424997268655</v>
+        <v>-0.02526106114565099</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-24.93</v>
+        <v>0</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IE00B43HR379</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1019.5</v>
+        <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>995.5</v>
+        <v>94.27</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>647.08</v>
+        <v>639.15</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01476190193742549</v>
+        <v>0.0146881466208645</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-15.6</v>
+        <v>89.97</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.02354077382748838</v>
+        <v>0.1638260679558615</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>-25.75</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>326.4</v>
+        <v>322.19</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>561.6</v>
+        <v>553.49</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01281183799230104</v>
+        <v>0.01271961554123804</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>72.33</v>
+        <v>64.22</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1478324851309093</v>
+        <v>0.1312567702904327</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-32.24</v>
+        <v>-32.96</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.796</v>
+        <v>3.781</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>531.4400000000001</v>
+        <v>529.34</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01212379484086265</v>
+        <v>0.01216463041897585</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-6.93</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.01287218827200624</v>
+        <v>-0.01677285138473541</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>338.58</v>
+        <v>331.13</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>500.04</v>
+        <v>488.27</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01140746344314496</v>
+        <v>0.01122081099987406</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>92.12</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2258285938419298</v>
+        <v>0.196974897038635</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-10.01</v>
+        <v>-10.63</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>232.68</v>
+        <v>239.51</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>190.76</v>
+        <v>196.05</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004351827306644134</v>
+        <v>0.004505376116749566</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-5.76</v>
+        <v>-0.47</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.02930999389375127</v>
+        <v>-0.002391614085080399</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-2.32</v>
+        <v>-2.63</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>135.05</v>
+        <v>139.99</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>132.2</v>
+        <v>136.82</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003015892063002487</v>
+        <v>0.00314422627030694</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>12.47</v>
+        <v>17.09</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.1041510064311367</v>
+        <v>0.1427378267769147</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.82</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>3.30858696</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>212.76482689</v>
+        <v>45.93199509</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>272</v>
+        <v>51.74</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>112.71</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>127.39</v>
+        <v>126.21</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.00290616104316102</v>
+        <v>0.002900400508518045</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>27.54</v>
+        <v>13.5</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2758137205808713</v>
+        <v>0.119776417354272</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.67</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>3.30858696</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45.93199509</v>
+        <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>51.5</v>
+        <v>213.93</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.82</v>
+        <v>124.7</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002870344473275136</v>
+        <v>0.002865699575407656</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>13.11</v>
+        <v>14.29</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1163162097418153</v>
+        <v>0.1294266823657277</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.63</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.63422137</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>188.32884805</v>
+        <v>212.76482689</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>210.15</v>
+        <v>265.22</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>110.41</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>122.68</v>
+        <v>124.02</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002798711333503367</v>
+        <v>0.002850072665132778</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>12.27</v>
+        <v>24.17</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1111312381124898</v>
+        <v>0.242063094641963</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.36</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.63422137</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.42010405</v>
+        <v>0.62445608</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>350.55601106</v>
+        <v>235.02053179</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>394.07</v>
+        <v>267</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>109.16</v>
+        <v>108.77</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>122.25</v>
+        <v>122.93</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002788901699712965</v>
+        <v>0.002825023647192166</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>13.09</v>
+        <v>14.16</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1199157200439721</v>
+        <v>0.1301829548588765</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.42010405</v>
+        <v>0.62445608</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2422,25 +2422,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>105.74</v>
+        <v>105.42</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>121.66</v>
+        <v>121.1</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002775441969628461</v>
+        <v>0.002782968873952422</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>16.38</v>
+        <v>15.82</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1555851063829787</v>
+        <v>0.1502659574468085</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>1.55804584</v>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>235.02053179</v>
+        <v>350.55601106</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>262.16</v>
+        <v>390.35</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>108.77</v>
+        <v>109.16</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>120.89</v>
+        <v>120.9</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002757875881213091</v>
+        <v>0.002778372723871576</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>12.12</v>
+        <v>11.74</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.111427783396157</v>
+        <v>0.1075485525833639</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.59</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.81488812</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>57.56703616</v>
+        <v>38.28159448</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>65</v>
+        <v>42.75</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>106.81</v>
+        <v>108.23</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>120.2</v>
+        <v>120.24</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002742134840944773</v>
+        <v>0.002763205428604784</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.39</v>
+        <v>12.01</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1253627937459039</v>
+        <v>0.1109673842742308</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.81488812</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.50421091</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>509.16500577</v>
+        <v>57.56703616</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>571.5700000000001</v>
+        <v>64.41</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>105.75</v>
+        <v>106.81</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.34</v>
+        <v>118.92</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002699702471525827</v>
+        <v>0.002732870838071198</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.59</v>
+        <v>12.11</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1190543735224586</v>
+        <v>0.1133788971070124</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.52</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.50421091</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.28038062</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>38.28159448</v>
+        <v>509.16500577</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>42.01</v>
+        <v>567.58</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>108.23</v>
+        <v>105.75</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>118.34</v>
+        <v>117.33</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002699702471525827</v>
+        <v>0.00269633144492847</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>10.11</v>
+        <v>11.58</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.09341217776956481</v>
+        <v>0.1095035460992908</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.5</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.28038062</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>269.25</v>
+        <v>267.9</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>117.67</v>
+        <v>116.9</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002684417693294272</v>
+        <v>0.002686449722254651</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>17.82</v>
+        <v>17.05</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1784677015523285</v>
+        <v>0.170756134201302</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.36</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.59183053</v>
@@ -2764,25 +2764,25 @@
         <v>54.82621761</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>57.44</v>
+        <v>57</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>117.34</v>
+        <v>116.26</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002676889369687684</v>
+        <v>0.002671742041995943</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4.86</v>
+        <v>3.78</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.0432076813655761</v>
+        <v>0.03360597439544807</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.65</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>2.76637723</v>
@@ -2821,25 +2821,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>56.78</v>
+        <v>56.44</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.51</v>
+        <v>112.65</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002589515189647597</v>
+        <v>0.002588781533036667</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>5.87</v>
+        <v>5.01</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.05453363062058714</v>
+        <v>0.04654403567447046</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.55</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>2.70722512</v>
@@ -2878,25 +2878,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>88.45</v>
+        <v>87.58</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.26</v>
+        <v>111.97</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002583811914188061</v>
+        <v>0.00257315462276179</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>11.73</v>
+        <v>10.44</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1155323549689747</v>
+        <v>0.1028267507140747</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.39</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.73400968</v>
@@ -2935,25 +2935,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>213.4</v>
+        <v>210.08</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.31</v>
+        <v>108.42</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.00251651326376554</v>
+        <v>0.002491572958826768</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-8.449999999999999</v>
+        <v>-10.34</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.07115190299764229</v>
+        <v>-0.08706635230717413</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-2.13</v>
+        <v>-2.32</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
@@ -2992,25 +2992,25 @@
         <v>12.56856884</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>13.06</v>
+        <v>12.86</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.95</v>
+        <v>108.09</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002508300547103808</v>
+        <v>0.002483989311193372</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3.8</v>
+        <v>1.94</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.03579839849269901</v>
+        <v>0.01827602449364107</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>11.40066159</v>
@@ -3049,25 +3049,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>93.09999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>109.32</v>
+        <v>107.98</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002493928292945778</v>
+        <v>0.002481461428648907</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>19.66</v>
+        <v>18.32</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.2192728083872407</v>
+        <v>0.2043274592906536</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.34</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>1.59010207</v>
@@ -3106,25 +3106,25 @@
         <v>194.45976548</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>240.49</v>
+        <v>238.33</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>88.09</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>108.71</v>
+        <v>107.57</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002480012300824511</v>
+        <v>0.002472039320983172</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20.62</v>
+        <v>19.48</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2340787830627767</v>
+        <v>0.2211374730389374</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>0.61215748</v>
@@ -3163,25 +3163,25 @@
         <v>306.99401668</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>353.65</v>
+        <v>354.75</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>106.72</v>
+        <v>106.89</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002434614228166607</v>
+        <v>0.002456412410708294</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>13.89</v>
+        <v>14.06</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1496283529031563</v>
+        <v>0.1514596574383281</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.33</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>0.40867246</v>
@@ -3220,25 +3220,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>339.9</v>
+        <v>337.62</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>106.06</v>
+        <v>105.18</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002419557580953433</v>
+        <v>0.002417115327517059</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4.67</v>
+        <v>3.79</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.04605976920800868</v>
+        <v>0.03738041226945458</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.43</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0.42255419</v>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.74206342</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>176.50746647</v>
+        <v>74.99726962</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>209.15</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>105.79</v>
+        <v>104.77</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002413398043457134</v>
+        <v>0.002407693219851324</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>16.33</v>
+        <v>8.09</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1825396825396825</v>
+        <v>0.08367811336367396</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.35</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.74206342</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.68495686</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>221.99877812</v>
+        <v>176.50746647</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>256.6</v>
+        <v>206.81</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>105.17</v>
+        <v>104.44</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002399253920317485</v>
+        <v>0.002400109572217927</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>13.99</v>
+        <v>14.98</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1534327703443737</v>
+        <v>0.1674491392801252</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.68495686</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.5550481</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>10.85229847</v>
+        <v>221.99877812</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>10.7</v>
+        <v>255</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>106.96</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>105.1</v>
+        <v>104.35</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002397657003188815</v>
+        <v>0.002398041304681547</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>-1.86</v>
+        <v>13.17</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>-0.01738967838444279</v>
+        <v>0.1444395700811581</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.5550481</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>13.30225117</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>322.35040597</v>
+        <v>10.85229847</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>326.09</v>
+        <v>10.56</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>104.04</v>
+        <v>106.96</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>104.95</v>
+        <v>103.57</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002394235037913094</v>
+        <v>0.002380116319366246</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.91</v>
+        <v>-3.39</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.008746635909265667</v>
+        <v>-0.03169409124906507</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.52</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>13.30225117</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.43583007</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>322.35040597</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1102</v>
+        <v>319.62</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>98.89</v>
+        <v>104.04</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>104.62</v>
+        <v>102.7</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002386706714306507</v>
+        <v>0.002360123066514565</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>5.73</v>
+        <v>-1.34</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.05794316917787441</v>
+        <v>-0.012879661668589</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.46</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.43583007</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.80409618</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>257.81779936</v>
+        <v>148.63893521</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>278.11</v>
+        <v>172.63</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>104.07</v>
+        <v>102.34</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002374159508295528</v>
+        <v>0.002351849996369042</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>7.39</v>
+        <v>13.9</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.07643773272652048</v>
+        <v>0.1571687019448214</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.32</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.80409618</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.1285649</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>148.63893521</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>175.23</v>
+        <v>1074</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>88.44</v>
+        <v>98.89</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>104.05</v>
+        <v>101.8</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002373703246258766</v>
+        <v>0.002339440391150756</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>15.61</v>
+        <v>2.91</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1765038444142922</v>
+        <v>0.02942663565577915</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.36</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.1285649</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>104.90344487</v>
+        <v>257.81779936</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>121</v>
+        <v>272.21</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>103.05</v>
+        <v>101.7</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002350890144420623</v>
+        <v>0.002337142316110333</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>13.52</v>
+        <v>5.02</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1510108343571987</v>
+        <v>0.05192387256930078</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.1533463</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.717382</v>
+        <v>104.90344487</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>103.2</v>
+        <v>119.14</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.95</v>
+        <v>101.31</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002348608834236808</v>
+        <v>0.002328179823452683</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>6.27</v>
+        <v>11.78</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.06485312370707488</v>
+        <v>0.1315760080419971</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.1533463</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.74206342</v>
+        <v>2.27580753</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>74.99726962</v>
+        <v>62.95787236</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>79.84</v>
+        <v>60.24</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>102.71</v>
+        <v>101.08</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002343133689795654</v>
+        <v>0.00232289425085971</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>6.03</v>
+        <v>-5.07</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.06237070748862226</v>
+        <v>-0.04776260009420631</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.51</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1.74206342</v>
+        <v>2.27580753</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3847,25 +3847,25 @@
         <v>249.91595261</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>268.05</v>
+        <v>263.99</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>102.69</v>
+        <v>100.98</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002342677427758891</v>
+        <v>0.002320596175819287</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>6.75</v>
+        <v>5.04</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.07035647279549719</v>
+        <v>0.0525328330206379</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>0.51881442</v>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>62.95787236</v>
+        <v>137.713206</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>61.07</v>
+        <v>150.34</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>102.63</v>
+        <v>100.36</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002341308641648603</v>
+        <v>0.002306348110568663</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-3.52</v>
+        <v>8.09</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.03316062176165803</v>
+        <v>0.08767746829955565</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.34</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>137.713206</v>
+        <v>113.12478542</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>152.15</v>
+        <v>114.74</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>92.27</v>
+        <v>98.72</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>101.73</v>
+        <v>99.78</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002320776849994274</v>
+        <v>0.002293019275334209</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1025251977890972</v>
+        <v>0.01073743922204214</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.34</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.11796351</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>113.12478542</v>
+        <v>127.23134407</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>116.44</v>
+        <v>120.4</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>98.72</v>
+        <v>105.36</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>101.42</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.00231370478842445</v>
+        <v>0.002280609670115924</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.7</v>
+        <v>-6.12</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.02735008103727715</v>
+        <v>-0.0580865603644647</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.49</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.11796351</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4075,25 +4075,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>73.37</v>
+        <v>72.25</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>100.72</v>
+        <v>99.03</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.00229773561713775</v>
+        <v>0.002275783712531035</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-4.26</v>
+        <v>-5.95</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.04057915793484473</v>
+        <v>-0.05667746237378548</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.48</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>1.85908491</v>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>341.38450299</v>
+        <v>96.717382</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>357</v>
+        <v>98.98</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>99.68000000000001</v>
+        <v>98.59</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002274009991226081</v>
+        <v>0.002265672182353174</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>4.17</v>
+        <v>1.91</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.04366034970160192</v>
+        <v>0.01975589573851882</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.34</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>127.23134407</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>120.72</v>
+        <v>1278.83</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>99.66</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002273553729189318</v>
+        <v>0.002263374107312751</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-5.7</v>
+        <v>9.6</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.0541002277904328</v>
+        <v>0.1079986500168748</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-0.32</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.37810738</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>341.38450299</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1289.17</v>
+        <v>352.88</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>88.89</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>99.44</v>
+        <v>98.37</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002268534846784927</v>
+        <v>0.002260616417264243</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>10.55</v>
+        <v>2.86</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1186860164247947</v>
+        <v>0.02994450842843681</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.34</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.37810738</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4303,25 +4303,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>138.21</v>
+        <v>137</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>99.31</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002265569143545968</v>
+        <v>0.002258777957231904</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-12.13</v>
+        <v>-13.15</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.1088478104809763</v>
+        <v>-0.1180007178750897</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.63</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>0.97307689</v>
@@ -4360,25 +4360,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>145.51</v>
+        <v>142.79</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.45999999999999</v>
+        <v>96.47</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002246178006983547</v>
+        <v>0.002216952991496203</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-1.39</v>
+        <v>-3.38</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.01392088132198297</v>
+        <v>-0.03385077616424637</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.39</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,55 +4411,55 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.93456659</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>105.04894536</v>
+        <v>127.79185697</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>22.81</v>
+        <v>137.82</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>452.96</v>
+        <v>88.38</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>95.86</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002186863942204375</v>
+        <v>0.002182252058385814</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-357.1</v>
+        <v>6.58</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.7883698339809255</v>
+        <v>0.07445123331070379</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-11.48</v>
+        <v>-0.33</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0</v>
+        <v>0.93456659</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,55 +4468,55 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>5.691347</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>107.56862839</v>
+        <v>105.04894536</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>109.72</v>
+        <v>22.04</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>92.77</v>
+        <v>452.96</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>94.44</v>
+        <v>92.48</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002154469337594213</v>
+        <v>0.00212525979738332</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.67</v>
+        <v>-360.48</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.01800150910854802</v>
+        <v>-0.7958318615330273</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.18</v>
+        <v>-12.17</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>127.79185697</v>
+        <v>107.56862839</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>136.74</v>
+        <v>107.16</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>94.37</v>
+        <v>92.09</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002152872420465543</v>
+        <v>0.00211629730472567</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>5.99</v>
+        <v>-0.68</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.06777551482235801</v>
+        <v>-0.007329955804678237</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.33</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>234.11448729</v>
+        <v>126.99866255</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>201.08</v>
+        <v>105.85</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>92.28</v>
+        <v>91.55</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002105193037623824</v>
+        <v>0.002103887699507384</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-15.54</v>
+        <v>-18.9</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1441291040623261</v>
+        <v>-0.1711181530104119</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.61</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4620,17 +4620,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4639,34 +4639,34 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>126.99866255</v>
+        <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>105.95</v>
+        <v>199.19</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>110.45</v>
+        <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>91.78</v>
+        <v>91.27</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002093786486704752</v>
+        <v>0.0020974530893942</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-18.67</v>
+        <v>-16.55</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1690357627885921</v>
+        <v>-0.1534965683546652</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.55</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>59.48</v>
+        <v>57</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>81.12</v>
+        <v>77.62</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001850598821110149</v>
+        <v>0.001783765846376441</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-29.41</v>
+        <v>-32.91</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2660816068035827</v>
+        <v>-0.2977472179498779</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.61</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>109.42</v>
+        <v>107.74</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>51.08</v>
+        <v>50.22</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001165293241892338</v>
+        <v>0.001154093285300501</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>3.21</v>
+        <v>2.35</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.06705661165656988</v>
+        <v>0.0490912889074577</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.18</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>256</v>
+        <v>253.6</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.82</v>
+        <v>45.32</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001045296326223706</v>
+        <v>0.001041487608319767</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.29</v>
+        <v>-6.79</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1207061984264057</v>
+        <v>-0.1303012857417002</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.19</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4867,7 +4867,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-08 21:17:55</t>
+          <t>2026-09-09 21:03:40</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44018.42</v>
+        <v>43677.19</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43862.83</v>
+        <v>43521.58</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37740.21</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6122.62</v>
+        <v>5781.37</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1622306818112565</v>
+        <v>0.1531886017592377</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>184.24</v>
+        <v>184.26</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109.84</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7029.76</v>
+        <v>6976</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>983.99</v>
+        <v>930.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>15.064</v>
+        <v>14.968</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4368.56</v>
+        <v>4340.72</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>937.85</v>
+        <v>910.01</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1574.8</v>
+        <v>1549.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2777.84</v>
+        <v>2732.68</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1581.88</v>
+        <v>1536.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>26.9</v>
+        <v>26.31</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2284.34</v>
+        <v>2230.75</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>358.53</v>
+        <v>304.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>109.2</v>
+        <v>109.58</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2000.29</v>
+        <v>2004.11</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>353.72</v>
+        <v>357.54</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>504.91</v>
+        <v>521.3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1864.21</v>
+        <v>1921.72</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-34.34</v>
+        <v>23.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>225.72</v>
+        <v>223.68</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1821.14</v>
+        <v>1801.86</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>568.46</v>
+        <v>549.1799999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>225.7</v>
+        <v>235.21</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1599.98</v>
+        <v>1664.79</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-396.08</v>
+        <v>-331.27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>35</v>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>44.57</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1434.94</v>
+        <v>1419.03</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>206.6</v>
+        <v>190.69</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,22 +5277,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.32</v>
+        <v>119.38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1401.13</v>
+        <v>1399.64</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>57.34</v>
+        <v>55.85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5304,22 +5304,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D12" t="n">
-        <v>149.76</v>
+        <v>146.58</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1391.44</v>
+        <v>1359.77</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-480.4</v>
+        <v>-512.0700000000001</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>445.4</v>
+        <v>437.1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1231.74</v>
+        <v>1207.8</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>317.25</v>
+        <v>293.31</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>112.1</v>
+        <v>109.65</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1137.1</v>
+        <v>1112.25</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>529.91</v>
+        <v>505.06</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>696.4</v>
+        <v>688</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1114.24</v>
+        <v>1100.8</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>360.78</v>
+        <v>347.34</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>28.83</v>
+        <v>28.215</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1107.03</v>
+        <v>1081.72</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>11.25</v>
+        <v>-14.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>336</v>
+        <v>331.89</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1087.09</v>
+        <v>1072.11</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>445.1</v>
+        <v>430.12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>316.3</v>
+        <v>315.95</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>714.6900000000001</v>
+        <v>712.78</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>223.64</v>
+        <v>221.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>493.52</v>
+        <v>491.9</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>679.6799999999999</v>
+        <v>676.39</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>145.3</v>
+        <v>142.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,76 +5520,76 @@
         <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>45.29</v>
+        <v>44.71</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>668.87</v>
+        <v>659.27</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-198.71</v>
+        <v>-208.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>96</v>
+        <v>993.75</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>651.9</v>
+        <v>645.9400000000001</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>102.72</v>
+        <v>-16.74</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>995.5</v>
+        <v>94.27</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>647.08</v>
+        <v>639.15</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-15.6</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>326.4</v>
+        <v>322.19</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>561.6</v>
+        <v>553.49</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>72.33</v>
+        <v>64.22</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.796</v>
+        <v>3.781</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>531.4400000000001</v>
+        <v>529.34</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-6.93</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>338.58</v>
+        <v>331.13</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>500.04</v>
+        <v>488.27</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>92.12</v>
+        <v>80.34999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>232.68</v>
+        <v>239.51</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>190.76</v>
+        <v>196.05</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-5.76</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,130 +5709,130 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>135.05</v>
+        <v>139.99</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>132.2</v>
+        <v>136.82</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>12.47</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>3.30858696</v>
       </c>
       <c r="D28" t="n">
-        <v>272</v>
+        <v>51.74</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>127.39</v>
+        <v>126.21</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>112.71</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>27.54</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>51.5</v>
+        <v>213.93</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.82</v>
+        <v>124.7</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>13.11</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.63422137</v>
       </c>
       <c r="D30" t="n">
-        <v>210.15</v>
+        <v>265.22</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>122.68</v>
+        <v>124.02</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>110.41</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>12.27</v>
+        <v>24.17</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.42010405</v>
+        <v>0.62445608</v>
       </c>
       <c r="D31" t="n">
-        <v>394.07</v>
+        <v>267</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>122.25</v>
+        <v>122.93</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>109.16</v>
+        <v>108.77</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>13.09</v>
+        <v>14.16</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5844,130 +5844,130 @@
         <v>1.55804584</v>
       </c>
       <c r="D32" t="n">
-        <v>105.74</v>
+        <v>105.42</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>121.66</v>
+        <v>121.1</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>16.38</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="D33" t="n">
-        <v>262.16</v>
+        <v>390.35</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>120.89</v>
+        <v>120.9</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>108.77</v>
+        <v>109.16</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>12.12</v>
+        <v>11.74</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.81488812</v>
       </c>
       <c r="D34" t="n">
-        <v>65</v>
+        <v>42.75</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>120.2</v>
+        <v>120.24</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>106.81</v>
+        <v>108.23</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>13.39</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.50421091</v>
       </c>
       <c r="D35" t="n">
-        <v>571.5700000000001</v>
+        <v>64.41</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>118.34</v>
+        <v>118.92</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>105.75</v>
+        <v>106.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.59</v>
+        <v>12.11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.28038062</v>
       </c>
       <c r="D36" t="n">
-        <v>42.01</v>
+        <v>567.58</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>118.34</v>
+        <v>117.33</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>108.23</v>
+        <v>105.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10.11</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,22 +5979,22 @@
         <v>0.59183053</v>
       </c>
       <c r="D37" t="n">
-        <v>269.25</v>
+        <v>267.9</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>117.67</v>
+        <v>116.9</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>17.82</v>
+        <v>17.05</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6006,22 +6006,22 @@
         <v>2.76637723</v>
       </c>
       <c r="D38" t="n">
-        <v>57.44</v>
+        <v>57</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>117.34</v>
+        <v>116.26</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4.86</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6033,22 +6033,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>56.78</v>
+        <v>56.44</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.51</v>
+        <v>112.65</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>5.87</v>
+        <v>5.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6060,22 +6060,22 @@
         <v>1.73400968</v>
       </c>
       <c r="D40" t="n">
-        <v>88.45</v>
+        <v>87.58</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.26</v>
+        <v>111.97</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>11.73</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,22 +6087,22 @@
         <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>213.4</v>
+        <v>210.08</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.31</v>
+        <v>108.42</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-8.449999999999999</v>
+        <v>-10.34</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6114,22 +6114,22 @@
         <v>11.40066159</v>
       </c>
       <c r="D42" t="n">
-        <v>13.06</v>
+        <v>12.86</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>109.95</v>
+        <v>108.09</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3.8</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6141,22 +6141,22 @@
         <v>1.59010207</v>
       </c>
       <c r="D43" t="n">
-        <v>93.09999999999999</v>
+        <v>92.11</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>109.32</v>
+        <v>107.98</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>19.66</v>
+        <v>18.32</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6168,22 +6168,22 @@
         <v>0.61215748</v>
       </c>
       <c r="D44" t="n">
-        <v>240.49</v>
+        <v>238.33</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>108.71</v>
+        <v>107.57</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>88.09</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20.62</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6195,22 +6195,22 @@
         <v>0.40867246</v>
       </c>
       <c r="D45" t="n">
-        <v>353.65</v>
+        <v>354.75</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>106.72</v>
+        <v>106.89</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>13.89</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6222,292 +6222,292 @@
         <v>0.42255419</v>
       </c>
       <c r="D46" t="n">
-        <v>339.9</v>
+        <v>337.62</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>106.06</v>
+        <v>105.18</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4.67</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.74206342</v>
       </c>
       <c r="D47" t="n">
-        <v>209.15</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>105.79</v>
+        <v>104.77</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>16.33</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.68495686</v>
       </c>
       <c r="D48" t="n">
-        <v>256.6</v>
+        <v>206.81</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>105.17</v>
+        <v>104.44</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>13.99</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.5550481</v>
       </c>
       <c r="D49" t="n">
-        <v>10.7</v>
+        <v>255</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>105.1</v>
+        <v>104.35</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>106.96</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-1.86</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>13.30225117</v>
       </c>
       <c r="D50" t="n">
-        <v>326.09</v>
+        <v>10.56</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>104.95</v>
+        <v>103.57</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>104.04</v>
+        <v>106.96</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.91</v>
+        <v>-3.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.43583007</v>
       </c>
       <c r="D51" t="n">
-        <v>1102</v>
+        <v>319.62</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>104.62</v>
+        <v>102.7</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>98.89</v>
+        <v>104.04</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>5.73</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.80409618</v>
       </c>
       <c r="D52" t="n">
-        <v>278.11</v>
+        <v>172.63</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>104.07</v>
+        <v>102.34</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>7.39</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.1285649</v>
       </c>
       <c r="D53" t="n">
-        <v>175.23</v>
+        <v>1074</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>104.05</v>
+        <v>101.8</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>88.44</v>
+        <v>98.89</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>15.61</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="D54" t="n">
-        <v>121</v>
+        <v>272.21</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>103.05</v>
+        <v>101.7</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>13.52</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.1533463</v>
       </c>
       <c r="D55" t="n">
-        <v>103.2</v>
+        <v>119.14</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.95</v>
+        <v>101.31</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>6.27</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1.74206342</v>
+        <v>2.27580753</v>
       </c>
       <c r="D56" t="n">
-        <v>79.84</v>
+        <v>60.24</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>102.71</v>
+        <v>101.08</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>6.03</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6519,103 +6519,103 @@
         <v>0.51881442</v>
       </c>
       <c r="D57" t="n">
-        <v>268.05</v>
+        <v>263.99</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>102.69</v>
+        <v>100.98</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>6.75</v>
+        <v>5.04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="D58" t="n">
-        <v>61.07</v>
+        <v>150.34</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>102.63</v>
+        <v>100.36</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-3.52</v>
+        <v>8.09</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="D59" t="n">
-        <v>152.15</v>
+        <v>114.74</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>101.73</v>
+        <v>99.78</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>92.27</v>
+        <v>98.72</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>9.460000000000001</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.11796351</v>
       </c>
       <c r="D60" t="n">
-        <v>116.44</v>
+        <v>120.4</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>101.42</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>98.72</v>
+        <v>105.36</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2.7</v>
+        <v>-6.12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6627,103 +6627,103 @@
         <v>1.85908491</v>
       </c>
       <c r="D61" t="n">
-        <v>73.37</v>
+        <v>72.25</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>100.72</v>
+        <v>99.03</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-4.26</v>
+        <v>-5.95</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="D62" t="n">
-        <v>357</v>
+        <v>98.98</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>99.68000000000001</v>
+        <v>98.59</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>4.17</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="D63" t="n">
-        <v>120.72</v>
+        <v>1278.83</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>99.66</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-5.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.37810738</v>
       </c>
       <c r="D64" t="n">
-        <v>1289.17</v>
+        <v>352.88</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>99.44</v>
+        <v>98.37</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>88.89</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>10.55</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6735,22 +6735,22 @@
         <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>138.21</v>
+        <v>137</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>99.31</v>
+        <v>98.29000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-12.13</v>
+        <v>-13.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6762,157 +6762,157 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D66" t="n">
-        <v>145.51</v>
+        <v>142.79</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.45999999999999</v>
+        <v>96.47</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-1.39</v>
+        <v>-3.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.93456659</v>
       </c>
       <c r="D67" t="n">
-        <v>22.81</v>
+        <v>137.82</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>95.86</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>452.96</v>
+        <v>88.38</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-357.1</v>
+        <v>6.58</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>5.691347</v>
       </c>
       <c r="D68" t="n">
-        <v>109.72</v>
+        <v>22.04</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>94.44</v>
+        <v>92.48</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>92.77</v>
+        <v>452.96</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1.67</v>
+        <v>-360.48</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="D69" t="n">
-        <v>136.74</v>
+        <v>107.16</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>94.37</v>
+        <v>92.09</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>5.99</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="D70" t="n">
-        <v>201.08</v>
+        <v>105.85</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>92.28</v>
+        <v>91.55</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-15.54</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>105.95</v>
+        <v>199.19</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>91.78</v>
+        <v>91.27</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>110.45</v>
+        <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-18.67</v>
+        <v>-16.55</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>59.48</v>
+        <v>57</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>81.12</v>
+        <v>77.62</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-29.41</v>
+        <v>-32.91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>109.42</v>
+        <v>107.74</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>51.08</v>
+        <v>50.22</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>3.21</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>256</v>
+        <v>253.6</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.82</v>
+        <v>45.32</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.29</v>
+        <v>-6.79</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43677.19</v>
+        <v>43421.5</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43521.58</v>
+        <v>43265.02</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37740.21</v>
+        <v>37743.8</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5781.37</v>
+        <v>5521.22</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1531886017592377</v>
+        <v>0.1462815084861619</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>155.61</v>
+        <v>156.48</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>28.65</v>
+        <v>32.24</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-09 21:03:40</t>
+          <t>2026-09-10 21:01:43</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109</v>
+        <v>108.76</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6976</v>
+        <v>6960.64</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1603137148199182</v>
+        <v>0.1610033099792057</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>930.23</v>
+        <v>914.87</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1538646028545578</v>
+        <v>0.1513239835455202</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.968</v>
+        <v>14.748</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4340.72</v>
+        <v>4276.92</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09975300289465533</v>
+        <v>0.09892743720638682</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>910.01</v>
+        <v>846.21</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.265254131069079</v>
+        <v>0.2466573974483416</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1549.2</v>
+        <v>1529</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2732.68</v>
+        <v>2697.05</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06279903701463506</v>
+        <v>0.06238420277150042</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1536.72</v>
+        <v>1501.09</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.284925917254758</v>
+        <v>1.25513395096826</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.31</v>
+        <v>26.15</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2230.75</v>
+        <v>2221.5</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.0512643089642392</v>
+        <v>0.05138447802483757</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>304.94</v>
+        <v>295.69</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.158343761845665</v>
+        <v>0.1535405881161693</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-17.25</v>
+        <v>-13.54</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>109.58</v>
+        <v>107.44</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2004.11</v>
+        <v>1968.8</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04605595169262418</v>
+        <v>0.04553939245343246</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>357.54</v>
+        <v>322.23</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2171423018760211</v>
+        <v>0.1956977231456908</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-17.77</v>
+        <v>-14.59</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>521.3</v>
+        <v>503.66</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1921.72</v>
+        <v>1860.31</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04416256766681956</v>
+        <v>0.04302996097879162</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>23.17</v>
+        <v>-38.24</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01220405045956125</v>
+        <v>-0.0201416870769798</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-18.6</v>
+        <v>-14.93</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>223.68</v>
+        <v>219.69</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1801.86</v>
+        <v>1773.17</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04140809492336839</v>
+        <v>0.04101436637375703</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>520.49</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4384040616917328</v>
+        <v>0.4155011655011655</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-43.59</v>
+        <v>-41.23</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>235.21</v>
+        <v>228.17</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1664.79</v>
+        <v>1618.11</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03825812346546039</v>
+        <v>0.03742774599899613</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-331.27</v>
+        <v>-377.95</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1659619450317125</v>
+        <v>-0.1893480155907137</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-24.5</v>
+        <v>-20.66</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1143,57 +1143,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>US75734B1008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>35</v>
+        <v>12.5822526</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>37.05</v>
+        <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>44.57</v>
+        <v>155.34</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1228.34</v>
+        <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1419.03</v>
+        <v>1443.84</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03261037424611648</v>
+        <v>0.0333967880942523</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>190.69</v>
+        <v>-428</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.1552420339645375</v>
+        <v>-0.2286520215403026</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-48.73</v>
+        <v>-91.67</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-03-22</t>
         </is>
       </c>
     </row>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.38</v>
+        <v>119.34</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1399.64</v>
+        <v>1401.9</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03216477749577844</v>
+        <v>0.03242669355976583</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>55.85</v>
+        <v>58.11</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04156155351654649</v>
+        <v>0.0432433639184694</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-18.48</v>
+        <v>-15.9</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1257,57 +1257,57 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US75734B1008</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>12.5822526</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>191.52532353</v>
+        <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>146.58</v>
+        <v>43.95</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1871.84</v>
+        <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1359.77</v>
+        <v>1396.9</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03124853497716173</v>
+        <v>0.03231104089709458</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-512.0700000000001</v>
+        <v>168.56</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>-0.2735650482947261</v>
+        <v>0.1372258495204911</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-95.13</v>
+        <v>-50.75</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>437.1</v>
+        <v>439.5</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1207.8</v>
+        <v>1214.33</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02775615033823068</v>
+        <v>0.02808809957231646</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>293.31</v>
+        <v>299.84</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3207361480169275</v>
+        <v>0.3278767400408971</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.75</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>109.65</v>
+        <v>109.1</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1112.25</v>
+        <v>1106.67</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02556033963710637</v>
+        <v>0.02559786643967905</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>505.06</v>
+        <v>499.48</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8317989426703337</v>
+        <v>0.8226090680017787</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>688</v>
+        <v>682.4</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1100.8</v>
+        <v>1091.84</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02529721004497792</v>
+        <v>0.02525484064219611</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>347.34</v>
+        <v>338.38</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4609932843150266</v>
+        <v>0.4491014785124625</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.215</v>
+        <v>27.775</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1081.72</v>
+        <v>1066.93</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02485873732726519</v>
+        <v>0.02467865907676793</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-14.06</v>
+        <v>-28.85</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.0128310427275548</v>
+        <v>-0.02632827757396558</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-1.73</v>
+        <v>0.4</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>331.89</v>
+        <v>329.5</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1072.11</v>
+        <v>1066.47</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02463789231588052</v>
+        <v>0.02466801903180217</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>430.12</v>
+        <v>424.48</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6699792831664044</v>
+        <v>0.6611940995965669</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-35.11</v>
+        <v>-33.92</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>315.95</v>
+        <v>325.9</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>712.78</v>
+        <v>736.67</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01638021927312806</v>
+        <v>0.01703956940200634</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>221.73</v>
+        <v>245.62</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.4515426127685571</v>
+        <v>0.5001934629874758</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-22.09</v>
+        <v>-21.17</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>491.9</v>
+        <v>492.87</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>676.39</v>
+        <v>679.04</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01554394976591808</v>
+        <v>0.01570655681205748</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>142.01</v>
+        <v>144.66</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2657472210786332</v>
+        <v>0.2707062390059508</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-26.35</v>
+        <v>-25.36</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,25 +1738,25 @@
         <v>57.84</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44.71</v>
+        <v>44.08</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>659.27</v>
+        <v>651.25</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01515051931899764</v>
+        <v>0.01506375931293066</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-208.31</v>
+        <v>-216.33</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.2401046589363517</v>
+        <v>-0.249348763226446</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-14.7</v>
+        <v>-13.04</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
         <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>993.75</v>
+        <v>988</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>645.9400000000001</v>
+        <v>642.2</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01484418591610923</v>
+        <v>0.0148544279934957</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-16.74</v>
+        <v>-20.48</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.02526106114565099</v>
+        <v>-0.03090481076839501</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>94.27</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>639.15</v>
+        <v>625.04</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.0146881466208645</v>
+        <v>0.01445750805520796</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>89.97</v>
+        <v>75.86</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1638260679558615</v>
+        <v>0.1381332167959503</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-25.75</v>
+        <v>-24.73</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>322.19</v>
+        <v>320.71</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>553.49</v>
+        <v>552.02</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01271961554123804</v>
+        <v>0.01276851656955698</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>64.22</v>
+        <v>62.75</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1312567702904327</v>
+        <v>0.1282522942342674</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-32.96</v>
+        <v>-32.07</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.781</v>
+        <v>3.7705</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>529.34</v>
+        <v>527.87</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01216463041897585</v>
+        <v>0.01220991420885483</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10.5</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.01677285138473541</v>
+        <v>-0.01950331556364582</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>331.13</v>
+        <v>332.23</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>488.27</v>
+        <v>490.85</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01122081099987406</v>
+        <v>0.01135362189443688</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>80.34999999999999</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.196974897038635</v>
+        <v>0.2032996666012944</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-10.63</v>
+        <v>-9.85</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>239.51</v>
+        <v>234.02</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>196.05</v>
+        <v>191.93</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004505376116749566</v>
+        <v>0.004439443109298706</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-0.47</v>
+        <v>-4.59</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.002391614085080399</v>
+        <v>-0.02335640138408304</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-2.63</v>
+        <v>-2.25</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>139.99</v>
+        <v>135.11</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>136.82</v>
+        <v>132.3</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.00314422627030694</v>
+        <v>0.003060169454281347</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>17.09</v>
+        <v>12.57</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.1427378267769147</v>
+        <v>0.1049862189927337</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.59</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.63422137</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>45.93199509</v>
+        <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>51.74</v>
+        <v>267.33</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>112.71</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.21</v>
+        <v>125.25</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002900400508518045</v>
+        <v>0.00289709919991488</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>13.5</v>
+        <v>25.4</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.119776417354272</v>
+        <v>0.2543815723585378</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.16</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.63422137</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>213.93</v>
+        <v>212.99</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124.7</v>
+        <v>124.39</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002865699575407656</v>
+        <v>0.002877206941935424</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.29</v>
+        <v>13.98</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1294266823657277</v>
+        <v>0.1266189656733992</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.42</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.7905852</v>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.63422137</v>
+        <v>3.30858696</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>212.76482689</v>
+        <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>265.22</v>
+        <v>50.8</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.02</v>
+        <v>124.16</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002850072665132778</v>
+        <v>0.002871886919452547</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>24.17</v>
+        <v>11.45</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.242063094641963</v>
+        <v>0.1015881465708455</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.45</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.63422137</v>
+        <v>3.30858696</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>235.02053179</v>
+        <v>350.55601106</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>267</v>
+        <v>388.58</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>108.77</v>
+        <v>109.16</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>122.93</v>
+        <v>120.59</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002825023647192166</v>
+        <v>0.002789310918305273</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>14.16</v>
+        <v>11.43</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1301829548588765</v>
+        <v>0.1047086844998168</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.37</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.55804584</v>
+        <v>3.81488812</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>91.20399179</v>
+        <v>38.28159448</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>105.42</v>
+        <v>42.5</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>105.28</v>
+        <v>108.23</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>121.1</v>
+        <v>119.77</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002782968873952422</v>
+        <v>0.002770343881627187</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>15.82</v>
+        <v>11.54</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1502659574468085</v>
+        <v>0.1066247805599187</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.35</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.55804584</v>
+        <v>3.81488812</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>350.55601106</v>
+        <v>91.20399179</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>390.35</v>
+        <v>103.36</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>120.9</v>
+        <v>118.96</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002778372723871576</v>
+        <v>0.002751608150274444</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>11.74</v>
+        <v>13.68</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1075485525833639</v>
+        <v>0.1299392097264438</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.31</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.50421091</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>38.28159448</v>
+        <v>57.56703616</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>42.75</v>
+        <v>63.75</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>108.23</v>
+        <v>106.81</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>120.24</v>
+        <v>117.93</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002763205428604784</v>
+        <v>0.002727783701764166</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>12.01</v>
+        <v>11.12</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1109673842742308</v>
+        <v>0.1041101020503698</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.32</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.50421091</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.62445608</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>57.56703616</v>
+        <v>235.02053179</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>64.41</v>
+        <v>253.98</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>106.81</v>
+        <v>108.77</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.92</v>
+        <v>117.16</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002732870838071198</v>
+        <v>0.002709973191712793</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.11</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1133788971070124</v>
+        <v>0.07713523949618462</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.36</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.62445608</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>567.58</v>
+        <v>565.37</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.33</v>
+        <v>117.1</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.00269633144492847</v>
+        <v>0.002708585359760738</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>11.58</v>
+        <v>11.35</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1095035460992908</v>
+        <v>0.1073286052009456</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.29</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.28038062</v>
@@ -2707,25 +2707,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>267.9</v>
+        <v>266.35</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.9</v>
+        <v>116.45</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002686449722254651</v>
+        <v>0.002693550513613475</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>17.05</v>
+        <v>16.6</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.170756134201302</v>
+        <v>0.1662493740610917</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.16</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.59183053</v>
@@ -2764,25 +2764,25 @@
         <v>54.82621761</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>57</v>
+        <v>55.95</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>116.26</v>
+        <v>114.34</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002671742041995943</v>
+        <v>0.002644745089966207</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>3.78</v>
+        <v>1.86</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.03360597439544807</v>
+        <v>0.01653627311522048</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.44</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>2.76637723</v>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>53.65641702</v>
+        <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>56.44</v>
+        <v>87.87</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.65</v>
+        <v>112.56</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002588781533036667</v>
+        <v>0.002603572742055241</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>5.01</v>
+        <v>11.03</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.04654403567447046</v>
+        <v>0.1086378410322072</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.2</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>87.58</v>
+        <v>56.14</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.97</v>
+        <v>112.27</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.00257315462276179</v>
+        <v>0.002596864887620308</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10.44</v>
+        <v>4.63</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1028267507140747</v>
+        <v>0.04301374953548866</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.34</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2935,25 +2935,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>210.08</v>
+        <v>216.96</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>108.42</v>
+        <v>112.19</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002491572958826768</v>
+        <v>0.002595014445017568</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-10.34</v>
+        <v>-6.57</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.08706635230717413</v>
+        <v>-0.05532165712361065</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-2.32</v>
+        <v>-2.09</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>12.56856884</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>12.86</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>108.09</v>
+        <v>109.06</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002483989311193372</v>
+        <v>0.002522615878185364</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1.94</v>
+        <v>19.4</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.01827602449364107</v>
+        <v>0.216372964532679</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.16</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>92.11</v>
+        <v>12.9</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>89.66</v>
+        <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>107.98</v>
+        <v>108.64</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002481461428648907</v>
+        <v>0.002512901054520979</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>18.32</v>
+        <v>2.49</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.2043274592906536</v>
+        <v>0.02345737164390014</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>194.45976548</v>
+        <v>306.99401668</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>238.33</v>
+        <v>353.56</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.57</v>
+        <v>106.74</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002472039320983172</v>
+        <v>0.002468953042705902</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>19.48</v>
+        <v>13.91</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2211374730389374</v>
+        <v>0.1498438004955295</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.15</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.61215748</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>306.99401668</v>
+        <v>194.45976548</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>354.75</v>
+        <v>236.02</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>92.83</v>
+        <v>88.09</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>106.89</v>
+        <v>106.73</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002456412410708294</v>
+        <v>0.00246872173738056</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>14.06</v>
+        <v>18.64</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1514596574383281</v>
+        <v>0.2116017709161085</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.15</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.61215748</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.74206342</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>324.07677699</v>
+        <v>74.99726962</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>337.62</v>
+        <v>82.31</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>101.39</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>105.18</v>
+        <v>105.92</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002417115327517059</v>
+        <v>0.002449986006027817</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>3.79</v>
+        <v>9.24</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.03738041226945458</v>
+        <v>0.09557302441042614</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.17</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.74206342</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.42255419</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>74.99726962</v>
+        <v>324.07677699</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>81.56999999999999</v>
+        <v>338.67</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>104.77</v>
+        <v>105.72</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002407693219851324</v>
+        <v>0.002445359899520967</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>8.09</v>
+        <v>4.33</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.08367811336367396</v>
+        <v>0.04270638129993096</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.23</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.42255419</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.5550481</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>176.50746647</v>
+        <v>221.99877812</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>206.81</v>
+        <v>255.46</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>104.44</v>
+        <v>104.74</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002400109572217927</v>
+        <v>0.002422691977637401</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>14.98</v>
+        <v>13.56</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1674491392801252</v>
+        <v>0.1487168238648826</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.5550481</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.68495686</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>221.99877812</v>
+        <v>176.50746647</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.35</v>
+        <v>104.23</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002398041304681547</v>
+        <v>0.002410895406044934</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>13.17</v>
+        <v>14.77</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1444395700811581</v>
+        <v>0.1651017214397496</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.15</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.68495686</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.80409618</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>10.85229847</v>
+        <v>148.63893521</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>10.56</v>
+        <v>173.69</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>106.96</v>
+        <v>88.44</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>103.57</v>
+        <v>103.17</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002380116319366246</v>
+        <v>0.002386377041558628</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>-3.39</v>
+        <v>14.73</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>-0.03169409124906507</v>
+        <v>0.1665535956580733</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.15</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.80409618</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3505,25 +3505,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>319.62</v>
+        <v>317.44</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>102.7</v>
+        <v>102.2</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002360123066514565</v>
+        <v>0.002363940425000405</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-1.34</v>
+        <v>-1.84</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.012879661668589</v>
+        <v>-0.01768550557477893</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.26</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>0.43583007</v>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>148.63893521</v>
+        <v>104.90344487</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>172.63</v>
+        <v>119.82</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>88.44</v>
+        <v>89.53</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>102.34</v>
+        <v>102.09</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002351849996369042</v>
+        <v>0.002361396066421638</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>13.9</v>
+        <v>12.56</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1571687019448214</v>
+        <v>0.1402881715626047</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.15</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>257.81779936</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1074</v>
+        <v>271.6</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>101.8</v>
+        <v>101.67</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002339440391150756</v>
+        <v>0.002351681242757252</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2.91</v>
+        <v>4.99</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.02942663565577915</v>
+        <v>0.0516135705419942</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.17</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>257.81779936</v>
+        <v>249.91595261</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>272.21</v>
+        <v>265.2</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>101.7</v>
+        <v>101.64</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002337142316110333</v>
+        <v>0.002350987326781225</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.02</v>
+        <v>5.7</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.05192387256930078</v>
+        <v>0.05941213258286429</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.16</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.1285649</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>104.90344487</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>119.14</v>
+        <v>1062.4</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>89.53</v>
+        <v>98.89</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>101.31</v>
+        <v>100.9</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002328179823452683</v>
+        <v>0.00233387073270588</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>11.78</v>
+        <v>2.01</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1315760080419971</v>
+        <v>0.02032561431894023</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.1285649</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2.27580753</v>
+        <v>13.30225117</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>62.95787236</v>
+        <v>10.85229847</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>60.24</v>
+        <v>10.25</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>106.15</v>
+        <v>106.96</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.08</v>
+        <v>100.72</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.00232289425085971</v>
+        <v>0.002329707236849714</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>-5.07</v>
+        <v>-6.24</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.04776260009420631</v>
+        <v>-0.05833956619296934</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.32</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>2.27580753</v>
+        <v>13.30225117</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.51881442</v>
+        <v>2.27580753</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>249.91595261</v>
+        <v>62.95787236</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>263.99</v>
+        <v>59.57</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>95.94</v>
+        <v>106.15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.98</v>
+        <v>100.15</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002320596175819287</v>
+        <v>0.002316522833305191</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>5.04</v>
+        <v>-6</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.0525328330206379</v>
+        <v>-0.05652378709373528</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.51881442</v>
+        <v>2.27580753</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>137.713206</v>
+        <v>113.12478542</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>150.34</v>
+        <v>114.47</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>92.27</v>
+        <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.36</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002306348110568663</v>
+        <v>0.002307039314966149</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>8.09</v>
+        <v>1.02</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.08767746829955565</v>
+        <v>0.0103322528363047</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.15</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>113.12478542</v>
+        <v>137.713206</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>114.74</v>
+        <v>148.37</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>98.72</v>
+        <v>92.27</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.78</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002293019275334209</v>
+        <v>0.002295474048699024</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.06</v>
+        <v>6.97</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.01073743922204214</v>
+        <v>0.07553917849788663</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.16</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>127.23134407</v>
+        <v>341.38450299</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>120.4</v>
+        <v>354.25</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>105.36</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>99.23999999999999</v>
+        <v>98.95</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002280609670115924</v>
+        <v>0.002288766194264091</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-6.12</v>
+        <v>3.44</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.0580865603644647</v>
+        <v>0.03601717097686106</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.15</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>76.24181082</v>
+        <v>127.23134407</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>72.25</v>
+        <v>119.37</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>99.03</v>
+        <v>98.58</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002275783712531035</v>
+        <v>0.002280207897226418</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-5.95</v>
+        <v>-6.78</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.05667746237378548</v>
+        <v>-0.06435079726651481</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.29</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4132,25 +4132,25 @@
         <v>96.717382</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>98.98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98.59</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002265672182353174</v>
+        <v>0.002276044401370253</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.01975589573851882</v>
+        <v>0.01779064956557716</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.16</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>1.35094641</v>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.85908491</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>76.24181082</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1278.83</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>88.89</v>
+        <v>104.98</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.48999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002263374107312751</v>
+        <v>0.002276044401370253</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>9.6</v>
+        <v>-6.58</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.1079986500168748</v>
+        <v>-0.06267860544865689</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.27</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.85908491</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.97307689</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>341.38450299</v>
+        <v>154.44822659</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>352.88</v>
+        <v>136.72</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>111.44</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.37</v>
+        <v>98.28</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002260616417264243</v>
+        <v>0.002273268737466143</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>2.86</v>
+        <v>-13.16</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.02994450842843681</v>
+        <v>-0.1180904522613065</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.42</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.97307689</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.10445851</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>154.44822659</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>137</v>
+        <v>1271.49</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>111.44</v>
+        <v>88.89</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.29000000000001</v>
+        <v>98.11</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002258777957231904</v>
+        <v>0.00226933654693532</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-13.15</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.1180007178750897</v>
+        <v>0.1037237034537068</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.63</v>
+        <v>-0.15</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.10445851</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4360,25 +4360,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>142.79</v>
+        <v>142.88</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>96.47</v>
+        <v>96.72</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002216952991496203</v>
+        <v>0.002237185106712712</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-3.38</v>
+        <v>-3.13</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.03385077616424637</v>
+        <v>-0.03134702053079619</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.2</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4417,25 +4417,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>137.82</v>
+        <v>138.5</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>94.95999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002182252058385814</v>
+        <v>0.002211741520925037</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>6.58</v>
+        <v>7.24</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.07445123331070379</v>
+        <v>0.08191898619597195</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.15</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.93456659</v>
@@ -4474,25 +4474,25 @@
         <v>105.04894536</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>22.04</v>
+        <v>22.26</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>92.48</v>
+        <v>93.59</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.00212525979738332</v>
+        <v>0.002164786539880508</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-360.48</v>
+        <v>-359.37</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.7958318615330273</v>
+        <v>-0.7933813140233134</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-12.17</v>
+        <v>-11.3</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>0</v>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>1.17308322</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>107.56862839</v>
+        <v>126.99866255</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>107.16</v>
+        <v>105.84</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>92.77</v>
+        <v>110.45</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>92.09</v>
+        <v>91.72</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.00211629730472567</v>
+        <v>0.00212153244404146</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-0.68</v>
+        <v>-18.73</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.007329955804678237</v>
+        <v>-0.1695789950203712</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.39</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>1.17308322</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.16558147</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>126.99866255</v>
+        <v>107.56862839</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>105.85</v>
+        <v>105.05</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>110.45</v>
+        <v>92.77</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>91.55</v>
+        <v>90.45</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002103887699507384</v>
+        <v>0.002092156667722962</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-18.9</v>
+        <v>-2.32</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1711181530104119</v>
+        <v>-0.02500808451007869</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.15</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.16558147</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4645,25 +4645,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>199.19</v>
+        <v>196.42</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>91.27</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.0020974530893942</v>
+        <v>0.002085911423938714</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-16.55</v>
+        <v>-17.64</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1534965683546652</v>
+        <v>-0.1636060100166945</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.33</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>0.6214908</v>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>57</v>
+        <v>56.73</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.62</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001783765846376441</v>
+        <v>0.001790303218150992</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-32.91</v>
+        <v>-33.13</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2977472179498779</v>
+        <v>-0.2997376277933593</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.4</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>107.74</v>
+        <v>107.55</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>50.22</v>
+        <v>50.23</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001154093285300501</v>
+        <v>0.001161846649195404</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.0490912889074577</v>
+        <v>0.04930018800919156</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>253.6</v>
+        <v>253</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.32</v>
+        <v>45.3</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001041487608319767</v>
+        <v>0.001047813123801549</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.79</v>
+        <v>-6.81</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1303012857417002</v>
+        <v>-0.130685089234312</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.09</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,9 +4865,9 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-09 21:03:40</t>
+          <t>2026-09-10 21:01:43</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43677.19</v>
+        <v>43421.5</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43521.58</v>
+        <v>43265.02</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37740.21</v>
+        <v>37743.8</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5781.37</v>
+        <v>5521.22</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1531886017592377</v>
+        <v>0.1462815084861619</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>184.26</v>
+        <v>188.72</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109</v>
+        <v>108.76</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6976</v>
+        <v>6960.64</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>930.23</v>
+        <v>914.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.968</v>
+        <v>14.748</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4340.72</v>
+        <v>4276.92</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>910.01</v>
+        <v>846.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1549.2</v>
+        <v>1529</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2732.68</v>
+        <v>2697.05</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1536.72</v>
+        <v>1501.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>26.31</v>
+        <v>26.15</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2230.75</v>
+        <v>2221.5</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>304.94</v>
+        <v>295.69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>109.58</v>
+        <v>107.44</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2004.11</v>
+        <v>1968.8</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>357.54</v>
+        <v>322.23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>521.3</v>
+        <v>503.66</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1921.72</v>
+        <v>1860.31</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>23.17</v>
+        <v>-38.24</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>223.68</v>
+        <v>219.69</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1801.86</v>
+        <v>1773.17</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>520.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,49 +5223,49 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>235.21</v>
+        <v>228.17</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1664.79</v>
+        <v>1618.11</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-331.27</v>
+        <v>-377.95</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>35</v>
+        <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>44.57</v>
+        <v>155.34</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1419.03</v>
+        <v>1443.84</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1228.34</v>
+        <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>190.69</v>
+        <v>-428</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,49 +5277,49 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.38</v>
+        <v>119.34</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1399.64</v>
+        <v>1401.9</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>55.85</v>
+        <v>58.11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12.5822526</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>146.58</v>
+        <v>43.95</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1359.77</v>
+        <v>1396.9</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1871.84</v>
+        <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-512.0700000000001</v>
+        <v>168.56</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>437.1</v>
+        <v>439.5</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1207.8</v>
+        <v>1214.33</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>293.31</v>
+        <v>299.84</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>109.65</v>
+        <v>109.1</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1112.25</v>
+        <v>1106.67</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>505.06</v>
+        <v>499.48</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>688</v>
+        <v>682.4</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1100.8</v>
+        <v>1091.84</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>347.34</v>
+        <v>338.38</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>28.215</v>
+        <v>27.775</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1081.72</v>
+        <v>1066.93</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-14.06</v>
+        <v>-28.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>331.89</v>
+        <v>329.5</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1072.11</v>
+        <v>1066.47</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>430.12</v>
+        <v>424.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>315.95</v>
+        <v>325.9</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>712.78</v>
+        <v>736.67</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>221.73</v>
+        <v>245.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>491.9</v>
+        <v>492.87</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>676.39</v>
+        <v>679.04</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>142.01</v>
+        <v>144.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,22 +5520,22 @@
         <v>20</v>
       </c>
       <c r="D20" t="n">
-        <v>44.71</v>
+        <v>44.08</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>659.27</v>
+        <v>651.25</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-208.31</v>
+        <v>-216.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>993.75</v>
+        <v>988</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>645.9400000000001</v>
+        <v>642.2</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-16.74</v>
+        <v>-20.48</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>94.27</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>639.15</v>
+        <v>625.04</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>89.97</v>
+        <v>75.86</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>322.19</v>
+        <v>320.71</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>553.49</v>
+        <v>552.02</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>64.22</v>
+        <v>62.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.781</v>
+        <v>3.7705</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>529.34</v>
+        <v>527.87</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-9.029999999999999</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>331.13</v>
+        <v>332.23</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>488.27</v>
+        <v>490.85</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>80.34999999999999</v>
+        <v>82.93000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>239.51</v>
+        <v>234.02</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>196.05</v>
+        <v>191.93</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.47</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,49 +5709,49 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>139.99</v>
+        <v>135.11</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>136.82</v>
+        <v>132.3</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>17.09</v>
+        <v>12.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>51.74</v>
+        <v>267.33</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.21</v>
+        <v>125.25</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>112.71</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>13.5</v>
+        <v>25.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,184 +5763,184 @@
         <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>213.93</v>
+        <v>212.99</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124.7</v>
+        <v>124.39</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.29</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.63422137</v>
+        <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>265.22</v>
+        <v>50.8</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.02</v>
+        <v>124.16</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>24.17</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="D31" t="n">
-        <v>267</v>
+        <v>388.58</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>122.93</v>
+        <v>120.59</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>108.77</v>
+        <v>109.16</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>14.16</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.55804584</v>
+        <v>3.81488812</v>
       </c>
       <c r="D32" t="n">
-        <v>105.42</v>
+        <v>42.5</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>121.1</v>
+        <v>119.77</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>105.28</v>
+        <v>108.23</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>15.82</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="D33" t="n">
-        <v>390.35</v>
+        <v>103.36</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>120.9</v>
+        <v>118.96</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>11.74</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.50421091</v>
       </c>
       <c r="D34" t="n">
-        <v>42.75</v>
+        <v>63.75</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>120.24</v>
+        <v>117.93</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>108.23</v>
+        <v>106.81</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.01</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.62445608</v>
       </c>
       <c r="D35" t="n">
-        <v>64.41</v>
+        <v>253.98</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>118.92</v>
+        <v>117.16</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>106.81</v>
+        <v>108.77</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.11</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5952,22 +5952,22 @@
         <v>0.28038062</v>
       </c>
       <c r="D36" t="n">
-        <v>567.58</v>
+        <v>565.37</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.33</v>
+        <v>117.1</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>11.58</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,22 +5979,22 @@
         <v>0.59183053</v>
       </c>
       <c r="D37" t="n">
-        <v>267.9</v>
+        <v>266.35</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.9</v>
+        <v>116.45</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>17.05</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6006,76 +6006,76 @@
         <v>2.76637723</v>
       </c>
       <c r="D38" t="n">
-        <v>57</v>
+        <v>55.95</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>116.26</v>
+        <v>114.34</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3.78</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>56.44</v>
+        <v>87.87</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.65</v>
+        <v>112.56</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>5.01</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D40" t="n">
-        <v>87.58</v>
+        <v>56.14</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.97</v>
+        <v>112.27</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>10.44</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,265 +6087,265 @@
         <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>210.08</v>
+        <v>216.96</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>108.42</v>
+        <v>112.19</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-10.34</v>
+        <v>-6.57</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="D42" t="n">
-        <v>12.86</v>
+        <v>92.84999999999999</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>108.09</v>
+        <v>109.06</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1.94</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="D43" t="n">
-        <v>92.11</v>
+        <v>12.9</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>107.98</v>
+        <v>108.64</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>89.66</v>
+        <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>18.32</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="D44" t="n">
-        <v>238.33</v>
+        <v>353.56</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.57</v>
+        <v>106.74</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>19.48</v>
+        <v>13.91</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.61215748</v>
       </c>
       <c r="D45" t="n">
-        <v>354.75</v>
+        <v>236.02</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>106.89</v>
+        <v>106.73</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.83</v>
+        <v>88.09</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>14.06</v>
+        <v>18.64</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.74206342</v>
       </c>
       <c r="D46" t="n">
-        <v>337.62</v>
+        <v>82.31</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>105.18</v>
+        <v>105.92</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>101.39</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>3.79</v>
+        <v>9.24</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.42255419</v>
       </c>
       <c r="D47" t="n">
-        <v>81.56999999999999</v>
+        <v>338.67</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>104.77</v>
+        <v>105.72</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>8.09</v>
+        <v>4.33</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.5550481</v>
       </c>
       <c r="D48" t="n">
-        <v>206.81</v>
+        <v>255.46</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104.44</v>
+        <v>104.74</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>14.98</v>
+        <v>13.56</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.68495686</v>
       </c>
       <c r="D49" t="n">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.35</v>
+        <v>104.23</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>13.17</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.80409618</v>
       </c>
       <c r="D50" t="n">
-        <v>10.56</v>
+        <v>173.69</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>103.57</v>
+        <v>103.17</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>106.96</v>
+        <v>88.44</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-3.39</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6357,292 +6357,292 @@
         <v>0.43583007</v>
       </c>
       <c r="D51" t="n">
-        <v>319.62</v>
+        <v>317.44</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>102.7</v>
+        <v>102.2</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-1.34</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="D52" t="n">
-        <v>172.63</v>
+        <v>119.82</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>102.34</v>
+        <v>102.09</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>88.44</v>
+        <v>89.53</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>13.9</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="D53" t="n">
-        <v>1074</v>
+        <v>271.6</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>101.8</v>
+        <v>101.67</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>2.91</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="D54" t="n">
-        <v>272.21</v>
+        <v>265.2</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>101.7</v>
+        <v>101.64</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5.02</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.1285649</v>
       </c>
       <c r="D55" t="n">
-        <v>119.14</v>
+        <v>1062.4</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>101.31</v>
+        <v>100.9</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>89.53</v>
+        <v>98.89</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>11.78</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2.27580753</v>
+        <v>13.30225117</v>
       </c>
       <c r="D56" t="n">
-        <v>60.24</v>
+        <v>10.25</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>101.08</v>
+        <v>100.72</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>106.15</v>
+        <v>106.96</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-5.07</v>
+        <v>-6.24</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.51881442</v>
+        <v>2.27580753</v>
       </c>
       <c r="D57" t="n">
-        <v>263.99</v>
+        <v>59.57</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.98</v>
+        <v>100.15</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>95.94</v>
+        <v>106.15</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>5.04</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="D58" t="n">
-        <v>150.34</v>
+        <v>114.47</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.36</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>92.27</v>
+        <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>8.09</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="D59" t="n">
-        <v>114.74</v>
+        <v>148.37</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.78</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>98.72</v>
+        <v>92.27</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1.06</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="D60" t="n">
-        <v>120.4</v>
+        <v>354.25</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>99.23999999999999</v>
+        <v>98.95</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>105.36</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-6.12</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="D61" t="n">
-        <v>72.25</v>
+        <v>119.37</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>99.03</v>
+        <v>98.58</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-5.95</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6654,103 +6654,103 @@
         <v>1.35094641</v>
       </c>
       <c r="D62" t="n">
-        <v>98.98</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>98.59</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.85908491</v>
       </c>
       <c r="D63" t="n">
-        <v>1278.83</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.48999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>88.89</v>
+        <v>104.98</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>9.6</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.97307689</v>
       </c>
       <c r="D64" t="n">
-        <v>352.88</v>
+        <v>136.72</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.37</v>
+        <v>98.28</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>111.44</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>2.86</v>
+        <v>-13.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.10445851</v>
       </c>
       <c r="D65" t="n">
-        <v>137</v>
+        <v>1271.49</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.29000000000001</v>
+        <v>98.11</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>111.44</v>
+        <v>88.89</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-13.15</v>
+        <v>9.220000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6762,22 +6762,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D66" t="n">
-        <v>142.79</v>
+        <v>142.88</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>96.47</v>
+        <v>96.72</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-3.38</v>
+        <v>-3.13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6789,22 +6789,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D67" t="n">
-        <v>137.82</v>
+        <v>138.5</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>94.95999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>6.58</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,76 +6816,76 @@
         <v>5.691347</v>
       </c>
       <c r="D68" t="n">
-        <v>22.04</v>
+        <v>22.26</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>92.48</v>
+        <v>93.59</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-360.48</v>
+        <v>-359.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>1.17308322</v>
       </c>
       <c r="D69" t="n">
-        <v>107.16</v>
+        <v>105.84</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.09</v>
+        <v>91.72</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>92.77</v>
+        <v>110.45</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-0.68</v>
+        <v>-18.73</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.16558147</v>
       </c>
       <c r="D70" t="n">
-        <v>105.85</v>
+        <v>105.05</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.55</v>
+        <v>90.45</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>110.45</v>
+        <v>92.77</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-18.9</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>199.19</v>
+        <v>196.42</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>91.27</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-16.55</v>
+        <v>-17.64</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>57</v>
+        <v>56.73</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.62</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-32.91</v>
+        <v>-33.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>107.74</v>
+        <v>107.55</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>50.22</v>
+        <v>50.23</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>253.6</v>
+        <v>253</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.32</v>
+        <v>45.3</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.79</v>
+        <v>-6.81</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43421.5</v>
+        <v>43915.91</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43265.02</v>
+        <v>43759.41</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37743.8</v>
+        <v>37744.56</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5521.22</v>
+        <v>6014.85</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1462815084861619</v>
+        <v>0.1593567390903484</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>156.48</v>
+        <v>156.5</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>32.24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-10 21:01:43</t>
+          <t>2026-09-11 21:06:30</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>108.76</v>
+        <v>109.74</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6960.64</v>
+        <v>7023.36</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1610033099792057</v>
+        <v>0.1606204392582611</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>914.87</v>
+        <v>977.59</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1513239835455202</v>
+        <v>0.1616981790574236</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.748</v>
+        <v>14.922</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4276.92</v>
+        <v>4327.38</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09892743720638682</v>
+        <v>0.09896483683556219</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>846.21</v>
+        <v>896.67</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2466573974483416</v>
+        <v>0.2613657231301975</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1529</v>
+        <v>1552.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2697.05</v>
+        <v>2738.68</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06238420277150042</v>
+        <v>0.06263212829583199</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1501.09</v>
+        <v>1542.72</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.25513395096826</v>
+        <v>1.289942807451754</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.15</v>
+        <v>26.53</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2221.5</v>
+        <v>2253.69</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05138447802483757</v>
+        <v>0.05154066967262828</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>295.69</v>
+        <v>327.88</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1535405881161693</v>
+        <v>0.1702556326948141</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-13.54</v>
+        <v>-13.61</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>107.44</v>
+        <v>111.98</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1968.8</v>
+        <v>2051.91</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04553939245343246</v>
+        <v>0.04692607035926089</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>322.23</v>
+        <v>405.34</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1956977231456908</v>
+        <v>0.2461723461498752</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-14.59</v>
+        <v>-14.66</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>503.66</v>
+        <v>515.04</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1860.31</v>
+        <v>1902.26</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04302996097879162</v>
+        <v>0.04350365591161778</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-38.24</v>
+        <v>3.71</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.0201416870769798</v>
+        <v>0.001954122883253009</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-14.93</v>
+        <v>-15.02</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>219.69</v>
+        <v>218.36</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1773.17</v>
+        <v>1762.36</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04101436637375703</v>
+        <v>0.04030421868324977</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>520.49</v>
+        <v>509.68</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4155011655011655</v>
+        <v>0.4068716671456397</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-41.23</v>
+        <v>-41.28</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>228.17</v>
+        <v>235.98</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1618.11</v>
+        <v>1673.42</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03742774599899613</v>
+        <v>0.03827020905429301</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-377.95</v>
+        <v>-322.64</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1893480155907137</v>
+        <v>-0.1616384277025741</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-20.66</v>
+        <v>-20.75</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>155.34</v>
+        <v>157.78</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1443.84</v>
+        <v>1466.45</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.0333967880942523</v>
+        <v>0.03353691725189611</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-428</v>
+        <v>-405.39</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2286520215403026</v>
+        <v>-0.2165729976921104</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-91.67</v>
+        <v>-91.75</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1200,114 +1200,114 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>113.04005874</v>
+        <v>37.05</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.34</v>
+        <v>44.56</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1401.9</v>
+        <v>1410.39</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03242669355976583</v>
+        <v>0.03225485541471018</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>58.11</v>
+        <v>182.05</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.0432433639184694</v>
+        <v>0.148208150837716</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-15.9</v>
+        <v>-55.65</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>37.05</v>
+        <v>113.04005874</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>43.95</v>
+        <v>119.4</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1396.9</v>
+        <v>1402.54</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03231104089709458</v>
+        <v>0.03207533016637074</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>168.56</v>
+        <v>58.75</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1372258495204911</v>
+        <v>0.04371962881104935</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-50.75</v>
+        <v>-15.96</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>439.5</v>
+        <v>442.3</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1214.33</v>
+        <v>1221.02</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02808809957231646</v>
+        <v>0.02792406607992784</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>299.84</v>
+        <v>306.53</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3278767400408971</v>
+        <v>0.335192292972039</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-0.75</v>
+        <v>-1.53</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>109.1</v>
+        <v>111.15</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1106.67</v>
+        <v>1127.46</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02559786643967905</v>
+        <v>0.02578439955322226</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>499.48</v>
+        <v>520.27</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8226090680017787</v>
+        <v>0.8568487623313953</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>682.4</v>
+        <v>697.8</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1091.84</v>
+        <v>1116.48</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02525484064219611</v>
+        <v>0.0255332929001309</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>338.38</v>
+        <v>363.02</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4491014785124625</v>
+        <v>0.4818039444695139</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>27.775</v>
+        <v>28.177</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1066.93</v>
+        <v>1082.32</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02467865907676793</v>
+        <v>0.02475207220162446</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-28.85</v>
+        <v>-13.46</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.02632827757396558</v>
+        <v>-0.01228348756137181</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>329.5</v>
+        <v>328.65</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1066.47</v>
+        <v>1063.67</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02466801903180217</v>
+        <v>0.02432555680270335</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>424.48</v>
+        <v>421.68</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6611940995965669</v>
+        <v>0.6568326609448746</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-33.92</v>
+        <v>-33.95</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>325.9</v>
+        <v>332.5</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>736.67</v>
+        <v>751.55</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01703956940200634</v>
+        <v>0.01718754145089332</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>245.62</v>
+        <v>260.5</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5001934629874758</v>
+        <v>0.530495876183688</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-21.17</v>
+        <v>-21.2</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>492.87</v>
+        <v>495.19</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>679.04</v>
+        <v>682.21</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01570655681205748</v>
+        <v>0.01560177320632551</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>144.66</v>
+        <v>147.83</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2707062390059508</v>
+        <v>0.2766383472435346</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.36</v>
+        <v>-25.38</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1713,114 +1713,114 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US6701002056</t>
+          <t>IE00B43HR379</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>57.84</v>
+        <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>44.08</v>
+        <v>984.75</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>867.58</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>651.25</v>
+        <v>640.09</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01506375931293066</v>
+        <v>0.01463851161905703</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-216.33</v>
+        <v>-22.59</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.249348763226446</v>
+        <v>-0.03408885133095914</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-13.04</v>
+        <v>0</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IE00B43HR379</t>
+          <t>US6701002056</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1019.5</v>
+        <v>57.84</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>988</v>
+        <v>43.1</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>867.58</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>642.2</v>
+        <v>636.75</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.0148544279934957</v>
+        <v>0.01456212762804381</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-20.48</v>
+        <v>-230.83</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.03090481076839501</v>
+        <v>-0.2660619193619032</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>-13.07</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1852,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>625.04</v>
+        <v>614.76</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01445750805520796</v>
+        <v>0.01405922823810948</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>75.86</v>
+        <v>65.58</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1381332167959503</v>
+        <v>0.1194143996503879</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-24.73</v>
+        <v>-24.75</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>320.71</v>
+        <v>324.69</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>552.02</v>
+        <v>558.84</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01276851656955698</v>
+        <v>0.01278036812509777</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>62.75</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1282522942342674</v>
+        <v>0.1421914280458642</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-32.07</v>
+        <v>-32.1</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.7705</v>
+        <v>3.772</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>527.87</v>
+        <v>528.08</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01220991420885483</v>
+        <v>0.01207690358510777</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-10.5</v>
+        <v>-10.29</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.01950331556364582</v>
+        <v>-0.0191132492523729</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>332.23</v>
+        <v>338.5</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>490.85</v>
+        <v>500.09</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01135362189443688</v>
+        <v>0.0114367874448503</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>82.93000000000001</v>
+        <v>92.17</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2032996666012944</v>
+        <v>0.2259511668954697</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-9.85</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>234.02</v>
+        <v>242.82</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>191.93</v>
+        <v>199.14</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004439443109298706</v>
+        <v>0.004554223943225197</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-4.59</v>
+        <v>2.62</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.02335640138408304</v>
+        <v>0.01333197638917159</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-2.25</v>
+        <v>-2.26</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>135.11</v>
+        <v>133.07</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>132.3</v>
+        <v>130.3</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003060169454281347</v>
+        <v>0.002979890427850975</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>12.57</v>
+        <v>10.57</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.1049862189927337</v>
+        <v>0.08828196776079512</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.6</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2194,25 +2194,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>267.33</v>
+        <v>268.37</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>125.25</v>
+        <v>125.73</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.00289709919991488</v>
+        <v>0.002875377003021513</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>25.4</v>
+        <v>25.88</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2543815723585378</v>
+        <v>0.2591887831747621</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2251,25 +2251,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>212.99</v>
+        <v>213.92</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124.39</v>
+        <v>124.93</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002877206941935424</v>
+        <v>0.00285708143631176</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>13.98</v>
+        <v>14.52</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1266189656733992</v>
+        <v>0.1315098270084231</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.7905852</v>
@@ -2308,22 +2308,22 @@
         <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>50.8</v>
+        <v>50.07</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.16</v>
+        <v>122.37</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002871886919452547</v>
+        <v>0.002798535622840551</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>11.45</v>
+        <v>9.66</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1015881465708455</v>
+        <v>0.08570668086239021</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-0.45</v>
@@ -2365,25 +2365,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>388.58</v>
+        <v>388.51</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120.59</v>
+        <v>120.56</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002789310918305273</v>
+        <v>0.002757141903159736</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>11.43</v>
+        <v>11.4</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1047086844998168</v>
+        <v>0.1044338585562477</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.38</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>0.42010405</v>
@@ -2422,22 +2422,22 @@
         <v>38.28159448</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>42.5</v>
+        <v>42.27</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.77</v>
+        <v>119.12</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002770343881627187</v>
+        <v>0.002724209883082181</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>11.54</v>
+        <v>10.89</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1066247805599187</v>
+        <v>0.1006190520188488</v>
       </c>
       <c r="M32" s="2" t="n">
         <v>-0.35</v>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.28038062</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>91.20399179</v>
+        <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>103.36</v>
+        <v>569.35</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>105.28</v>
+        <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>118.96</v>
+        <v>117.92</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002751608150274444</v>
+        <v>0.002696766533017552</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.68</v>
+        <v>12.17</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1299392097264438</v>
+        <v>0.1150827423167849</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.3</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.28038062</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2536,22 +2536,22 @@
         <v>57.56703616</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>63.75</v>
+        <v>63.64</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002727783701764166</v>
+        <v>0.002692192641340113</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>11.12</v>
+        <v>10.91</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1041101020503698</v>
+        <v>0.1021439940080517</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-0.32</v>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.55804584</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>235.02053179</v>
+        <v>91.20399179</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>253.98</v>
+        <v>101.95</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>108.77</v>
+        <v>105.28</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.16</v>
+        <v>117.33</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002709973191712793</v>
+        <v>0.002683273552569109</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>12.05</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.07713523949618462</v>
+        <v>0.1144566869300912</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.55804584</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.62445608</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>509.16500577</v>
+        <v>235.02053179</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>565.37</v>
+        <v>253.4</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>105.75</v>
+        <v>108.77</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.1</v>
+        <v>116.89</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002708585359760738</v>
+        <v>0.002673210990878745</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>11.35</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1073286052009456</v>
+        <v>0.07465293739082467</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.36</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.62445608</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>266.35</v>
+        <v>265.95</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.45</v>
+        <v>116.27</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002693550513613475</v>
+        <v>0.002659031926678687</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>16.6</v>
+        <v>16.42</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1662493740610917</v>
+        <v>0.1644466700050075</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.59183053</v>
@@ -2764,22 +2764,22 @@
         <v>54.82621761</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>55.95</v>
+        <v>56.06</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.34</v>
+        <v>114.56</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002644745089966207</v>
+        <v>0.00261992515283659</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.01653627311522048</v>
+        <v>0.01849217638691323</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-0.44</v>
@@ -2821,25 +2821,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>87.87</v>
+        <v>88.41</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.56</v>
+        <v>113.24</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002603572742055241</v>
+        <v>0.002589737467765498</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>11.03</v>
+        <v>11.71</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1086378410322072</v>
+        <v>0.1153353688564956</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>1.73400968</v>
@@ -2878,22 +2878,22 @@
         <v>53.65641702</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>56.14</v>
+        <v>56.55</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.27</v>
+        <v>113.09</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002596864887620308</v>
+        <v>0.00258630704900742</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.63</v>
+        <v>5.45</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.04301374953548866</v>
+        <v>0.05063173541434411</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>-0.34</v>
@@ -2935,22 +2935,22 @@
         <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>216.96</v>
+        <v>216.46</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>112.19</v>
+        <v>111.93</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002595014445017568</v>
+        <v>0.002559778477278278</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-6.57</v>
+        <v>-6.83</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.05532165712361065</v>
+        <v>-0.05751094644661502</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-2.09</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>12.56856884</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>92.84999999999999</v>
+        <v>13.15</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>89.66</v>
+        <v>106.15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.06</v>
+        <v>110.74</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002522615878185364</v>
+        <v>0.002532563821797521</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>19.4</v>
+        <v>4.59</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.216372964532679</v>
+        <v>0.04324069712670749</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.31</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>12.56856884</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.9</v>
+        <v>93.77</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.64</v>
+        <v>110.14</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002512901054520979</v>
+        <v>0.002518842146765207</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.49</v>
+        <v>20.48</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.02345737164390014</v>
+        <v>0.2284184697747045</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3106,22 +3106,22 @@
         <v>306.99401668</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>353.56</v>
+        <v>356.02</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>106.74</v>
+        <v>107.48</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002468953042705902</v>
+        <v>0.002458009387455279</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>13.91</v>
+        <v>14.65</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1498438004955295</v>
+        <v>0.1578153614133362</v>
       </c>
       <c r="M44" s="2" t="n">
         <v>-0.15</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>194.45976548</v>
+        <v>74.99726962</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>236.02</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>106.73</v>
+        <v>107.08</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.00246872173738056</v>
+        <v>0.002448861604100402</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>18.64</v>
+        <v>10.4</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.2116017709161085</v>
+        <v>0.1075713694662805</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.5550481</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>74.99726962</v>
+        <v>221.99877812</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>82.31</v>
+        <v>259.3</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>105.92</v>
+        <v>106.31</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002449986006027817</v>
+        <v>0.002431252121142265</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>9.24</v>
+        <v>15.13</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.09557302441042614</v>
+        <v>0.1659355121737223</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.5550481</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.61215748</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>324.07677699</v>
+        <v>194.45976548</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>338.67</v>
+        <v>234.57</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>101.39</v>
+        <v>88.09</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>105.72</v>
+        <v>106.07</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002445359899520967</v>
+        <v>0.002425763451129339</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4.33</v>
+        <v>17.98</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.04270638129993096</v>
+        <v>0.2041094335338858</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.16</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.61215748</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.42255419</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>221.99877812</v>
+        <v>324.07677699</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>255.46</v>
+        <v>337.86</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>104.74</v>
+        <v>105.46</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002422691977637401</v>
+        <v>0.002411813081513153</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>13.56</v>
+        <v>4.07</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1487168238648826</v>
+        <v>0.04014202584081271</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.42255419</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3391,22 +3391,22 @@
         <v>176.50746647</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>206</v>
+        <v>205.9</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.23</v>
+        <v>104.18</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002410895406044934</v>
+        <v>0.002382540174777549</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>14.77</v>
+        <v>14.72</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1651017214397496</v>
+        <v>0.1645428124301364</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>-0.15</v>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.43583007</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>148.63893521</v>
+        <v>322.35040597</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>173.69</v>
+        <v>323.31</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>88.44</v>
+        <v>104.04</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>103.17</v>
+        <v>104.09</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002386377041558628</v>
+        <v>0.002380481923522702</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>14.73</v>
+        <v>0.05</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1665535956580733</v>
+        <v>0.0004805843906189927</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.43583007</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.80409618</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>322.35040597</v>
+        <v>148.63893521</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>317.44</v>
+        <v>174.88</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>104.04</v>
+        <v>88.44</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>102.2</v>
+        <v>103.87</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002363940425000405</v>
+        <v>0.00237545064267752</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-1.84</v>
+        <v>15.43</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.01768550557477893</v>
+        <v>0.174468566259611</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.16</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.80409618</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3562,25 +3562,25 @@
         <v>104.90344487</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>119.82</v>
+        <v>121.5</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>102.09</v>
+        <v>103.51</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002361396066421638</v>
+        <v>0.002367217637658131</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>12.56</v>
+        <v>13.98</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1402881715626047</v>
+        <v>0.156148776946275</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>1.1533463</v>
@@ -3619,22 +3619,22 @@
         <v>257.81779936</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>271.6</v>
+        <v>276.18</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>101.67</v>
+        <v>103.38</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002351681242757252</v>
+        <v>0.002364244608067796</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.99</v>
+        <v>6.7</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.0516135705419942</v>
+        <v>0.06930078609846918</v>
       </c>
       <c r="M53" s="2" t="n">
         <v>-0.17</v>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>249.91595261</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>265.2</v>
+        <v>1079.65</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>101.64</v>
+        <v>102.53</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002350987326781225</v>
+        <v>0.002344805568438684</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.7</v>
+        <v>3.64</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.05941213258286429</v>
+        <v>0.03680857518454849</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>249.91595261</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1062.4</v>
+        <v>267</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>100.9</v>
+        <v>102.32</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.00233387073270588</v>
+        <v>0.002340002982177374</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.01</v>
+        <v>6.38</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.02032561431894023</v>
+        <v>0.06649989576818845</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-0.17</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.90543241</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>10.85229847</v>
+        <v>137.713206</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10.25</v>
+        <v>152.19</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>106.96</v>
+        <v>92.27</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>100.72</v>
+        <v>101.79</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002329707236849714</v>
+        <v>0.002327882169232162</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>-6.24</v>
+        <v>9.52</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.05833956619296934</v>
+        <v>0.1031754633141866</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.16</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.90543241</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>62.95787236</v>
+        <v>113.12478542</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>59.57</v>
+        <v>115.28</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.15</v>
+        <v>100.44</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002316522833305191</v>
+        <v>0.002297008400409454</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>-6</v>
+        <v>1.72</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>-0.05652378709373528</v>
+        <v>0.01742301458670989</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.16</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>2.27580753</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>113.12478542</v>
+        <v>62.95787236</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>114.47</v>
+        <v>59.64</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>98.72</v>
+        <v>106.15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>99.73999999999999</v>
+        <v>100.26</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002307039314966149</v>
+        <v>0.00229289189789976</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>1.02</v>
+        <v>-5.89</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.0103322528363047</v>
+        <v>-0.05548751766368346</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.31</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>2.27580753</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>137.713206</v>
+        <v>10.85229847</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>148.37</v>
+        <v>10.17</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>92.27</v>
+        <v>106.96</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.23999999999999</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002295474048699024</v>
+        <v>0.002285344976631987</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>6.97</v>
+        <v>-7.03</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.07553917849788663</v>
+        <v>-0.06572550486163052</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.33</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4018,25 +4018,25 @@
         <v>341.38450299</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>354.25</v>
+        <v>357</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>98.95</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002288766194264091</v>
+        <v>0.002280313695786805</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.03601717097686106</v>
+        <v>0.04397445293686525</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>0.37810738</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>127.23134407</v>
+        <v>76.24181082</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>119.37</v>
+        <v>72</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>105.36</v>
+        <v>104.98</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>98.58</v>
+        <v>98.88</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002280207897226418</v>
+        <v>0.002261332045325437</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-6.78</v>
+        <v>-6.1</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.06435079726651481</v>
+        <v>-0.05810630596304057</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.10445851</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>96.717382</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>98.59999999999999</v>
+        <v>1280</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.77</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002276044401370253</v>
+        <v>0.002258816404902846</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.72</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.01779064956557716</v>
+        <v>0.111148610642367</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.10445851</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>76.24181082</v>
+        <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>71.65000000000001</v>
+        <v>119.42</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.62</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002276044401370253</v>
+        <v>0.002255385986144767</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-6.58</v>
+        <v>-6.74</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.06267860544865689</v>
+        <v>-0.06397114654517844</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.29</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.35094641</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>154.44822659</v>
+        <v>96.717382</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>136.72</v>
+        <v>98.5</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>111.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.28</v>
+        <v>98.3</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002273268737466143</v>
+        <v>0.002248067759460866</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-13.16</v>
+        <v>1.62</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.1180904522613065</v>
+        <v>0.01675630947455523</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.16</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.35094641</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>147.21071381</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>1271.49</v>
+        <v>144.98</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>88.89</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.11</v>
+        <v>98.14</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.00226933654693532</v>
+        <v>0.002244408646118916</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>-1.71</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.1037237034537068</v>
+        <v>-0.0171256885327992</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.2</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>147.21071381</v>
+        <v>154.44822659</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>142.88</v>
+        <v>136.42</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>96.72</v>
+        <v>98.06</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002237185106712712</v>
+        <v>0.002242579089447941</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-3.13</v>
+        <v>-13.38</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.03134702053079619</v>
+        <v>-0.1200646087580761</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.42</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,55 +4411,55 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.93456659</v>
+        <v>5.691347</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>127.79185697</v>
+        <v>105.04894536</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>138.5</v>
+        <v>23.19</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>88.38</v>
+        <v>452.96</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>95.62</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002211741520925037</v>
+        <v>0.002229543498167241</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>7.24</v>
+        <v>-355.47</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.08191898619597195</v>
+        <v>-0.7847712822324268</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.15</v>
+        <v>-11.33</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.93456659</v>
+        <v>0</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,38 +4468,38 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.93456659</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>105.04894536</v>
+        <v>127.79185697</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>22.26</v>
+        <v>138.8</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>452.96</v>
+        <v>88.38</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>93.59</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002164786539880508</v>
+        <v>0.002191351502660633</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-359.37</v>
+        <v>7.44</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.7933813140233134</v>
+        <v>0.08418194161575018</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-11.3</v>
+        <v>-0.16</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0</v>
+        <v>0.93456659</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4531,25 +4531,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>105.84</v>
+        <v>107.05</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>91.72</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.00212153244404146</v>
+        <v>0.002121370959995829</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-18.73</v>
+        <v>-17.69</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1695789950203712</v>
+        <v>-0.1601629696695337</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.4</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>1.17308322</v>
@@ -4588,22 +4588,22 @@
         <v>107.56862839</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>105.05</v>
+        <v>105.5</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>90.45</v>
+        <v>90.84</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002092156667722962</v>
+        <v>0.002077461599892422</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-2.32</v>
+        <v>-1.93</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.02500808451007869</v>
+        <v>-0.02080413926916029</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>-0.15</v>
@@ -4645,25 +4645,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>196.42</v>
+        <v>197.29</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002085911423938714</v>
+        <v>0.00207128684612788</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.64</v>
+        <v>-17.25</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1636060100166945</v>
+        <v>-0.1599888703394547</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.34</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>0.6214908</v>
@@ -4702,22 +4702,22 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>56.73</v>
+        <v>56.58</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.19</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001790303218150992</v>
+        <v>0.001765293492907266</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33.13</v>
+        <v>-33.34</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2997376277933593</v>
+        <v>-0.301637564462137</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>-0.4</v>
@@ -4759,22 +4759,22 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>107.55</v>
+        <v>106.29</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>50.23</v>
+        <v>49.64</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001161846649195404</v>
+        <v>0.001135239914340157</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.04930018800919156</v>
+        <v>0.03697514100689368</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>-0.08</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>253</v>
+        <v>252.55</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.3</v>
+        <v>45.21</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001047813123801549</v>
+        <v>0.001033928213684901</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.81</v>
+        <v>-6.9</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.130685089234312</v>
+        <v>-0.1324122049510651</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,7 +4865,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-10 21:01:43</t>
+          <t>2026-09-11 21:06:29</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43421.5</v>
+        <v>43915.91</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43265.02</v>
+        <v>43759.41</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37743.8</v>
+        <v>37744.56</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5521.22</v>
+        <v>6014.85</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1462815084861619</v>
+        <v>0.1593567390903484</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>188.72</v>
+        <v>189.5</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>108.76</v>
+        <v>109.74</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6960.64</v>
+        <v>7023.36</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>914.87</v>
+        <v>977.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.748</v>
+        <v>14.922</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4276.92</v>
+        <v>4327.38</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>846.21</v>
+        <v>896.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1529</v>
+        <v>1552.6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2697.05</v>
+        <v>2738.68</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1501.09</v>
+        <v>1542.72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>26.15</v>
+        <v>26.53</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2221.5</v>
+        <v>2253.69</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>295.69</v>
+        <v>327.88</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>107.44</v>
+        <v>111.98</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1968.8</v>
+        <v>2051.91</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>322.23</v>
+        <v>405.34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>503.66</v>
+        <v>515.04</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1860.31</v>
+        <v>1902.26</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-38.24</v>
+        <v>3.71</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>219.69</v>
+        <v>218.36</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1773.17</v>
+        <v>1762.36</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>520.49</v>
+        <v>509.68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>228.17</v>
+        <v>235.98</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1618.11</v>
+        <v>1673.42</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-377.95</v>
+        <v>-322.64</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,76 +5250,76 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>155.34</v>
+        <v>157.78</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1443.84</v>
+        <v>1466.45</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-428</v>
+        <v>-405.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="D11" t="n">
-        <v>119.34</v>
+        <v>44.56</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1401.9</v>
+        <v>1410.39</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>58.11</v>
+        <v>182.05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="D12" t="n">
-        <v>43.95</v>
+        <v>119.4</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1396.9</v>
+        <v>1402.54</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>168.56</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>439.5</v>
+        <v>442.3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1214.33</v>
+        <v>1221.02</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>299.84</v>
+        <v>306.53</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>109.1</v>
+        <v>111.15</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1106.67</v>
+        <v>1127.46</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>499.48</v>
+        <v>520.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>682.4</v>
+        <v>697.8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1091.84</v>
+        <v>1116.48</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>338.38</v>
+        <v>363.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>27.775</v>
+        <v>28.177</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1066.93</v>
+        <v>1082.32</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-28.85</v>
+        <v>-13.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>329.5</v>
+        <v>328.65</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1066.47</v>
+        <v>1063.67</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>424.48</v>
+        <v>421.68</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>325.9</v>
+        <v>332.5</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>736.67</v>
+        <v>751.55</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>245.62</v>
+        <v>260.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,76 +5493,76 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>492.87</v>
+        <v>495.19</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>679.04</v>
+        <v>682.21</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>144.66</v>
+        <v>147.83</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>44.08</v>
+        <v>984.75</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>651.25</v>
+        <v>640.09</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>867.58</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-216.33</v>
+        <v>-22.59</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>65</v>
+        <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>988</v>
+        <v>43.1</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>642.2</v>
+        <v>636.75</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>867.58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-20.48</v>
+        <v>-230.83</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>92.01000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>625.04</v>
+        <v>614.76</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>75.86</v>
+        <v>65.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>320.71</v>
+        <v>324.69</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>552.02</v>
+        <v>558.84</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>62.75</v>
+        <v>69.56999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.7705</v>
+        <v>3.772</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>527.87</v>
+        <v>528.08</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-10.5</v>
+        <v>-10.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>332.23</v>
+        <v>338.5</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>490.85</v>
+        <v>500.09</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>82.93000000000001</v>
+        <v>92.17</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>234.02</v>
+        <v>242.82</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>191.93</v>
+        <v>199.14</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-4.59</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,22 +5709,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>135.11</v>
+        <v>133.07</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>132.3</v>
+        <v>130.3</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>12.57</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5736,22 +5736,22 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>267.33</v>
+        <v>268.37</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125.25</v>
+        <v>125.73</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>25.4</v>
+        <v>25.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,22 +5763,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>212.99</v>
+        <v>213.92</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124.39</v>
+        <v>124.93</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>13.98</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5790,22 +5790,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>50.8</v>
+        <v>50.07</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.16</v>
+        <v>122.37</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.45</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5817,22 +5817,22 @@
         <v>0.42010405</v>
       </c>
       <c r="D31" t="n">
-        <v>388.58</v>
+        <v>388.51</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120.59</v>
+        <v>120.56</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.43</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5844,49 +5844,49 @@
         <v>3.81488812</v>
       </c>
       <c r="D32" t="n">
-        <v>42.5</v>
+        <v>42.27</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.77</v>
+        <v>119.12</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.54</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>103.36</v>
+        <v>569.35</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>118.96</v>
+        <v>117.92</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>105.28</v>
+        <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.68</v>
+        <v>12.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5898,76 +5898,76 @@
         <v>2.50421091</v>
       </c>
       <c r="D34" t="n">
-        <v>63.75</v>
+        <v>63.64</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>117.93</v>
+        <v>117.72</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11.12</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.55804584</v>
       </c>
       <c r="D35" t="n">
-        <v>253.98</v>
+        <v>101.95</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.16</v>
+        <v>117.33</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>108.77</v>
+        <v>105.28</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8.390000000000001</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.62445608</v>
       </c>
       <c r="D36" t="n">
-        <v>565.37</v>
+        <v>253.4</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.1</v>
+        <v>116.89</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>105.75</v>
+        <v>108.77</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>11.35</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,22 +5979,22 @@
         <v>0.59183053</v>
       </c>
       <c r="D37" t="n">
-        <v>266.35</v>
+        <v>265.95</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.45</v>
+        <v>116.27</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>16.6</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6006,22 +6006,22 @@
         <v>2.76637723</v>
       </c>
       <c r="D38" t="n">
-        <v>55.95</v>
+        <v>56.06</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.34</v>
+        <v>114.56</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6033,22 +6033,22 @@
         <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>87.87</v>
+        <v>88.41</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.56</v>
+        <v>113.24</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>11.03</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6060,22 +6060,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D40" t="n">
-        <v>56.14</v>
+        <v>56.55</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.27</v>
+        <v>113.09</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.63</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,76 +6087,76 @@
         <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>216.96</v>
+        <v>216.46</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>112.19</v>
+        <v>111.93</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-6.57</v>
+        <v>-6.83</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="D42" t="n">
-        <v>92.84999999999999</v>
+        <v>13.15</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>109.06</v>
+        <v>110.74</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>89.66</v>
+        <v>106.15</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>19.4</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="D43" t="n">
-        <v>12.9</v>
+        <v>93.77</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.64</v>
+        <v>110.14</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2.49</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6168,130 +6168,130 @@
         <v>0.40867246</v>
       </c>
       <c r="D44" t="n">
-        <v>353.56</v>
+        <v>356.02</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>106.74</v>
+        <v>107.48</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13.91</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="D45" t="n">
-        <v>236.02</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>106.73</v>
+        <v>107.08</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>18.64</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.5550481</v>
       </c>
       <c r="D46" t="n">
-        <v>82.31</v>
+        <v>259.3</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>105.92</v>
+        <v>106.31</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>9.24</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.61215748</v>
       </c>
       <c r="D47" t="n">
-        <v>338.67</v>
+        <v>234.57</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>105.72</v>
+        <v>106.07</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>101.39</v>
+        <v>88.09</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4.33</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.42255419</v>
       </c>
       <c r="D48" t="n">
-        <v>255.46</v>
+        <v>337.86</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104.74</v>
+        <v>105.46</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>13.56</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6303,76 +6303,76 @@
         <v>0.68495686</v>
       </c>
       <c r="D49" t="n">
-        <v>206</v>
+        <v>205.9</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.23</v>
+        <v>104.18</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>14.77</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.43583007</v>
       </c>
       <c r="D50" t="n">
-        <v>173.69</v>
+        <v>323.31</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>103.17</v>
+        <v>104.09</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>88.44</v>
+        <v>104.04</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>14.73</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.80409618</v>
       </c>
       <c r="D51" t="n">
-        <v>317.44</v>
+        <v>174.88</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>102.2</v>
+        <v>103.87</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>104.04</v>
+        <v>88.44</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-1.84</v>
+        <v>15.43</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6384,22 +6384,22 @@
         <v>1.1533463</v>
       </c>
       <c r="D52" t="n">
-        <v>119.82</v>
+        <v>121.5</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>102.09</v>
+        <v>103.51</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>12.56</v>
+        <v>13.98</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6411,184 +6411,184 @@
         <v>0.50675322</v>
       </c>
       <c r="D53" t="n">
-        <v>271.6</v>
+        <v>276.18</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>101.67</v>
+        <v>103.38</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>4.99</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="D54" t="n">
-        <v>265.2</v>
+        <v>1079.65</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>101.64</v>
+        <v>102.53</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5.7</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="D55" t="n">
-        <v>1062.4</v>
+        <v>267</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>100.9</v>
+        <v>102.32</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2.01</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.90543241</v>
       </c>
       <c r="D56" t="n">
-        <v>10.25</v>
+        <v>152.19</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>100.72</v>
+        <v>101.79</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>106.96</v>
+        <v>92.27</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-6.24</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="D57" t="n">
-        <v>59.57</v>
+        <v>115.28</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.15</v>
+        <v>100.44</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>-6</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>2.27580753</v>
       </c>
       <c r="D58" t="n">
-        <v>114.47</v>
+        <v>59.64</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>99.73999999999999</v>
+        <v>100.26</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>98.72</v>
+        <v>106.15</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>1.02</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="D59" t="n">
-        <v>148.37</v>
+        <v>10.17</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.23999999999999</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>92.27</v>
+        <v>106.96</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>6.97</v>
+        <v>-7.03</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6600,238 +6600,238 @@
         <v>0.37810738</v>
       </c>
       <c r="D60" t="n">
-        <v>354.25</v>
+        <v>357</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>98.95</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>3.44</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="D61" t="n">
-        <v>119.37</v>
+        <v>72</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98.58</v>
+        <v>98.88</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>105.36</v>
+        <v>104.98</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-6.78</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.10445851</v>
       </c>
       <c r="D62" t="n">
-        <v>98.59999999999999</v>
+        <v>1280</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.77</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1.72</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>71.65000000000001</v>
+        <v>119.42</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.62</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-6.58</v>
+        <v>-6.74</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.35094641</v>
       </c>
       <c r="D64" t="n">
-        <v>136.72</v>
+        <v>98.5</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.28</v>
+        <v>98.3</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>111.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-13.16</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D65" t="n">
-        <v>1271.49</v>
+        <v>144.98</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.11</v>
+        <v>98.14</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>88.89</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>9.220000000000001</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="D66" t="n">
-        <v>142.88</v>
+        <v>136.42</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>96.72</v>
+        <v>98.06</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-3.13</v>
+        <v>-13.38</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.93456659</v>
+        <v>5.691347</v>
       </c>
       <c r="D67" t="n">
-        <v>138.5</v>
+        <v>23.19</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>95.62</v>
+        <v>97.48999999999999</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>88.38</v>
+        <v>452.96</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>7.24</v>
+        <v>-355.47</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.93456659</v>
       </c>
       <c r="D68" t="n">
-        <v>22.26</v>
+        <v>138.8</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>93.59</v>
+        <v>95.81999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>452.96</v>
+        <v>88.38</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-359.37</v>
+        <v>7.44</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6843,22 +6843,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D69" t="n">
-        <v>105.84</v>
+        <v>107.05</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>91.72</v>
+        <v>92.76000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-18.73</v>
+        <v>-17.69</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6870,22 +6870,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D70" t="n">
-        <v>105.05</v>
+        <v>105.5</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>90.45</v>
+        <v>90.84</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-2.32</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>196.42</v>
+        <v>197.29</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.18000000000001</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.64</v>
+        <v>-17.25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>56.73</v>
+        <v>56.58</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.19</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33.13</v>
+        <v>-33.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>107.55</v>
+        <v>106.29</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>50.23</v>
+        <v>49.64</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>253</v>
+        <v>252.55</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.3</v>
+        <v>45.21</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.81</v>
+        <v>-6.9</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43915.91</v>
+        <v>43926.06</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43759.41</v>
+        <v>43769.54</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6014.85</v>
+        <v>6024.98</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1593567390903484</v>
+        <v>0.1596251221368059</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>156.5</v>
+        <v>156.52</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-11 21:06:30</t>
+          <t>2026-09-12 20:44:12</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>7023.36</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1606204392582611</v>
+        <v>0.1605833474710162</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>977.59</v>
@@ -778,7 +778,7 @@
         <v>4327.38</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09896483683556219</v>
+        <v>0.09894198306496123</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>896.67</v>
@@ -835,7 +835,7 @@
         <v>2738.68</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06263212829583199</v>
+        <v>0.06261766477183607</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1542.72</v>
@@ -892,7 +892,7 @@
         <v>2253.69</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05154066967262828</v>
+        <v>0.05152876747909185</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>327.88</v>
@@ -940,22 +940,22 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>111.98</v>
+        <v>112.04</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2051.91</v>
+        <v>2053.01</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04692607035926089</v>
+        <v>0.04694038440169249</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>405.34</v>
+        <v>406.44</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2461723461498752</v>
+        <v>0.246840401562035</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>-14.66</v>
@@ -997,22 +997,22 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>515.04</v>
+        <v>515.77</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1902.26</v>
+        <v>1904.95</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04350365591161778</v>
+        <v>0.04355511432774517</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3.71</v>
+        <v>6.4</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.001954122883253009</v>
+        <v>0.003370993653051013</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-15.02</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>218.36</v>
+        <v>218.26</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1762.36</v>
+        <v>1761.55</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04030421868324977</v>
+        <v>0.04027639131947794</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>509.68</v>
+        <v>508.87</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4068716671456397</v>
+        <v>0.4062250534853274</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-41.28</v>
+        <v>-41.29</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,22 +1111,22 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>235.98</v>
+        <v>236.13</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1673.42</v>
+        <v>1674.48</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03827020905429301</v>
+        <v>0.0382856074120175</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-322.64</v>
+        <v>-321.58</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1616384277025741</v>
+        <v>-0.161107381541637</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>-20.75</v>
@@ -1168,22 +1168,22 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>157.78</v>
+        <v>157.97</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1466.45</v>
+        <v>1468.22</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03353691725189611</v>
+        <v>0.03356964222592825</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-405.39</v>
+        <v>-403.62</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2165729976921104</v>
+        <v>-0.2156274040516284</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-91.75</v>
@@ -1234,7 +1234,7 @@
         <v>1410.39</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03225485541471018</v>
+        <v>0.03224740685934461</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>182.05</v>
@@ -1291,7 +1291,7 @@
         <v>1402.54</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03207533016637074</v>
+        <v>0.03206792306844573</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>58.75</v>
@@ -1348,7 +1348,7 @@
         <v>1221.02</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02792406607992784</v>
+        <v>0.02791761762590273</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>306.53</v>
@@ -1405,7 +1405,7 @@
         <v>1127.46</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02578439955322226</v>
+        <v>0.02577844520851443</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>520.27</v>
@@ -1462,7 +1462,7 @@
         <v>1116.48</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0255332929001309</v>
+        <v>0.02552739654302786</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>363.02</v>
@@ -1519,7 +1519,7 @@
         <v>1082.32</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02475207220162446</v>
+        <v>0.02474635625040298</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>-13.46</v>
@@ -1567,22 +1567,22 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>328.65</v>
+        <v>328.18</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1063.67</v>
+        <v>1062.15</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02432555680270335</v>
+        <v>0.02428518579659022</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>421.68</v>
+        <v>420.16</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6568326609448746</v>
+        <v>0.6544650228196701</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>-33.95</v>
@@ -1624,22 +1624,22 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>332.5</v>
+        <v>332.55</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>751.55</v>
+        <v>751.66</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01718754145089332</v>
+        <v>0.01718608742255331</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>260.5</v>
+        <v>260.61</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.530495876183688</v>
+        <v>0.53071988595866</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-21.2</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>495.19</v>
+        <v>494.89</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>682.21</v>
+        <v>681.79</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01560177320632551</v>
+        <v>0.01558856736266746</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>147.83</v>
+        <v>147.41</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2766383472435346</v>
+        <v>0.2758523896852427</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.38</v>
+        <v>-25.39</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1747,7 +1747,7 @@
         <v>640.09</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01463851161905703</v>
+        <v>0.01463513117407092</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>-22.59</v>
@@ -1804,7 +1804,7 @@
         <v>636.75</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01456212762804381</v>
+        <v>0.01455876482227446</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>-230.83</v>
@@ -1852,22 +1852,22 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>90.5</v>
+        <v>91.8</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>614.76</v>
+        <v>623.59</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01405922823810948</v>
+        <v>0.01425787225052553</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>65.58</v>
+        <v>74.41</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1194143996503879</v>
+        <v>0.1354929167121891</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-24.75</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>324.69</v>
+        <v>324.82</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>558.84</v>
+        <v>559.0700000000001</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01278036812509777</v>
+        <v>0.01278267553857712</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1421914280458642</v>
+        <v>0.1426615161362847</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-32.1</v>
+        <v>-32.09</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>528.08</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01207690358510777</v>
+        <v>0.01207411468762732</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>-10.29</v>
@@ -2023,22 +2023,22 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>338.5</v>
+        <v>338.38</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>500.09</v>
+        <v>499.91</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.0114367874448503</v>
+        <v>0.01143003081633801</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>92.17</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2259511668954697</v>
+        <v>0.225509903902726</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-9.869999999999999</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>242.82</v>
+        <v>242.78</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>199.14</v>
+        <v>199.1</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004554223943225197</v>
+        <v>0.004552257677447735</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.01333197638917159</v>
+        <v>0.01312843476490942</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-2.26</v>
+        <v>-2.27</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>133.07</v>
+        <v>134.22</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.3</v>
+        <v>131.43</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002979890427850975</v>
+        <v>0.003005038807367935</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>10.57</v>
+        <v>11.7</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.08828196776079512</v>
+        <v>0.09771986970684038</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.59</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2194,22 +2194,22 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>268.37</v>
+        <v>268.1</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>125.73</v>
+        <v>125.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002875377003021513</v>
+        <v>0.002871740654381896</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>25.88</v>
+        <v>25.75</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2591887831747621</v>
+        <v>0.2578868302453681</v>
       </c>
       <c r="M28" s="2" t="n">
         <v>-0.17</v>
@@ -2251,22 +2251,22 @@
         <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>213.92</v>
+        <v>214.23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124.93</v>
+        <v>125.11</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.00285708143631176</v>
+        <v>0.002860537207561457</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.52</v>
+        <v>14.7</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1315098270084231</v>
+        <v>0.1331401141200978</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-0.43</v>
@@ -2308,25 +2308,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>50.07</v>
+        <v>50.01</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>122.37</v>
+        <v>122.22</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002798535622840551</v>
+        <v>0.002794459735498052</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>9.66</v>
+        <v>9.51</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.08570668086239021</v>
+        <v>0.08437583178067608</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.46</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>3.30858696</v>
@@ -2365,25 +2365,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>388.51</v>
+        <v>387.56</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120.56</v>
+        <v>120.27</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002757141903159736</v>
+        <v>0.002749874589988142</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>11.4</v>
+        <v>11.11</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1044338585562477</v>
+        <v>0.1017772077684133</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.37</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>0.42010405</v>
@@ -2431,7 +2431,7 @@
         <v>119.12</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002724209883082181</v>
+        <v>0.002723580786225888</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>10.89</v>
@@ -2479,22 +2479,22 @@
         <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>569.35</v>
+        <v>570</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>117.92</v>
+        <v>118.05</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002696766533017552</v>
+        <v>0.002699116116638398</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>12.17</v>
+        <v>12.3</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1150827423167849</v>
+        <v>0.1163120567375887</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>-0.3</v>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>1.55804584</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>57.56703616</v>
+        <v>91.20399179</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>63.64</v>
+        <v>102.39</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>106.81</v>
+        <v>105.28</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>117.72</v>
+        <v>117.84</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002692192641340113</v>
+        <v>0.002694314639429639</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>10.91</v>
+        <v>12.56</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1021439940080517</v>
+        <v>0.1193009118541034</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>1.55804584</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.55804584</v>
+        <v>2.50421091</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>91.20399179</v>
+        <v>57.56703616</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>101.95</v>
+        <v>63.5</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>105.28</v>
+        <v>106.81</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.33</v>
+        <v>117.46</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002683273552569109</v>
+        <v>0.002685626252099502</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.05</v>
+        <v>10.65</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1144566869300912</v>
+        <v>0.09970976500327684</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>-0.32</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>1.55804584</v>
+        <v>2.50421091</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>116.89</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002673210990878745</v>
+        <v>0.002672593671104298</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>8.119999999999999</v>
@@ -2707,25 +2707,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>265.95</v>
+        <v>265.99</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.27</v>
+        <v>116.28</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002659031926678687</v>
+        <v>0.002658646523021711</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>16.42</v>
+        <v>16.43</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1644466700050075</v>
+        <v>0.1645468202303455</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.18</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.59183053</v>
@@ -2764,22 +2764,22 @@
         <v>54.82621761</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>56.06</v>
+        <v>56.05</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.56</v>
+        <v>114.54</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.00261992515283659</v>
+        <v>0.00261886285472056</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.01849217638691323</v>
+        <v>0.01831436699857752</v>
       </c>
       <c r="M38" s="2" t="n">
         <v>-0.44</v>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>88.41</v>
+        <v>56.57</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.24</v>
+        <v>113.13</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002589737467765498</v>
+        <v>0.002586624364890318</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>11.71</v>
+        <v>5.49</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1153353688564956</v>
+        <v>0.05100334448160535</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.34</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>53.65641702</v>
+        <v>79.10567143</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>56.55</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.09</v>
+        <v>113.03</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.00258630704900742</v>
+        <v>0.002584337947171861</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>5.45</v>
+        <v>11.5</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.05063173541434411</v>
+        <v>0.1132670146754654</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.2</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2935,25 +2935,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>216.46</v>
+        <v>215.95</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.93</v>
+        <v>111.66</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002559778477278278</v>
+        <v>0.002553014024429001</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-6.83</v>
+        <v>-7.1</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.05751094644661502</v>
+        <v>-0.05978443920511956</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-2.09</v>
+        <v>-2.1</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>12.56856884</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>13.15</v>
+        <v>93.45</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.74</v>
+        <v>109.76</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002532563821797521</v>
+        <v>0.00250957208777832</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.59</v>
+        <v>20.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.04324069712670749</v>
+        <v>0.2241802364488066</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.17</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>93.77</v>
+        <v>12.9</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>89.66</v>
+        <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.14</v>
+        <v>108.64</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002518842146765207</v>
+        <v>0.002483964209331602</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>20.48</v>
+        <v>2.49</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.2284184697747045</v>
+        <v>0.02345737164390014</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.3</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3106,25 +3106,25 @@
         <v>306.99401668</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>356.02</v>
+        <v>356.84</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.48</v>
+        <v>107.72</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002458009387455279</v>
+        <v>0.002462929166321798</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14.65</v>
+        <v>14.89</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1578153614133362</v>
+        <v>0.1604007325218141</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>0.40867246</v>
@@ -3163,22 +3163,22 @@
         <v>74.99726962</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>83.20999999999999</v>
+        <v>83.38</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>107.08</v>
+        <v>107.3</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002448861604100402</v>
+        <v>0.002453326211904279</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>10.4</v>
+        <v>10.62</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1075713694662805</v>
+        <v>0.1098469176665287</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-0.17</v>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.61215748</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>221.99877812</v>
+        <v>194.45976548</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>259.3</v>
+        <v>234.56</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>106.31</v>
+        <v>106.07</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002431252121142265</v>
+        <v>0.002425203273967259</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>15.13</v>
+        <v>17.98</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1659355121737223</v>
+        <v>0.2041094335338858</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.61215748</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.42255419</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>194.45976548</v>
+        <v>324.07677699</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>234.57</v>
+        <v>338.25</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>88.09</v>
+        <v>101.39</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>106.07</v>
+        <v>105.58</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002425763451129339</v>
+        <v>0.00241399982714682</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>17.98</v>
+        <v>4.19</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.2041094335338858</v>
+        <v>0.0413255745142519</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.42255419</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.5550481</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>324.07677699</v>
+        <v>221.99877812</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>337.86</v>
+        <v>256.5</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>101.39</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>105.46</v>
+        <v>105.17</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002411813081513153</v>
+        <v>0.002404625514501147</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4.07</v>
+        <v>13.99</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.04014202584081271</v>
+        <v>0.1534327703443737</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.16</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.5550481</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3400,7 +3400,7 @@
         <v>104.18</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002382540174777549</v>
+        <v>0.002381989979088423</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>14.72</v>
@@ -3457,7 +3457,7 @@
         <v>104.09</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002380481923522702</v>
+        <v>0.002379932203141812</v>
       </c>
       <c r="K50" s="2" t="n">
         <v>0.05</v>
@@ -3514,7 +3514,7 @@
         <v>103.87</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.00237545064267752</v>
+        <v>0.002374902084161207</v>
       </c>
       <c r="K51" s="2" t="n">
         <v>15.43</v>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>104.90344487</v>
+        <v>257.81779936</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>121.5</v>
+        <v>276.18</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>103.51</v>
+        <v>103.38</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002367217637658131</v>
+        <v>0.002363698637340767</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>13.98</v>
+        <v>6.7</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.156148776946275</v>
+        <v>0.06930078609846918</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>257.81779936</v>
+        <v>249.91595261</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>276.18</v>
+        <v>268.16</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>103.38</v>
+        <v>102.77</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002364244608067796</v>
+        <v>0.002349751489258181</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.06930078609846918</v>
+        <v>0.07119032728788827</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.1533463</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>104.90344487</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>1079.65</v>
+        <v>120.37</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>98.89</v>
+        <v>89.53</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.53</v>
+        <v>102.55</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002344805568438684</v>
+        <v>0.002344721370277575</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3.64</v>
+        <v>13.02</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.03680857518454849</v>
+        <v>0.145426114151681</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.1533463</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>249.91595261</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>267</v>
+        <v>1072.02</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.32</v>
+        <v>101.81</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002340002982177374</v>
+        <v>0.002327801879160994</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>6.38</v>
+        <v>2.92</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.06649989576818845</v>
+        <v>0.02952775811507736</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-0.17</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>101.79</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002327882169232162</v>
+        <v>0.002327344595617303</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>9.52</v>
@@ -3847,22 +3847,22 @@
         <v>113.12478542</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>115.28</v>
+        <v>115.81</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.44</v>
+        <v>100.9</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002297008400409454</v>
+        <v>0.002306995477923036</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.01742301458670989</v>
+        <v>0.02208265802269044</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-0.16</v>
@@ -3904,25 +3904,25 @@
         <v>62.95787236</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>59.64</v>
+        <v>59.88</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.26</v>
+        <v>100.66</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.00229289189789976</v>
+        <v>0.002301508075398739</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-5.89</v>
+        <v>-5.49</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.05548751766368346</v>
+        <v>-0.05171926519076778</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.32</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>2.27580753</v>
@@ -3961,25 +3961,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.93000000000001</v>
+        <v>100.03</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002285344976631987</v>
+        <v>0.002287103643772461</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-7.03</v>
+        <v>-6.93</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.06572550486163052</v>
+        <v>-0.06479057591623037</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>13.30225117</v>
@@ -4018,22 +4018,22 @@
         <v>341.38450299</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>357</v>
+        <v>356.29</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>99.70999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002280313695786805</v>
+        <v>0.002275214271636485</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.04397445293686525</v>
+        <v>0.04188043136844309</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-0.16</v>
@@ -4075,25 +4075,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>72</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>98.88</v>
+        <v>99.36</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002261332045325437</v>
+        <v>0.0022717846450588</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-6.1</v>
+        <v>-5.62</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.05810630596304057</v>
+        <v>-0.05353400647742427</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.28</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>1.85908491</v>
@@ -4141,7 +4141,7 @@
         <v>98.77</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002258816404902846</v>
+        <v>0.002258294780519904</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>9.880000000000001</v>
@@ -4189,22 +4189,22 @@
         <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>119.42</v>
+        <v>119.59</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.62</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002255385986144767</v>
+        <v>0.002258066138748058</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-6.74</v>
+        <v>-6.6</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.06397114654517844</v>
+        <v>-0.06264236902050113</v>
       </c>
       <c r="M63" s="2" t="n">
         <v>-0.29</v>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>96.717382</v>
+        <v>147.21071381</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>98.5</v>
+        <v>145</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.3</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002248067759460866</v>
+        <v>0.002244118990665471</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.62</v>
+        <v>-1.7</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.01675630947455523</v>
+        <v>-0.01702553830746119</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>147.21071381</v>
+        <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>144.98</v>
+        <v>136.5</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.14</v>
+        <v>98.12</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002244408646118916</v>
+        <v>0.002243433065349934</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-1.71</v>
+        <v>-13.32</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.0171256885327992</v>
+        <v>-0.1195262024407753</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.42</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.35094641</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>154.44822659</v>
+        <v>96.717382</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>136.42</v>
+        <v>98.3</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>111.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.06</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002242579089447941</v>
+        <v>0.002242975781806242</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-13.38</v>
+        <v>1.42</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.1200646087580761</v>
+        <v>0.01468762929251138</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.16</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.35094641</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
         <v>105.04894536</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>23.19</v>
+        <v>23.13</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002229543498167241</v>
+        <v>0.002223312589427512</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-355.47</v>
+        <v>-355.72</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.7847712822324268</v>
+        <v>-0.7853232073472273</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-11.33</v>
+        <v>-11.32</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0</v>
@@ -4474,22 +4474,22 @@
         <v>127.79185697</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>138.8</v>
+        <v>138.69</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>95.81999999999999</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002191351502660633</v>
+        <v>0.002189016323650659</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>7.44</v>
+        <v>7.36</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.08418194161575018</v>
+        <v>0.08327675944783888</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>-0.16</v>
@@ -4531,22 +4531,22 @@
         <v>126.99866255</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>107.05</v>
+        <v>107.07</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>92.76000000000001</v>
+        <v>92.78</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002121370959995829</v>
+        <v>0.002121338359184334</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-17.69</v>
+        <v>-17.67</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1601629696695337</v>
+        <v>-0.1599818922589407</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>-0.4</v>
@@ -4597,7 +4597,7 @@
         <v>90.84</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002077461599892422</v>
+        <v>0.00207698185544627</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>-1.93</v>
@@ -4645,22 +4645,22 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>197.29</v>
+        <v>197.15</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.56999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.00207128684612788</v>
+        <v>0.002069436676975362</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.25</v>
+        <v>-17.31</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1599888703394547</v>
+        <v>-0.1605453533667223</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>-0.34</v>
@@ -4711,7 +4711,7 @@
         <v>77.19</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001765293492907266</v>
+        <v>0.001764885836876899</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>-33.34</v>
@@ -4768,7 +4768,7 @@
         <v>49.64</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001135239914340157</v>
+        <v>0.001134977755442017</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>1.77</v>
@@ -4816,7 +4816,7 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>252.55</v>
+        <v>252.52</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
@@ -4825,7 +4825,7 @@
         <v>45.21</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001033928213684901</v>
+        <v>0.001033689450514375</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>-6.9</v>
@@ -4834,7 +4834,7 @@
         <v>-0.1324122049510651</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,7 +4865,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-11 21:06:29</t>
+          <t>2026-09-12 20:44:12</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43915.91</v>
+        <v>43926.06</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43759.41</v>
+        <v>43769.54</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37744.56</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6014.85</v>
+        <v>6024.98</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1593567390903484</v>
+        <v>0.1596251221368059</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>189.5</v>
+        <v>189.52</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5076,7 +5076,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>111.98</v>
+        <v>112.04</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2051.91</v>
+        <v>2053.01</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>405.34</v>
+        <v>406.44</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>515.04</v>
+        <v>515.77</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1902.26</v>
+        <v>1904.95</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3.71</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>218.36</v>
+        <v>218.26</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1762.36</v>
+        <v>1761.55</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>509.68</v>
+        <v>508.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>235.98</v>
+        <v>236.13</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1673.42</v>
+        <v>1674.48</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-322.64</v>
+        <v>-321.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>157.78</v>
+        <v>157.97</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1466.45</v>
+        <v>1468.22</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-405.39</v>
+        <v>-403.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>328.65</v>
+        <v>328.18</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1063.67</v>
+        <v>1062.15</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>421.68</v>
+        <v>420.16</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>332.5</v>
+        <v>332.55</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>751.55</v>
+        <v>751.66</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>260.5</v>
+        <v>260.61</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>495.19</v>
+        <v>494.89</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>682.21</v>
+        <v>681.79</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>147.83</v>
+        <v>147.41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5535,7 +5535,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5562,7 +5562,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>90.5</v>
+        <v>91.8</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>614.76</v>
+        <v>623.59</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>65.58</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>324.69</v>
+        <v>324.82</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>558.84</v>
+        <v>559.0700000000001</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>69.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5643,7 +5643,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>338.5</v>
+        <v>338.38</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>500.09</v>
+        <v>499.91</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>92.17</v>
+        <v>91.98999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>242.82</v>
+        <v>242.78</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>199.14</v>
+        <v>199.1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,22 +5709,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>133.07</v>
+        <v>134.22</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.3</v>
+        <v>131.43</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>10.57</v>
+        <v>11.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5736,22 +5736,22 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>268.37</v>
+        <v>268.1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125.73</v>
+        <v>125.6</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>25.88</v>
+        <v>25.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,22 +5763,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>213.92</v>
+        <v>214.23</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124.93</v>
+        <v>125.11</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.52</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5790,22 +5790,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>50.07</v>
+        <v>50.01</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>122.37</v>
+        <v>122.22</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>9.66</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5817,22 +5817,22 @@
         <v>0.42010405</v>
       </c>
       <c r="D31" t="n">
-        <v>388.51</v>
+        <v>387.56</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120.56</v>
+        <v>120.27</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.4</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5871,76 +5871,76 @@
         <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>569.35</v>
+        <v>570</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>117.92</v>
+        <v>118.05</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>12.17</v>
+        <v>12.3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>1.55804584</v>
       </c>
       <c r="D34" t="n">
-        <v>63.64</v>
+        <v>102.39</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>117.72</v>
+        <v>117.84</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>106.81</v>
+        <v>105.28</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.91</v>
+        <v>12.56</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.55804584</v>
+        <v>2.50421091</v>
       </c>
       <c r="D35" t="n">
-        <v>101.95</v>
+        <v>63.5</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.33</v>
+        <v>117.46</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>105.28</v>
+        <v>106.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.05</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,22 +5979,22 @@
         <v>0.59183053</v>
       </c>
       <c r="D37" t="n">
-        <v>265.95</v>
+        <v>265.99</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.27</v>
+        <v>116.28</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>16.42</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6006,76 +6006,76 @@
         <v>2.76637723</v>
       </c>
       <c r="D38" t="n">
-        <v>56.06</v>
+        <v>56.05</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.56</v>
+        <v>114.54</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>88.41</v>
+        <v>56.57</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.24</v>
+        <v>113.13</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>11.71</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="D40" t="n">
-        <v>56.55</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.09</v>
+        <v>113.03</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5.45</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,76 +6087,76 @@
         <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>216.46</v>
+        <v>215.95</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.93</v>
+        <v>111.66</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-6.83</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>1.59010207</v>
       </c>
       <c r="D42" t="n">
-        <v>13.15</v>
+        <v>93.45</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.74</v>
+        <v>109.76</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>106.15</v>
+        <v>89.66</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>4.59</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1.59010207</v>
+        <v>11.40066159</v>
       </c>
       <c r="D43" t="n">
-        <v>93.77</v>
+        <v>12.9</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.14</v>
+        <v>108.64</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>89.66</v>
+        <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>20.48</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6168,22 +6168,22 @@
         <v>0.40867246</v>
       </c>
       <c r="D44" t="n">
-        <v>356.02</v>
+        <v>356.84</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.48</v>
+        <v>107.72</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14.65</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6195,103 +6195,103 @@
         <v>1.74206342</v>
       </c>
       <c r="D45" t="n">
-        <v>83.20999999999999</v>
+        <v>83.38</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>107.08</v>
+        <v>107.3</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>10.4</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.61215748</v>
       </c>
       <c r="D46" t="n">
-        <v>259.3</v>
+        <v>234.56</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>106.31</v>
+        <v>106.07</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>15.13</v>
+        <v>17.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.42255419</v>
       </c>
       <c r="D47" t="n">
-        <v>234.57</v>
+        <v>338.25</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>106.07</v>
+        <v>105.58</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>88.09</v>
+        <v>101.39</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>17.98</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.5550481</v>
       </c>
       <c r="D48" t="n">
-        <v>337.86</v>
+        <v>256.5</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>105.46</v>
+        <v>105.17</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>101.39</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>4.07</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6372,115 +6372,115 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="D52" t="n">
-        <v>121.5</v>
+        <v>276.18</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.51</v>
+        <v>103.38</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>13.98</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="D53" t="n">
-        <v>276.18</v>
+        <v>268.16</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>103.38</v>
+        <v>102.77</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>6.7</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.1533463</v>
       </c>
       <c r="D54" t="n">
-        <v>1079.65</v>
+        <v>120.37</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.53</v>
+        <v>102.55</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>98.89</v>
+        <v>89.53</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>3.64</v>
+        <v>13.02</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="D55" t="n">
-        <v>267</v>
+        <v>1072.02</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.32</v>
+        <v>101.81</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>6.38</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6519,22 +6519,22 @@
         <v>1.17949395</v>
       </c>
       <c r="D57" t="n">
-        <v>115.28</v>
+        <v>115.81</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.44</v>
+        <v>100.9</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.72</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6546,22 +6546,22 @@
         <v>2.27580753</v>
       </c>
       <c r="D58" t="n">
-        <v>59.64</v>
+        <v>59.88</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.26</v>
+        <v>100.66</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-5.89</v>
+        <v>-5.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6573,22 +6573,22 @@
         <v>13.30225117</v>
       </c>
       <c r="D59" t="n">
-        <v>10.17</v>
+        <v>10.18</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.93000000000001</v>
+        <v>100.03</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-7.03</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6600,22 +6600,22 @@
         <v>0.37810738</v>
       </c>
       <c r="D60" t="n">
-        <v>357</v>
+        <v>356.29</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>99.70999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6627,22 +6627,22 @@
         <v>1.85908491</v>
       </c>
       <c r="D61" t="n">
-        <v>72</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98.88</v>
+        <v>99.36</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-6.1</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6681,103 +6681,103 @@
         <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>119.42</v>
+        <v>119.59</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.62</v>
+        <v>98.76000000000001</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-6.74</v>
+        <v>-6.6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D64" t="n">
-        <v>98.5</v>
+        <v>145</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.3</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1.62</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>144.98</v>
+        <v>136.5</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.14</v>
+        <v>98.12</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-1.71</v>
+        <v>-13.32</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.35094641</v>
       </c>
       <c r="D66" t="n">
-        <v>136.42</v>
+        <v>98.3</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.06</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>111.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-13.38</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6789,22 +6789,22 @@
         <v>5.691347</v>
       </c>
       <c r="D67" t="n">
-        <v>23.19</v>
+        <v>23.13</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>97.48999999999999</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-355.47</v>
+        <v>-355.72</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,22 +6816,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D68" t="n">
-        <v>138.8</v>
+        <v>138.69</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>95.81999999999999</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>7.44</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6843,22 +6843,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D69" t="n">
-        <v>107.05</v>
+        <v>107.07</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.76000000000001</v>
+        <v>92.78</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-17.69</v>
+        <v>-17.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6885,7 +6885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>197.29</v>
+        <v>197.15</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.56999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.25</v>
+        <v>-17.31</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,7 +6978,7 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>252.55</v>
+        <v>252.52</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>45.21</v>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43926.06</v>
+        <v>43926.08</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>156.52</v>
+        <v>156.54</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-12 20:44:12</t>
+          <t>2026-09-13 20:59:51</t>
         </is>
       </c>
     </row>
@@ -4926,16 +4926,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12 20:44:12</t>
+          <t>2026-09-13 20:59:51</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43926.06</v>
+        <v>43926.08</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>43769.54</v>
@@ -4953,7 +4953,7 @@
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>189.52</v>
+        <v>189.54</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5076,7 +5076,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5157,7 +5157,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5184,7 +5184,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5238,7 +5238,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5454,7 +5454,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5481,7 +5481,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5508,7 +5508,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5535,7 +5535,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5562,7 +5562,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5616,7 +5616,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5643,7 +5643,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5697,7 +5697,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5724,7 +5724,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5751,7 +5751,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5805,7 +5805,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5832,7 +5832,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5940,7 +5940,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5994,7 +5994,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6021,7 +6021,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6075,7 +6075,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6129,7 +6129,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6156,7 +6156,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6237,7 +6237,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6264,7 +6264,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6291,7 +6291,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6372,7 +6372,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6426,7 +6426,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6480,7 +6480,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6588,7 +6588,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6615,7 +6615,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6642,7 +6642,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6723,7 +6723,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6750,7 +6750,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6777,7 +6777,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6804,7 +6804,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6831,7 +6831,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6885,7 +6885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43926.08</v>
+        <v>43421.37</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43769.54</v>
+        <v>43264.53</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6024.98</v>
+        <v>5519.97</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1596251221368059</v>
+        <v>0.1462454457013143</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>156.54</v>
+        <v>156.84</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-13 20:59:51</t>
+          <t>2026-09-14 21:56:25</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109.74</v>
+        <v>109.32</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7023.36</v>
+        <v>6996.48</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1605833474710162</v>
+        <v>0.1618327948914677</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>977.59</v>
+        <v>950.71</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1616981790574236</v>
+        <v>0.1572520952666079</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.922</v>
+        <v>14.116</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4327.38</v>
+        <v>4093.64</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09894198306496123</v>
+        <v>0.09468835792848805</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>896.67</v>
+        <v>662.9299999999999</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2613657231301975</v>
+        <v>0.1932340535924051</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1552.6</v>
+        <v>1536.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2738.68</v>
+        <v>2710.81</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06261766477183607</v>
+        <v>0.06270266744416331</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1542.72</v>
+        <v>1514.85</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.289942807451754</v>
+        <v>1.266639352486705</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.53</v>
+        <v>26.81</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2253.69</v>
+        <v>2282.21</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05152876747909185</v>
+        <v>0.05278889138956398</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>327.88</v>
+        <v>356.4</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1702556326948141</v>
+        <v>0.185064985642405</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-13.61</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>112.04</v>
+        <v>110.05</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2053.01</v>
+        <v>2020.74</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04694038440169249</v>
+        <v>0.0467409328618083</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>406.44</v>
+        <v>374.17</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.246840401562035</v>
+        <v>0.2272420850616737</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-14.66</v>
+        <v>-11.26</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>515.77</v>
+        <v>494</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1904.95</v>
+        <v>1828.34</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04355511432774517</v>
+        <v>0.04229060502021962</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>6.4</v>
+        <v>-70.20999999999999</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.003370993653051013</v>
+        <v>-0.03698085380948619</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-15.02</v>
+        <v>-11.1</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>218.26</v>
+        <v>212.48</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1761.55</v>
+        <v>1718.47</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04027639131947794</v>
+        <v>0.03974924576889245</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>508.87</v>
+        <v>465.79</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4062250534853274</v>
+        <v>0.3718347862183479</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-41.29</v>
+        <v>-38.77</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>236.13</v>
+        <v>220.5</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1674.48</v>
+        <v>1566.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.0382856074120175</v>
+        <v>0.03624334041052656</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-321.58</v>
+        <v>-429.16</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.161107381541637</v>
+        <v>-0.2150035570073044</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-20.75</v>
+        <v>-16.64</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>157.97</v>
+        <v>161.59</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1468.22</v>
+        <v>1504.99</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03356964222592825</v>
+        <v>0.03481132483530433</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-403.62</v>
+        <v>-366.85</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2156274040516284</v>
+        <v>-0.1959836310795795</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-91.75</v>
+        <v>-88.04000000000001</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1200,114 +1200,114 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37.05</v>
+        <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>44.56</v>
+        <v>119.42</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1410.39</v>
+        <v>1405.7</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03224740685934461</v>
+        <v>0.03251468735406036</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>182.05</v>
+        <v>61.91</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.148208150837716</v>
+        <v>0.04607118671816281</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-55.65</v>
+        <v>-13.19</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>113.04005874</v>
+        <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>119.4</v>
+        <v>43.33</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1402.54</v>
+        <v>1373.16</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03206792306844573</v>
+        <v>0.03176201756214095</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>58.75</v>
+        <v>144.82</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04371962881104935</v>
+        <v>0.1178989530585994</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-15.96</v>
+        <v>-54.2</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>442.3</v>
+        <v>444.5</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1221.02</v>
+        <v>1224.41</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02791761762590273</v>
+        <v>0.02832134050166113</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>306.53</v>
+        <v>309.92</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.335192292972039</v>
+        <v>0.3388992771927523</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-1.53</v>
+        <v>-3.53</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>111.15</v>
+        <v>109.35</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1127.46</v>
+        <v>1109.21</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02577844520851443</v>
+        <v>0.02565669514120886</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>520.27</v>
+        <v>502.02</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8568487623313953</v>
+        <v>0.8267922726000098</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>697.8</v>
+        <v>682.8</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1116.48</v>
+        <v>1092.48</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02552739654302786</v>
+        <v>0.02526972016828901</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>363.02</v>
+        <v>339.02</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4818039444695139</v>
+        <v>0.4499508932126456</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1485,17 +1485,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KOIDl_EQ</t>
+          <t>SNOW_US_EQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KraneShares Global Humanoid Robotics and Physical AI Index (Acc)</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>IE000O6Z73N7</t>
+          <t>US8334451098</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1504,55 +1504,55 @@
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>52</v>
+        <v>4.3814255</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>28.53653846</v>
+        <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>28.177</v>
+        <v>331.92</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>1095.78</v>
+        <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1082.32</v>
+        <v>1076.49</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02474635625040298</v>
+        <v>0.02489986184091373</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>-13.46</v>
+        <v>434.5</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>-0.01228348756137181</v>
+        <v>0.6768018193429804</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0.35</v>
+        <v>-32.68</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2024-11-21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW_US_EQ</t>
+          <t>KOIDl_EQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>KraneShares Global Humanoid Robotics and Physical AI Index (Acc)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US8334451098</t>
+          <t>IE000O6Z73N7</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1561,38 +1561,38 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.3814255</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>187.8703632</v>
+        <v>28.53653846</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>328.18</v>
+        <v>27.282</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>641.99</v>
+        <v>1095.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1062.15</v>
+        <v>1050.12</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02428518579659022</v>
+        <v>0.02428990786387271</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>420.16</v>
+        <v>-45.66</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6544650228196701</v>
+        <v>-0.04166894814652576</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-33.95</v>
+        <v>2.63</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>332.55</v>
+        <v>332.77</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>751.66</v>
+        <v>753.73</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01718608742255331</v>
+        <v>0.01743422871122993</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>260.61</v>
+        <v>262.68</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.53071988595866</v>
+        <v>0.5349353426331331</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-21.2</v>
+        <v>-20.21</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>494.89</v>
+        <v>504.81</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>681.79</v>
+        <v>696.91</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01558856736266746</v>
+        <v>0.01611994790063186</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>147.41</v>
+        <v>162.53</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2758523896852427</v>
+        <v>0.3041468617837494</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.39</v>
+        <v>-24.32</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>984.75</v>
+        <v>1001</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>640.09</v>
+        <v>650.65</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01463513117407092</v>
+        <v>0.01504992624807525</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-22.59</v>
+        <v>-12.03</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.03408885133095914</v>
+        <v>-0.01815355827850546</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>57.84</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43.1</v>
+        <v>43.66</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>636.75</v>
+        <v>646.36</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01455876482227446</v>
+        <v>0.0149506959651209</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-230.83</v>
+        <v>-221.22</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.2660619193619032</v>
+        <v>-0.2549851310541967</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-13.07</v>
+        <v>-11.29</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>91.8</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>623.59</v>
+        <v>623.3200000000001</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01425787225052553</v>
+        <v>0.01441776689303045</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>74.41</v>
+        <v>74.14</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1354929167121891</v>
+        <v>0.1350012746276266</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-24.75</v>
+        <v>-23.66</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>324.82</v>
+        <v>327.78</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>559.0700000000001</v>
+        <v>565.34</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01278267553857712</v>
+        <v>0.01307665458401116</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>69.8</v>
+        <v>76.06999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1426615161362847</v>
+        <v>0.1554765262533979</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-32.09</v>
+        <v>-31.14</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.772</v>
+        <v>3.7485</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>528.08</v>
+        <v>524.79</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01207411468762732</v>
+        <v>0.01213870866937279</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-10.29</v>
+        <v>-13.58</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.0191132492523729</v>
+        <v>-0.02522428812898193</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>338.38</v>
+        <v>347.85</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>499.91</v>
+        <v>514.97</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01143003081633801</v>
+        <v>0.01191156615687591</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>91.98999999999999</v>
+        <v>107.05</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.225509903902726</v>
+        <v>0.2624289076289468</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>242.78</v>
+        <v>248.81</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>199.1</v>
+        <v>204.47</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004552257677447735</v>
+        <v>0.004729514208781904</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>2.58</v>
+        <v>7.95</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.01312843476490942</v>
+        <v>0.04045389782210462</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-2.27</v>
+        <v>-1.86</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,34 +2131,34 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>121.66614911</v>
+        <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>134.22</v>
+        <v>276.54</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>131.43</v>
+        <v>129.83</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003005038807367935</v>
+        <v>0.003003046068988872</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>11.7</v>
+        <v>29.98</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.09771986970684038</v>
+        <v>0.3002503755633451</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.59</v>
+        <v>0.04</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>212.76482689</v>
+        <v>121.66614911</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>268.1</v>
+        <v>131.57</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>125.6</v>
+        <v>129.1</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002871740654381896</v>
+        <v>0.002986160729465172</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>25.75</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2578868302453681</v>
+        <v>0.078259417021632</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.35</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>214.23</v>
+        <v>212.95</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.11</v>
+        <v>124.62</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002860537207561457</v>
+        <v>0.002882535632114251</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.7</v>
+        <v>14.21</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1331401141200978</v>
+        <v>0.1287021103160946</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.2</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.7905852</v>
@@ -2308,25 +2308,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>50.01</v>
+        <v>50.32</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>122.22</v>
+        <v>123.24</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002794459735498052</v>
+        <v>0.002850615401233833</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>9.51</v>
+        <v>10.53</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.08437583178067608</v>
+        <v>0.09342560553633218</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.22</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>3.30858696</v>
@@ -2365,25 +2365,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>387.56</v>
+        <v>394.61</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120.27</v>
+        <v>122.71</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002749874589988142</v>
+        <v>0.002838356182127585</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>11.11</v>
+        <v>13.55</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1017772077684133</v>
+        <v>0.1241297178453646</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.15</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>0.42010405</v>
@@ -2422,25 +2422,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>42.27</v>
+        <v>42.64</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.12</v>
+        <v>120.41</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002723580786225888</v>
+        <v>0.002785155797326889</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>10.89</v>
+        <v>12.18</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1006190520188488</v>
+        <v>0.1125381132772799</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.13</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>3.81488812</v>
@@ -2479,25 +2479,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>570</v>
+        <v>575.15</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>118.05</v>
+        <v>119.37</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002699116116638398</v>
+        <v>0.002761099971156139</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>12.3</v>
+        <v>13.62</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1163120567375887</v>
+        <v>0.1287943262411347</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0.28038062</v>
@@ -2536,25 +2536,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>102.39</v>
+        <v>103.09</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>117.84</v>
+        <v>118.89</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002694314639429639</v>
+        <v>0.002749997282154255</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>12.56</v>
+        <v>13.61</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1193009118541034</v>
+        <v>0.1292743161094225</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.1</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>1.55804584</v>
@@ -2593,25 +2593,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>63.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.46</v>
+        <v>118.82</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002685626252099502</v>
+        <v>0.002748378140008147</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>10.65</v>
+        <v>12.01</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.09970976500327684</v>
+        <v>0.112442655182099</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.1</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>2.50421091</v>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>235.02053179</v>
+        <v>228.00445932</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>253.4</v>
+        <v>266.96</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>108.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.89</v>
+        <v>116.95</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002672593671104298</v>
+        <v>0.002705123914104972</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>17.1</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07465293739082467</v>
+        <v>0.171256885327992</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.36</v>
+        <v>0.03</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,55 +2701,55 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>228.00445932</v>
+        <v>225.62857143</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>265.99</v>
+        <v>223</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.28</v>
+        <v>115.55</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002658646523021711</v>
+        <v>0.002672741071182809</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>16.43</v>
+        <v>-3.21</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1645468202303455</v>
+        <v>-0.02702930279555406</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.18</v>
+        <v>-1.85</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.62445608</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>54.82621761</v>
+        <v>235.02053179</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>56.05</v>
+        <v>249.57</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>112.48</v>
+        <v>108.77</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.54</v>
+        <v>115.36</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.00261886285472056</v>
+        <v>0.00266834625678623</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>2.06</v>
+        <v>6.59</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.01831436699857752</v>
+        <v>0.06058655879378505</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.14</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.62445608</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>53.65641702</v>
+        <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>56.57</v>
+        <v>89.23</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.13</v>
+        <v>114.53</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002586624364890318</v>
+        <v>0.002649147857053804</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>5.49</v>
+        <v>13</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.05100334448160535</v>
+        <v>0.1280409731113956</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>88.23999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.03</v>
+        <v>113.02</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002584337947171861</v>
+        <v>0.002614220647902043</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>11.5</v>
+        <v>5.38</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1132670146754654</v>
+        <v>0.04998141954663694</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.12</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.7</v>
+        <v>1.59010207</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>225.62857143</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>215.95</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>118.76</v>
+        <v>89.66</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.66</v>
+        <v>109.97</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002553014024429001</v>
+        <v>0.002543672311535902</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-7.1</v>
+        <v>20.31</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.05978443920511956</v>
+        <v>0.2265224180236449</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-2.1</v>
+        <v>0.03</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0</v>
+        <v>1.59010207</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>2.76637723</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>54.82621761</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>93.45</v>
+        <v>53.6</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>89.66</v>
+        <v>112.48</v>
       </c>
       <c r="I42" s="2" t="n">
         <v>109.76</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.00250957208777832</v>
+        <v>0.002538814885097578</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>20.1</v>
+        <v>-2.72</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.2241802364488066</v>
+        <v>-0.02418207681365576</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>2.76637723</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.61215748</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>12.56856884</v>
+        <v>194.45976548</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.9</v>
+        <v>235.4</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>106.15</v>
+        <v>88.09</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.64</v>
+        <v>106.67</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002483964209331602</v>
+        <v>0.002467341324647947</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.49</v>
+        <v>18.58</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.02345737164390014</v>
+        <v>0.2109206493359064</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.3</v>
+        <v>0.03</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.61215748</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.42255419</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>306.99401668</v>
+        <v>324.07677699</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>356.84</v>
+        <v>340.54</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>92.83</v>
+        <v>101.39</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.72</v>
+        <v>106.52</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002462929166321798</v>
+        <v>0.002463871734334858</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14.89</v>
+        <v>5.13</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1604007325218141</v>
+        <v>0.05059670578952559</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.42255419</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1.74206342</v>
+        <v>11.40066159</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>74.99726962</v>
+        <v>12.56856884</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>83.38</v>
+        <v>12.6</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>107.3</v>
+        <v>106.33</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002453326211904279</v>
+        <v>0.002459476919938278</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>10.62</v>
+        <v>0.18</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1098469176665287</v>
+        <v>0.001695713612812058</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.09</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>1.74206342</v>
+        <v>11.40066159</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>194.45976548</v>
+        <v>306.99401668</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>234.56</v>
+        <v>350.44</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>106.07</v>
+        <v>106.01</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002425203273967259</v>
+        <v>0.002452075127270355</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>17.98</v>
+        <v>13.18</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.2041094335338858</v>
+        <v>0.1419799633739093</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.5550481</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>324.07677699</v>
+        <v>221.99877812</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>338.25</v>
+        <v>256.75</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>101.39</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>105.58</v>
+        <v>105.49</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.00241399982714682</v>
+        <v>0.00244004721418498</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>4.19</v>
+        <v>14.31</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.0413255745142519</v>
+        <v>0.1569423119105067</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.5550481</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.74206342</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>221.99877812</v>
+        <v>74.99726962</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>256.5</v>
+        <v>81.44</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>105.17</v>
+        <v>105.02</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002404625514501147</v>
+        <v>0.002429175831203969</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>13.99</v>
+        <v>8.34</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1534327703443737</v>
+        <v>0.08626396359122879</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.03</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.74206342</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>176.50746647</v>
+        <v>322.35040597</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>205.9</v>
+        <v>324.09</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.18</v>
+        <v>104.55</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002381989979088423</v>
+        <v>0.002418304448222957</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>14.72</v>
+        <v>0.51</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1645428124301364</v>
+        <v>0.004901960784313725</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.68495686</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>322.35040597</v>
+        <v>176.50746647</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>323.31</v>
+        <v>205.16</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>104.04</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>104.09</v>
+        <v>104.02</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002379932203141812</v>
+        <v>0.002406045229116709</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.05</v>
+        <v>14.56</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.0004805843906189927</v>
+        <v>0.162754303599374</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.26</v>
+        <v>0.03</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.68495686</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3505,25 +3505,25 @@
         <v>148.63893521</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>174.88</v>
+        <v>174.28</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103.87</v>
+        <v>103.73</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002374902084161207</v>
+        <v>0.002399337354511404</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>15.43</v>
+        <v>15.29</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.174468566259611</v>
+        <v>0.1728855721393035</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.03</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>0.80409618</v>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>257.81779936</v>
+        <v>249.91595261</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>276.18</v>
+        <v>269.04</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>103.38</v>
+        <v>103.32</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002363698637340767</v>
+        <v>0.002389853807655628</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>6.7</v>
+        <v>7.38</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.06930078609846918</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.04</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.1533463</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>249.91595261</v>
+        <v>104.90344487</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>268.16</v>
+        <v>121.02</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>95.94</v>
+        <v>89.53</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>102.77</v>
+        <v>103.32</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002349751489258181</v>
+        <v>0.002389853807655628</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>6.83</v>
+        <v>13.79</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.07119032728788827</v>
+        <v>0.1540265832681783</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.03</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.1533463</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>104.90344487</v>
+        <v>257.81779936</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>120.37</v>
+        <v>274.51</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.55</v>
+        <v>102.97</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002344721370277575</v>
+        <v>0.002381758096925087</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>13.02</v>
+        <v>6.29</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.145426114151681</v>
+        <v>0.06505999172527926</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.03</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>113.12478542</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1072.02</v>
+        <v>116.34</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>98.89</v>
+        <v>98.72</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>101.81</v>
+        <v>101.57</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002327801879160994</v>
+        <v>0.002349375254002924</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.02952775811507736</v>
+        <v>0.02886952998379255</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.04</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.1285649</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>137.713206</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>152.19</v>
+        <v>1065.6</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>92.27</v>
+        <v>98.89</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.79</v>
+        <v>101.41</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002327344595617303</v>
+        <v>0.002345674357668963</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>9.52</v>
+        <v>2.52</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1031754633141866</v>
+        <v>0.02548285974314895</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.03</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.1285649</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,38 +3841,38 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>5.691347</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>113.12478542</v>
+        <v>105.04894536</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>115.81</v>
+        <v>23.94</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>98.72</v>
+        <v>452.96</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.9</v>
+        <v>100.86</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002306995477923036</v>
+        <v>0.00233295252652097</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.18</v>
+        <v>-352.1</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.02208265802269044</v>
+        <v>-0.7773313316849171</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.16</v>
+        <v>-10.4</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
@@ -3904,25 +3904,25 @@
         <v>62.95787236</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>59.88</v>
+        <v>59.35</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.66</v>
+        <v>99.98</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002301508075398739</v>
+        <v>0.002312597596684182</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-5.49</v>
+        <v>-6.17</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.05171926519076778</v>
+        <v>-0.05812529439472444</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.09</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>2.27580753</v>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.37810738</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>10.85229847</v>
+        <v>341.38450299</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>10.18</v>
+        <v>357.2</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>106.96</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>100.03</v>
+        <v>99.97</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002287103643772461</v>
+        <v>0.00231236629066331</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-6.93</v>
+        <v>4.46</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.06479057591623037</v>
+        <v>0.04669668097581404</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.32</v>
+        <v>0.03</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.37810738</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>341.38450299</v>
+        <v>96.717382</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>356.29</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002275214271636485</v>
+        <v>0.00230172621370317</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.04188043136844309</v>
+        <v>0.02927182457592056</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.04</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.90543241</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>76.24181082</v>
+        <v>137.713206</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>72.34999999999999</v>
+        <v>148.3</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>104.98</v>
+        <v>92.27</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>99.36</v>
+        <v>99.39</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.0022717846450588</v>
+        <v>0.002298950541452699</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-5.62</v>
+        <v>7.12</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.05353400647742427</v>
+        <v>0.07716484231061017</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.28</v>
+        <v>0.02</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.90543241</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.10445851</v>
+        <v>13.30225117</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>10.85229847</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1280</v>
+        <v>10.07</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>88.89</v>
+        <v>106.96</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98.77</v>
+        <v>99.16</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002258294780519904</v>
+        <v>0.002293630502972629</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>-7.8</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.111148610642367</v>
+        <v>-0.07292445774121167</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.10445851</v>
+        <v>13.30225117</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>127.23134407</v>
+        <v>147.21071381</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>119.59</v>
+        <v>146.12</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>105.36</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.76000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002258066138748058</v>
+        <v>0.002292705278889139</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-6.6</v>
+        <v>-0.73</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.06264236902050113</v>
+        <v>-0.007310966449674512</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.29</v>
+        <v>0.01</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.10445851</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>147.21071381</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>145</v>
+        <v>1277.51</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.15000000000001</v>
+        <v>98.78</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002244118990665471</v>
+        <v>0.002284840874179471</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-1.7</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.01702553830746119</v>
+        <v>0.1112611092361346</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.03</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.10445851</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.11796351</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>154.44822659</v>
+        <v>127.23134407</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>136.5</v>
+        <v>119.02</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>111.44</v>
+        <v>105.36</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.12</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002243433065349934</v>
+        <v>0.002278132999574166</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-13.32</v>
+        <v>-6.87</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.1195262024407753</v>
+        <v>-0.06520501138952164</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.11796351</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.97307689</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>96.717382</v>
+        <v>154.44822659</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>98.3</v>
+        <v>136.21</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>111.44</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.09999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002242975781806242</v>
+        <v>0.002269343370781007</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.42</v>
+        <v>-13.33</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.01468762929251138</v>
+        <v>-0.1196159368269921</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.19</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.97307689</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,55 +4411,55 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.85908491</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>105.04894536</v>
+        <v>76.24181082</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>23.13</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>452.96</v>
+        <v>104.98</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.91</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002223312589427512</v>
+        <v>0.002264717250363555</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-355.72</v>
+        <v>-7.07</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.7853232073472273</v>
+        <v>-0.06734616117355686</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-11.32</v>
+        <v>-0.06</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0</v>
+        <v>1.85908491</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>127.79185697</v>
+        <v>126.99866255</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>138.69</v>
+        <v>109.1</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>95.73999999999999</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002189016323650659</v>
+        <v>0.002191393241746943</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>7.36</v>
+        <v>-15.71</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.08327675944783888</v>
+        <v>-0.1422363060208239</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>126.99866255</v>
+        <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>107.07</v>
+        <v>136.6</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>92.78</v>
+        <v>94.5</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002121338359184334</v>
+        <v>0.002185841897246001</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-17.67</v>
+        <v>6.12</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1599818922589407</v>
+        <v>0.06924643584521385</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.4</v>
+        <v>0.03</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>107.56862839</v>
+        <v>234.11448729</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>105.5</v>
+        <v>200</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>92.77</v>
+        <v>107.82</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>90.84</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.00207698185544627</v>
+        <v>0.002128246698048726</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-1.93</v>
+        <v>-15.81</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.02080413926916029</v>
+        <v>-0.1466332776850306</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.12</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4620,17 +4620,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4639,34 +4639,34 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>234.11448729</v>
+        <v>107.56862839</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>197.15</v>
+        <v>104.28</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>107.82</v>
+        <v>92.77</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.51000000000001</v>
+        <v>89.97</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002069436676975362</v>
+        <v>0.002081060269790717</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.31</v>
+        <v>-2.8</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1605453533667223</v>
+        <v>-0.0301821709604398</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.34</v>
+        <v>0.04</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>56.58</v>
+        <v>56.18</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.19</v>
+        <v>76.81</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001764885836876899</v>
+        <v>0.001776661546322385</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33.34</v>
+        <v>-33.72</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.301637564462137</v>
+        <v>-0.3050755451008776</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.17</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>106.29</v>
+        <v>105.8</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49.64</v>
+        <v>49.51</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001134977755442017</v>
+        <v>0.001145196109340207</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.03697514100689368</v>
+        <v>0.03425945268435346</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.08</v>
+        <v>0.01</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>252.52</v>
+        <v>257.55</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.21</v>
+        <v>46.2</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001033689450514375</v>
+        <v>0.001068633816431378</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.9</v>
+        <v>-5.91</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1324122049510651</v>
+        <v>-0.1134139320667818</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,7 +4865,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13 20:59:51</t>
+          <t>2026-09-14 21:56:25</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43926.08</v>
+        <v>43421.37</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43769.54</v>
+        <v>43264.53</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37744.56</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6024.98</v>
+        <v>5519.97</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1596251221368059</v>
+        <v>0.1462454457013143</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>189.54</v>
+        <v>189.84</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109.74</v>
+        <v>109.32</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7023.36</v>
+        <v>6996.48</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>977.59</v>
+        <v>950.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.922</v>
+        <v>14.116</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4327.38</v>
+        <v>4093.64</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>896.67</v>
+        <v>662.9299999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1552.6</v>
+        <v>1536.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2738.68</v>
+        <v>2710.81</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1542.72</v>
+        <v>1514.85</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>26.53</v>
+        <v>26.81</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2253.69</v>
+        <v>2282.21</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>327.88</v>
+        <v>356.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>112.04</v>
+        <v>110.05</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2053.01</v>
+        <v>2020.74</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>406.44</v>
+        <v>374.17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>515.77</v>
+        <v>494</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1904.95</v>
+        <v>1828.34</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>6.4</v>
+        <v>-70.20999999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>218.26</v>
+        <v>212.48</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1761.55</v>
+        <v>1718.47</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>508.87</v>
+        <v>465.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>236.13</v>
+        <v>220.5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1674.48</v>
+        <v>1566.9</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-321.58</v>
+        <v>-429.16</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,76 +5250,76 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>157.97</v>
+        <v>161.59</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1468.22</v>
+        <v>1504.99</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-403.62</v>
+        <v>-366.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>44.56</v>
+        <v>119.42</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1410.39</v>
+        <v>1405.7</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>182.05</v>
+        <v>61.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>119.4</v>
+        <v>43.33</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1402.54</v>
+        <v>1373.16</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>58.75</v>
+        <v>144.82</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>442.3</v>
+        <v>444.5</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1221.02</v>
+        <v>1224.41</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>306.53</v>
+        <v>309.92</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>111.15</v>
+        <v>109.35</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1127.46</v>
+        <v>1109.21</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>520.27</v>
+        <v>502.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,76 +5385,76 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>697.8</v>
+        <v>682.8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1116.48</v>
+        <v>1092.48</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>363.02</v>
+        <v>339.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>KOIDl_EQ</t>
+          <t>SNOW_US_EQ</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>52</v>
+        <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>28.177</v>
+        <v>331.92</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1082.32</v>
+        <v>1076.49</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>1095.78</v>
+        <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-13.46</v>
+        <v>434.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SNOW_US_EQ</t>
+          <t>KOIDl_EQ</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.3814255</v>
+        <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>328.18</v>
+        <v>27.282</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1062.15</v>
+        <v>1050.12</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>641.99</v>
+        <v>1095.78</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>420.16</v>
+        <v>-45.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>332.55</v>
+        <v>332.77</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>751.66</v>
+        <v>753.73</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>260.61</v>
+        <v>262.68</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>494.89</v>
+        <v>504.81</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>681.79</v>
+        <v>696.91</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>147.41</v>
+        <v>162.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,22 +5520,22 @@
         <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>984.75</v>
+        <v>1001</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>640.09</v>
+        <v>650.65</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-22.59</v>
+        <v>-12.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>43.1</v>
+        <v>43.66</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>636.75</v>
+        <v>646.36</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-230.83</v>
+        <v>-221.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>91.8</v>
+        <v>91.56999999999999</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>623.59</v>
+        <v>623.3200000000001</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>74.41</v>
+        <v>74.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>324.82</v>
+        <v>327.78</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>559.0700000000001</v>
+        <v>565.34</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>69.8</v>
+        <v>76.06999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.772</v>
+        <v>3.7485</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>528.08</v>
+        <v>524.79</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-10.29</v>
+        <v>-13.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>338.38</v>
+        <v>347.85</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>499.91</v>
+        <v>514.97</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>91.98999999999999</v>
+        <v>107.05</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,76 +5682,76 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>242.78</v>
+        <v>248.81</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>199.1</v>
+        <v>204.47</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>2.58</v>
+        <v>7.95</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>134.22</v>
+        <v>276.54</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>131.43</v>
+        <v>129.83</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>11.7</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="D28" t="n">
-        <v>268.1</v>
+        <v>131.57</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125.6</v>
+        <v>129.1</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>25.75</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,22 +5763,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>214.23</v>
+        <v>212.95</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.11</v>
+        <v>124.62</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.7</v>
+        <v>14.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5790,22 +5790,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>50.01</v>
+        <v>50.32</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>122.22</v>
+        <v>123.24</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>9.51</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5817,22 +5817,22 @@
         <v>0.42010405</v>
       </c>
       <c r="D31" t="n">
-        <v>387.56</v>
+        <v>394.61</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120.27</v>
+        <v>122.71</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.11</v>
+        <v>13.55</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5844,22 +5844,22 @@
         <v>3.81488812</v>
       </c>
       <c r="D32" t="n">
-        <v>42.27</v>
+        <v>42.64</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.12</v>
+        <v>120.41</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.89</v>
+        <v>12.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5871,22 +5871,22 @@
         <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>570</v>
+        <v>575.15</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>118.05</v>
+        <v>119.37</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>12.3</v>
+        <v>13.62</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5898,22 +5898,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D34" t="n">
-        <v>102.39</v>
+        <v>103.09</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>117.84</v>
+        <v>118.89</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.56</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5925,427 +5925,427 @@
         <v>2.50421091</v>
       </c>
       <c r="D35" t="n">
-        <v>63.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.46</v>
+        <v>118.82</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10.65</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="D36" t="n">
-        <v>253.4</v>
+        <v>266.96</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.89</v>
+        <v>116.95</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>108.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.119999999999999</v>
+        <v>17.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7</v>
       </c>
       <c r="D37" t="n">
-        <v>265.99</v>
+        <v>223</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.28</v>
+        <v>115.55</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>16.43</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.62445608</v>
       </c>
       <c r="D38" t="n">
-        <v>56.05</v>
+        <v>249.57</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.54</v>
+        <v>115.36</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>112.48</v>
+        <v>108.77</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>2.06</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>56.57</v>
+        <v>89.23</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.13</v>
+        <v>114.53</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>5.49</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D40" t="n">
-        <v>88.23999999999999</v>
+        <v>56.4</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.03</v>
+        <v>113.02</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>11.5</v>
+        <v>5.38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.7</v>
+        <v>1.59010207</v>
       </c>
       <c r="D41" t="n">
-        <v>215.95</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.66</v>
+        <v>109.97</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>118.76</v>
+        <v>89.66</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-7.1</v>
+        <v>20.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>2.76637723</v>
       </c>
       <c r="D42" t="n">
-        <v>93.45</v>
+        <v>53.6</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>109.76</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>89.66</v>
+        <v>112.48</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>20.1</v>
+        <v>-2.72</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.61215748</v>
       </c>
       <c r="D43" t="n">
-        <v>12.9</v>
+        <v>235.4</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.64</v>
+        <v>106.67</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>106.15</v>
+        <v>88.09</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2.49</v>
+        <v>18.58</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.42255419</v>
       </c>
       <c r="D44" t="n">
-        <v>356.84</v>
+        <v>340.54</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.72</v>
+        <v>106.52</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>92.83</v>
+        <v>101.39</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14.89</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1.74206342</v>
+        <v>11.40066159</v>
       </c>
       <c r="D45" t="n">
-        <v>83.38</v>
+        <v>12.6</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>107.3</v>
+        <v>106.33</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>10.62</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="D46" t="n">
-        <v>234.56</v>
+        <v>350.44</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>106.07</v>
+        <v>106.01</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>17.98</v>
+        <v>13.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.5550481</v>
       </c>
       <c r="D47" t="n">
-        <v>338.25</v>
+        <v>256.75</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>105.58</v>
+        <v>105.49</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>101.39</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>4.19</v>
+        <v>14.31</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.74206342</v>
       </c>
       <c r="D48" t="n">
-        <v>256.5</v>
+        <v>81.44</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>105.17</v>
+        <v>105.02</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>13.99</v>
+        <v>8.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="D49" t="n">
-        <v>205.9</v>
+        <v>324.09</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.18</v>
+        <v>104.55</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>14.72</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.68495686</v>
       </c>
       <c r="D50" t="n">
-        <v>323.31</v>
+        <v>205.16</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>104.09</v>
+        <v>104.02</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>104.04</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.05</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6357,184 +6357,184 @@
         <v>0.80409618</v>
       </c>
       <c r="D51" t="n">
-        <v>174.88</v>
+        <v>174.28</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>103.87</v>
+        <v>103.73</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15.43</v>
+        <v>15.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.51881442</v>
       </c>
       <c r="D52" t="n">
-        <v>276.18</v>
+        <v>269.04</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.38</v>
+        <v>103.32</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6.7</v>
+        <v>7.38</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.1533463</v>
       </c>
       <c r="D53" t="n">
-        <v>268.16</v>
+        <v>121.02</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>102.77</v>
+        <v>103.32</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>95.94</v>
+        <v>89.53</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>6.83</v>
+        <v>13.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="D54" t="n">
-        <v>120.37</v>
+        <v>274.51</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.55</v>
+        <v>102.97</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>13.02</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="D55" t="n">
-        <v>1072.02</v>
+        <v>116.34</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>101.81</v>
+        <v>101.57</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>98.89</v>
+        <v>98.72</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.1285649</v>
       </c>
       <c r="D56" t="n">
-        <v>152.19</v>
+        <v>1065.6</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>101.79</v>
+        <v>101.41</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>92.27</v>
+        <v>98.89</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>9.52</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>5.691347</v>
       </c>
       <c r="D57" t="n">
-        <v>115.81</v>
+        <v>23.94</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.9</v>
+        <v>100.86</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>98.72</v>
+        <v>452.96</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2.18</v>
+        <v>-352.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6546,373 +6546,373 @@
         <v>2.27580753</v>
       </c>
       <c r="D58" t="n">
-        <v>59.88</v>
+        <v>59.35</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.66</v>
+        <v>99.98</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-5.49</v>
+        <v>-6.17</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.37810738</v>
       </c>
       <c r="D59" t="n">
-        <v>10.18</v>
+        <v>357.2</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>100.03</v>
+        <v>99.97</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>106.96</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-6.93</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="D60" t="n">
-        <v>356.29</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>99.51000000000001</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>4</v>
+        <v>2.83</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.90543241</v>
       </c>
       <c r="D61" t="n">
-        <v>72.34999999999999</v>
+        <v>148.3</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>99.36</v>
+        <v>99.39</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>104.98</v>
+        <v>92.27</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-5.62</v>
+        <v>7.12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.10445851</v>
+        <v>13.30225117</v>
       </c>
       <c r="D62" t="n">
-        <v>1280</v>
+        <v>10.07</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>98.77</v>
+        <v>99.16</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>88.89</v>
+        <v>106.96</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>9.880000000000001</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D63" t="n">
-        <v>119.59</v>
+        <v>146.12</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.76000000000001</v>
+        <v>99.12</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>105.36</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-6.6</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>145</v>
+        <v>1277.51</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.15000000000001</v>
+        <v>98.78</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-1.7</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.11796351</v>
       </c>
       <c r="D65" t="n">
-        <v>136.5</v>
+        <v>119.02</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.12</v>
+        <v>98.48999999999999</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>111.44</v>
+        <v>105.36</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-13.32</v>
+        <v>-6.87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.97307689</v>
       </c>
       <c r="D66" t="n">
-        <v>98.3</v>
+        <v>136.21</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.09999999999999</v>
+        <v>98.11</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>111.44</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1.42</v>
+        <v>-13.33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.85908491</v>
       </c>
       <c r="D67" t="n">
-        <v>23.13</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.91</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>452.96</v>
+        <v>104.98</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-355.72</v>
+        <v>-7.07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="D68" t="n">
-        <v>138.69</v>
+        <v>109.1</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>95.73999999999999</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>7.36</v>
+        <v>-15.71</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>107.07</v>
+        <v>136.6</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.78</v>
+        <v>94.5</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-17.67</v>
+        <v>6.12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="D70" t="n">
-        <v>105.5</v>
+        <v>200</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>90.84</v>
+        <v>92.01000000000001</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>92.77</v>
+        <v>107.82</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-1.93</v>
+        <v>-15.81</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="D71" t="n">
-        <v>197.15</v>
+        <v>104.28</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.51000000000001</v>
+        <v>89.97</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>107.82</v>
+        <v>92.77</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.31</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>56.58</v>
+        <v>56.18</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.19</v>
+        <v>76.81</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33.34</v>
+        <v>-33.72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>106.29</v>
+        <v>105.8</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>49.64</v>
+        <v>49.51</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>252.52</v>
+        <v>257.55</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.21</v>
+        <v>46.2</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.9</v>
+        <v>-5.91</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43421.37</v>
+        <v>43254.94</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43264.53</v>
+        <v>43076.98</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37744.56</v>
+        <v>37745.71</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5519.97</v>
+        <v>5331.27</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1462454457013143</v>
+        <v>0.1412417464130361</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>156.84</v>
+        <v>177.96</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>33</v>
+        <v>34.15</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-14 21:56:25</t>
+          <t>2026-09-15 21:34:04</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109.32</v>
+        <v>108.82</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6996.48</v>
+        <v>6964.48</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1618327948914677</v>
+        <v>0.1618040512347279</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>950.71</v>
+        <v>918.71</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1572520952666079</v>
+        <v>0.1519591383727796</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.116</v>
+        <v>14.114</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4093.64</v>
+        <v>4093.06</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09468835792848805</v>
+        <v>0.09509305647324934</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>662.9299999999999</v>
+        <v>662.35</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1932340535924051</v>
+        <v>0.1930649923776711</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1536.8</v>
+        <v>1503.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2710.81</v>
+        <v>2652.6</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06270266744416331</v>
+        <v>0.06162720351056207</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1514.85</v>
+        <v>1456.64</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.266639352486705</v>
+        <v>1.217967156092177</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.81</v>
+        <v>26.42</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2282.21</v>
+        <v>2254.18</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05278889138956398</v>
+        <v>0.05237080962430778</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>356.4</v>
+        <v>328.37</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.185064985642405</v>
+        <v>0.1705100710869712</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-9.640000000000001</v>
+        <v>-5.24</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>110.05</v>
+        <v>110.23</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2020.74</v>
+        <v>2028.7</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0467409328618083</v>
+        <v>0.04713228823112316</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>374.17</v>
+        <v>382.13</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2272420850616737</v>
+        <v>0.2320763769533029</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-11.26</v>
+        <v>-7.5</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>494</v>
+        <v>503.33</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1828.34</v>
+        <v>1867.16</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04229060502021962</v>
+        <v>0.0433792691347286</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-70.20999999999999</v>
+        <v>-31.39</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.03698085380948619</v>
+        <v>-0.01653367043269864</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-11.1</v>
+        <v>-6.76</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>212.48</v>
+        <v>212.34</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1718.47</v>
+        <v>1721.29</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.03974924576889245</v>
+        <v>0.03999030729499185</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>465.79</v>
+        <v>468.61</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3718347862183479</v>
+        <v>0.3740859597023981</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-38.77</v>
+        <v>-35.97</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>220.5</v>
+        <v>221.52</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1566.9</v>
+        <v>1577.77</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03624334041052656</v>
+        <v>0.03665594242737674</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-429.16</v>
+        <v>-418.29</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.2150035570073044</v>
+        <v>-0.2095578289229783</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-16.64</v>
+        <v>-12.08</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>161.59</v>
+        <v>158.94</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1504.99</v>
+        <v>1483.71</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03481132483530433</v>
+        <v>0.0344706695772661</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-366.85</v>
+        <v>-388.13</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.1959836310795795</v>
+        <v>-0.2073521241131721</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-88.04000000000001</v>
+        <v>-83.94</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.42</v>
+        <v>119.38</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1405.7</v>
+        <v>1408.46</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03251468735406036</v>
+        <v>0.0327224048316694</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>61.91</v>
+        <v>64.67</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04607118671816281</v>
+        <v>0.04812507906741381</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-13.19</v>
+        <v>-10.13</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>43.33</v>
+        <v>41.86</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1373.16</v>
+        <v>1326.76</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03176201756214095</v>
+        <v>0.03082428882216442</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>144.82</v>
+        <v>98.42</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1178989530585994</v>
+        <v>0.0801243955256688</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-54.2</v>
+        <v>-54.03</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>444.5</v>
+        <v>444.6</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1224.41</v>
+        <v>1225.96</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02832134050166113</v>
+        <v>0.02848242720945815</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>309.92</v>
+        <v>311.47</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3388992771927523</v>
+        <v>0.340594210980984</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-3.53</v>
+        <v>-2.58</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>109.35</v>
+        <v>108.9</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1109.21</v>
+        <v>1104.64</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02565669514120886</v>
+        <v>0.02566382948273667</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>502.02</v>
+        <v>497.45</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8267922726000098</v>
+        <v>0.8192657981850821</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>682.8</v>
+        <v>689.2</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1092.48</v>
+        <v>1102.72</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02526972016828901</v>
+        <v>0.0256192225948756</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>339.02</v>
+        <v>349.26</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4499508932126456</v>
+        <v>0.4635415284155761</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>331.92</v>
+        <v>323.64</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1076.49</v>
+        <v>1052.05</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02489986184091373</v>
+        <v>0.024442018944917</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>434.5</v>
+        <v>410.06</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6768018193429804</v>
+        <v>0.6387326905403511</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-32.68</v>
+        <v>-31.28</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>27.282</v>
+        <v>27.102</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1050.12</v>
+        <v>1045.59</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02428990786387271</v>
+        <v>0.02429193535346777</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-45.66</v>
+        <v>-50.19</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.04166894814652576</v>
+        <v>-0.04580298965120736</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2.63</v>
+        <v>5.15</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>332.77</v>
+        <v>331.6</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>753.73</v>
+        <v>752.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01743422871122993</v>
+        <v>0.01748961728219525</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>262.68</v>
+        <v>261.75</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5349353426331331</v>
+        <v>0.5330414418083698</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-20.21</v>
+        <v>-19.14</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>504.81</v>
+        <v>497.8</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>696.91</v>
+        <v>688.8099999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01611994790063186</v>
+        <v>0.01600295334770047</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>162.53</v>
+        <v>154.43</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.3041468617837494</v>
+        <v>0.2889891088738351</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-24.32</v>
+        <v>-23.15</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1001</v>
+        <v>1002.5</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>650.65</v>
+        <v>651.63</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01504992624807525</v>
+        <v>0.01513915955047409</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-12.03</v>
+        <v>-11.05</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.01815355827850546</v>
+        <v>-0.01667471479447094</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>57.84</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43.66</v>
+        <v>42.5</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>646.36</v>
+        <v>630.63</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.0149506959651209</v>
+        <v>0.01465127171449361</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-221.22</v>
+        <v>-236.95</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.2549851310541967</v>
+        <v>-0.2731160238825238</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-11.29</v>
+        <v>-9.33</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>91.56999999999999</v>
+        <v>89.03</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>623.3200000000001</v>
+        <v>607.4299999999999</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01441776689303045</v>
+        <v>0.01411227181950566</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>74.14</v>
+        <v>58.25</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1350012746276266</v>
+        <v>0.1060672275028224</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-23.66</v>
+        <v>-22.45</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>327.78</v>
+        <v>324.27</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>565.34</v>
+        <v>560.5700000000001</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01307665458401116</v>
+        <v>0.01302358496264638</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1554765262533979</v>
+        <v>0.1457273080303309</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31.14</v>
+        <v>-30.09</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.7485</v>
+        <v>3.745</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>524.79</v>
+        <v>524.3</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01213870866937279</v>
+        <v>0.01218093297164582</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-13.58</v>
+        <v>-14.07</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.02522428812898193</v>
+        <v>-0.0261344428552854</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>347.85</v>
+        <v>344.18</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>514.97</v>
+        <v>510.71</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01191156615687591</v>
+        <v>0.01186519984350417</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>107.05</v>
+        <v>102.79</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2624289076289468</v>
+        <v>0.2519856834673466</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-9.050000000000001</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>248.81</v>
+        <v>248.21</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>204.47</v>
+        <v>204.45</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004729514208781904</v>
+        <v>0.004749936574581322</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>7.95</v>
+        <v>7.93</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.04045389782210462</v>
+        <v>0.04035212700997354</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.86</v>
+        <v>-1.41</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,34 +2131,34 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>212.76482689</v>
+        <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>276.54</v>
+        <v>135.7</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>129.83</v>
+        <v>133.46</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003003046068988872</v>
+        <v>0.00310064336142638</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>29.98</v>
+        <v>13.73</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.3002503755633451</v>
+        <v>0.114674684707258</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>121.66614911</v>
+        <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>131.57</v>
+        <v>276.78</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>129.1</v>
+        <v>130.24</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002986160729465172</v>
+        <v>0.003025833893242707</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>30.39</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.078259417021632</v>
+        <v>0.3043565348022033</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.35</v>
+        <v>0.27</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>212.95</v>
+        <v>217.7</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124.62</v>
+        <v>127.69</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002882535632114251</v>
+        <v>0.002966590370302221</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.21</v>
+        <v>17.28</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1287021103160946</v>
+        <v>0.1565075627207681</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.05</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.7905852</v>
@@ -2308,25 +2308,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>50.32</v>
+        <v>51.45</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>123.24</v>
+        <v>126.3</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002850615401233833</v>
+        <v>0.002934296842111132</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>10.53</v>
+        <v>13.59</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.09342560553633218</v>
+        <v>0.1205749268033005</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.04</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>3.30858696</v>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.42010405</v>
+        <v>3.81488812</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>350.55601106</v>
+        <v>38.28159448</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>394.61</v>
+        <v>43.46</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>109.16</v>
+        <v>108.23</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>122.71</v>
+        <v>123.01</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002838356182127585</v>
+        <v>0.002857861081140859</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>13.55</v>
+        <v>14.78</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1241297178453646</v>
+        <v>0.1365610274415596</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.12</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.42010405</v>
+        <v>3.81488812</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.42010405</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>38.28159448</v>
+        <v>350.55601106</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>42.64</v>
+        <v>383.94</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>108.23</v>
+        <v>109.16</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>120.41</v>
+        <v>119.67</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002785155797326889</v>
+        <v>0.002780263682465869</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>12.18</v>
+        <v>10.51</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1125381132772799</v>
+        <v>0.09628068889703188</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.1</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.42010405</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>575.15</v>
+        <v>574</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.37</v>
+        <v>119.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002761099971156139</v>
+        <v>0.002773990838860406</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.62</v>
+        <v>13.65</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1287943262411347</v>
+        <v>0.1290780141843972</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0.28038062</v>
@@ -2536,25 +2536,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>103.09</v>
+        <v>103.02</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.89</v>
+        <v>119.09</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002749997282154255</v>
+        <v>0.00276678868509117</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.61</v>
+        <v>13.81</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1292743161094225</v>
+        <v>0.1311740121580547</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>1.55804584</v>
@@ -2593,25 +2593,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>64.09999999999999</v>
+        <v>63.73</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.82</v>
+        <v>118.41</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002748378140008147</v>
+        <v>0.00275099041230704</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.01</v>
+        <v>11.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.112442655182099</v>
+        <v>0.1086040632899541</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.15</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>2.50421091</v>
@@ -2650,25 +2650,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>266.96</v>
+        <v>265.35</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.95</v>
+        <v>116.51</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002705123914104972</v>
+        <v>0.002706848179527855</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>17.1</v>
+        <v>16.66</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.171256885327992</v>
+        <v>0.1668502754131197</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.03</v>
+        <v>0.26</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.59183053</v>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,55 +2701,55 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.7</v>
+        <v>0.62445608</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>225.62857143</v>
+        <v>235.02053179</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>118.76</v>
+        <v>108.77</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>115.55</v>
+        <v>116.29</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002672741071182809</v>
+        <v>0.002701736973627107</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>-3.21</v>
+        <v>7.52</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.02702930279555406</v>
+        <v>0.06913671049002482</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-1.85</v>
+        <v>0.12</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0</v>
+        <v>0.62445608</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.73400968</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>235.02053179</v>
+        <v>79.10567143</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>249.57</v>
+        <v>88.77</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>108.77</v>
+        <v>101.53</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>115.36</v>
+        <v>114.2</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.00266834625678623</v>
+        <v>0.002653180517570003</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>6.59</v>
+        <v>12.67</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.06058655879378505</v>
+        <v>0.124790702255491</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.73400968</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>89.23</v>
+        <v>56.43</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>114.53</v>
+        <v>113.34</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002649147857053804</v>
+        <v>0.002633200349048897</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>13</v>
+        <v>5.7</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1280409731113956</v>
+        <v>0.05295429208472687</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.76637723</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>53.65641702</v>
+        <v>54.82621761</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>56.4</v>
+        <v>53.95</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>107.64</v>
+        <v>112.48</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.02</v>
+        <v>110.73</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002614220647902043</v>
+        <v>0.002572562860862753</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>5.38</v>
+        <v>-1.75</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.04998141954663694</v>
+        <v>-0.01555832147937411</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.12</v>
+        <v>0.05</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.76637723</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.7</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>93.43000000000001</v>
+        <v>213.09</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>89.66</v>
+        <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>109.97</v>
+        <v>110.67</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002543672311535902</v>
+        <v>0.002571168895617094</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>20.31</v>
+        <v>-8.09</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.2265224180236449</v>
+        <v>-0.06812057931963623</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.03</v>
+        <v>-1.58</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.59010207</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>54.82621761</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>53.6</v>
+        <v>93.28</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>112.48</v>
+        <v>89.66</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.76</v>
+        <v>110.05</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002538814885097578</v>
+        <v>0.002556764588078623</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-2.72</v>
+        <v>20.39</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.02418207681365576</v>
+        <v>0.2274146776712023</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.21</v>
+        <v>0.24</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.59010207</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.61215748</v>
+        <v>11.40066159</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>194.45976548</v>
+        <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>235.4</v>
+        <v>12.79</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>106.67</v>
+        <v>108.18</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002467341324647947</v>
+        <v>0.002513319337922267</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>18.58</v>
+        <v>2.03</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.2109206493359064</v>
+        <v>0.0191238813000471</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.03</v>
+        <v>0.16</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.61215748</v>
+        <v>11.40066159</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3106,25 +3106,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>340.54</v>
+        <v>342</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>106.52</v>
+        <v>107.22</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002463871734334858</v>
+        <v>0.002491015893991731</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>5.13</v>
+        <v>5.83</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.05059670578952559</v>
+        <v>0.0575007397179209</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>0.42255419</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.40867246</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>12.56856884</v>
+        <v>306.99401668</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>12.6</v>
+        <v>352.1</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>106.15</v>
+        <v>92.83</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>106.33</v>
+        <v>106.76</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002459476919938278</v>
+        <v>0.002480328827108349</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.18</v>
+        <v>13.93</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.001695713612812058</v>
+        <v>0.1500592480879026</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.25</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.40867246</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.5550481</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>306.99401668</v>
+        <v>221.99877812</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>350.44</v>
+        <v>257.47</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>92.83</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>106.01</v>
+        <v>106.03</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002452075127270355</v>
+        <v>0.002463368916619504</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>13.18</v>
+        <v>14.85</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1419799633739093</v>
+        <v>0.162864663303356</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.5550481</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.61215748</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>221.99877812</v>
+        <v>194.45976548</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>256.75</v>
+        <v>232.65</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>105.49</v>
+        <v>105.66</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.00244004721418498</v>
+        <v>0.00245477279760461</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>14.31</v>
+        <v>17.57</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1569423119105067</v>
+        <v>0.1994551027358383</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.61215748</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.43583007</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>74.99726962</v>
+        <v>322.35040597</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>81.44</v>
+        <v>323.22</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>105.02</v>
+        <v>104.51</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002429175831203969</v>
+        <v>0.002428055130396156</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>8.34</v>
+        <v>0.47</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.08626396359122879</v>
+        <v>0.00451749327181853</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.43583007</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.50675322</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>322.35040597</v>
+        <v>257.81779936</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>324.09</v>
+        <v>277.16</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>104.04</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.55</v>
+        <v>104.2</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002418304448222957</v>
+        <v>0.00242085297662692</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.51</v>
+        <v>7.52</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.004901960784313725</v>
+        <v>0.07778237484484897</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.25</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.50675322</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.1533463</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>176.50746647</v>
+        <v>104.90344487</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>205.16</v>
+        <v>121.47</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>104.02</v>
+        <v>103.94</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002406045229116709</v>
+        <v>0.0024148124605624</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>14.56</v>
+        <v>14.41</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.162754303599374</v>
+        <v>0.1609516363230202</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.03</v>
+        <v>0.23</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.1533463</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>148.63893521</v>
+        <v>176.50746647</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>174.28</v>
+        <v>204.23</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>88.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103.73</v>
+        <v>103.79</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002399337354511404</v>
+        <v>0.002411327547448254</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>15.29</v>
+        <v>14.33</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1728855721393035</v>
+        <v>0.1601833221551532</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.80409618</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>249.91595261</v>
+        <v>148.63893521</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>269.04</v>
+        <v>173.7</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>95.94</v>
+        <v>88.44</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>103.32</v>
+        <v>103.63</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002389853807655628</v>
+        <v>0.002407610306793164</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>7.38</v>
+        <v>15.19</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.1717548620533695</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.04</v>
+        <v>0.24</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.80409618</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.51881442</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>104.90344487</v>
+        <v>249.91595261</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>121.02</v>
+        <v>268.6</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>89.53</v>
+        <v>95.94</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>103.32</v>
+        <v>103.39</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002389853807655628</v>
+        <v>0.00240203444581053</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>13.79</v>
+        <v>7.45</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1540265832681783</v>
+        <v>0.07765269960391911</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.03</v>
+        <v>0.26</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.51881442</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.74206342</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>257.81779936</v>
+        <v>74.99726962</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>274.51</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.97</v>
+        <v>102.88</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002381758096925087</v>
+        <v>0.002390185741222433</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>6.29</v>
+        <v>6.2</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.06505999172527926</v>
+        <v>0.06412908564335953</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.74206342</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
         <v>113.12478542</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>116.34</v>
+        <v>117.55</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>101.57</v>
+        <v>102.87</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002349375254002924</v>
+        <v>0.00238995341368149</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.02886952998379255</v>
+        <v>0.04203808752025932</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.04</v>
+        <v>0.28</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>1.17949395</v>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.37810738</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>341.38450299</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1065.6</v>
+        <v>360.19</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>98.89</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.41</v>
+        <v>101.04</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002345674357668963</v>
+        <v>0.002347437473688906</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.52</v>
+        <v>5.53</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.02548285974314895</v>
+        <v>0.05789969636687258</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.37810738</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,55 +3841,55 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.1285649</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>105.04894536</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>23.94</v>
+        <v>1058.66</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>452.96</v>
+        <v>98.89</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.86</v>
+        <v>100.98</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.00233295252652097</v>
+        <v>0.002346043508443247</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>-352.1</v>
+        <v>2.09</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>-0.7773313316849171</v>
+        <v>0.02113459399332591</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-10.4</v>
+        <v>0.26</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0</v>
+        <v>0.1285649</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,55 +3898,55 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>62.95787236</v>
+        <v>105.04894536</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>59.35</v>
+        <v>23.9</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>99.98</v>
+        <v>100.92</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002312597596684182</v>
+        <v>0.002344649543197589</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-6.17</v>
+        <v>-352.04</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.05812529439472444</v>
+        <v>-0.777198869657365</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.09</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>341.38450299</v>
+        <v>147.21071381</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>357.2</v>
+        <v>146.61</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.97</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.00231236629066331</v>
+        <v>0.002315840928120647</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.46</v>
+        <v>-0.17</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.04669668097581404</v>
+        <v>-0.001702553830746119</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.27580753</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>96.717382</v>
+        <v>62.95787236</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>58.85</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.37</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.00230172621370317</v>
+        <v>0.002308638774351411</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.83</v>
+        <v>-6.78</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.02927182457592056</v>
+        <v>-0.06387187941592086</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.27580753</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.35094641</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>137.713206</v>
+        <v>96.717382</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>148.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>92.27</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>99.39</v>
+        <v>99.13</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002298950541452699</v>
+        <v>0.002303062913368777</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>7.12</v>
+        <v>2.45</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.07716484231061017</v>
+        <v>0.02534133223003724</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.35094641</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.90543241</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>10.85229847</v>
+        <v>137.713206</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>10.07</v>
+        <v>147</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>106.96</v>
+        <v>92.27</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>99.16</v>
+        <v>98.75</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002293630502972629</v>
+        <v>0.00229423446681294</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-7.8</v>
+        <v>6.48</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.07292445774121167</v>
+        <v>0.07022867670965645</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.24</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.90543241</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>13.30225117</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>147.21071381</v>
+        <v>10.85229847</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>146.12</v>
+        <v>10</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>106.96</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>99.12</v>
+        <v>98.69</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002292705278889139</v>
+        <v>0.002292840501567282</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-0.73</v>
+        <v>-8.27</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.007310966449674512</v>
+        <v>-0.07731862378459237</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>13.30225117</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4246,25 +4246,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1277.51</v>
+        <v>1269.53</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.78</v>
+        <v>98.39</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002284840874179471</v>
+        <v>0.002285870675338989</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1112611092361346</v>
+        <v>0.106873664079199</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.03</v>
+        <v>0.24</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.10445851</v>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.97307689</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>127.23134407</v>
+        <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>119.02</v>
+        <v>135.45</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>105.36</v>
+        <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.48999999999999</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002278132999574166</v>
+        <v>0.002271931022882404</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-6.87</v>
+        <v>-13.65</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.06520501138952164</v>
+        <v>-0.1224874371859297</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.97307689</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.11796351</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>154.44822659</v>
+        <v>127.23134407</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>136.21</v>
+        <v>117.82</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>111.44</v>
+        <v>105.36</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.11</v>
+        <v>97.72</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002269343370781007</v>
+        <v>0.002270304730095803</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-13.33</v>
+        <v>-7.64</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.1196159368269921</v>
+        <v>-0.07251328777524677</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.19</v>
+        <v>0.17</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.11796351</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>71.15000000000001</v>
+        <v>70</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>97.91</v>
+        <v>96.55</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002264717250363555</v>
+        <v>0.002243122407805462</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-7.07</v>
+        <v>-8.43</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.06734616117355686</v>
+        <v>-0.08030100971613641</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.18</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>1.85908491</v>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>126.99866255</v>
+        <v>127.79185697</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>109.1</v>
+        <v>136.43</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>94.73999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002191393241746943</v>
+        <v>0.002197818537321561</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-15.71</v>
+        <v>6.22</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.1422363060208239</v>
+        <v>0.07037791355510296</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.23</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>127.79185697</v>
+        <v>126.99866255</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>136.6</v>
+        <v>108.12</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>94.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002185841897246001</v>
+        <v>0.002186202160274407</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6.12</v>
+        <v>-16.35</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.06924643584521385</v>
+        <v>-0.1480307831598008</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>234.11448729</v>
+        <v>107.56862839</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>200</v>
+        <v>104.92</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>107.82</v>
+        <v>92.77</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>90.73</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002128246698048726</v>
+        <v>0.002107907778976588</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-15.81</v>
+        <v>-2.04</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1466332776850306</v>
+        <v>-0.02198986741403471</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.12</v>
+        <v>0.25</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4620,17 +4620,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4639,34 +4639,34 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>107.56862839</v>
+        <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>104.28</v>
+        <v>194.61</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>92.77</v>
+        <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>89.97</v>
+        <v>89.73</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002081060269790717</v>
+        <v>0.00208467502488228</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-2.8</v>
+        <v>-18.09</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.0301821709604398</v>
+        <v>-0.167779632721202</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.04</v>
+        <v>0.13</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>56.18</v>
+        <v>56.58</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>76.81</v>
+        <v>77.53</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001776661546322385</v>
+        <v>0.001801235424931719</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33.72</v>
+        <v>-33</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.3050755451008776</v>
+        <v>-0.2985614765222112</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.08</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>105.8</v>
+        <v>104.23</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49.51</v>
+        <v>48.89</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001145196109340207</v>
+        <v>0.001135849347670731</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.03425945268435346</v>
+        <v>0.02130770837685398</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>257.55</v>
+        <v>253.08</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>46.2</v>
+        <v>45.51</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001068633816431378</v>
+        <v>0.001057322638831969</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-5.91</v>
+        <v>-6.6</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1134139320667818</v>
+        <v>-0.1266551525618883</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.01</v>
+        <v>0.14</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,7 +4865,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-14 21:56:25</t>
+          <t>2026-09-15 21:34:04</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43421.37</v>
+        <v>43254.94</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43264.53</v>
+        <v>43076.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37744.56</v>
+        <v>37745.71</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5519.97</v>
+        <v>5331.27</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1462454457013143</v>
+        <v>0.1412417464130361</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>189.84</v>
+        <v>212.11</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109.32</v>
+        <v>108.82</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6996.48</v>
+        <v>6964.48</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>950.71</v>
+        <v>918.71</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.116</v>
+        <v>14.114</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4093.64</v>
+        <v>4093.06</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>662.9299999999999</v>
+        <v>662.35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1536.8</v>
+        <v>1503.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2710.81</v>
+        <v>2652.6</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1514.85</v>
+        <v>1456.64</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>26.81</v>
+        <v>26.42</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2282.21</v>
+        <v>2254.18</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>356.4</v>
+        <v>328.37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>110.05</v>
+        <v>110.23</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2020.74</v>
+        <v>2028.7</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>374.17</v>
+        <v>382.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>494</v>
+        <v>503.33</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1828.34</v>
+        <v>1867.16</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-70.20999999999999</v>
+        <v>-31.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>212.48</v>
+        <v>212.34</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1718.47</v>
+        <v>1721.29</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>465.79</v>
+        <v>468.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>220.5</v>
+        <v>221.52</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1566.9</v>
+        <v>1577.77</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-429.16</v>
+        <v>-418.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>161.59</v>
+        <v>158.94</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1504.99</v>
+        <v>1483.71</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-366.85</v>
+        <v>-388.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,22 +5277,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.42</v>
+        <v>119.38</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1405.7</v>
+        <v>1408.46</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>61.91</v>
+        <v>64.67</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5304,22 +5304,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>43.33</v>
+        <v>41.86</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1373.16</v>
+        <v>1326.76</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>144.82</v>
+        <v>98.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>444.5</v>
+        <v>444.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1224.41</v>
+        <v>1225.96</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>309.92</v>
+        <v>311.47</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>109.35</v>
+        <v>108.9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1109.21</v>
+        <v>1104.64</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>502.02</v>
+        <v>497.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>682.8</v>
+        <v>689.2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1092.48</v>
+        <v>1102.72</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>339.02</v>
+        <v>349.26</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>331.92</v>
+        <v>323.64</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1076.49</v>
+        <v>1052.05</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>434.5</v>
+        <v>410.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>27.282</v>
+        <v>27.102</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1050.12</v>
+        <v>1045.59</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-45.66</v>
+        <v>-50.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>332.77</v>
+        <v>331.6</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>753.73</v>
+        <v>752.8</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>262.68</v>
+        <v>261.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>504.81</v>
+        <v>497.8</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>696.91</v>
+        <v>688.8099999999999</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>162.53</v>
+        <v>154.43</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,22 +5520,22 @@
         <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>1001</v>
+        <v>1002.5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>650.65</v>
+        <v>651.63</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-12.03</v>
+        <v>-11.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>43.66</v>
+        <v>42.5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>646.36</v>
+        <v>630.63</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-221.22</v>
+        <v>-236.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>91.56999999999999</v>
+        <v>89.03</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>623.3200000000001</v>
+        <v>607.4299999999999</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>74.14</v>
+        <v>58.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>327.78</v>
+        <v>324.27</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>565.34</v>
+        <v>560.5700000000001</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>76.06999999999999</v>
+        <v>71.3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.7485</v>
+        <v>3.745</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>524.79</v>
+        <v>524.3</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-13.58</v>
+        <v>-14.07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>347.85</v>
+        <v>344.18</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>514.97</v>
+        <v>510.71</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>107.05</v>
+        <v>102.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,76 +5682,76 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>248.81</v>
+        <v>248.21</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>204.47</v>
+        <v>204.45</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7.95</v>
+        <v>7.93</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>276.54</v>
+        <v>135.7</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>129.83</v>
+        <v>133.46</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>29.98</v>
+        <v>13.73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>131.57</v>
+        <v>276.78</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>129.1</v>
+        <v>130.24</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>30.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,22 +5763,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>212.95</v>
+        <v>217.7</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124.62</v>
+        <v>127.69</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.21</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5790,76 +5790,76 @@
         <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>50.32</v>
+        <v>51.45</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>123.24</v>
+        <v>126.3</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.53</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.42010405</v>
+        <v>3.81488812</v>
       </c>
       <c r="D31" t="n">
-        <v>394.61</v>
+        <v>43.46</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>122.71</v>
+        <v>123.01</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>109.16</v>
+        <v>108.23</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>13.55</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.42010405</v>
       </c>
       <c r="D32" t="n">
-        <v>42.64</v>
+        <v>383.94</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>120.41</v>
+        <v>119.67</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>108.23</v>
+        <v>109.16</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12.18</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5871,22 +5871,22 @@
         <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>575.15</v>
+        <v>574</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.37</v>
+        <v>119.4</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.62</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5898,22 +5898,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D34" t="n">
-        <v>103.09</v>
+        <v>103.02</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.89</v>
+        <v>119.09</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>13.61</v>
+        <v>13.81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5925,22 +5925,22 @@
         <v>2.50421091</v>
       </c>
       <c r="D35" t="n">
-        <v>64.09999999999999</v>
+        <v>63.73</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>118.82</v>
+        <v>118.41</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.01</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5952,211 +5952,211 @@
         <v>0.59183053</v>
       </c>
       <c r="D36" t="n">
-        <v>266.96</v>
+        <v>265.35</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.95</v>
+        <v>116.51</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>17.1</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.7</v>
+        <v>0.62445608</v>
       </c>
       <c r="D37" t="n">
-        <v>223</v>
+        <v>251</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>115.55</v>
+        <v>116.29</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>118.76</v>
+        <v>108.77</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-3.21</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.73400968</v>
       </c>
       <c r="D38" t="n">
-        <v>249.57</v>
+        <v>88.77</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>115.36</v>
+        <v>114.2</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>108.77</v>
+        <v>101.53</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6.59</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>89.23</v>
+        <v>56.43</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>114.53</v>
+        <v>113.34</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>13</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.76637723</v>
       </c>
       <c r="D40" t="n">
-        <v>56.4</v>
+        <v>53.95</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.02</v>
+        <v>110.73</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>107.64</v>
+        <v>112.48</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>5.38</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>93.43000000000001</v>
+        <v>213.09</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>109.97</v>
+        <v>110.67</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>89.66</v>
+        <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>20.31</v>
+        <v>-8.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.59010207</v>
       </c>
       <c r="D42" t="n">
-        <v>53.6</v>
+        <v>93.28</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>109.76</v>
+        <v>110.05</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>112.48</v>
+        <v>89.66</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-2.72</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.61215748</v>
+        <v>11.40066159</v>
       </c>
       <c r="D43" t="n">
-        <v>235.4</v>
+        <v>12.79</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>106.67</v>
+        <v>108.18</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>18.58</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6168,292 +6168,292 @@
         <v>0.42255419</v>
       </c>
       <c r="D44" t="n">
-        <v>340.54</v>
+        <v>342</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>106.52</v>
+        <v>107.22</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>5.13</v>
+        <v>5.83</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.40867246</v>
       </c>
       <c r="D45" t="n">
-        <v>12.6</v>
+        <v>352.1</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>106.33</v>
+        <v>106.76</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>106.15</v>
+        <v>92.83</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.18</v>
+        <v>13.93</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.5550481</v>
       </c>
       <c r="D46" t="n">
-        <v>350.44</v>
+        <v>257.47</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>106.01</v>
+        <v>106.03</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>92.83</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>13.18</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.61215748</v>
       </c>
       <c r="D47" t="n">
-        <v>256.75</v>
+        <v>232.65</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>105.49</v>
+        <v>105.66</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>14.31</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.43583007</v>
       </c>
       <c r="D48" t="n">
-        <v>81.44</v>
+        <v>323.22</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>105.02</v>
+        <v>104.51</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>8.34</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.50675322</v>
       </c>
       <c r="D49" t="n">
-        <v>324.09</v>
+        <v>277.16</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.55</v>
+        <v>104.2</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>104.04</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.51</v>
+        <v>7.52</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.1533463</v>
       </c>
       <c r="D50" t="n">
-        <v>205.16</v>
+        <v>121.47</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>104.02</v>
+        <v>103.94</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>89.53</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>14.56</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="D51" t="n">
-        <v>174.28</v>
+        <v>204.23</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>103.73</v>
+        <v>103.79</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>88.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15.29</v>
+        <v>14.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.80409618</v>
       </c>
       <c r="D52" t="n">
-        <v>269.04</v>
+        <v>173.7</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.32</v>
+        <v>103.63</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>95.94</v>
+        <v>88.44</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>7.38</v>
+        <v>15.19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.51881442</v>
       </c>
       <c r="D53" t="n">
-        <v>121.02</v>
+        <v>268.6</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>103.32</v>
+        <v>103.39</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>89.53</v>
+        <v>95.94</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>13.79</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.74206342</v>
       </c>
       <c r="D54" t="n">
-        <v>274.51</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.97</v>
+        <v>102.88</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>6.29</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6465,238 +6465,238 @@
         <v>1.17949395</v>
       </c>
       <c r="D55" t="n">
-        <v>116.34</v>
+        <v>117.55</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>101.57</v>
+        <v>102.87</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>2.85</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.37810738</v>
       </c>
       <c r="D56" t="n">
-        <v>1065.6</v>
+        <v>360.19</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>101.41</v>
+        <v>101.04</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>98.89</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2.52</v>
+        <v>5.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.1285649</v>
       </c>
       <c r="D57" t="n">
-        <v>23.94</v>
+        <v>1058.66</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.86</v>
+        <v>100.98</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>452.96</v>
+        <v>98.89</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>-352.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="D58" t="n">
-        <v>59.35</v>
+        <v>23.9</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>99.98</v>
+        <v>100.92</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-6.17</v>
+        <v>-352.04</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D59" t="n">
-        <v>357.2</v>
+        <v>146.61</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.97</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4.46</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.27580753</v>
       </c>
       <c r="D60" t="n">
-        <v>99.51000000000001</v>
+        <v>58.85</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.37</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2.83</v>
+        <v>-6.78</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.35094641</v>
       </c>
       <c r="D61" t="n">
-        <v>148.3</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>99.39</v>
+        <v>99.13</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>92.27</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>7.12</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.90543241</v>
       </c>
       <c r="D62" t="n">
-        <v>10.07</v>
+        <v>147</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>99.16</v>
+        <v>98.75</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>106.96</v>
+        <v>92.27</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-7.8</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>13.30225117</v>
       </c>
       <c r="D63" t="n">
-        <v>146.12</v>
+        <v>10</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>99.12</v>
+        <v>98.69</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>106.96</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-0.73</v>
+        <v>-8.27</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6708,76 +6708,76 @@
         <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>1277.51</v>
+        <v>1269.53</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.78</v>
+        <v>98.39</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>119.02</v>
+        <v>135.45</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.48999999999999</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>105.36</v>
+        <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-6.87</v>
+        <v>-13.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.11796351</v>
       </c>
       <c r="D66" t="n">
-        <v>136.21</v>
+        <v>117.82</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.11</v>
+        <v>97.72</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>111.44</v>
+        <v>105.36</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-13.33</v>
+        <v>-7.64</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6789,130 +6789,130 @@
         <v>1.85908491</v>
       </c>
       <c r="D67" t="n">
-        <v>71.15000000000001</v>
+        <v>70</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>97.91</v>
+        <v>96.55</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-7.07</v>
+        <v>-8.43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="D68" t="n">
-        <v>109.1</v>
+        <v>136.43</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>94.73999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-15.71</v>
+        <v>6.22</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="D69" t="n">
-        <v>136.6</v>
+        <v>108.12</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>94.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>6.12</v>
+        <v>-16.35</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="D70" t="n">
-        <v>200</v>
+        <v>104.92</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>92.01000000000001</v>
+        <v>90.73</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>107.82</v>
+        <v>92.77</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-15.81</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>104.28</v>
+        <v>194.61</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>89.97</v>
+        <v>89.73</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>92.77</v>
+        <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-2.8</v>
+        <v>-18.09</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>56.18</v>
+        <v>56.58</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>76.81</v>
+        <v>77.53</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33.72</v>
+        <v>-33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>105.8</v>
+        <v>104.23</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>49.51</v>
+        <v>48.89</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.64</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>257.55</v>
+        <v>253.08</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>46.2</v>
+        <v>45.51</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-5.91</v>
+        <v>-6.6</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43254.94</v>
+        <v>43564.51</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43076.98</v>
+        <v>43386.53</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37745.71</v>
+        <v>37746.75</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5331.27</v>
+        <v>5639.78</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1412417464130361</v>
+        <v>0.1494110088948055</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>177.96</v>
+        <v>177.98</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>34.15</v>
+        <v>35.19</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-15 21:34:04</t>
+          <t>2026-09-16 21:29:34</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>108.82</v>
+        <v>109.52</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6964.48</v>
+        <v>7009.28</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1618040512347279</v>
+        <v>0.1616827808604207</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>918.71</v>
+        <v>963.51</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1519591383727796</v>
+        <v>0.1593692780241392</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.114</v>
+        <v>14.454</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4093.06</v>
+        <v>4191.66</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09509305647324934</v>
+        <v>0.09668885323762083</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>662.35</v>
+        <v>760.95</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1930649923776711</v>
+        <v>0.2218053988824471</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1503.8</v>
+        <v>1507.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2652.6</v>
+        <v>2659.66</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06162720351056207</v>
+        <v>0.06135027063310731</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1456.64</v>
+        <v>1463.7</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.217967156092177</v>
+        <v>1.22387036355731</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.42</v>
+        <v>25.91</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2254.18</v>
+        <v>2223.54</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05237080962430778</v>
+        <v>0.05129030807078327</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>328.37</v>
+        <v>297.73</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1705100710869712</v>
+        <v>0.1545998826467824</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-5.24</v>
+        <v>5.95</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>110.23</v>
+        <v>107.96</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2028.7</v>
+        <v>1998.48</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04713228823112316</v>
+        <v>0.04609885807014893</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>382.13</v>
+        <v>351.91</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2320763769533029</v>
+        <v>0.2137230728119667</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-7.5</v>
+        <v>2.03</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>503.33</v>
+        <v>513.7</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1867.16</v>
+        <v>1916.72</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.0433792691347286</v>
+        <v>0.04421290342671224</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-31.39</v>
+        <v>18.17</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01653367043269864</v>
+        <v>0.009570461668115142</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-6.76</v>
+        <v>4.25</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>212.34</v>
+        <v>214.43</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1721.29</v>
+        <v>1748.35</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.03999030729499185</v>
+        <v>0.04032911938420444</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>468.61</v>
+        <v>495.67</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3740859597023981</v>
+        <v>0.3956876456876457</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-35.97</v>
+        <v>-28.89</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>221.52</v>
+        <v>229.93</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1577.77</v>
+        <v>1647.2</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03665594242737674</v>
+        <v>0.03799589638782942</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-418.29</v>
+        <v>-348.86</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.2095578289229783</v>
+        <v>-0.1747743053816018</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-12.08</v>
+        <v>-0.54</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>158.94</v>
+        <v>158.4</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1483.71</v>
+        <v>1487.28</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.0344706695772661</v>
+        <v>0.03430702815668463</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-388.13</v>
+        <v>-384.56</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2073521241131721</v>
+        <v>-0.2054449098213523</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-83.94</v>
+        <v>-73.53</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.38</v>
+        <v>119.44</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1408.46</v>
+        <v>1417.37</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.0327224048316694</v>
+        <v>0.03269441698835465</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>64.67</v>
+        <v>73.58</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04812507906741381</v>
+        <v>0.05475557936880018</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-10.13</v>
+        <v>-2.37</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>41.86</v>
+        <v>41.76</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1326.76</v>
+        <v>1319.87</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03082428882216442</v>
+        <v>0.03044538839570447</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>98.42</v>
+        <v>91.53</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.0801243955256688</v>
+        <v>0.07451519937476594</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-54.03</v>
+        <v>-57.33</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>444.6</v>
+        <v>449.2</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1225.96</v>
+        <v>1238.47</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02848242720945815</v>
+        <v>0.02856773785784063</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>311.47</v>
+        <v>323.98</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.340594210980984</v>
+        <v>0.3542739669105184</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-2.58</v>
+        <v>-2.71</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>108.9</v>
+        <v>111.25</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1104.64</v>
+        <v>1128.48</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02566382948273667</v>
+        <v>0.02603060293573199</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>497.45</v>
+        <v>521.29</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8192657981850821</v>
+        <v>0.8585286318944645</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>689.2</v>
+        <v>702.2</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1102.72</v>
+        <v>1123.52</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0256192225948756</v>
+        <v>0.02591619081450589</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>349.26</v>
+        <v>370.06</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4635415284155761</v>
+        <v>0.4911475061715286</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>323.64</v>
+        <v>332</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1052.05</v>
+        <v>1085.51</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.024442018944917</v>
+        <v>0.02503941566777119</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>410.06</v>
+        <v>443.52</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6387326905403511</v>
+        <v>0.6908518824280752</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-31.28</v>
+        <v>-27.73</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>27.102</v>
+        <v>27.285</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1045.59</v>
+        <v>1058.78</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02429193535346777</v>
+        <v>0.02442283582898618</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-50.19</v>
+        <v>-37</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.04580298965120736</v>
+        <v>-0.0337659019146179</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>5.15</v>
+        <v>11.57</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>331.6</v>
+        <v>332.49</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>752.8</v>
+        <v>759.22</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01748961728219525</v>
+        <v>0.01751289731396785</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>261.75</v>
+        <v>268.17</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5330414418083698</v>
+        <v>0.5461154668567356</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-19.14</v>
+        <v>-16.39</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>497.8</v>
+        <v>490.77</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>688.8099999999999</v>
+        <v>683.04</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01600295334770047</v>
+        <v>0.01575565630691052</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>154.43</v>
+        <v>148.66</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2889891088738351</v>
+        <v>0.2781915490849208</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-23.15</v>
+        <v>-20.17</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1002.5</v>
+        <v>1011</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>651.63</v>
+        <v>657.15</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01513915955047409</v>
+        <v>0.01515845271446218</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-11.05</v>
+        <v>-5.53</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.01667471479447094</v>
+        <v>-0.008344902517051972</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>57.84</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>42.5</v>
+        <v>41.87</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>630.63</v>
+        <v>624.9</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01465127171449361</v>
+        <v>0.01441454325689327</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-236.95</v>
+        <v>-242.68</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.2731160238825238</v>
+        <v>-0.2797206021346735</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-9.33</v>
+        <v>-4.33</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>89.03</v>
+        <v>88.44</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>607.4299999999999</v>
+        <v>606.91</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01411227181950566</v>
+        <v>0.01399956864784941</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>58.25</v>
+        <v>57.73</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1060672275028224</v>
+        <v>0.1051203612658873</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-22.45</v>
+        <v>-19.39</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>324.27</v>
+        <v>313.43</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>560.5700000000001</v>
+        <v>544.98</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01302358496264638</v>
+        <v>0.01257103181971787</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>71.3</v>
+        <v>55.71</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1457273080303309</v>
+        <v>0.1138635109448771</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-30.09</v>
+        <v>-27.42</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.745</v>
+        <v>3.7585</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>524.3</v>
+        <v>526.1900000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01218093297164582</v>
+        <v>0.01213760364273431</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-14.07</v>
+        <v>-12.18</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.0261344428552854</v>
+        <v>-0.02262384605382915</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>344.18</v>
+        <v>343.51</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>510.71</v>
+        <v>512.6799999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01186519984350417</v>
+        <v>0.01182596901415273</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>102.79</v>
+        <v>104.76</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2519856834673466</v>
+        <v>0.256815061776819</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-8.130000000000001</v>
+        <v>-5.8</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>248.21</v>
+        <v>237.9</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>204.45</v>
+        <v>197.1</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004749936574581322</v>
+        <v>0.004546497801142045</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>7.93</v>
+        <v>0.58</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.04035212700997354</v>
+        <v>0.002951353551801343</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.41</v>
+        <v>-0.27</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>135.7</v>
+        <v>131.99</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>133.46</v>
+        <v>130.57</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.00310064336142638</v>
+        <v>0.003011852957357265</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>13.73</v>
+        <v>10.84</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.114674684707258</v>
+        <v>0.09053704167710681</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2194,25 +2194,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>276.78</v>
+        <v>270.74</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>130.24</v>
+        <v>128.14</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.003025833893242707</v>
+        <v>0.002955800244740445</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>30.39</v>
+        <v>28.29</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.3043565348022033</v>
+        <v>0.2833249874812218</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.27</v>
+        <v>0.85</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2251,25 +2251,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>217.7</v>
+        <v>211.9</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>127.69</v>
+        <v>125.01</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002966590370302221</v>
+        <v>0.002883600660176394</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>17.28</v>
+        <v>14.6</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1565075627207681</v>
+        <v>0.1322343990580563</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.05</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.7905852</v>
@@ -2308,25 +2308,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>51.45</v>
+        <v>50.07</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>126.3</v>
+        <v>123.62</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002934296842111132</v>
+        <v>0.002851537585881176</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>13.59</v>
+        <v>10.91</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1205749268033005</v>
+        <v>0.09679708987667465</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.04</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>3.30858696</v>
@@ -2365,25 +2365,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>43.46</v>
+        <v>42.85</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>123.01</v>
+        <v>121.99</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002857861081140859</v>
+        <v>0.002813938441204049</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>14.78</v>
+        <v>13.76</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1365610274415596</v>
+        <v>0.1271366534232653</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>3.81488812</v>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>350.55601106</v>
+        <v>57.56703616</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>383.94</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.67</v>
+        <v>119.73</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002780263682465869</v>
+        <v>0.002761807111774415</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>10.51</v>
+        <v>12.92</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.09628068889703188</v>
+        <v>0.120962456698811</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.1</v>
+        <v>0.77</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>1.55804584</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>509.16500577</v>
+        <v>91.20399179</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>574</v>
+        <v>102.16</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>105.75</v>
+        <v>105.28</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.4</v>
+        <v>118.78</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002773990838860406</v>
+        <v>0.002739893499846028</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.65</v>
+        <v>13.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1290780141843972</v>
+        <v>0.1282294832826748</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.16</v>
+        <v>0.76</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>1.55804584</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>91.20399179</v>
+        <v>228.00445932</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>103.02</v>
+        <v>268.68</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>119.09</v>
+        <v>118.66</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.00276678868509117</v>
+        <v>0.002737125464655074</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.81</v>
+        <v>18.81</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1311740121580547</v>
+        <v>0.1883825738607912</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.15</v>
+        <v>0.85</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>57.56703616</v>
+        <v>509.16500577</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>63.73</v>
+        <v>566.42</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>106.81</v>
+        <v>105.75</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.41</v>
+        <v>118.51</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.00275099041230704</v>
+        <v>0.002733665420666382</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>11.6</v>
+        <v>12.76</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1086040632899541</v>
+        <v>0.120661938534279</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.15</v>
+        <v>0.78</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.42010405</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>228.00445932</v>
+        <v>350.55601106</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>265.35</v>
+        <v>375.82</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>109.16</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.51</v>
+        <v>117.82</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002706848179527855</v>
+        <v>0.002717749218318396</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>16.66</v>
+        <v>8.66</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1668502754131197</v>
+        <v>0.07933308904360573</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.26</v>
+        <v>0.74</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.42010405</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
         <v>235.02053179</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>251</v>
+        <v>245.51</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.29</v>
+        <v>114.41</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002701736973627107</v>
+        <v>0.002639090884975451</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>7.52</v>
+        <v>5.64</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.06913671049002482</v>
+        <v>0.05185253286751862</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.62445608</v>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>88.77</v>
+        <v>56.49</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.2</v>
+        <v>114.12</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002653180517570003</v>
+        <v>0.002632401466597312</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>12.67</v>
+        <v>6.48</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.124790702255491</v>
+        <v>0.06020066889632107</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.24</v>
+        <v>0.76</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>53.65641702</v>
+        <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>56.43</v>
+        <v>87.95</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.34</v>
+        <v>113.81</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002633200349048897</v>
+        <v>0.002625250709020681</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>5.7</v>
+        <v>12.28</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.05295429208472687</v>
+        <v>0.1209494730621491</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.13</v>
+        <v>0.84</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,55 +2872,55 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.7</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>54.82621761</v>
+        <v>225.62857143</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>53.95</v>
+        <v>214.95</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>112.48</v>
+        <v>118.76</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>110.73</v>
+        <v>112.28</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002572562860862753</v>
+        <v>0.002589958260336016</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-1.75</v>
+        <v>-6.48</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.01555832147937411</v>
+        <v>-0.05456382620410913</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.9</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.7</v>
+        <v>1.59010207</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>225.62857143</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>213.09</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>118.76</v>
+        <v>89.66</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.67</v>
+        <v>110.31</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002571168895617094</v>
+        <v>0.002544516349284521</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-8.09</v>
+        <v>20.65</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.06812057931963623</v>
+        <v>0.230314521525764</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-1.58</v>
+        <v>0.76</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0</v>
+        <v>1.59010207</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.5550481</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>221.99877812</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>93.28</v>
+        <v>263.03</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>89.66</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.05</v>
+        <v>108.95</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002556764588078623</v>
+        <v>0.002513145283787042</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>20.39</v>
+        <v>17.77</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.2274146776712023</v>
+        <v>0.1948892300943189</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.24</v>
+        <v>0.77</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.5550481</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>12.56856884</v>
+        <v>54.82621761</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.79</v>
+        <v>52.34</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>106.15</v>
+        <v>112.48</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.18</v>
+        <v>108.05</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002513319337922267</v>
+        <v>0.002492385019854886</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.03</v>
+        <v>-4.43</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.0191238813000471</v>
+        <v>-0.03938477951635846</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.16</v>
+        <v>0.7</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3106,25 +3106,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>342</v>
+        <v>341.35</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.22</v>
+        <v>107.64</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002491015893991731</v>
+        <v>0.002482927566285793</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.0575007397179209</v>
+        <v>0.06164316007495808</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.21</v>
+        <v>0.8</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>0.42255419</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.61215748</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>306.99401668</v>
+        <v>194.45976548</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>352.1</v>
+        <v>234.91</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>92.83</v>
+        <v>88.09</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>106.76</v>
+        <v>107.31</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002480328827108349</v>
+        <v>0.00247531546951067</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>13.93</v>
+        <v>19.22</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1500592480879026</v>
+        <v>0.2181859461913951</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.25</v>
+        <v>0.74</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.61215748</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>221.99877812</v>
+        <v>12.56856884</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>257.47</v>
+        <v>12.54</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>106.03</v>
+        <v>106.69</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002463368916619504</v>
+        <v>0.002461013954357407</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>14.85</v>
+        <v>0.54</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.162864663303356</v>
+        <v>0.005087140838436175</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.24</v>
+        <v>0.78</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>194.45976548</v>
+        <v>306.99401668</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>232.65</v>
+        <v>348.31</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>105.66</v>
+        <v>106.22</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.00245477279760461</v>
+        <v>0.002450172483192836</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>17.57</v>
+        <v>13.39</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1994551027358383</v>
+        <v>0.1442421630938274</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.23</v>
+        <v>0.79</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3334,25 +3334,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>323.22</v>
+        <v>321.46</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>104.51</v>
+        <v>104.55</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002428055130396156</v>
+        <v>0.002411650660118726</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.00451749327181853</v>
+        <v>0.004901960784313725</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.19</v>
+        <v>0.8</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>0.43583007</v>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>257.81779936</v>
+        <v>104.90344487</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>277.16</v>
+        <v>120.6</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.2</v>
+        <v>103.8</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.00242085297662692</v>
+        <v>0.002394350440175263</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>7.52</v>
+        <v>14.27</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.07778237484484897</v>
+        <v>0.1593879146654752</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.25</v>
+        <v>0.76</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>104.90344487</v>
+        <v>257.81779936</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>121.47</v>
+        <v>274.08</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>103.94</v>
+        <v>103.65</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.0024148124605624</v>
+        <v>0.002390890396186571</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>14.41</v>
+        <v>6.97</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1609516363230202</v>
+        <v>0.07209350434422837</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.23</v>
+        <v>0.82</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.80409618</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>176.50746647</v>
+        <v>148.63893521</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>204.23</v>
+        <v>172.6</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103.79</v>
+        <v>103.57</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002411327547448254</v>
+        <v>0.002389045039392601</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>14.33</v>
+        <v>15.13</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1601833221551532</v>
+        <v>0.1710764360018092</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.24</v>
+        <v>0.75</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.80409618</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.51881442</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>148.63893521</v>
+        <v>249.91595261</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>173.7</v>
+        <v>267.33</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>88.44</v>
+        <v>95.94</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>103.63</v>
+        <v>103.5</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002407610306793164</v>
+        <v>0.002387430352197878</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>15.19</v>
+        <v>7.56</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1717548620533695</v>
+        <v>0.07879924953095685</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.24</v>
+        <v>0.82</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.51881442</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>249.91595261</v>
+        <v>176.50746647</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>268.6</v>
+        <v>202.29</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>95.94</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>103.39</v>
+        <v>103.4</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.00240203444581053</v>
+        <v>0.002385123656205416</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>7.45</v>
+        <v>13.94</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.07765269960391911</v>
+        <v>0.1558238318801699</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.26</v>
+        <v>0.76</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.37810738</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>74.99726962</v>
+        <v>341.38450299</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>79.59999999999999</v>
+        <v>365</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.88</v>
+        <v>102.99</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002390185741222433</v>
+        <v>0.002375666202636323</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>6.2</v>
+        <v>7.48</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.06412908564335953</v>
+        <v>0.07831640665898859</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.37810738</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
         <v>113.12478542</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>117.55</v>
+        <v>116.81</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.87</v>
+        <v>102.81</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.00238995341368149</v>
+        <v>0.002371514149849892</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.15</v>
+        <v>4.09</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.04203808752025932</v>
+        <v>0.04143030794165316</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.28</v>
+        <v>0.85</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>1.17949395</v>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.74206342</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>341.38450299</v>
+        <v>74.99726962</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>360.19</v>
+        <v>78.8</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.04</v>
+        <v>102.44</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002347437473688906</v>
+        <v>0.002362979374677783</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>5.53</v>
+        <v>5.76</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.05789969636687258</v>
+        <v>0.05957798924286305</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.25</v>
+        <v>0.82</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.74206342</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>147.21071381</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1058.66</v>
+        <v>147.34</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>98.89</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.98</v>
+        <v>100.76</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002346043508443247</v>
+        <v>0.002324226882004427</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>2.09</v>
+        <v>0.91</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.02113459399332591</v>
+        <v>0.009113670505758639</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.26</v>
+        <v>0.82</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,55 +3898,55 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.35094641</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>105.04894536</v>
+        <v>96.717382</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>23.9</v>
+        <v>98.8</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>452.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.92</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002344649543197589</v>
+        <v>0.002297469208491871</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-352.04</v>
+        <v>2.92</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.777198869657365</v>
+        <v>0.0302027306578403</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-9.390000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0</v>
+        <v>1.35094641</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.1285649</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>147.21071381</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>146.61</v>
+        <v>1037.24</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.68000000000001</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002315840928120647</v>
+        <v>0.002295393182098655</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.62</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.001702553830746119</v>
+        <v>0.006269592476489028</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.24</v>
+        <v>0.83</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.1285649</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2.27580753</v>
+        <v>13.30225117</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>62.95787236</v>
+        <v>10.85229847</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>58.85</v>
+        <v>10.01</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>106.15</v>
+        <v>106.96</v>
       </c>
       <c r="I60" s="2" t="n">
         <v>99.37</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002308638774351411</v>
+        <v>0.002292163807709209</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-6.78</v>
+        <v>-7.59</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.06387187941592086</v>
+        <v>-0.07096110695587135</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.16</v>
+        <v>0.77</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>2.27580753</v>
+        <v>13.30225117</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.90543241</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>96.717382</v>
+        <v>137.713206</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>98.90000000000001</v>
+        <v>145.83</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>99.13</v>
+        <v>98.53</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002303062913368777</v>
+        <v>0.002272787561372531</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.45</v>
+        <v>6.26</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.02534133223003724</v>
+        <v>0.0678443697843286</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.26</v>
+        <v>0.78</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.90543241</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.11796351</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>137.713206</v>
+        <v>127.23134407</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>147</v>
+        <v>117.97</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>92.27</v>
+        <v>105.36</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98.75</v>
+        <v>98.42</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.00229423446681294</v>
+        <v>0.002270250195780823</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>6.48</v>
+        <v>-6.94</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.07022867670965645</v>
+        <v>-0.0658694001518603</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.24</v>
+        <v>0.79</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.11796351</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>10.85229847</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>10</v>
+        <v>1258.26</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>106.96</v>
+        <v>88.89</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.69</v>
+        <v>98.08</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002292840501567282</v>
+        <v>0.002262407429406453</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-8.27</v>
+        <v>9.19</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.07731862378459237</v>
+        <v>0.1033862076724041</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.14</v>
+        <v>0.75</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.97307689</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>154.44822659</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1269.53</v>
+        <v>134.71</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>88.89</v>
+        <v>111.44</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002285870675338989</v>
+        <v>0.002256410019826052</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>9.5</v>
+        <v>-13.62</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.106873664079199</v>
+        <v>-0.1222182340272792</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.97307689</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,55 +4297,55 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>5.691347</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>154.44822659</v>
+        <v>105.04894536</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>135.45</v>
+        <v>23.03</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>111.44</v>
+        <v>452.96</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>97.79000000000001</v>
+        <v>97.81</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002271931022882404</v>
+        <v>0.002256179350226806</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-13.65</v>
+        <v>-355.15</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.1224874371859297</v>
+        <v>-0.7840648180854821</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-6.81</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>2.27580753</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>127.23134407</v>
+        <v>62.95787236</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>117.82</v>
+        <v>57.35</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>105.36</v>
+        <v>106.15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>97.72</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002270304730095803</v>
+        <v>0.002246721896657713</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-7.64</v>
+        <v>-8.75</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.07251328777524677</v>
+        <v>-0.08243052284503061</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.17</v>
+        <v>0.77</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>2.27580753</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>70</v>
+        <v>68.75</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>96.55</v>
+        <v>95.38</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002243122407805462</v>
+        <v>0.002200126637609986</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-8.43</v>
+        <v>-9.6</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.08030100971613641</v>
+        <v>-0.09144598971232615</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.18</v>
+        <v>0.79</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>1.85908491</v>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>127.79185697</v>
+        <v>126.99866255</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>136.43</v>
+        <v>107.52</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002197818537321561</v>
+        <v>0.002171062268104969</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>6.22</v>
+        <v>-16.33</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.07037791355510296</v>
+        <v>-0.1478497057492078</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.23</v>
+        <v>0.72</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>126.99866255</v>
+        <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>108.12</v>
+        <v>133.05</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002186202160274407</v>
+        <v>0.002140383211405228</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-16.35</v>
+        <v>4.41</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1480307831598008</v>
+        <v>0.04989816700610998</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.08</v>
+        <v>0.74</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4588,25 +4588,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>104.92</v>
+        <v>104.98</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>90.73</v>
+        <v>91.31</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002107907778976588</v>
+        <v>0.002106244110716794</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-2.04</v>
+        <v>-1.46</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.02198986741403471</v>
+        <v>-0.01573784628651504</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.25</v>
+        <v>0.79</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>1.16558147</v>
@@ -4645,25 +4645,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>194.61</v>
+        <v>194.66</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>89.73</v>
+        <v>90.28</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.00208467502488228</v>
+        <v>0.002082485141994439</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-18.09</v>
+        <v>-17.54</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.167779632721202</v>
+        <v>-0.1626785383045817</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.13</v>
+        <v>0.76</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>0.6214908</v>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>56.58</v>
+        <v>56.46</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.53</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001801235424931719</v>
+        <v>0.001795070821333709</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33</v>
+        <v>-32.71</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2985614765222112</v>
+        <v>-0.2959377544558038</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.08</v>
+        <v>0.73</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>104.23</v>
+        <v>102.4</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>48.89</v>
+        <v>48.31</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001135849347670731</v>
+        <v>0.001114364833958256</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.02130770837685398</v>
+        <v>0.009191560476289953</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>253.08</v>
+        <v>249.19</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.51</v>
+        <v>45.07</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001057322638831969</v>
+        <v>0.001039627883802496</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.6</v>
+        <v>-7.04</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1266551525618883</v>
+        <v>-0.1350988293993475</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-15 21:34:04</t>
+          <t>2026-09-16 21:29:34</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43254.94</v>
+        <v>43564.51</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43076.98</v>
+        <v>43386.53</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37745.71</v>
+        <v>37746.75</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5331.27</v>
+        <v>5639.78</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1412417464130361</v>
+        <v>0.1494110088948055</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>212.11</v>
+        <v>213.17</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>108.82</v>
+        <v>109.52</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6964.48</v>
+        <v>7009.28</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>918.71</v>
+        <v>963.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.114</v>
+        <v>14.454</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4093.06</v>
+        <v>4191.66</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>662.35</v>
+        <v>760.95</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1503.8</v>
+        <v>1507.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2652.6</v>
+        <v>2659.66</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1456.64</v>
+        <v>1463.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>26.42</v>
+        <v>25.91</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2254.18</v>
+        <v>2223.54</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>328.37</v>
+        <v>297.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>110.23</v>
+        <v>107.96</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2028.7</v>
+        <v>1998.48</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>382.13</v>
+        <v>351.91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>503.33</v>
+        <v>513.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1867.16</v>
+        <v>1916.72</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-31.39</v>
+        <v>18.17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>212.34</v>
+        <v>214.43</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1721.29</v>
+        <v>1748.35</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>468.61</v>
+        <v>495.67</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>221.52</v>
+        <v>229.93</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1577.77</v>
+        <v>1647.2</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-418.29</v>
+        <v>-348.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>158.94</v>
+        <v>158.4</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1483.71</v>
+        <v>1487.28</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-388.13</v>
+        <v>-384.56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,22 +5277,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.38</v>
+        <v>119.44</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1408.46</v>
+        <v>1417.37</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>64.67</v>
+        <v>73.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5304,22 +5304,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>41.86</v>
+        <v>41.76</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1326.76</v>
+        <v>1319.87</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>98.42</v>
+        <v>91.53</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>444.6</v>
+        <v>449.2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1225.96</v>
+        <v>1238.47</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>311.47</v>
+        <v>323.98</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>108.9</v>
+        <v>111.25</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1104.64</v>
+        <v>1128.48</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>497.45</v>
+        <v>521.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>689.2</v>
+        <v>702.2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1102.72</v>
+        <v>1123.52</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>349.26</v>
+        <v>370.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>323.64</v>
+        <v>332</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1052.05</v>
+        <v>1085.51</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>410.06</v>
+        <v>443.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>27.102</v>
+        <v>27.285</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1045.59</v>
+        <v>1058.78</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-50.19</v>
+        <v>-37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>331.6</v>
+        <v>332.49</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>752.8</v>
+        <v>759.22</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>261.75</v>
+        <v>268.17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>497.8</v>
+        <v>490.77</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>688.8099999999999</v>
+        <v>683.04</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>154.43</v>
+        <v>148.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,22 +5520,22 @@
         <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>1002.5</v>
+        <v>1011</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>651.63</v>
+        <v>657.15</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-11.05</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>42.5</v>
+        <v>41.87</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>630.63</v>
+        <v>624.9</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-236.95</v>
+        <v>-242.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>89.03</v>
+        <v>88.44</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>607.4299999999999</v>
+        <v>606.91</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>58.25</v>
+        <v>57.73</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>324.27</v>
+        <v>313.43</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>560.5700000000001</v>
+        <v>544.98</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>71.3</v>
+        <v>55.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.745</v>
+        <v>3.7585</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>524.3</v>
+        <v>526.1900000000001</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-14.07</v>
+        <v>-12.18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>344.18</v>
+        <v>343.51</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>510.71</v>
+        <v>512.6799999999999</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>102.79</v>
+        <v>104.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>248.21</v>
+        <v>237.9</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>204.45</v>
+        <v>197.1</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>7.93</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,22 +5709,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>135.7</v>
+        <v>131.99</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>133.46</v>
+        <v>130.57</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>13.73</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5736,22 +5736,22 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>276.78</v>
+        <v>270.74</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>130.24</v>
+        <v>128.14</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>30.39</v>
+        <v>28.29</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,22 +5763,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>217.7</v>
+        <v>211.9</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>127.69</v>
+        <v>125.01</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>17.28</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5790,22 +5790,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>51.45</v>
+        <v>50.07</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>126.3</v>
+        <v>123.62</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>13.59</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5817,157 +5817,157 @@
         <v>3.81488812</v>
       </c>
       <c r="D31" t="n">
-        <v>43.46</v>
+        <v>42.85</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>123.01</v>
+        <v>121.99</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>14.78</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="D32" t="n">
-        <v>383.94</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.67</v>
+        <v>119.73</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.51</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>1.55804584</v>
       </c>
       <c r="D33" t="n">
-        <v>574</v>
+        <v>102.16</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.4</v>
+        <v>118.78</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>105.75</v>
+        <v>105.28</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.65</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="D34" t="n">
-        <v>103.02</v>
+        <v>268.68</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>119.09</v>
+        <v>118.66</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>13.81</v>
+        <v>18.81</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="D35" t="n">
-        <v>63.73</v>
+        <v>566.42</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>118.41</v>
+        <v>118.51</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>106.81</v>
+        <v>105.75</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>11.6</v>
+        <v>12.76</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.42010405</v>
       </c>
       <c r="D36" t="n">
-        <v>265.35</v>
+        <v>375.82</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.51</v>
+        <v>117.82</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>109.16</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>16.66</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,184 +5979,184 @@
         <v>0.62445608</v>
       </c>
       <c r="D37" t="n">
-        <v>251</v>
+        <v>245.51</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.29</v>
+        <v>114.41</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7.52</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D38" t="n">
-        <v>88.77</v>
+        <v>56.49</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.2</v>
+        <v>114.12</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>12.67</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>56.43</v>
+        <v>87.95</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.34</v>
+        <v>113.81</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>5.7</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.7</v>
       </c>
       <c r="D40" t="n">
-        <v>53.95</v>
+        <v>214.95</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>110.73</v>
+        <v>112.28</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>112.48</v>
+        <v>118.76</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-1.75</v>
+        <v>-6.48</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.7</v>
+        <v>1.59010207</v>
       </c>
       <c r="D41" t="n">
-        <v>213.09</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.67</v>
+        <v>110.31</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>118.76</v>
+        <v>89.66</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-8.09</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.5550481</v>
       </c>
       <c r="D42" t="n">
-        <v>93.28</v>
+        <v>263.03</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.05</v>
+        <v>108.95</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>89.66</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>20.39</v>
+        <v>17.77</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="D43" t="n">
-        <v>12.79</v>
+        <v>52.34</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.18</v>
+        <v>108.05</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>106.15</v>
+        <v>112.48</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2.03</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6168,103 +6168,103 @@
         <v>0.42255419</v>
       </c>
       <c r="D44" t="n">
-        <v>342</v>
+        <v>341.35</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.22</v>
+        <v>107.64</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>5.83</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.61215748</v>
       </c>
       <c r="D45" t="n">
-        <v>352.1</v>
+        <v>234.91</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>106.76</v>
+        <v>107.31</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.83</v>
+        <v>88.09</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>13.93</v>
+        <v>19.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="D46" t="n">
-        <v>257.47</v>
+        <v>12.54</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>106.03</v>
+        <v>106.69</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>14.85</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="D47" t="n">
-        <v>232.65</v>
+        <v>348.31</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>105.66</v>
+        <v>106.22</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>17.57</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6276,184 +6276,184 @@
         <v>0.43583007</v>
       </c>
       <c r="D48" t="n">
-        <v>323.22</v>
+        <v>321.46</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104.51</v>
+        <v>104.55</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.47</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="D49" t="n">
-        <v>277.16</v>
+        <v>120.6</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.2</v>
+        <v>103.8</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>7.52</v>
+        <v>14.27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="D50" t="n">
-        <v>121.47</v>
+        <v>274.08</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>103.94</v>
+        <v>103.65</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>14.41</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.80409618</v>
       </c>
       <c r="D51" t="n">
-        <v>204.23</v>
+        <v>172.6</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>103.79</v>
+        <v>103.57</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>14.33</v>
+        <v>15.13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.51881442</v>
       </c>
       <c r="D52" t="n">
-        <v>173.7</v>
+        <v>267.33</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.63</v>
+        <v>103.5</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>88.44</v>
+        <v>95.94</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>15.19</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="D53" t="n">
-        <v>268.6</v>
+        <v>202.29</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>103.39</v>
+        <v>103.4</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>95.94</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7.45</v>
+        <v>13.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.37810738</v>
       </c>
       <c r="D54" t="n">
-        <v>79.59999999999999</v>
+        <v>365</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.88</v>
+        <v>102.99</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>6.2</v>
+        <v>7.48</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6465,319 +6465,319 @@
         <v>1.17949395</v>
       </c>
       <c r="D55" t="n">
-        <v>117.55</v>
+        <v>116.81</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.87</v>
+        <v>102.81</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>4.15</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.74206342</v>
       </c>
       <c r="D56" t="n">
-        <v>360.19</v>
+        <v>78.8</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>101.04</v>
+        <v>102.44</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5.53</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D57" t="n">
-        <v>1058.66</v>
+        <v>147.34</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.98</v>
+        <v>100.76</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>98.89</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>2.09</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.35094641</v>
       </c>
       <c r="D58" t="n">
-        <v>23.9</v>
+        <v>98.8</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.92</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>452.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-352.04</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.1285649</v>
       </c>
       <c r="D59" t="n">
-        <v>146.61</v>
+        <v>1037.24</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.68000000000001</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>2.27580753</v>
+        <v>13.30225117</v>
       </c>
       <c r="D60" t="n">
-        <v>58.85</v>
+        <v>10.01</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>99.37</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>106.15</v>
+        <v>106.96</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-6.78</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.90543241</v>
       </c>
       <c r="D61" t="n">
-        <v>98.90000000000001</v>
+        <v>145.83</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>99.13</v>
+        <v>98.53</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2.45</v>
+        <v>6.26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.11796351</v>
       </c>
       <c r="D62" t="n">
-        <v>147</v>
+        <v>117.97</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>98.75</v>
+        <v>98.42</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>92.27</v>
+        <v>105.36</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>6.48</v>
+        <v>-6.94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="D63" t="n">
-        <v>10</v>
+        <v>1258.26</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.69</v>
+        <v>98.08</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>106.96</v>
+        <v>88.89</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-8.27</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.97307689</v>
       </c>
       <c r="D64" t="n">
-        <v>1269.53</v>
+        <v>134.71</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>88.89</v>
+        <v>111.44</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>9.5</v>
+        <v>-13.62</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>5.691347</v>
       </c>
       <c r="D65" t="n">
-        <v>135.45</v>
+        <v>23.03</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>97.79000000000001</v>
+        <v>97.81</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>111.44</v>
+        <v>452.96</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-13.65</v>
+        <v>-355.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>2.27580753</v>
       </c>
       <c r="D66" t="n">
-        <v>117.82</v>
+        <v>57.35</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>97.72</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>105.36</v>
+        <v>106.15</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-7.64</v>
+        <v>-8.75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6789,76 +6789,76 @@
         <v>1.85908491</v>
       </c>
       <c r="D67" t="n">
-        <v>70</v>
+        <v>68.75</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>96.55</v>
+        <v>95.38</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-8.43</v>
+        <v>-9.6</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="D68" t="n">
-        <v>136.43</v>
+        <v>107.52</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>94.59999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>6.22</v>
+        <v>-16.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>108.12</v>
+        <v>133.05</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-16.35</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6870,22 +6870,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D70" t="n">
-        <v>104.92</v>
+        <v>104.98</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>90.73</v>
+        <v>91.31</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-2.04</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>194.61</v>
+        <v>194.66</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>89.73</v>
+        <v>90.28</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-18.09</v>
+        <v>-17.54</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>56.58</v>
+        <v>56.46</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.53</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33</v>
+        <v>-32.71</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>104.23</v>
+        <v>102.4</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.89</v>
+        <v>48.31</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.02</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>253.08</v>
+        <v>249.19</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.51</v>
+        <v>45.07</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.6</v>
+        <v>-7.04</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43564.51</v>
+        <v>44240.62</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43386.53</v>
+        <v>44062.62</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5639.78</v>
+        <v>6315.87</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1494110088948055</v>
+        <v>0.1673222197937571</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>177.98</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-16 21:29:34</t>
+          <t>2026-09-17 21:33:43</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109.52</v>
+        <v>110.62</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7009.28</v>
+        <v>7079.68</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1616827808604207</v>
+        <v>0.1608010982212051</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>963.51</v>
+        <v>1033.91</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1593692780241392</v>
+        <v>0.1710137831905613</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.454</v>
+        <v>14.798</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4191.66</v>
+        <v>4291.42</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09668885323762083</v>
+        <v>0.09747122029928527</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>760.95</v>
+        <v>860.71</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2218053988824471</v>
+        <v>0.250883927816691</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1507.8</v>
+        <v>1537.4</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2659.66</v>
+        <v>2711.87</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06135027063310731</v>
+        <v>0.06159482833025496</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1463.7</v>
+        <v>1515.91</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.22387036355731</v>
+        <v>1.267525669754841</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -889,19 +889,19 @@
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2223.54</v>
+        <v>2230.24</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05129030807078327</v>
+        <v>0.05065554393657064</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>297.73</v>
+        <v>304.43</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1545998826467824</v>
+        <v>0.1580789382130117</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>5.95</v>
+        <v>11.77</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>107.96</v>
+        <v>110.25</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1998.48</v>
+        <v>2047.03</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04609885807014893</v>
+        <v>0.04649428676038372</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>351.91</v>
+        <v>400.46</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2137230728119667</v>
+        <v>0.2432086094122934</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2.03</v>
+        <v>7.01</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>513.7</v>
+        <v>546.13</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1916.72</v>
+        <v>2043.87</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04421290342671224</v>
+        <v>0.04642251353470417</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>18.17</v>
+        <v>145.32</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.009570461668115142</v>
+        <v>0.07654262463458955</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4.25</v>
+        <v>9.99</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>214.43</v>
+        <v>219.31</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1748.35</v>
+        <v>1793.53</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04032911938420444</v>
+        <v>0.04073652957374881</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>495.67</v>
+        <v>540.85</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3956876456876457</v>
+        <v>0.4317543187406201</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-28.89</v>
+        <v>-25.2</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>229.93</v>
+        <v>241</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1647.2</v>
+        <v>1731.71</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03799589638782942</v>
+        <v>0.03933240906377733</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-348.86</v>
+        <v>-264.35</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1747743053816018</v>
+        <v>-0.1324358987204794</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-0.54</v>
+        <v>5.48</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>158.4</v>
+        <v>153.11</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1487.28</v>
+        <v>1441.95</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03430702815668463</v>
+        <v>0.03275107682551566</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-384.56</v>
+        <v>-429.89</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2054449098213523</v>
+        <v>-0.2296617232242072</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-73.53</v>
+        <v>-68.11</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.44</v>
+        <v>119.46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1417.37</v>
+        <v>1421.88</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03269441698835465</v>
+        <v>0.0322952259902661</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>73.58</v>
+        <v>78.09</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.05475557936880018</v>
+        <v>0.05811175853369947</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-2.37</v>
+        <v>1.68</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>41.76</v>
+        <v>41.89</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1319.87</v>
+        <v>1329.59</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03044538839570447</v>
+        <v>0.03019903896559337</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>91.53</v>
+        <v>101.25</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.07451519937476594</v>
+        <v>0.08242831789244021</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-57.33</v>
+        <v>-52.37</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>449.2</v>
+        <v>451.1</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1238.47</v>
+        <v>1248.16</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02856773785784063</v>
+        <v>0.02834951562157885</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>323.98</v>
+        <v>333.67</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3542739669105184</v>
+        <v>0.3648700368511411</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-2.71</v>
+        <v>0.55</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1371,17 +1371,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LLOYl_EQ</t>
+          <t>RBSl_EQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lloyds Banking Group</t>
+          <t>NatWest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GB0008706128</t>
+          <t>GB00BM8PJY71</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1390,28 +1390,28 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>1014.362806</v>
+        <v>160</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>59.85909543</v>
+        <v>470.9125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>111.25</v>
+        <v>712.8</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>607.1900000000001</v>
+        <v>753.46</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1128.48</v>
+        <v>1140.48</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02603060293573199</v>
+        <v>0.02590377481740982</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>521.29</v>
+        <v>387.02</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8585286318944645</v>
+        <v>0.5136569957263822</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RBSl_EQ</t>
+          <t>LLOYl_EQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NatWest</t>
+          <t>Lloyds Banking Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GB00BM8PJY71</t>
+          <t>GB0008706128</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1447,28 +1447,28 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>160</v>
+        <v>1014.362806</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>470.9125</v>
+        <v>59.85909543</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>702.2</v>
+        <v>112.2</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>753.46</v>
+        <v>607.1900000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1123.52</v>
+        <v>1138.12</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02591619081450589</v>
+        <v>0.02585017202861117</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>370.06</v>
+        <v>530.9299999999999</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4911475061715286</v>
+        <v>0.8744050461964128</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-08-08</t>
         </is>
       </c>
     </row>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>332</v>
+        <v>338.39</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1085.51</v>
+        <v>1109.74</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02503941566777119</v>
+        <v>0.02520557578026127</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>443.52</v>
+        <v>467.75</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6908518824280752</v>
+        <v>0.7285939033318276</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-27.73</v>
+        <v>-25.87</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>27.285</v>
+        <v>27.612</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1058.78</v>
+        <v>1074.7</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02442283582898618</v>
+        <v>0.02440971064487789</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-37</v>
+        <v>-21.08</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.0337659019146179</v>
+        <v>-0.01923743817189582</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11.57</v>
+        <v>14.9</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>332.49</v>
+        <v>336.83</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>759.22</v>
+        <v>771.45</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01751289731396785</v>
+        <v>0.01752197941471206</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>268.17</v>
+        <v>280.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5461154668567356</v>
+        <v>0.5710212809286223</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-16.39</v>
+        <v>-14.95</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>490.77</v>
+        <v>496.73</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>683.04</v>
+        <v>693.42</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01575565630691052</v>
+        <v>0.01574968042744136</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>148.66</v>
+        <v>159.04</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2781915490849208</v>
+        <v>0.297615928739848</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-20.17</v>
+        <v>-18.62</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1011</v>
+        <v>1017.5</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>657.15</v>
+        <v>661.38</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01515845271446218</v>
+        <v>0.01502195443036135</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-5.53</v>
+        <v>-1.3</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.008344902517051972</v>
+        <v>-0.001961731152290699</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>57.84</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>41.87</v>
+        <v>43.31</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>624.9</v>
+        <v>648.34</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01441454325689327</v>
+        <v>0.01472577630920269</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-242.68</v>
+        <v>-219.24</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.2797206021346735</v>
+        <v>-0.2527029207681136</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-4.33</v>
+        <v>-1.73</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>88.44</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>606.91</v>
+        <v>629.53</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01399956864784941</v>
+        <v>0.01429854391204055</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>57.73</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1051203612658873</v>
+        <v>0.1463090425725627</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-19.39</v>
+        <v>-17.79</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>313.43</v>
+        <v>311.7</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>544.98</v>
+        <v>543.61</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01257103181971787</v>
+        <v>0.01234703899103198</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>55.71</v>
+        <v>54.34</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1138635109448771</v>
+        <v>0.1110634210149815</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-27.42</v>
+        <v>-26.02</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.7585</v>
+        <v>3.7495</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>526.1900000000001</v>
+        <v>524.9299999999999</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01213760364273431</v>
+        <v>0.01192275928986299</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-12.18</v>
+        <v>-13.44</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.02262384605382915</v>
+        <v>-0.02496424392146665</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>343.51</v>
+        <v>346.55</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>512.6799999999999</v>
+        <v>518.78</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01182596901415273</v>
+        <v>0.01178307405634107</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>104.76</v>
+        <v>110.86</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.256815061776819</v>
+        <v>0.271768974308688</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-5.8</v>
+        <v>-4.59</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>237.9</v>
+        <v>237.95</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>197.1</v>
+        <v>197.73</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004546497801142045</v>
+        <v>0.004491050605575235</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.002951353551801343</v>
+        <v>0.006157134133930388</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.27</v>
+        <v>0.31</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>131.99</v>
+        <v>133.82</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.57</v>
+        <v>132.78</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003011852957357265</v>
+        <v>0.003015838261307236</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>10.84</v>
+        <v>13.05</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.09053704167710681</v>
+        <v>0.1089952392883989</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.63</v>
+        <v>0.99</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.32559468</v>
@@ -2194,25 +2194,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>270.74</v>
+        <v>272.24</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>128.14</v>
+        <v>129.23</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002955800244740445</v>
+        <v>0.002935206947648246</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>28.29</v>
+        <v>29.38</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2833249874812218</v>
+        <v>0.2942413620430646</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.7905852</v>
+        <v>3.30858696</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>188.32884805</v>
+        <v>45.93199509</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>211.9</v>
+        <v>50.62</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>110.41</v>
+        <v>112.71</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.01</v>
+        <v>125.36</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002883600660176394</v>
+        <v>0.002847307459236896</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.6</v>
+        <v>12.65</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1322343990580563</v>
+        <v>0.1122349392245586</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.04</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7905852</v>
+        <v>3.30858696</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45.93199509</v>
+        <v>188.32884805</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>50.07</v>
+        <v>211.8</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>123.62</v>
+        <v>125.33</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002851537585881176</v>
+        <v>0.002846626067853862</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>10.91</v>
+        <v>14.92</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.09679708987667465</v>
+        <v>0.1351326872565891</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2365,25 +2365,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>42.85</v>
+        <v>43.5</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>121.99</v>
+        <v>124.21</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002813938441204049</v>
+        <v>0.002821187456220604</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>13.76</v>
+        <v>15.98</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1271366534232653</v>
+        <v>0.1476485262866118</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.75</v>
+        <v>1.08</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>3.81488812</v>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.59183053</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>57.56703616</v>
+        <v>228.00445932</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>64.06999999999999</v>
+        <v>270.97</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>106.81</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.73</v>
+        <v>120.03</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002761807111774415</v>
+        <v>0.002726246923517906</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>12.92</v>
+        <v>20.18</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.120962456698811</v>
+        <v>0.2021031547320982</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.59183053</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2485,19 +2485,19 @@
         <v>105.28</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>118.78</v>
+        <v>119.14</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002739893499846028</v>
+        <v>0.002706032312487905</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.5</v>
+        <v>13.86</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1282294832826748</v>
+        <v>0.1316489361702128</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.76</v>
+        <v>1.08</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>1.55804584</v>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>228.00445932</v>
+        <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>268.68</v>
+        <v>565.99</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.66</v>
+        <v>118.78</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002737125464655074</v>
+        <v>0.002697855615891501</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>18.81</v>
+        <v>13.03</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1883825738607912</v>
+        <v>0.1232151300236407</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.42010405</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>509.16500577</v>
+        <v>350.55601106</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>566.42</v>
+        <v>374.76</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>105.75</v>
+        <v>109.16</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.51</v>
+        <v>117.84</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002733665420666382</v>
+        <v>0.002676505352556445</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.76</v>
+        <v>8.68</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.120661938534279</v>
+        <v>0.07951630633931843</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.78</v>
+        <v>1.07</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.42010405</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>350.55601106</v>
+        <v>57.56703616</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>375.82</v>
+        <v>62.84</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.82</v>
+        <v>117.79</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002717749218318396</v>
+        <v>0.002675369700251388</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.66</v>
+        <v>10.98</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07933308904360573</v>
+        <v>0.1027993633554911</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.74</v>
+        <v>1.1</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
         <v>235.02053179</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>245.51</v>
+        <v>251.45</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>114.41</v>
+        <v>117.53</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002639090884975451</v>
+        <v>0.002669464308265096</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5.64</v>
+        <v>8.76</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.05185253286751862</v>
+        <v>0.08053691275167785</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.75</v>
+        <v>1.08</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.62445608</v>
@@ -2764,25 +2764,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>56.49</v>
+        <v>57.4</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.12</v>
+        <v>116.31</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002632401466597312</v>
+        <v>0.002641754392021725</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>6.48</v>
+        <v>8.67</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.06020066889632107</v>
+        <v>0.08054626532887402</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.76</v>
+        <v>1.08</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>2.70722512</v>
@@ -2821,25 +2821,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>87.95</v>
+        <v>88.09</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.81</v>
+        <v>114.33</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002625250709020681</v>
+        <v>0.002596782560741499</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>12.28</v>
+        <v>12.8</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1209494730621491</v>
+        <v>0.126071111986605</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.84</v>
+        <v>1.14</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>1.73400968</v>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,55 +2872,55 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.7</v>
+        <v>1.59010207</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>225.62857143</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>214.95</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>118.76</v>
+        <v>89.66</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.28</v>
+        <v>112</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002589958260336016</v>
+        <v>0.002543861163325881</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-6.48</v>
+        <v>22.34</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.05456382620410913</v>
+        <v>0.2491635065804149</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.9</v>
+        <v>1.03</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0</v>
+        <v>1.59010207</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.7</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>92.95999999999999</v>
+        <v>210.62</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>89.66</v>
+        <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.31</v>
+        <v>110.35</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002544516349284521</v>
+        <v>0.002506384637259026</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>20.65</v>
+        <v>-8.41</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.230314521525764</v>
+        <v>-0.07081508925564163</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.76</v>
+        <v>-0.55</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>221.99877812</v>
+        <v>12.56856884</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>263.03</v>
+        <v>12.87</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>108.95</v>
+        <v>109.82</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002513145283787042</v>
+        <v>0.00249434672282543</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>17.77</v>
+        <v>3.67</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1948892300943189</v>
+        <v>0.03457371643900141</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.77</v>
+        <v>1.1</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.42255419</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>54.82621761</v>
+        <v>324.07677699</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>52.34</v>
+        <v>342.02</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>112.48</v>
+        <v>101.39</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.05</v>
+        <v>108.17</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002492385019854886</v>
+        <v>0.002456870196758576</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>-4.43</v>
+        <v>6.78</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>-0.03938477951635846</v>
+        <v>0.06687050004931452</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.7</v>
+        <v>1.1</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.42255419</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.42255419</v>
+        <v>2.76637723</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>324.07677699</v>
+        <v>54.82621761</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>341.35</v>
+        <v>52.08</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>101.39</v>
+        <v>112.48</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.64</v>
+        <v>107.84</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002482927566285793</v>
+        <v>0.002449374891545205</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>6.25</v>
+        <v>-4.64</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.06164316007495808</v>
+        <v>-0.04125177809388336</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.8</v>
+        <v>1.05</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.42255419</v>
+        <v>2.76637723</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>194.45976548</v>
+        <v>306.99401668</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>234.91</v>
+        <v>349.12</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>107.31</v>
+        <v>106.79</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.00247531546951067</v>
+        <v>0.002425526193139025</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>19.22</v>
+        <v>13.96</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.2181859461913951</v>
+        <v>0.1503824194764624</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.74</v>
+        <v>1.07</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.5550481</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>12.56856884</v>
+        <v>221.99877812</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>12.54</v>
+        <v>255.13</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>106.15</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>106.69</v>
+        <v>105.99</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002461013954357407</v>
+        <v>0.002407355756258125</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.54</v>
+        <v>14.81</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.005087140838436175</v>
+        <v>0.1624259706075894</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.78</v>
+        <v>1.05</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.5550481</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.40867246</v>
+        <v>1.1533463</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>306.99401668</v>
+        <v>104.90344487</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>348.31</v>
+        <v>121.81</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>92.83</v>
+        <v>89.53</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>106.22</v>
+        <v>105.15</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002450172483192836</v>
+        <v>0.002388276797533182</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>13.39</v>
+        <v>15.62</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1442421630938274</v>
+        <v>0.174466659220373</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.79</v>
+        <v>1.03</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.40867246</v>
+        <v>1.1533463</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.80409618</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>322.35040597</v>
+        <v>148.63893521</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>321.46</v>
+        <v>173.79</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>104.04</v>
+        <v>88.44</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>104.55</v>
+        <v>104.6</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002411650660118726</v>
+        <v>0.002375784622177564</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.51</v>
+        <v>16.16</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.004901960784313725</v>
+        <v>0.182722749886929</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.8</v>
+        <v>1.02</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.80409618</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.43583007</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>104.90344487</v>
+        <v>322.35040597</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>120.6</v>
+        <v>320.21</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>89.53</v>
+        <v>104.04</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>103.8</v>
+        <v>104.46</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002394350440175263</v>
+        <v>0.002372604795723406</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>14.27</v>
+        <v>0.42</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1593879146654752</v>
+        <v>0.004036908881199538</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.76</v>
+        <v>1.12</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.43583007</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.68495686</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>257.81779936</v>
+        <v>176.50746647</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>274.08</v>
+        <v>203.57</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>103.65</v>
+        <v>104.37</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002390890396186571</v>
+        <v>0.002370560621574305</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>6.97</v>
+        <v>14.91</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.07209350434422837</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.82</v>
+        <v>1.04</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.68495686</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.51881442</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>148.63893521</v>
+        <v>249.91595261</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>172.6</v>
+        <v>267.51</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>88.44</v>
+        <v>95.94</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103.57</v>
+        <v>103.88</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002389045039392601</v>
+        <v>0.002359431228984754</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>15.13</v>
+        <v>7.94</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1710764360018092</v>
+        <v>0.08276005836981447</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.51881442</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.61215748</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>249.91595261</v>
+        <v>194.45976548</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>267.33</v>
+        <v>226.55</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>95.94</v>
+        <v>88.09</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>103.5</v>
+        <v>103.8</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002387430352197878</v>
+        <v>0.002357614185296664</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>7.56</v>
+        <v>15.71</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.07879924953095685</v>
+        <v>0.1783403337495743</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.61215748</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.74206342</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>176.50746647</v>
+        <v>74.99726962</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>202.29</v>
+        <v>79.11</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>103.4</v>
+        <v>103.15</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002385123656205416</v>
+        <v>0.002342850705330934</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>13.94</v>
+        <v>6.47</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1558238318801699</v>
+        <v>0.06692180388911874</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.76</v>
+        <v>1.11</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.74206342</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.50675322</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>341.38450299</v>
+        <v>257.81779936</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>365</v>
+        <v>271.68</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.99</v>
+        <v>103.05</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002375666202636323</v>
+        <v>0.002340579400720821</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>7.48</v>
+        <v>6.37</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.07831640665898859</v>
+        <v>0.0658874637980968</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.82</v>
+        <v>1.11</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.50675322</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
         <v>113.12478542</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>116.81</v>
+        <v>116.6</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.81</v>
+        <v>102.94</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002371514149849892</v>
+        <v>0.002338080965649698</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.09</v>
+        <v>4.22</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.04143030794165316</v>
+        <v>0.04274716369529984</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.85</v>
+        <v>1.15</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>1.17949395</v>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.1285649</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>74.99726962</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>78.8</v>
+        <v>1053.96</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>102.44</v>
+        <v>101.42</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002362979374677783</v>
+        <v>0.00230355713557599</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>5.76</v>
+        <v>2.53</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.05957798924286305</v>
+        <v>0.02558398220244716</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.82</v>
+        <v>1.14</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.1285649</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3847,25 +3847,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>147.34</v>
+        <v>147.31</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.76</v>
+        <v>101.04</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002324226882004427</v>
+        <v>0.002294926178057562</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.91</v>
+        <v>1.19</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.009113670505758639</v>
+        <v>0.01191787681522283</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.82</v>
+        <v>1.12</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>96.717382</v>
+        <v>341.38450299</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>98.8</v>
+        <v>356</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>100.75</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002297469208491871</v>
+        <v>0.002288339394688236</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.92</v>
+        <v>5.24</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.0302027306578403</v>
+        <v>0.05486336509266045</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.82</v>
+        <v>1.1</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.90543241</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>137.713206</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>1037.24</v>
+        <v>147.4</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>98.89</v>
+        <v>92.27</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.89</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002295393182098655</v>
+        <v>0.00226880617504127</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.62</v>
+        <v>7.62</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.006269592476489028</v>
+        <v>0.08258372168635526</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.83</v>
+        <v>1.06</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.90543241</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>10.85229847</v>
+        <v>96.717382</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>10.01</v>
+        <v>98.39</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>99.37</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002292163807709209</v>
+        <v>0.00225972095660082</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-7.59</v>
+        <v>2.81</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.07096110695587135</v>
+        <v>0.02906495655771617</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.77</v>
+        <v>1.12</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>137.713206</v>
+        <v>10.85229847</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>145.83</v>
+        <v>9.99</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>92.27</v>
+        <v>106.96</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>98.53</v>
+        <v>99.47</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002272787561372531</v>
+        <v>0.002259266695678798</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>6.26</v>
+        <v>-7.49</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.0678443697843286</v>
+        <v>-0.07002617801047122</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.78</v>
+        <v>1.1</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,55 +4126,55 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>5.691347</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>127.23134407</v>
+        <v>105.04894536</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>117.97</v>
+        <v>23.3</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>105.36</v>
+        <v>452.96</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98.42</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002270250195780823</v>
+        <v>0.002254496955997562</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-6.94</v>
+        <v>-353.7</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.0658694001518603</v>
+        <v>-0.7808636524196397</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.79</v>
+        <v>-5.46</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1258.26</v>
+        <v>118.43</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>88.89</v>
+        <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.08</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002262407429406453</v>
+        <v>0.002250862868621382</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>9.19</v>
+        <v>-6.26</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.1033862076724041</v>
+        <v>-0.05941533788914199</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.10445851</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>154.44822659</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>134.71</v>
+        <v>1262.61</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>111.44</v>
+        <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>97.81999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002256410019826052</v>
+        <v>0.002242231911102955</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-13.62</v>
+        <v>9.83</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.1222182340272792</v>
+        <v>0.1105861176735291</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.10445851</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,55 +4297,55 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>105.04894536</v>
+        <v>62.95787236</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>23.03</v>
+        <v>57.41</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>97.81</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002256179350226806</v>
+        <v>0.00222110877822891</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-355.15</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.7840648180854821</v>
+        <v>-0.07875647668393781</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-6.81</v>
+        <v>1.09</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0</v>
+        <v>2.27580753</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.97307689</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>62.95787236</v>
+        <v>154.44822659</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>57.35</v>
+        <v>133.74</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>106.15</v>
+        <v>111.44</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>97.41</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002246721896657713</v>
+        <v>0.002212477820710482</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-8.75</v>
+        <v>-14.03</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.08243052284503061</v>
+        <v>-0.125897343862168</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.77</v>
+        <v>1.05</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.97307689</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>68.75</v>
+        <v>68.27</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>95.38</v>
+        <v>95</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002200126637609986</v>
+        <v>0.002157739379606774</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-9.6</v>
+        <v>-9.98</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.09144598971232615</v>
+        <v>-0.09506572680510574</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.79</v>
+        <v>1.11</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>1.85908491</v>
@@ -4474,25 +4474,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>107.52</v>
+        <v>106.74</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>94.12</v>
+        <v>93.72</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002171062268104969</v>
+        <v>0.002128666680597335</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-16.33</v>
+        <v>-16.73</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.1478497057492078</v>
+        <v>-0.1514712539610684</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.72</v>
+        <v>1.06</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.17308322</v>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>127.79185697</v>
+        <v>107.56862839</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>133.05</v>
+        <v>106</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>92.79000000000001</v>
+        <v>92.48</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002140383211405228</v>
+        <v>0.002100502503431941</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>4.41</v>
+        <v>-0.29</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.04989816700610998</v>
+        <v>-0.003126010563759836</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.74</v>
+        <v>1.08</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>107.56862839</v>
+        <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>104.98</v>
+        <v>132.13</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>92.77</v>
+        <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>91.31</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002106244110716794</v>
+        <v>0.002099366851126885</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-1.46</v>
+        <v>4.05</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.01573784628651504</v>
+        <v>0.04582484725050916</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4645,25 +4645,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>194.66</v>
+        <v>194.75</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.28</v>
+        <v>90.59</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002082485141994439</v>
+        <v>0.002057574846300817</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.54</v>
+        <v>-17.23</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1626785383045817</v>
+        <v>-0.1598033759970321</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.76</v>
+        <v>1.08</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>0.6214908</v>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>56.46</v>
+        <v>55.72</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.81999999999999</v>
+        <v>77.03</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001795070821333709</v>
+        <v>0.001749585941169577</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-32.71</v>
+        <v>-33.5</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.2959377544558038</v>
+        <v>-0.3030851352573962</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>102.4</v>
+        <v>102.8</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>48.31</v>
+        <v>48.65</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001114364833958256</v>
+        <v>0.001104989692819679</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.009191560476289953</v>
+        <v>0.01629412993524128</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>249.19</v>
+        <v>248.93</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.07</v>
+        <v>45.16</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001039627883802496</v>
+        <v>0.001025721161926757</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-7.04</v>
+        <v>-6.95</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1350988293993475</v>
+        <v>-0.1333717136825945</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.44</v>
+        <v>0.6</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-16 21:29:34</t>
+          <t>2026-09-17 21:33:43</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43564.51</v>
+        <v>44240.62</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43386.53</v>
+        <v>44062.62</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37746.75</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5639.78</v>
+        <v>6315.87</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1494110088948055</v>
+        <v>0.1673222197937571</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>213.17</v>
+        <v>213.19</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109.52</v>
+        <v>110.62</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7009.28</v>
+        <v>7079.68</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>963.51</v>
+        <v>1033.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.454</v>
+        <v>14.798</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4191.66</v>
+        <v>4291.42</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>760.95</v>
+        <v>860.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1507.8</v>
+        <v>1537.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2659.66</v>
+        <v>2711.87</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1463.7</v>
+        <v>1515.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5118,19 +5118,19 @@
         <v>25.91</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2223.54</v>
+        <v>2230.24</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>297.73</v>
+        <v>304.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>107.96</v>
+        <v>110.25</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1998.48</v>
+        <v>2047.03</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>351.91</v>
+        <v>400.46</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>513.7</v>
+        <v>546.13</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1916.72</v>
+        <v>2043.87</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>18.17</v>
+        <v>145.32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>214.43</v>
+        <v>219.31</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1748.35</v>
+        <v>1793.53</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>495.67</v>
+        <v>540.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>229.93</v>
+        <v>241</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1647.2</v>
+        <v>1731.71</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-348.86</v>
+        <v>-264.35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>158.4</v>
+        <v>153.11</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1487.28</v>
+        <v>1441.95</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-384.56</v>
+        <v>-429.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,22 +5277,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.44</v>
+        <v>119.46</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1417.37</v>
+        <v>1421.88</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>73.58</v>
+        <v>78.09</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5304,22 +5304,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>41.76</v>
+        <v>41.89</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1319.87</v>
+        <v>1329.59</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>91.53</v>
+        <v>101.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,76 +5331,76 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>449.2</v>
+        <v>451.1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1238.47</v>
+        <v>1248.16</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>323.98</v>
+        <v>333.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LLOYl_EQ</t>
+          <t>RBSl_EQ</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1014.362806</v>
+        <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>111.25</v>
+        <v>712.8</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1128.48</v>
+        <v>1140.48</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>607.1900000000001</v>
+        <v>753.46</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>521.29</v>
+        <v>387.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RBSl_EQ</t>
+          <t>LLOYl_EQ</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>160</v>
+        <v>1014.362806</v>
       </c>
       <c r="D15" t="n">
-        <v>702.2</v>
+        <v>112.2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1123.52</v>
+        <v>1138.12</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>753.46</v>
+        <v>607.1900000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>370.06</v>
+        <v>530.9299999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>332</v>
+        <v>338.39</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1085.51</v>
+        <v>1109.74</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>443.52</v>
+        <v>467.75</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>27.285</v>
+        <v>27.612</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1058.78</v>
+        <v>1074.7</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-37</v>
+        <v>-21.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>332.49</v>
+        <v>336.83</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>759.22</v>
+        <v>771.45</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>268.17</v>
+        <v>280.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>490.77</v>
+        <v>496.73</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>683.04</v>
+        <v>693.42</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>148.66</v>
+        <v>159.04</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,22 +5520,22 @@
         <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>1011</v>
+        <v>1017.5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>657.15</v>
+        <v>661.38</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-5.53</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>41.87</v>
+        <v>43.31</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>624.9</v>
+        <v>648.34</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-242.68</v>
+        <v>-219.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>88.44</v>
+        <v>91.45999999999999</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>606.91</v>
+        <v>629.53</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>57.73</v>
+        <v>80.34999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>313.43</v>
+        <v>311.7</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>544.98</v>
+        <v>543.61</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>55.71</v>
+        <v>54.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.7585</v>
+        <v>3.7495</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>526.1900000000001</v>
+        <v>524.9299999999999</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-12.18</v>
+        <v>-13.44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>343.51</v>
+        <v>346.55</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>512.6799999999999</v>
+        <v>518.78</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>104.76</v>
+        <v>110.86</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>237.9</v>
+        <v>237.95</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>197.1</v>
+        <v>197.73</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0.58</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,22 +5709,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D27" t="n">
-        <v>131.99</v>
+        <v>133.82</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.57</v>
+        <v>132.78</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>10.84</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5736,76 +5736,76 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>270.74</v>
+        <v>272.24</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>128.14</v>
+        <v>129.23</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>28.29</v>
+        <v>29.38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.7905852</v>
+        <v>3.30858696</v>
       </c>
       <c r="D29" t="n">
-        <v>211.9</v>
+        <v>50.62</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.01</v>
+        <v>125.36</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>110.41</v>
+        <v>112.71</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.6</v>
+        <v>12.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="D30" t="n">
-        <v>50.07</v>
+        <v>211.8</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>123.62</v>
+        <v>125.33</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.91</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5817,49 +5817,49 @@
         <v>3.81488812</v>
       </c>
       <c r="D31" t="n">
-        <v>42.85</v>
+        <v>43.5</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>121.99</v>
+        <v>124.21</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>13.76</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.59183053</v>
       </c>
       <c r="D32" t="n">
-        <v>64.06999999999999</v>
+        <v>270.97</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.73</v>
+        <v>120.03</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>106.81</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12.92</v>
+        <v>20.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5874,100 +5874,100 @@
         <v>102.16</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>118.78</v>
+        <v>119.14</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.5</v>
+        <v>13.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="D34" t="n">
-        <v>268.68</v>
+        <v>565.99</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.66</v>
+        <v>118.78</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>18.81</v>
+        <v>13.03</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.42010405</v>
       </c>
       <c r="D35" t="n">
-        <v>566.42</v>
+        <v>374.76</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>118.51</v>
+        <v>117.84</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>105.75</v>
+        <v>109.16</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.76</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="D36" t="n">
-        <v>375.82</v>
+        <v>62.84</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.82</v>
+        <v>117.79</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.66</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,22 +5979,22 @@
         <v>0.62445608</v>
       </c>
       <c r="D37" t="n">
-        <v>245.51</v>
+        <v>251.45</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>114.41</v>
+        <v>117.53</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5.64</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6006,22 +6006,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D38" t="n">
-        <v>56.49</v>
+        <v>57.4</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.12</v>
+        <v>116.31</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6.48</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6033,427 +6033,427 @@
         <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>87.95</v>
+        <v>88.09</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.81</v>
+        <v>114.33</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>12.28</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.7</v>
+        <v>1.59010207</v>
       </c>
       <c r="D40" t="n">
-        <v>214.95</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.28</v>
+        <v>112</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>118.76</v>
+        <v>89.66</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-6.48</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>92.95999999999999</v>
+        <v>210.62</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.31</v>
+        <v>110.35</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>89.66</v>
+        <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>20.65</v>
+        <v>-8.41</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="D42" t="n">
-        <v>263.03</v>
+        <v>12.87</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>108.95</v>
+        <v>109.82</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>17.77</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.42255419</v>
       </c>
       <c r="D43" t="n">
-        <v>52.34</v>
+        <v>342.02</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.05</v>
+        <v>108.17</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>112.48</v>
+        <v>101.39</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-4.43</v>
+        <v>6.78</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.42255419</v>
+        <v>2.76637723</v>
       </c>
       <c r="D44" t="n">
-        <v>341.35</v>
+        <v>52.08</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.64</v>
+        <v>107.84</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>101.39</v>
+        <v>112.48</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>6.25</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="D45" t="n">
-        <v>234.91</v>
+        <v>349.12</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>107.31</v>
+        <v>106.79</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>19.22</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.5550481</v>
       </c>
       <c r="D46" t="n">
-        <v>12.54</v>
+        <v>255.13</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>106.69</v>
+        <v>105.99</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>106.15</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0.54</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.40867246</v>
+        <v>1.1533463</v>
       </c>
       <c r="D47" t="n">
-        <v>348.31</v>
+        <v>121.81</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>106.22</v>
+        <v>105.15</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>92.83</v>
+        <v>89.53</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>13.39</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.80409618</v>
       </c>
       <c r="D48" t="n">
-        <v>321.46</v>
+        <v>173.79</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104.55</v>
+        <v>104.6</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>104.04</v>
+        <v>88.44</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.51</v>
+        <v>16.16</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.43583007</v>
       </c>
       <c r="D49" t="n">
-        <v>120.6</v>
+        <v>320.21</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>103.8</v>
+        <v>104.46</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>89.53</v>
+        <v>104.04</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>14.27</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.68495686</v>
       </c>
       <c r="D50" t="n">
-        <v>274.08</v>
+        <v>203.57</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>103.65</v>
+        <v>104.37</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>6.97</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.51881442</v>
       </c>
       <c r="D51" t="n">
-        <v>172.6</v>
+        <v>267.51</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>103.57</v>
+        <v>103.88</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>88.44</v>
+        <v>95.94</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15.13</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.61215748</v>
       </c>
       <c r="D52" t="n">
-        <v>267.33</v>
+        <v>226.55</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.5</v>
+        <v>103.8</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>95.94</v>
+        <v>88.09</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>7.56</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.68495686</v>
+        <v>1.74206342</v>
       </c>
       <c r="D53" t="n">
-        <v>202.29</v>
+        <v>79.11</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>103.4</v>
+        <v>103.15</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>13.94</v>
+        <v>6.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.50675322</v>
       </c>
       <c r="D54" t="n">
-        <v>365</v>
+        <v>271.68</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.99</v>
+        <v>103.05</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>7.48</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6465,49 +6465,49 @@
         <v>1.17949395</v>
       </c>
       <c r="D55" t="n">
-        <v>116.81</v>
+        <v>116.6</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.81</v>
+        <v>102.94</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>4.09</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.1285649</v>
       </c>
       <c r="D56" t="n">
-        <v>78.8</v>
+        <v>1053.96</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>102.44</v>
+        <v>101.42</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5.76</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6519,265 +6519,265 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D57" t="n">
-        <v>147.34</v>
+        <v>147.31</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.76</v>
+        <v>101.04</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.91</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="D58" t="n">
-        <v>98.8</v>
+        <v>356</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>99.59999999999999</v>
+        <v>100.75</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>2.92</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.90543241</v>
       </c>
       <c r="D59" t="n">
-        <v>1037.24</v>
+        <v>147.4</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.89</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>98.89</v>
+        <v>92.27</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.62</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="D60" t="n">
-        <v>10.01</v>
+        <v>98.39</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>99.37</v>
+        <v>99.48999999999999</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-7.59</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="D61" t="n">
-        <v>145.83</v>
+        <v>9.99</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98.53</v>
+        <v>99.47</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>92.27</v>
+        <v>106.96</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>6.26</v>
+        <v>-7.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>5.691347</v>
       </c>
       <c r="D62" t="n">
-        <v>117.97</v>
+        <v>23.3</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>98.42</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>105.36</v>
+        <v>452.96</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-6.94</v>
+        <v>-353.7</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>1258.26</v>
+        <v>118.43</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.08</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>88.89</v>
+        <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>9.19</v>
+        <v>-6.26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>134.71</v>
+        <v>1262.61</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>97.81999999999999</v>
+        <v>98.72</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>111.44</v>
+        <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-13.62</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="D65" t="n">
-        <v>23.03</v>
+        <v>57.41</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>97.81</v>
+        <v>97.79000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-355.15</v>
+        <v>-8.359999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.97307689</v>
       </c>
       <c r="D66" t="n">
-        <v>57.35</v>
+        <v>133.74</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>97.40000000000001</v>
+        <v>97.41</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>106.15</v>
+        <v>111.44</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-8.75</v>
+        <v>-14.03</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6789,22 +6789,22 @@
         <v>1.85908491</v>
       </c>
       <c r="D67" t="n">
-        <v>68.75</v>
+        <v>68.27</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>95.38</v>
+        <v>95</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-9.6</v>
+        <v>-9.98</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,76 +6816,76 @@
         <v>1.17308322</v>
       </c>
       <c r="D68" t="n">
-        <v>107.52</v>
+        <v>106.74</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>94.12</v>
+        <v>93.72</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-16.33</v>
+        <v>-16.73</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="D69" t="n">
-        <v>133.05</v>
+        <v>106</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.79000000000001</v>
+        <v>92.48</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>4.41</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>104.98</v>
+        <v>132.13</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.31</v>
+        <v>92.43000000000001</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>92.77</v>
+        <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-1.46</v>
+        <v>4.05</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>194.66</v>
+        <v>194.75</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.28</v>
+        <v>90.59</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.54</v>
+        <v>-17.23</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>56.46</v>
+        <v>55.72</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.81999999999999</v>
+        <v>77.03</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-32.71</v>
+        <v>-33.5</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>102.4</v>
+        <v>102.8</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.31</v>
+        <v>48.65</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.44</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>249.19</v>
+        <v>248.93</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.07</v>
+        <v>45.16</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-7.04</v>
+        <v>-6.95</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44240.62</v>
+        <v>44105.21</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44062.62</v>
+        <v>43907.99</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6315.87</v>
+        <v>6161.24</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1673222197937571</v>
+        <v>0.1632257081735514</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>178</v>
+        <v>197.22</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-17 21:33:43</t>
+          <t>2026-09-18 21:04:33</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>110.62</v>
+        <v>110.3</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7079.68</v>
+        <v>7059.2</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1608010982212051</v>
+        <v>0.160901441940591</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1033.91</v>
+        <v>1013.43</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1710137831905613</v>
+        <v>0.1676262907785112</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.798</v>
+        <v>14.95</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4291.42</v>
+        <v>4335.5</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09747122029928527</v>
+        <v>0.09881972483191187</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>860.71</v>
+        <v>904.79</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.250883927816691</v>
+        <v>0.2637325801364732</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1537.4</v>
+        <v>1512.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2711.87</v>
+        <v>2668.12</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06159482833025496</v>
+        <v>0.06081487353673641</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1515.91</v>
+        <v>1472.16</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.267525669754841</v>
+        <v>1.230944178735075</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>25.91</v>
+        <v>26.11</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2230.24</v>
+        <v>2240.77</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05065554393657064</v>
+        <v>0.05107421861644636</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>304.43</v>
+        <v>314.96</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1580789382130117</v>
+        <v>0.1635467673342645</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11.77</v>
+        <v>6.01</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -915,17 +915,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CSCO_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US17275R1023</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -934,55 +934,55 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>24.80610988</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>89.05910724</v>
+        <v>509.97</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>110.25</v>
+        <v>557.28</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1646.57</v>
+        <v>1898.55</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2047.03</v>
+        <v>2079.39</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04649428676038372</v>
+        <v>0.04739585921306175</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>400.46</v>
+        <v>180.84</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2432086094122934</v>
+        <v>0.09525163940902268</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7.01</v>
+        <v>4.31</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.15856288</v>
+        <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>CSCO_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US17275R1023</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,38 +991,38 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>24.80610988</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>509.97</v>
+        <v>89.05910724</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>546.13</v>
+        <v>109.7</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1646.57</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2043.87</v>
+        <v>2030.75</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04642251353470417</v>
+        <v>0.04628720013894708</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>145.32</v>
+        <v>384.18</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.07654262463458955</v>
+        <v>0.2333213893123281</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9.99</v>
+        <v>2.08</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0</v>
+        <v>1.15856288</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
     </row>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>219.31</v>
+        <v>221.87</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1793.53</v>
+        <v>1809.06</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04073652957374881</v>
+        <v>0.04123418553901937</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>540.85</v>
+        <v>556.38</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4317543187406201</v>
+        <v>0.4441517386722866</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-25.2</v>
+        <v>-28.86</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>241</v>
+        <v>242.68</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1731.71</v>
+        <v>1738.59</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03933240906377733</v>
+        <v>0.03962795188456087</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-264.35</v>
+        <v>-257.47</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1324358987204794</v>
+        <v>-0.1289891085438314</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>5.48</v>
+        <v>-0.48</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>153.11</v>
+        <v>151.66</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1441.95</v>
+        <v>1424.04</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03275107682551566</v>
+        <v>0.03245836488285914</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-429.89</v>
+        <v>-447.8</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2296617232242072</v>
+        <v>-0.2392298487050175</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-68.11</v>
+        <v>-73.48</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1231,19 +1231,19 @@
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1421.88</v>
+        <v>1417.65</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.0322952259902661</v>
+        <v>0.03231271662044975</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>78.09</v>
+        <v>73.86</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.05811175853369947</v>
+        <v>0.05496394525930391</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1.68</v>
+        <v>-2.33</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>41.89</v>
+        <v>41.55</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1329.59</v>
+        <v>1318.86</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03019903896559337</v>
+        <v>0.03006098080770737</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>101.25</v>
+        <v>90.52</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.08242831789244021</v>
+        <v>0.07369295146295</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-52.37</v>
+        <v>-52.32</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>451.1</v>
+        <v>443.3</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1248.16</v>
+        <v>1224.36</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02834951562157885</v>
+        <v>0.02790702763123045</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>333.67</v>
+        <v>309.87</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3648700368511411</v>
+        <v>0.3388446019092609</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>0.55</v>
+        <v>-1.1</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>470.9125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>712.8</v>
+        <v>699.4</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1140.48</v>
+        <v>1119.04</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02590377481740982</v>
+        <v>0.02550645251433575</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>387.02</v>
+        <v>365.58</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.5136569957263822</v>
+        <v>0.4852016032702465</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>112.2</v>
+        <v>108.95</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1138.12</v>
+        <v>1105.15</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02585017202861117</v>
+        <v>0.02518985558712661</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>530.9299999999999</v>
+        <v>497.96</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.8744050461964128</v>
+        <v>0.8201057329666166</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>338.39</v>
+        <v>332.25</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1109.74</v>
+        <v>1086.36</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02520557578026127</v>
+        <v>0.02476157219891495</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>467.75</v>
+        <v>444.37</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.7285939033318276</v>
+        <v>0.6921758905901961</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-25.87</v>
+        <v>-27.71</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>27.612</v>
+        <v>27.762</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1074.7</v>
+        <v>1077.32</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02440971064487789</v>
+        <v>0.02455552207494298</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-21.08</v>
+        <v>-18.46</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.01923743817189582</v>
+        <v>-0.01684644727956342</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>14.9</v>
+        <v>11.6</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>336.83</v>
+        <v>335.4</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>771.45</v>
+        <v>765.88</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01752197941471206</v>
+        <v>0.01745682178624488</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>280.4</v>
+        <v>274.83</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5710212809286223</v>
+        <v>0.5596782405050402</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-14.95</v>
+        <v>-16.38</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>496.73</v>
+        <v>494.8</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>693.42</v>
+        <v>688.66</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01574968042744136</v>
+        <v>0.01569673433346659</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>159.04</v>
+        <v>154.28</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.297615928739848</v>
+        <v>0.2887084097458738</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-18.62</v>
+        <v>-20.16</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1017.5</v>
+        <v>1015.5</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>661.38</v>
+        <v>660.08</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01502195443036135</v>
+        <v>0.015045305954803</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-1.3</v>
+        <v>-2.6</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.001961731152290699</v>
+        <v>-0.003923462304581397</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>57.84</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43.31</v>
+        <v>43.27</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>648.34</v>
+        <v>645.8200000000001</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01472577630920269</v>
+        <v>0.0147202755601304</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-219.24</v>
+        <v>-221.76</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.2527029207681136</v>
+        <v>-0.2556075520413103</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-1.73</v>
+        <v>-4.3</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>91.45999999999999</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>629.53</v>
+        <v>641.9299999999999</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01429854391204055</v>
+        <v>0.01463161018598759</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>80.34999999999999</v>
+        <v>92.75</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1463090425725627</v>
+        <v>0.1688881605302451</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-17.79</v>
+        <v>-19.37</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>311.7</v>
+        <v>311.96</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>543.61</v>
+        <v>542.4400000000001</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01234703899103198</v>
+        <v>0.01236391916453057</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>54.34</v>
+        <v>53.17</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1110634210149815</v>
+        <v>0.1086721033376254</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-26.02</v>
+        <v>-27.4</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.7495</v>
+        <v>3.742</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>524.9299999999999</v>
+        <v>523.88</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01192275928986299</v>
+        <v>0.01194087820203944</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-13.44</v>
+        <v>-14.49</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.02496424392146665</v>
+        <v>-0.02691457547783123</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>346.55</v>
+        <v>350.1</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>518.78</v>
+        <v>522.53</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01178307405634107</v>
+        <v>0.01191010744237548</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>110.86</v>
+        <v>114.61</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.271768974308688</v>
+        <v>0.2809619533241812</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-4.59</v>
+        <v>-5.79</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>237.95</v>
+        <v>230.08</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>197.73</v>
+        <v>190.63</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004491050605575235</v>
+        <v>0.004345059196103646</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1.21</v>
+        <v>-5.89</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.006157134133930388</v>
+        <v>-0.0299715041726033</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.31</v>
+        <v>-0.26</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,34 +2131,34 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>121.66614911</v>
+        <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>133.82</v>
+        <v>271.14</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>132.78</v>
+        <v>128.33</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003015838261307236</v>
+        <v>0.002925045620500347</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>13.05</v>
+        <v>28.48</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.1089952392883989</v>
+        <v>0.285227841762644</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.99</v>
+        <v>0.85</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>212.76482689</v>
+        <v>121.66614911</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>272.24</v>
+        <v>127.11</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>129.23</v>
+        <v>125.74</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002935206947648246</v>
+        <v>0.002866011348256164</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>29.38</v>
+        <v>6.01</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2942413620430646</v>
+        <v>0.05019627495197528</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1.15</v>
+        <v>0.62</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45.93199509</v>
+        <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>50.62</v>
+        <v>208.78</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.36</v>
+        <v>123.18</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002847307459236896</v>
+        <v>0.002807660870671181</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>12.65</v>
+        <v>12.77</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1122349392245586</v>
+        <v>0.1156598134226972</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1.04</v>
+        <v>0.7</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>3.30858696</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>188.32884805</v>
+        <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>211.8</v>
+        <v>49.11</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>110.41</v>
+        <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>125.33</v>
+        <v>121.26</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002846626067853862</v>
+        <v>0.002763898012482444</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>14.92</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1351326872565891</v>
+        <v>0.07585839765770562</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.03</v>
+        <v>0.7</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>3.30858696</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2365,25 +2365,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>43.5</v>
+        <v>42.55</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>124.21</v>
+        <v>121.14</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002821187456220604</v>
+        <v>0.002761162833845648</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>15.98</v>
+        <v>12.91</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1476485262866118</v>
+        <v>0.11928300840802</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1.08</v>
+        <v>0.76</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>3.81488812</v>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.59183053</v>
+        <v>1.55804584</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>228.00445932</v>
+        <v>91.20399179</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>270.97</v>
+        <v>102.7</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>120.03</v>
+        <v>119.41</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002726246923517906</v>
+        <v>0.002721730675165171</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>20.18</v>
+        <v>14.13</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.2021031547320982</v>
+        <v>0.1342135258358663</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1.15</v>
+        <v>0.76</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.59183053</v>
+        <v>1.55804584</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>91.20399179</v>
+        <v>228.00445932</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>102.16</v>
+        <v>269.99</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.14</v>
+        <v>119.24</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002706032312487905</v>
+        <v>0.002717855838763043</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.86</v>
+        <v>19.39</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1316489361702128</v>
+        <v>0.1941912869303956</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1.08</v>
+        <v>0.85</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2536,25 +2536,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>565.99</v>
+        <v>569</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.78</v>
+        <v>119.06</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002697855615891501</v>
+        <v>0.002713753070807849</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.03</v>
+        <v>13.31</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1232151300236407</v>
+        <v>0.1258628841607565</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0.28038062</v>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>350.55601106</v>
+        <v>57.56703616</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>374.76</v>
+        <v>63</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.84</v>
+        <v>117.73</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002676505352556445</v>
+        <v>0.002683438174250026</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>8.68</v>
+        <v>10.92</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.07951630633931843</v>
+        <v>0.102237618200543</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1.07</v>
+        <v>0.77</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.62445608</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>57.56703616</v>
+        <v>235.02053179</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>62.84</v>
+        <v>252.26</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>106.81</v>
+        <v>108.77</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.79</v>
+        <v>117.56</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002675369700251388</v>
+        <v>0.002679563337847897</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>10.98</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1027993633554911</v>
+        <v>0.08081272409671784</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.62445608</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>235.02053179</v>
+        <v>350.55601106</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>251.45</v>
+        <v>372.74</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>108.77</v>
+        <v>109.16</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>117.53</v>
+        <v>116.86</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002669464308265096</v>
+        <v>0.002663608129133254</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>8.76</v>
+        <v>7.7</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.08053691275167785</v>
+        <v>0.07053865884939539</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1.08</v>
+        <v>0.75</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>53.65641702</v>
+        <v>79.10567143</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>57.4</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>116.31</v>
+        <v>114.15</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002641754392021725</v>
+        <v>0.002601838678252276</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>8.67</v>
+        <v>12.62</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.08054626532887402</v>
+        <v>0.1242982369742933</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.08</v>
+        <v>0.84</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>88.09</v>
+        <v>56.06</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>114.33</v>
+        <v>113.26</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002596782560741499</v>
+        <v>0.002581552770029371</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>12.8</v>
+        <v>5.62</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.126071111986605</v>
+        <v>0.05221107395020438</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1.14</v>
+        <v>0.76</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2878,25 +2878,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>94.09999999999999</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112</v>
+        <v>111.63</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002543861163325881</v>
+        <v>0.002544399926879558</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>22.34</v>
+        <v>21.97</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.2491635065804149</v>
+        <v>0.2450368057104617</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.59010207</v>
@@ -2935,25 +2935,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>210.62</v>
+        <v>207.92</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.35</v>
+        <v>108.61</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002506384637259026</v>
+        <v>0.002475564597853523</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-8.41</v>
+        <v>-10.15</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.07081508925564163</v>
+        <v>-0.08546648703267093</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.9</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.42255419</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>12.56856884</v>
+        <v>324.07677699</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>12.87</v>
+        <v>340</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>106.15</v>
+        <v>101.39</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.82</v>
+        <v>107.21</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.00249434672282543</v>
+        <v>0.002443654180424235</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3.67</v>
+        <v>5.82</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.03457371643900141</v>
+        <v>0.05740211066180097</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.42255419</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.42255419</v>
+        <v>11.40066159</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>324.07677699</v>
+        <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>342.02</v>
+        <v>12.59</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>101.39</v>
+        <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.17</v>
+        <v>107.11</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002456870196758576</v>
+        <v>0.002441374864893572</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>6.78</v>
+        <v>0.96</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.06687050004931452</v>
+        <v>0.009043805934997644</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1.1</v>
+        <v>0.78</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.42255419</v>
+        <v>11.40066159</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.40867246</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>54.82621761</v>
+        <v>306.99401668</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>52.08</v>
+        <v>348.79</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>112.48</v>
+        <v>92.83</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.84</v>
+        <v>106.37</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002449374891545205</v>
+        <v>0.002424507929966663</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>-4.64</v>
+        <v>13.54</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>-0.04125177809388336</v>
+        <v>0.1458580200366261</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1.05</v>
+        <v>0.79</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.40867246</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>306.99401668</v>
+        <v>54.82621761</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>349.12</v>
+        <v>51.16</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>92.83</v>
+        <v>112.48</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>106.79</v>
+        <v>105.62</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002425526193139025</v>
+        <v>0.002407413063486687</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>13.96</v>
+        <v>-6.86</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1503824194764624</v>
+        <v>-0.06098862019914652</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.07</v>
+        <v>0.71</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.1533463</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>221.99877812</v>
+        <v>104.90344487</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>255.13</v>
+        <v>122.52</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>105.99</v>
+        <v>105.45</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002407355756258125</v>
+        <v>0.00240353822708456</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>14.81</v>
+        <v>15.92</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1624259706075894</v>
+        <v>0.1778174913436837</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1.05</v>
+        <v>0.76</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.1533463</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.80409618</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>104.90344487</v>
+        <v>148.63893521</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>121.81</v>
+        <v>174.49</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>89.53</v>
+        <v>88.44</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>105.15</v>
+        <v>104.71</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002388276797533182</v>
+        <v>0.00238667129215765</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>15.62</v>
+        <v>16.27</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.174466659220373</v>
+        <v>0.1839665309814563</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1.03</v>
+        <v>0.76</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.80409618</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.43583007</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>148.63893521</v>
+        <v>322.35040597</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>173.79</v>
+        <v>320.73</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>88.44</v>
+        <v>104.04</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>104.6</v>
+        <v>104.32</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002375784622177564</v>
+        <v>0.002377781961588063</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>16.16</v>
+        <v>0.28</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.182722749886929</v>
+        <v>0.002691272587466359</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1.02</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.43583007</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.51881442</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>322.35040597</v>
+        <v>249.91595261</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>320.21</v>
+        <v>269.42</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>104.04</v>
+        <v>95.94</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.46</v>
+        <v>104.31</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002372604795723406</v>
+        <v>0.002377554030034997</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.42</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.004036908881199538</v>
+        <v>0.0872420262664165</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1.12</v>
+        <v>0.82</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.51881442</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3448,25 +3448,25 @@
         <v>176.50746647</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>203.57</v>
+        <v>203.3</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>104.37</v>
+        <v>103.92</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002370560621574305</v>
+        <v>0.00236866469946541</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>14.91</v>
+        <v>14.46</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1616364855801476</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1.04</v>
+        <v>0.76</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.68495686</v>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.61215748</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>249.91595261</v>
+        <v>194.45976548</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>267.51</v>
+        <v>226.1</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>95.94</v>
+        <v>88.09</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103.88</v>
+        <v>103.29</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002359431228984754</v>
+        <v>0.00235430501162223</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>7.94</v>
+        <v>15.2</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.08276005836981447</v>
+        <v>0.1725508003178567</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1.11</v>
+        <v>0.75</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.61215748</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.5550481</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>194.45976548</v>
+        <v>221.99877812</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>226.55</v>
+        <v>248.21</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>88.09</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>103.8</v>
+        <v>102.81</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002357614185296664</v>
+        <v>0.002343364297075046</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>15.71</v>
+        <v>11.63</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1783403337495743</v>
+        <v>0.1275499012941435</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1.01</v>
+        <v>0.77</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.5550481</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
         <v>74.99726962</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>79.11</v>
+        <v>79.05</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>103.15</v>
+        <v>102.77</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002342850705330934</v>
+        <v>0.00234245257086278</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>6.47</v>
+        <v>6.09</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.06692180388911874</v>
+        <v>0.06299131154323541</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1.11</v>
+        <v>0.82</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>1.74206342</v>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.17949395</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>257.81779936</v>
+        <v>113.12478542</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>271.68</v>
+        <v>116.65</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>98.72</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>103.05</v>
+        <v>102.68</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002340579400720821</v>
+        <v>0.002340401186885183</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>6.37</v>
+        <v>3.96</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.0658874637980968</v>
+        <v>0.04011345218800649</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1.11</v>
+        <v>0.86</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.17949395</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.1285649</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>113.12478542</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>116.6</v>
+        <v>1070</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>98.72</v>
+        <v>98.89</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.94</v>
+        <v>102.66</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002338080965649698</v>
+        <v>0.00233994532377905</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>4.22</v>
+        <v>3.77</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.04274716369529984</v>
+        <v>0.03812316715542522</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1.15</v>
+        <v>0.84</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.1285649</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>257.81779936</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1053.96</v>
+        <v>269.46</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.42</v>
+        <v>101.9</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.00230355713557599</v>
+        <v>0.002322622525746009</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.53</v>
+        <v>5.22</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.02558398220244716</v>
+        <v>0.05399255275134464</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.90543241</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>147.21071381</v>
+        <v>137.713206</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>147.31</v>
+        <v>149.92</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>101.04</v>
+        <v>101.3</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002294926178057562</v>
+        <v>0.002308946632562028</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>1.19</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.01191787681522283</v>
+        <v>0.09786496152595643</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1.12</v>
+        <v>0.78</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.90543241</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>341.38450299</v>
+        <v>147.21071381</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>356</v>
+        <v>146.57</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.75</v>
+        <v>100.23</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002288339394688236</v>
+        <v>0.00228455795638393</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>5.24</v>
+        <v>0.38</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.05486336509266045</v>
+        <v>0.003805708562844267</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1.1</v>
+        <v>0.82</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.37810738</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>137.713206</v>
+        <v>341.38450299</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>147.4</v>
+        <v>353.05</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>92.27</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.89</v>
+        <v>99.62</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.00226880617504127</v>
+        <v>0.002270654131646883</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>7.62</v>
+        <v>4.11</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.08258372168635526</v>
+        <v>0.04303214323107528</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1.06</v>
+        <v>0.82</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.37810738</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4018,25 +4018,25 @@
         <v>96.717382</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>98.39</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>98.95</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.00225972095660082</v>
+        <v>0.002255382717591438</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.81</v>
+        <v>2.27</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.02906495655771617</v>
+        <v>0.02347952006619776</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1.12</v>
+        <v>0.83</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.35094641</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>10.85229847</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9.99</v>
+        <v>1266.61</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>106.96</v>
+        <v>88.89</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>99.47</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002259266695678798</v>
+        <v>0.002250596154977045</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-7.49</v>
+        <v>9.85</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.07002617801047122</v>
+        <v>0.1108111148610642</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1.1</v>
+        <v>0.76</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,38 +4126,38 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>5.691347</v>
+        <v>13.30225117</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>105.04894536</v>
+        <v>10.85229847</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>23.3</v>
+        <v>9.9</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>452.96</v>
+        <v>106.96</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>99.26000000000001</v>
+        <v>98.28</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002254496955997562</v>
+        <v>0.002240111303535994</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-353.7</v>
+        <v>-8.68</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.7808636524196397</v>
+        <v>-0.08115183246073299</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-5.46</v>
+        <v>0.77</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>0</v>
+        <v>13.30225117</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4189,25 +4189,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>118.43</v>
+        <v>117.55</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002250862868621382</v>
+        <v>0.0022353247409216</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-6.26</v>
+        <v>-7.29</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.05941533788914199</v>
+        <v>-0.06919134396355353</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1.1</v>
+        <v>0.79</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>1.11796351</v>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>2.27580753</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>62.95787236</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1262.61</v>
+        <v>56.95</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>88.89</v>
+        <v>106.15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.72</v>
+        <v>96.72</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002242231911102955</v>
+        <v>0.002204553981257644</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>9.83</v>
+        <v>-9.43</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1105861176735291</v>
+        <v>-0.08883655204898727</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1.03</v>
+        <v>0.77</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>2.27580753</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,55 +4297,55 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>62.95787236</v>
+        <v>105.04894536</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>57.41</v>
+        <v>22.74</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>97.79000000000001</v>
+        <v>96.58</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.00222110877822891</v>
+        <v>0.002201362939514715</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-8.359999999999999</v>
+        <v>-356.38</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.07875647668393781</v>
+        <v>-0.7867802896503002</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>1.09</v>
+        <v>-6.79</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.85908491</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>154.44822659</v>
+        <v>76.24181082</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>133.74</v>
+        <v>68.05</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>111.44</v>
+        <v>104.98</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>97.41</v>
+        <v>94.41</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002212477820710482</v>
+        <v>0.00215190179249932</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-14.03</v>
+        <v>-10.57</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.125897343862168</v>
+        <v>-0.1006858449228425</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>1.05</v>
+        <v>0.8</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.85908491</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>76.24181082</v>
+        <v>154.44822659</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>68.27</v>
+        <v>129.95</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>104.98</v>
+        <v>111.44</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>95</v>
+        <v>94.37</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002157739379606774</v>
+        <v>0.002150990066287054</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-9.98</v>
+        <v>-17.07</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.09506572680510574</v>
+        <v>-0.1531765972720747</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1.11</v>
+        <v>0.72</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>106.74</v>
+        <v>106.89</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>93.72</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002128666680597335</v>
+        <v>0.002132755542041747</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-16.73</v>
+        <v>-16.88</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.1514712539610684</v>
+        <v>-0.1528293345405161</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>1.06</v>
+        <v>0.72</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.17308322</v>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>107.56862839</v>
+        <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>106</v>
+        <v>132.03</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>92.77</v>
+        <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>92.48</v>
+        <v>92.08</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002100502503431941</v>
+        <v>0.002098793740634862</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-0.29</v>
+        <v>3.7</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.003126010563759836</v>
+        <v>0.04186467526589727</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1.08</v>
+        <v>0.74</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>127.79185697</v>
+        <v>107.56862839</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>132.13</v>
+        <v>104.52</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002099366851126885</v>
+        <v>0.002072125748926101</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>4.05</v>
+        <v>-1.86</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.04582484725050916</v>
+        <v>-0.0200495849951493</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1.02</v>
+        <v>0.79</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4645,25 +4645,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>194.75</v>
+        <v>192.75</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.59</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002057574846300817</v>
+        <v>0.002037708084413083</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-17.23</v>
+        <v>-18.42</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1598033759970321</v>
+        <v>-0.1708402893711742</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1.08</v>
+        <v>0.76</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>0.6214908</v>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>55.72</v>
+        <v>55.92</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.03</v>
+        <v>77.08</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001749585941169577</v>
+        <v>0.001756896411035352</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33.5</v>
+        <v>-33.45</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.3030851352573962</v>
+        <v>-0.3026327693838777</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>1.06</v>
+        <v>0.74</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>102.8</v>
+        <v>104.16</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>48.65</v>
+        <v>49.14</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001104989692819679</v>
+        <v>0.001120055651767997</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.78</v>
+        <v>1.27</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.01629412993524128</v>
+        <v>0.02653018592020055</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>248.93</v>
+        <v>249.17</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.16</v>
+        <v>45.07</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001025721161926757</v>
+        <v>0.001027287509669996</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-6.95</v>
+        <v>-7.04</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1333717136825945</v>
+        <v>-0.1350988293993475</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.6</v>
+        <v>0.45</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-17 21:33:43</t>
+          <t>2026-09-18 21:04:33</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44240.62</v>
+        <v>44105.21</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44062.62</v>
+        <v>43907.99</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37746.75</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6315.87</v>
+        <v>6161.24</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1673222197937571</v>
+        <v>0.1632257081735514</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>213.19</v>
+        <v>232.41</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>110.62</v>
+        <v>110.3</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7079.68</v>
+        <v>7059.2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1033.91</v>
+        <v>1013.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.798</v>
+        <v>14.95</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4291.42</v>
+        <v>4335.5</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>860.71</v>
+        <v>904.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1537.4</v>
+        <v>1512.6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2711.87</v>
+        <v>2668.12</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1515.91</v>
+        <v>1472.16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,76 +5115,76 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>25.91</v>
+        <v>26.11</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2230.24</v>
+        <v>2240.77</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>304.43</v>
+        <v>314.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSCO_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24.80610988</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>110.25</v>
+        <v>557.28</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2047.03</v>
+        <v>2079.39</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1646.57</v>
+        <v>1898.55</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>400.46</v>
+        <v>180.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>CSCO_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>24.80610988</v>
       </c>
       <c r="D7" t="n">
-        <v>546.13</v>
+        <v>109.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2043.87</v>
+        <v>2030.75</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1646.57</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>145.32</v>
+        <v>384.18</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>219.31</v>
+        <v>221.87</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1793.53</v>
+        <v>1809.06</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>540.85</v>
+        <v>556.38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>241</v>
+        <v>242.68</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1731.71</v>
+        <v>1738.59</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-264.35</v>
+        <v>-257.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>153.11</v>
+        <v>151.66</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1441.95</v>
+        <v>1424.04</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-429.89</v>
+        <v>-447.8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5280,19 +5280,19 @@
         <v>119.46</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1421.88</v>
+        <v>1417.65</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>78.09</v>
+        <v>73.86</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5304,22 +5304,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>41.89</v>
+        <v>41.55</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1329.59</v>
+        <v>1318.86</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>101.25</v>
+        <v>90.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>451.1</v>
+        <v>443.3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1248.16</v>
+        <v>1224.36</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>333.67</v>
+        <v>309.87</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>712.8</v>
+        <v>699.4</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1140.48</v>
+        <v>1119.04</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>387.02</v>
+        <v>365.58</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D15" t="n">
-        <v>112.2</v>
+        <v>108.95</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1138.12</v>
+        <v>1105.15</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>530.9299999999999</v>
+        <v>497.96</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>338.39</v>
+        <v>332.25</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1109.74</v>
+        <v>1086.36</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>467.75</v>
+        <v>444.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>27.612</v>
+        <v>27.762</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1074.7</v>
+        <v>1077.32</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-21.08</v>
+        <v>-18.46</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>336.83</v>
+        <v>335.4</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>771.45</v>
+        <v>765.88</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>280.4</v>
+        <v>274.83</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>496.73</v>
+        <v>494.8</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>693.42</v>
+        <v>688.66</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>159.04</v>
+        <v>154.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,22 +5520,22 @@
         <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>1017.5</v>
+        <v>1015.5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>661.38</v>
+        <v>660.08</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-1.3</v>
+        <v>-2.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>43.31</v>
+        <v>43.27</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>648.34</v>
+        <v>645.8200000000001</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-219.24</v>
+        <v>-221.76</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>91.45999999999999</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>629.53</v>
+        <v>641.9299999999999</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>80.34999999999999</v>
+        <v>92.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>311.7</v>
+        <v>311.96</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>543.61</v>
+        <v>542.4400000000001</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>54.34</v>
+        <v>53.17</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.7495</v>
+        <v>3.742</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>524.9299999999999</v>
+        <v>523.88</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-13.44</v>
+        <v>-14.49</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>346.55</v>
+        <v>350.1</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>518.78</v>
+        <v>522.53</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>110.86</v>
+        <v>114.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,130 +5682,130 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>237.95</v>
+        <v>230.08</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>197.73</v>
+        <v>190.63</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>1.21</v>
+        <v>-5.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>133.82</v>
+        <v>271.14</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>132.78</v>
+        <v>128.33</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>13.05</v>
+        <v>28.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.32559468</v>
       </c>
       <c r="D28" t="n">
-        <v>272.24</v>
+        <v>127.11</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>129.23</v>
+        <v>125.74</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>29.38</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>50.62</v>
+        <v>208.78</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.36</v>
+        <v>123.18</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>12.65</v>
+        <v>12.77</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>211.8</v>
+        <v>49.11</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>125.33</v>
+        <v>121.26</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>110.41</v>
+        <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>14.92</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5817,76 +5817,76 @@
         <v>3.81488812</v>
       </c>
       <c r="D31" t="n">
-        <v>43.5</v>
+        <v>42.55</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>124.21</v>
+        <v>121.14</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>15.98</v>
+        <v>12.91</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.59183053</v>
+        <v>1.55804584</v>
       </c>
       <c r="D32" t="n">
-        <v>270.97</v>
+        <v>102.7</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>120.03</v>
+        <v>119.41</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>20.18</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="D33" t="n">
-        <v>102.16</v>
+        <v>269.99</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.14</v>
+        <v>119.24</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.86</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5898,157 +5898,157 @@
         <v>0.28038062</v>
       </c>
       <c r="D34" t="n">
-        <v>565.99</v>
+        <v>569</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.78</v>
+        <v>119.06</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>13.03</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="D35" t="n">
-        <v>374.76</v>
+        <v>63</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.84</v>
+        <v>117.73</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>8.68</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.62445608</v>
       </c>
       <c r="D36" t="n">
-        <v>62.84</v>
+        <v>252.26</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.79</v>
+        <v>117.56</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>106.81</v>
+        <v>108.77</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10.98</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.42010405</v>
       </c>
       <c r="D37" t="n">
-        <v>251.45</v>
+        <v>372.74</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>117.53</v>
+        <v>116.86</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>108.77</v>
+        <v>109.16</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>8.76</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="D38" t="n">
-        <v>57.4</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>116.31</v>
+        <v>114.15</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.67</v>
+        <v>12.62</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>88.09</v>
+        <v>56.06</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>114.33</v>
+        <v>113.26</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>12.8</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6060,22 +6060,22 @@
         <v>1.59010207</v>
       </c>
       <c r="D40" t="n">
-        <v>94.09999999999999</v>
+        <v>94.06999999999999</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112</v>
+        <v>111.63</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>22.34</v>
+        <v>21.97</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,238 +6087,238 @@
         <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>210.62</v>
+        <v>207.92</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.35</v>
+        <v>108.61</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-8.41</v>
+        <v>-10.15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.42255419</v>
       </c>
       <c r="D42" t="n">
-        <v>12.87</v>
+        <v>340</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>109.82</v>
+        <v>107.21</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>106.15</v>
+        <v>101.39</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3.67</v>
+        <v>5.82</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.42255419</v>
+        <v>11.40066159</v>
       </c>
       <c r="D43" t="n">
-        <v>342.02</v>
+        <v>12.59</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.17</v>
+        <v>107.11</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>101.39</v>
+        <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>6.78</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.40867246</v>
       </c>
       <c r="D44" t="n">
-        <v>52.08</v>
+        <v>348.79</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.84</v>
+        <v>106.37</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>112.48</v>
+        <v>92.83</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-4.64</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="D45" t="n">
-        <v>349.12</v>
+        <v>51.16</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>106.79</v>
+        <v>105.62</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.83</v>
+        <v>112.48</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>13.96</v>
+        <v>-6.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.1533463</v>
       </c>
       <c r="D46" t="n">
-        <v>255.13</v>
+        <v>122.52</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>105.99</v>
+        <v>105.45</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>14.81</v>
+        <v>15.92</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.80409618</v>
       </c>
       <c r="D47" t="n">
-        <v>121.81</v>
+        <v>174.49</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>105.15</v>
+        <v>104.71</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>89.53</v>
+        <v>88.44</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>15.62</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.43583007</v>
       </c>
       <c r="D48" t="n">
-        <v>173.79</v>
+        <v>320.73</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104.6</v>
+        <v>104.32</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>88.44</v>
+        <v>104.04</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>16.16</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.51881442</v>
       </c>
       <c r="D49" t="n">
-        <v>320.21</v>
+        <v>269.42</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.46</v>
+        <v>104.31</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>104.04</v>
+        <v>95.94</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>0.42</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6330,76 +6330,76 @@
         <v>0.68495686</v>
       </c>
       <c r="D50" t="n">
-        <v>203.57</v>
+        <v>203.3</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>104.37</v>
+        <v>103.92</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>14.91</v>
+        <v>14.46</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.61215748</v>
       </c>
       <c r="D51" t="n">
-        <v>267.51</v>
+        <v>226.1</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>103.88</v>
+        <v>103.29</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>95.94</v>
+        <v>88.09</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>7.94</v>
+        <v>15.2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.5550481</v>
       </c>
       <c r="D52" t="n">
-        <v>226.55</v>
+        <v>248.21</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.8</v>
+        <v>102.81</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>88.09</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>15.71</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6411,184 +6411,184 @@
         <v>1.74206342</v>
       </c>
       <c r="D53" t="n">
-        <v>79.11</v>
+        <v>79.05</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>103.15</v>
+        <v>102.77</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>6.47</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.17949395</v>
       </c>
       <c r="D54" t="n">
-        <v>271.68</v>
+        <v>116.65</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>103.05</v>
+        <v>102.68</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>98.72</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>6.37</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.1285649</v>
       </c>
       <c r="D55" t="n">
-        <v>116.6</v>
+        <v>1070</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.94</v>
+        <v>102.66</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>98.72</v>
+        <v>98.89</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>4.22</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="D56" t="n">
-        <v>1053.96</v>
+        <v>269.46</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>101.42</v>
+        <v>101.9</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2.53</v>
+        <v>5.22</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.90543241</v>
       </c>
       <c r="D57" t="n">
-        <v>147.31</v>
+        <v>149.92</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>101.04</v>
+        <v>101.3</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>1.19</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D58" t="n">
-        <v>356</v>
+        <v>146.57</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.75</v>
+        <v>100.23</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>5.24</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.37810738</v>
       </c>
       <c r="D59" t="n">
-        <v>147.4</v>
+        <v>353.05</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.89</v>
+        <v>99.62</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>92.27</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>7.62</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6600,76 +6600,76 @@
         <v>1.35094641</v>
       </c>
       <c r="D60" t="n">
-        <v>98.39</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>99.48999999999999</v>
+        <v>98.95</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2.81</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="D61" t="n">
-        <v>9.99</v>
+        <v>1266.61</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>99.47</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>106.96</v>
+        <v>88.89</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-7.49</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>5.691347</v>
+        <v>13.30225117</v>
       </c>
       <c r="D62" t="n">
-        <v>23.3</v>
+        <v>9.9</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>99.26000000000001</v>
+        <v>98.28</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>452.96</v>
+        <v>106.96</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-353.7</v>
+        <v>-8.68</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6681,130 +6681,130 @@
         <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>118.43</v>
+        <v>117.55</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>99.09999999999999</v>
+        <v>98.06999999999999</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-6.26</v>
+        <v>-7.29</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>2.27580753</v>
       </c>
       <c r="D64" t="n">
-        <v>1262.61</v>
+        <v>56.95</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.72</v>
+        <v>96.72</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>88.89</v>
+        <v>106.15</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>9.83</v>
+        <v>-9.43</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="D65" t="n">
-        <v>57.41</v>
+        <v>22.74</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>97.79000000000001</v>
+        <v>96.58</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-8.359999999999999</v>
+        <v>-356.38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.85908491</v>
       </c>
       <c r="D66" t="n">
-        <v>133.74</v>
+        <v>68.05</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>97.41</v>
+        <v>94.41</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>111.44</v>
+        <v>104.98</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-14.03</v>
+        <v>-10.57</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="D67" t="n">
-        <v>68.27</v>
+        <v>129.95</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>95</v>
+        <v>94.37</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>104.98</v>
+        <v>111.44</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-9.98</v>
+        <v>-17.07</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,76 +6816,76 @@
         <v>1.17308322</v>
       </c>
       <c r="D68" t="n">
-        <v>106.74</v>
+        <v>106.89</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>93.72</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-16.73</v>
+        <v>-16.88</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>106</v>
+        <v>132.03</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.48</v>
+        <v>92.08</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>92.77</v>
+        <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-0.29</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="D70" t="n">
-        <v>132.13</v>
+        <v>104.52</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>92.43000000000001</v>
+        <v>90.91</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>4.05</v>
+        <v>-1.86</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>194.75</v>
+        <v>192.75</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.59</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-17.23</v>
+        <v>-18.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>55.72</v>
+        <v>55.92</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.03</v>
+        <v>77.08</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33.5</v>
+        <v>-33.45</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>102.8</v>
+        <v>104.16</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.65</v>
+        <v>49.14</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.78</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>248.93</v>
+        <v>249.17</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.16</v>
+        <v>45.07</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-6.95</v>
+        <v>-7.04</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44105.21</v>
+        <v>44110.19</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43907.99</v>
+        <v>43912.95</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6161.24</v>
+        <v>6166.2</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1632257081735514</v>
+        <v>0.1633571102147867</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>197.22</v>
+        <v>197.24</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-18 21:04:33</t>
+          <t>2026-09-19 20:53:04</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>7059.2</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.160901441940591</v>
+        <v>0.1608833267696437</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1013.43</v>
@@ -778,7 +778,7 @@
         <v>4335.5</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09881972483191187</v>
+        <v>0.09880859916276492</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>904.79</v>
@@ -835,7 +835,7 @@
         <v>2668.12</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06081487353673641</v>
+        <v>0.06080802666316604</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1472.16</v>
@@ -892,7 +892,7 @@
         <v>2240.77</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05107421861644636</v>
+        <v>0.05106846839948075</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>314.96</v>
@@ -940,22 +940,22 @@
         <v>509.97</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>557.28</v>
+        <v>557.98</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2079.39</v>
+        <v>2082</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04739585921306175</v>
+        <v>0.04745000656368967</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>180.84</v>
+        <v>183.45</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.09525163940902268</v>
+        <v>0.09662637275815754</v>
       </c>
       <c r="M6" s="2" t="n">
         <v>4.31</v>
@@ -997,25 +997,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>109.7</v>
+        <v>109.47</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2030.75</v>
+        <v>2026.5</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04628720013894708</v>
+        <v>0.04618512886710717</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>384.18</v>
+        <v>379.93</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2333213893123281</v>
+        <v>0.2307402661289833</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>1.15856288</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>221.87</v>
+        <v>222.53</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1809.06</v>
+        <v>1814.45</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04123418553901937</v>
+        <v>0.0413523844425969</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>556.38</v>
+        <v>561.77</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4441517386722866</v>
+        <v>0.4484545135230066</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-28.86</v>
+        <v>-28.85</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>242.68</v>
+        <v>243.39</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1738.59</v>
+        <v>1743.68</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03962795188456087</v>
+        <v>0.03973949445003574</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-257.47</v>
+        <v>-252.38</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1289891085438314</v>
+        <v>-0.126439084997445</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.47</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,22 +1168,22 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>151.66</v>
+        <v>151.79</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1424.04</v>
+        <v>1425.26</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03245836488285914</v>
+        <v>0.0324825150600213</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-447.8</v>
+        <v>-446.58</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2392298487050175</v>
+        <v>-0.2385780835968886</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-73.48</v>
@@ -1234,7 +1234,7 @@
         <v>1417.65</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03231271662044975</v>
+        <v>0.03230907867676017</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>73.86</v>
@@ -1291,7 +1291,7 @@
         <v>1318.86</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03006098080770737</v>
+        <v>0.03005759637684331</v>
       </c>
       <c r="K12" s="2" t="n">
         <v>90.52</v>
@@ -1348,7 +1348,7 @@
         <v>1224.36</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02790702763123045</v>
+        <v>0.0279038857042839</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>309.87</v>
@@ -1405,7 +1405,7 @@
         <v>1119.04</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02550645251433575</v>
+        <v>0.02550358085736373</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>365.58</v>
@@ -1462,7 +1462,7 @@
         <v>1105.15</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02518985558712661</v>
+        <v>0.02518701957438119</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>497.96</v>
@@ -1510,22 +1510,22 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>332.25</v>
+        <v>330.62</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1086.36</v>
+        <v>1081.03</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02476157219891495</v>
+        <v>0.02463731056462317</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>444.37</v>
+        <v>439.04</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6921758905901961</v>
+        <v>0.6838735805853674</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>-27.71</v>
@@ -1576,7 +1576,7 @@
         <v>1077.32</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02455552207494298</v>
+        <v>0.02455275747895973</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>-18.46</v>
@@ -1624,22 +1624,22 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>335.4</v>
+        <v>334.8</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>765.88</v>
+        <v>764.51</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01745682178624488</v>
+        <v>0.0174236332939512</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>274.83</v>
+        <v>273.46</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5596782405050402</v>
+        <v>0.556888300580389</v>
       </c>
       <c r="M18" s="2" t="n">
         <v>-16.38</v>
@@ -1681,22 +1681,22 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>494.8</v>
+        <v>493.99</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>688.66</v>
+        <v>687.54</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01569673433346659</v>
+        <v>0.01566944164879885</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>154.28</v>
+        <v>153.16</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2887084097458738</v>
+        <v>0.2866125229237621</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>-20.16</v>
@@ -1747,7 +1747,7 @@
         <v>660.08</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.015045305954803</v>
+        <v>0.0150436120713546</v>
       </c>
       <c r="K20" s="2" t="n">
         <v>-2.6</v>
@@ -1795,22 +1795,22 @@
         <v>57.84</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43.27</v>
+        <v>43.25</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>645.8200000000001</v>
+        <v>645.52</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.0147202755601304</v>
+        <v>0.01471178109365656</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-221.76</v>
+        <v>-222.06</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.2556075520413103</v>
+        <v>-0.2559533414785956</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>-4.3</v>
@@ -1852,22 +1852,22 @@
         <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>93.54000000000001</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>641.9299999999999</v>
+        <v>643.65</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01463161018598759</v>
+        <v>0.01466916269198792</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>92.75</v>
+        <v>94.47</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1688881605302451</v>
+        <v>0.1720201026985688</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>-19.37</v>
@@ -1909,22 +1909,22 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>311.96</v>
+        <v>312</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>542.4400000000001</v>
+        <v>542.51</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01236391916453057</v>
+        <v>0.01236412250762117</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>53.17</v>
+        <v>53.24</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1086721033376254</v>
+        <v>0.1088151736260143</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>-27.4</v>
@@ -1975,7 +1975,7 @@
         <v>523.88</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01194087820203944</v>
+        <v>0.01193953383217375</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>-14.49</v>
@@ -2023,22 +2023,22 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>350.1</v>
+        <v>350.83</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>522.53</v>
+        <v>523.62</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01191010744237548</v>
+        <v>0.01193360827900057</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>114.61</v>
+        <v>115.7</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2809619533241812</v>
+        <v>0.2836340458913512</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>-5.79</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>230.08</v>
+        <v>230.17</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>190.63</v>
+        <v>190.7</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004345059196103646</v>
+        <v>0.004346165346635744</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-5.89</v>
+        <v>-5.82</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.0299715041726033</v>
+        <v>-0.02961530633014451</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.27</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,22 +2137,22 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>271.14</v>
+        <v>271.45</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>128.33</v>
+        <v>128.48</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002925045620500347</v>
+        <v>0.002928134891115681</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.285227841762644</v>
+        <v>0.2867300951427141</v>
       </c>
       <c r="M27" s="2" t="n">
         <v>0.85</v>
@@ -2194,25 +2194,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>127.11</v>
+        <v>127.51</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>125.74</v>
+        <v>126.14</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002866011348256164</v>
+        <v>0.002874804912557068</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>6.01</v>
+        <v>6.41</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.05019627495197528</v>
+        <v>0.05353712519836298</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>1.32559468</v>
@@ -2251,22 +2251,22 @@
         <v>188.32884805</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>208.78</v>
+        <v>209.45</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>123.18</v>
+        <v>123.57</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002807660870671181</v>
+        <v>0.002816233098499103</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>12.77</v>
+        <v>13.16</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1156598134226972</v>
+        <v>0.119192102164659</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>0.7</v>
@@ -2308,22 +2308,22 @@
         <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>49.11</v>
+        <v>49.4</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>121.26</v>
+        <v>121.97</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002763898012482444</v>
+        <v>0.002779768155894923</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>9.26</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.07585839765770562</v>
+        <v>0.08215774997781919</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>0.7</v>
@@ -2374,7 +2374,7 @@
         <v>121.14</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002761162833845648</v>
+        <v>0.002760851966919004</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>12.91</v>
@@ -2422,25 +2422,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>102.7</v>
+        <v>103.17</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.41</v>
+        <v>119.96</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002721730675165171</v>
+        <v>0.002733959071748421</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>14.13</v>
+        <v>14.68</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1342135258358663</v>
+        <v>0.1394376899696049</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>1.55804584</v>
@@ -2479,22 +2479,22 @@
         <v>228.00445932</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>269.99</v>
+        <v>270.2</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.24</v>
+        <v>119.34</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002717855838763043</v>
+        <v>0.002719828906489302</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>19.39</v>
+        <v>19.49</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1941912869303956</v>
+        <v>0.1951927891837757</v>
       </c>
       <c r="M33" s="2" t="n">
         <v>0.85</v>
@@ -2536,22 +2536,22 @@
         <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>569</v>
+        <v>566.27</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>119.06</v>
+        <v>118.49</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002713753070807849</v>
+        <v>0.002700456905730831</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>13.31</v>
+        <v>12.74</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1258628841607565</v>
+        <v>0.1204728132387707</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>0.79</v>
@@ -2593,22 +2593,22 @@
         <v>57.56703616</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>63</v>
+        <v>63.04</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.73</v>
+        <v>117.81</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002683438174250026</v>
+        <v>0.002684959305124054</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.102237618200543</v>
+        <v>0.1029866117404737</v>
       </c>
       <c r="M35" s="2" t="n">
         <v>0.77</v>
@@ -2650,22 +2650,22 @@
         <v>235.02053179</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>252.26</v>
+        <v>251.36</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.56</v>
+        <v>117.14</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002679563337847897</v>
+        <v>0.002669689610408553</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.789999999999999</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.08081272409671784</v>
+        <v>0.07695136526615794</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>0.76</v>
@@ -2707,25 +2707,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>372.74</v>
+        <v>372.37</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.86</v>
+        <v>116.74</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002663608129133254</v>
+        <v>0.002660573374757508</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>7.7</v>
+        <v>7.58</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.07053865884939539</v>
+        <v>0.0694393550751191</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.75</v>
+        <v>0.74</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.42010405</v>
@@ -2773,7 +2773,7 @@
         <v>114.15</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002601838678252276</v>
+        <v>0.002601545748916992</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>12.62</v>
@@ -2821,25 +2821,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>56.06</v>
+        <v>56.5</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.26</v>
+        <v>114.15</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002581552770029371</v>
+        <v>0.002601545748916992</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>5.62</v>
+        <v>6.51</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.05221107395020438</v>
+        <v>0.060479375696767</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>2.70722512</v>
@@ -2887,7 +2887,7 @@
         <v>111.63</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002544399926879558</v>
+        <v>0.002544113464315407</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>21.97</v>
@@ -2935,22 +2935,22 @@
         <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>207.92</v>
+        <v>206.02</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>108.61</v>
+        <v>107.62</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002475564597853523</v>
+        <v>0.002452723201913681</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-10.15</v>
+        <v>-11.14</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.08546648703267093</v>
+        <v>-0.09380262714718761</v>
       </c>
       <c r="M41" s="2" t="n">
         <v>-0.9</v>
@@ -2992,22 +2992,22 @@
         <v>324.07677699</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>340</v>
+        <v>340.97</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>107.21</v>
+        <v>107.52</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002443654180424235</v>
+        <v>0.002450444143000919</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>5.82</v>
+        <v>6.13</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.05740211066180097</v>
+        <v>0.06045961140151888</v>
       </c>
       <c r="M42" s="2" t="n">
         <v>0.8</v>
@@ -3049,22 +3049,22 @@
         <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.59</v>
+        <v>12.61</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>107.11</v>
+        <v>107.28</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002441374864893572</v>
+        <v>0.002444974401610292</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.009043805934997644</v>
+        <v>0.01064531323598681</v>
       </c>
       <c r="M43" s="2" t="n">
         <v>0.78</v>
@@ -3106,25 +3106,25 @@
         <v>306.99401668</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>348.79</v>
+        <v>349.36</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>106.37</v>
+        <v>106.55</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002424507929966663</v>
+        <v>0.002428337271547135</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>13.54</v>
+        <v>13.72</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1458580200366261</v>
+        <v>0.1477970483679845</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>0.40867246</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>54.82621761</v>
+        <v>104.90344487</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>51.16</v>
+        <v>122.48</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>112.48</v>
+        <v>89.53</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>105.62</v>
+        <v>105.42</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002407413063486687</v>
+        <v>0.002402583905832932</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-6.86</v>
+        <v>15.89</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.06098862019914652</v>
+        <v>0.1774824081313526</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.71</v>
+        <v>0.76</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.80409618</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>104.90344487</v>
+        <v>148.63893521</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>122.52</v>
+        <v>174.49</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>89.53</v>
+        <v>88.44</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>105.45</v>
+        <v>104.71</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.00240353822708456</v>
+        <v>0.002386402587552327</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>15.92</v>
+        <v>16.27</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1778174913436837</v>
+        <v>0.1839665309814563</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>0.76</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.80409618</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>148.63893521</v>
+        <v>54.82621761</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>174.49</v>
+        <v>50.72</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="I47" s="2" t="n">
         <v>104.71</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.00238667129215765</v>
+        <v>0.002386402587552327</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>16.27</v>
+        <v>-7.77</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1839665309814563</v>
+        <v>-0.06907894736842105</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.76</v>
+        <v>0.71</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.51881442</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>322.35040597</v>
+        <v>249.91595261</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>320.73</v>
+        <v>269.42</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>104.04</v>
+        <v>95.94</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>104.32</v>
+        <v>104.31</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002377781961588063</v>
+        <v>0.002377286351901283</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.28</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.002691272587466359</v>
+        <v>0.0872420262664165</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.51881442</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>249.91595261</v>
+        <v>176.50746647</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>269.42</v>
+        <v>203.38</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>95.94</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.31</v>
+        <v>103.96</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002377554030034997</v>
+        <v>0.002369309645706618</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>14.5</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.0872420262664165</v>
+        <v>0.1620836127878381</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.82</v>
+        <v>0.76</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>176.50746647</v>
+        <v>322.35040597</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>203.3</v>
+        <v>318.25</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>103.92</v>
+        <v>103.51</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.00236866469946541</v>
+        <v>0.002359053880599192</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>14.46</v>
+        <v>-0.53</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1616364855801476</v>
+        <v>-0.005094194540561323</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.76</v>
+        <v>0.8</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>194.45976548</v>
+        <v>74.99726962</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>226.1</v>
+        <v>79.39</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103.29</v>
+        <v>103.21</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.00235430501162223</v>
+        <v>0.002352216703860908</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>15.2</v>
+        <v>6.53</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1725508003178567</v>
+        <v>0.0675424079437319</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>221.99877812</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>248.21</v>
+        <v>1072.44</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>102.81</v>
+        <v>102.89</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002343364297075046</v>
+        <v>0.002344923715340072</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>11.63</v>
+        <v>4</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1275499012941435</v>
+        <v>0.04044898371928405</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.5550481</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>74.99726962</v>
+        <v>221.99877812</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>79.05</v>
+        <v>248.2</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>102.77</v>
+        <v>102.81</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.00234245257086278</v>
+        <v>0.002343100468209864</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>6.09</v>
+        <v>11.63</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.06299131154323541</v>
+        <v>0.1275499012941435</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.5550481</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.61215748</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>113.12478542</v>
+        <v>194.45976548</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>116.65</v>
+        <v>225</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>98.72</v>
+        <v>88.09</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.68</v>
+        <v>102.79</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002340401186885183</v>
+        <v>0.002342644656427311</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>3.96</v>
+        <v>14.7</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.04011345218800649</v>
+        <v>0.1668747871495062</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.61215748</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>113.12478542</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>1070</v>
+        <v>116.5</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>98.89</v>
+        <v>98.72</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.66</v>
+        <v>102.54</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.00233994532377905</v>
+        <v>0.002336947009145408</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.03812316715542522</v>
+        <v>0.03869529983792545</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.90543241</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>257.81779936</v>
+        <v>137.713206</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>269.46</v>
+        <v>151.23</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.9</v>
+        <v>102.18</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002322622525746009</v>
+        <v>0.002328742397059467</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>5.22</v>
+        <v>9.91</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.05399255275134464</v>
+        <v>0.1074021892272678</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.90543241</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.50675322</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>137.713206</v>
+        <v>257.81779936</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>149.92</v>
+        <v>269.09</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>92.27</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>101.3</v>
+        <v>101.76</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002308946632562028</v>
+        <v>0.00231917034962587</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>9.029999999999999</v>
+        <v>5.08</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.09786496152595643</v>
+        <v>0.05254447662391394</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.50675322</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3904,22 +3904,22 @@
         <v>147.21071381</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>146.57</v>
+        <v>146.25</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.23</v>
+        <v>100.01</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.00228455795638393</v>
+        <v>0.002279286818652548</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.003805708562844267</v>
+        <v>0.001602403605408112</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>0.82</v>
@@ -3961,22 +3961,22 @@
         <v>341.38450299</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>353.05</v>
+        <v>353</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002270654131646883</v>
+        <v>0.002270170583001503</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.04303214323107528</v>
+        <v>0.04292744215265416</v>
       </c>
       <c r="M59" s="2" t="n">
         <v>0.82</v>
@@ -4018,22 +4018,22 @@
         <v>96.717382</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>98.15000000000001</v>
+        <v>98.14</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>98.95</v>
+        <v>98.94</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002255382717591438</v>
+        <v>0.002254900888286002</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.02347952006619776</v>
+        <v>0.02337608605709557</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>0.83</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>127.23134407</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1266.61</v>
+        <v>117.97</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>88.89</v>
+        <v>105.36</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>98.42</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002250596154977045</v>
+        <v>0.002243049781939644</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>9.85</v>
+        <v>-6.94</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1108111148610642</v>
+        <v>-0.0658694001518603</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.76</v>
+        <v>0.79</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
         <v>98.28</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002240111303535994</v>
+        <v>0.002239859099461778</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>-8.68</v>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>127.23134407</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>117.55</v>
+        <v>1252.5</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.06999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.0022353247409216</v>
+        <v>0.002225273122420106</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-7.29</v>
+        <v>8.75</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.06919134396355353</v>
+        <v>0.09843626954663066</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,55 +4240,55 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>62.95787236</v>
+        <v>105.04894536</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>56.95</v>
+        <v>22.76</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>96.72</v>
+        <v>96.67</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002204553981257644</v>
+        <v>0.002203166250966321</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-9.43</v>
+        <v>-356.29</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.08883655204898727</v>
+        <v>-0.7865815966089722</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.77</v>
+        <v>-6.79</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,38 +4297,38 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>105.04894536</v>
+        <v>62.95787236</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>22.74</v>
+        <v>56.91</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>96.58</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002201362939514715</v>
+        <v>0.002202710439183769</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-356.38</v>
+        <v>-9.5</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.7867802896503002</v>
+        <v>-0.08949599623174752</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-6.79</v>
+        <v>0.77</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0</v>
+        <v>2.27580753</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4369,7 @@
         <v>94.41</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.00215190179249932</v>
+        <v>0.002151659519537916</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>-10.57</v>
@@ -4417,22 +4417,22 @@
         <v>154.44822659</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>129.95</v>
+        <v>129.88</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>94.37</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002150990066287054</v>
+        <v>0.002149608366516431</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-17.07</v>
+        <v>-17.12</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1531765972720747</v>
+        <v>-0.1536252692031587</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>0.72</v>
@@ -4474,22 +4474,22 @@
         <v>126.99866255</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>106.89</v>
+        <v>106.82</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>93.56999999999999</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002132755542041747</v>
+        <v>0.002131147989323065</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-16.88</v>
+        <v>-16.94</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.1528293345405161</v>
+        <v>-0.1533725667722952</v>
       </c>
       <c r="M68" s="2" t="n">
         <v>0.72</v>
@@ -4531,22 +4531,22 @@
         <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>132.03</v>
+        <v>132.09</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>92.08</v>
+        <v>92.12</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002098793740634862</v>
+        <v>0.002099469070435683</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.04186467526589727</v>
+        <v>0.04231726634985291</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>0.74</v>
@@ -4597,7 +4597,7 @@
         <v>90.91</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002072125748926101</v>
+        <v>0.002071892457591272</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>-1.86</v>
@@ -4645,22 +4645,22 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>192.75</v>
+        <v>192.7</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>89.40000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002037708084413083</v>
+        <v>0.002036794950334749</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-18.42</v>
+        <v>-18.45</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1708402893711742</v>
+        <v>-0.171118530884808</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>0.76</v>
@@ -4702,22 +4702,22 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>55.92</v>
+        <v>56</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.08</v>
+        <v>77.19</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001756896411035352</v>
+        <v>0.001759205574760425</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33.45</v>
+        <v>-33.34</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.3026327693838777</v>
+        <v>-0.301637564462137</v>
       </c>
       <c r="M72" s="2" t="n">
         <v>0.74</v>
@@ -4759,22 +4759,22 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>104.16</v>
+        <v>104.5</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49.14</v>
+        <v>49.3</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001120055651767997</v>
+        <v>0.001123576043991307</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.02653018592020055</v>
+        <v>0.02987257154794234</v>
       </c>
       <c r="M73" s="2" t="n">
         <v>0.4</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>249.17</v>
+        <v>248.96</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.07</v>
+        <v>45.03</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001027287509669996</v>
+        <v>0.001026260228416401</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-7.04</v>
+        <v>-7.08</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1350988293993475</v>
+        <v>-0.1358664363845711</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,7 +4865,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-18 21:04:33</t>
+          <t>2026-09-19 20:53:04</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44105.21</v>
+        <v>44110.19</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43907.99</v>
+        <v>43912.95</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37746.75</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6161.24</v>
+        <v>6166.2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1632257081735514</v>
+        <v>0.1633571102147867</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>232.41</v>
+        <v>232.43</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5076,7 +5076,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>557.28</v>
+        <v>557.98</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2079.39</v>
+        <v>2082</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>180.84</v>
+        <v>183.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D7" t="n">
-        <v>109.7</v>
+        <v>109.47</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2030.75</v>
+        <v>2026.5</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>384.18</v>
+        <v>379.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>221.87</v>
+        <v>222.53</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1809.06</v>
+        <v>1814.45</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>556.38</v>
+        <v>561.77</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>242.68</v>
+        <v>243.39</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1738.59</v>
+        <v>1743.68</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-257.47</v>
+        <v>-252.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>151.66</v>
+        <v>151.79</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1424.04</v>
+        <v>1425.26</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-447.8</v>
+        <v>-446.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>332.25</v>
+        <v>330.62</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1086.36</v>
+        <v>1081.03</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>444.37</v>
+        <v>439.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5454,7 +5454,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>335.4</v>
+        <v>334.8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>765.88</v>
+        <v>764.51</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>274.83</v>
+        <v>273.46</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>494.8</v>
+        <v>493.99</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>688.66</v>
+        <v>687.54</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>154.28</v>
+        <v>153.16</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5535,7 +5535,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>20</v>
       </c>
       <c r="D21" t="n">
-        <v>43.27</v>
+        <v>43.25</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>645.8200000000001</v>
+        <v>645.52</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-221.76</v>
+        <v>-222.06</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>93.54000000000001</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>641.9299999999999</v>
+        <v>643.65</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>92.75</v>
+        <v>94.47</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>311.96</v>
+        <v>312</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>542.4400000000001</v>
+        <v>542.51</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>53.17</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5643,7 +5643,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>350.1</v>
+        <v>350.83</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>522.53</v>
+        <v>523.62</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>114.61</v>
+        <v>115.7</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>230.08</v>
+        <v>230.17</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>190.63</v>
+        <v>190.7</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-5.89</v>
+        <v>-5.82</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,22 +5709,22 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>271.14</v>
+        <v>271.45</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>128.33</v>
+        <v>128.48</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>28.48</v>
+        <v>28.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5736,22 +5736,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D28" t="n">
-        <v>127.11</v>
+        <v>127.51</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125.74</v>
+        <v>126.14</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6.01</v>
+        <v>6.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5763,22 +5763,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D29" t="n">
-        <v>208.78</v>
+        <v>209.45</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>123.18</v>
+        <v>123.57</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>12.77</v>
+        <v>13.16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5790,22 +5790,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>49.11</v>
+        <v>49.4</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>121.26</v>
+        <v>121.97</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>8.550000000000001</v>
+        <v>9.26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5832,7 +5832,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5844,22 +5844,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D32" t="n">
-        <v>102.7</v>
+        <v>103.17</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.41</v>
+        <v>119.96</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14.13</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5871,22 +5871,22 @@
         <v>0.59183053</v>
       </c>
       <c r="D33" t="n">
-        <v>269.99</v>
+        <v>270.2</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.24</v>
+        <v>119.34</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>19.39</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5898,22 +5898,22 @@
         <v>0.28038062</v>
       </c>
       <c r="D34" t="n">
-        <v>569</v>
+        <v>566.27</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>119.06</v>
+        <v>118.49</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>13.31</v>
+        <v>12.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5925,22 +5925,22 @@
         <v>2.50421091</v>
       </c>
       <c r="D35" t="n">
-        <v>63</v>
+        <v>63.04</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.73</v>
+        <v>117.81</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5952,22 +5952,22 @@
         <v>0.62445608</v>
       </c>
       <c r="D36" t="n">
-        <v>252.26</v>
+        <v>251.36</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.56</v>
+        <v>117.14</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.789999999999999</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,22 +5979,22 @@
         <v>0.42010405</v>
       </c>
       <c r="D37" t="n">
-        <v>372.74</v>
+        <v>372.37</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.86</v>
+        <v>116.74</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7.7</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6021,7 +6021,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6033,22 +6033,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>56.06</v>
+        <v>56.5</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.26</v>
+        <v>114.15</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>5.62</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6075,7 +6075,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,22 +6087,22 @@
         <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>207.92</v>
+        <v>206.02</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>108.61</v>
+        <v>107.62</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-10.15</v>
+        <v>-11.14</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6114,22 +6114,22 @@
         <v>0.42255419</v>
       </c>
       <c r="D42" t="n">
-        <v>340</v>
+        <v>340.97</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>107.21</v>
+        <v>107.52</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>5.82</v>
+        <v>6.13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6141,22 +6141,22 @@
         <v>11.40066159</v>
       </c>
       <c r="D43" t="n">
-        <v>12.59</v>
+        <v>12.61</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>107.11</v>
+        <v>107.28</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.96</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6168,373 +6168,373 @@
         <v>0.40867246</v>
       </c>
       <c r="D44" t="n">
-        <v>348.79</v>
+        <v>349.36</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>106.37</v>
+        <v>106.55</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13.54</v>
+        <v>13.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="D45" t="n">
-        <v>51.16</v>
+        <v>122.48</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>105.62</v>
+        <v>105.42</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>112.48</v>
+        <v>89.53</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-6.86</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.80409618</v>
       </c>
       <c r="D46" t="n">
-        <v>122.52</v>
+        <v>174.49</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>105.45</v>
+        <v>104.71</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>89.53</v>
+        <v>88.44</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>15.92</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="D47" t="n">
-        <v>174.49</v>
+        <v>50.72</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>104.71</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>16.27</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.51881442</v>
       </c>
       <c r="D48" t="n">
-        <v>320.73</v>
+        <v>269.42</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104.32</v>
+        <v>104.31</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>104.04</v>
+        <v>95.94</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.28</v>
+        <v>8.369999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="D49" t="n">
-        <v>269.42</v>
+        <v>203.38</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.31</v>
+        <v>103.96</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>95.94</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.43583007</v>
       </c>
       <c r="D50" t="n">
-        <v>203.3</v>
+        <v>318.25</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>103.92</v>
+        <v>103.51</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>14.46</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="D51" t="n">
-        <v>226.1</v>
+        <v>79.39</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>103.29</v>
+        <v>103.21</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15.2</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="D52" t="n">
-        <v>248.21</v>
+        <v>1072.44</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>102.81</v>
+        <v>102.89</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>11.63</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.5550481</v>
       </c>
       <c r="D53" t="n">
-        <v>79.05</v>
+        <v>248.2</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>102.77</v>
+        <v>102.81</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>6.09</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.61215748</v>
       </c>
       <c r="D54" t="n">
-        <v>116.65</v>
+        <v>225</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.68</v>
+        <v>102.79</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>98.72</v>
+        <v>88.09</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>3.96</v>
+        <v>14.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="D55" t="n">
-        <v>1070</v>
+        <v>116.5</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.66</v>
+        <v>102.54</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>98.89</v>
+        <v>98.72</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.90543241</v>
       </c>
       <c r="D56" t="n">
-        <v>269.46</v>
+        <v>151.23</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>101.9</v>
+        <v>102.18</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>5.22</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.50675322</v>
       </c>
       <c r="D57" t="n">
-        <v>149.92</v>
+        <v>269.09</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>101.3</v>
+        <v>101.76</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>92.27</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>9.029999999999999</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6546,22 +6546,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D58" t="n">
-        <v>146.57</v>
+        <v>146.25</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.23</v>
+        <v>100.01</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.38</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6573,22 +6573,22 @@
         <v>0.37810738</v>
       </c>
       <c r="D59" t="n">
-        <v>353.05</v>
+        <v>353</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.62</v>
+        <v>99.61</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6600,49 +6600,49 @@
         <v>1.35094641</v>
       </c>
       <c r="D60" t="n">
-        <v>98.15000000000001</v>
+        <v>98.14</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>98.95</v>
+        <v>98.94</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="D61" t="n">
-        <v>1266.61</v>
+        <v>117.97</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>98.42</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>88.89</v>
+        <v>105.36</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9.85</v>
+        <v>-6.94</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6669,88 +6669,88 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="D63" t="n">
-        <v>117.55</v>
+        <v>1252.5</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.06999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-7.29</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="D64" t="n">
-        <v>56.95</v>
+        <v>22.76</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>96.72</v>
+        <v>96.67</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-9.43</v>
+        <v>-356.29</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="D65" t="n">
-        <v>22.74</v>
+        <v>56.91</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>96.58</v>
+        <v>96.65000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-356.38</v>
+        <v>-9.5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6777,7 +6777,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6789,22 +6789,22 @@
         <v>0.97307689</v>
       </c>
       <c r="D67" t="n">
-        <v>129.95</v>
+        <v>129.88</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>94.37</v>
+        <v>94.31999999999999</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-17.07</v>
+        <v>-17.12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,22 +6816,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D68" t="n">
-        <v>106.89</v>
+        <v>106.82</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>93.56999999999999</v>
+        <v>93.51000000000001</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-16.88</v>
+        <v>-16.94</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6843,22 +6843,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>132.03</v>
+        <v>132.09</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.08</v>
+        <v>92.12</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6885,7 +6885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>192.75</v>
+        <v>192.7</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>89.40000000000001</v>
+        <v>89.37</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-18.42</v>
+        <v>-18.45</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>55.92</v>
+        <v>56</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.08</v>
+        <v>77.19</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33.45</v>
+        <v>-33.34</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>104.16</v>
+        <v>104.5</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>49.14</v>
+        <v>49.3</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>249.17</v>
+        <v>248.96</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.07</v>
+        <v>45.03</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-7.04</v>
+        <v>-7.08</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44110.19</v>
+        <v>44110.22</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>197.24</v>
+        <v>197.27</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-19 20:53:04</t>
+          <t>2026-09-20 20:58:09</t>
         </is>
       </c>
     </row>
@@ -4926,16 +4926,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19 20:53:04</t>
+          <t>2026-09-20 20:58:09</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44110.19</v>
+        <v>44110.22</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>43912.95</v>
@@ -4953,7 +4953,7 @@
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>232.43</v>
+        <v>232.46</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5049,7 +5049,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5076,7 +5076,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5103,7 +5103,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5130,7 +5130,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5157,7 +5157,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5184,7 +5184,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5211,7 +5211,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5238,7 +5238,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5292,7 +5292,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5319,7 +5319,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5346,7 +5346,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5400,7 +5400,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5427,7 +5427,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5454,7 +5454,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5481,7 +5481,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5508,7 +5508,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5535,7 +5535,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5562,7 +5562,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5589,7 +5589,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5616,7 +5616,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5643,7 +5643,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5670,7 +5670,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5697,7 +5697,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5724,7 +5724,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5751,7 +5751,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5805,7 +5805,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5832,7 +5832,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5859,7 +5859,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5886,7 +5886,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5913,7 +5913,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5940,7 +5940,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5967,7 +5967,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5994,7 +5994,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6021,7 +6021,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6048,7 +6048,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6075,7 +6075,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6102,7 +6102,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6129,7 +6129,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6156,7 +6156,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6183,7 +6183,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6210,7 +6210,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6237,7 +6237,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6264,7 +6264,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6291,7 +6291,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6318,7 +6318,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6345,7 +6345,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6372,7 +6372,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6399,7 +6399,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6426,7 +6426,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6453,7 +6453,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6480,7 +6480,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6507,7 +6507,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6534,7 +6534,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6561,7 +6561,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6588,7 +6588,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6615,7 +6615,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6642,7 +6642,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6669,7 +6669,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6696,7 +6696,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6723,7 +6723,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6750,7 +6750,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6777,7 +6777,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6804,7 +6804,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6831,7 +6831,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6858,7 +6858,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6885,7 +6885,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6912,7 +6912,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6966,7 +6966,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44110.22</v>
+        <v>44929.43</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43912.95</v>
+        <v>44717.68</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6166.2</v>
+        <v>6970.93</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1633571102147867</v>
+        <v>0.1846762966348096</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>197.27</v>
+        <v>211.75</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-20 20:58:09</t>
+          <t>2026-09-21 22:05:55</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>110.3</v>
+        <v>111.8</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7059.2</v>
+        <v>7155.2</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1608833267696437</v>
+        <v>0.160125859211791</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1013.43</v>
+        <v>1109.43</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1676262907785112</v>
+        <v>0.183505161459996</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.95</v>
+        <v>15.706</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4335.5</v>
+        <v>4554.74</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09880859916276492</v>
+        <v>0.1019302962861015</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>904.79</v>
+        <v>1124.03</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2637325801364732</v>
+        <v>0.3276377193059162</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1512.6</v>
+        <v>1533.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2668.12</v>
+        <v>2705.52</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06080802666316604</v>
+        <v>0.06054669535647989</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1472.16</v>
+        <v>1509.56</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.230944178735075</v>
+        <v>1.262216127629687</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -858,17 +858,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LCLN_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lincoln International</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US5337141015</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -877,55 +877,55 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>22.51</v>
+        <v>509.97</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>26.11</v>
+        <v>616.5</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1925.81</v>
+        <v>1898.55</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2240.77</v>
+        <v>2305.36</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05106846839948075</v>
+        <v>0.05159153493857539</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>314.96</v>
+        <v>406.81</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1635467673342645</v>
+        <v>0.2142740512496379</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>6.01</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>LCLN_US_EQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Lincoln International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US5337141015</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -934,38 +934,38 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>509.97</v>
+        <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>557.98</v>
+        <v>24.68</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1898.55</v>
+        <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2082</v>
+        <v>2122.65</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04745000656368967</v>
+        <v>0.04750267708182976</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>183.45</v>
+        <v>196.84</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.09662637275815754</v>
+        <v>0.1022115369636672</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4.31</v>
+        <v>10.2</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -997,25 +997,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>109.47</v>
+        <v>111.53</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2026.5</v>
+        <v>2069.12</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04618512886710717</v>
+        <v>0.04630473191696963</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>379.93</v>
+        <v>422.55</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2307402661289833</v>
+        <v>0.2566243767346666</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2.09</v>
+        <v>5.67</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>1.15856288</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>222.53</v>
+        <v>227.19</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1814.45</v>
+        <v>1856.47</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.0413523844425969</v>
+        <v>0.04154584831324264</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>561.77</v>
+        <v>603.79</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4484545135230066</v>
+        <v>0.4819985950122936</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-28.85</v>
+        <v>-26.19</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>243.39</v>
+        <v>257.62</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1743.68</v>
+        <v>1849.64</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03973949445003574</v>
+        <v>0.04139300008839686</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-252.38</v>
+        <v>-146.42</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.126439084997445</v>
+        <v>-0.07335450838151157</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-0.47</v>
+        <v>3.87</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>151.79</v>
+        <v>158.02</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1425.26</v>
+        <v>1486.98</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.0324825150600213</v>
+        <v>0.03327705027542893</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-446.58</v>
+        <v>-384.86</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2385780835968886</v>
+        <v>-0.2056051799299086</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-73.48</v>
+        <v>-69.56999999999999</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.46</v>
+        <v>119.5</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1417.65</v>
+        <v>1421.21</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03230907867676017</v>
+        <v>0.0318051867691175</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>73.86</v>
+        <v>77.42</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.05496394525930391</v>
+        <v>0.05761316872427984</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-2.33</v>
+        <v>0.59</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>41.55</v>
+        <v>41.75</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1318.86</v>
+        <v>1330.74</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03005759637684331</v>
+        <v>0.02978056321102119</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>90.52</v>
+        <v>102.4</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.07369295146295</v>
+        <v>0.08336454076232966</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-52.32</v>
+        <v>-47.41</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>443.3</v>
+        <v>445.1</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1224.36</v>
+        <v>1229.62</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.0279038857042839</v>
+        <v>0.02751760384112289</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>309.87</v>
+        <v>315.13</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3388446019092609</v>
+        <v>0.3445964417325504</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-1.1</v>
+        <v>-0.89</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>470.9125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>699.4</v>
+        <v>709</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1119.04</v>
+        <v>1134.4</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02550358085736373</v>
+        <v>0.02538668027306795</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>365.58</v>
+        <v>380.94</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.4852016032702465</v>
+        <v>0.5055875560746423</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>108.95</v>
+        <v>110</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1105.15</v>
+        <v>1115.8</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02518701957438119</v>
+        <v>0.02497043181301941</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>497.96</v>
+        <v>508.61</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.8201057329666166</v>
+        <v>0.8376455475221923</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>330.62</v>
+        <v>338.29</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1081.03</v>
+        <v>1108.51</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02463731056462317</v>
+        <v>0.02480728927141974</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>439.04</v>
+        <v>466.52</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6838735805853674</v>
+        <v>0.7266779856384056</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-27.71</v>
+        <v>-26.38</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>27.762</v>
+        <v>28.302</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1077.32</v>
+        <v>1100.67</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02455275747895973</v>
+        <v>0.02463183830761433</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>-18.46</v>
+        <v>4.89</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-0.01684644727956342</v>
+        <v>0.004462574604391392</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11.6</v>
+        <v>14.01</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>334.8</v>
+        <v>338.93</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>764.51</v>
+        <v>775.63</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.0174236332939512</v>
+        <v>0.01735778457351877</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>273.46</v>
+        <v>284.58</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.556888300580389</v>
+        <v>0.5795336523775583</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-16.38</v>
+        <v>-15.34</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>493.99</v>
+        <v>501.8</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>687.54</v>
+        <v>699.9299999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01566944164879885</v>
+        <v>0.01566369809902014</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>153.16</v>
+        <v>165.55</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2866125229237621</v>
+        <v>0.3097982708933718</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-20.16</v>
+        <v>-19.04</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1015.5</v>
+        <v>1020.5</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>660.08</v>
+        <v>663.33</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.0150436120713546</v>
+        <v>0.01484462854860205</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>-2.6</v>
+        <v>0.65</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>-0.003923462304581397</v>
+        <v>0.0009808655761453493</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1770,17 +1770,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US6701002056</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1789,55 +1789,55 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>20</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>57.84</v>
+        <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>43.25</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>867.58</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>645.52</v>
+        <v>640.85</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01471178109365656</v>
+        <v>0.0143415497646294</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-222.06</v>
+        <v>91.67</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.2559533414785956</v>
+        <v>0.1669215921919953</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-4.3</v>
+        <v>-18.22</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>US6701002056</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1846,38 +1846,38 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>20</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>77.20222067</v>
+        <v>57.84</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>93.79000000000001</v>
+        <v>39.89</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>867.58</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>643.65</v>
+        <v>596.66</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01466916269198792</v>
+        <v>0.01335262398777214</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>94.47</v>
+        <v>-270.92</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1720201026985688</v>
+        <v>-0.3122709144977985</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-19.37</v>
+        <v>-2.43</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>312</v>
+        <v>313.74</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>542.51</v>
+        <v>546.73</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01236412250762117</v>
+        <v>0.01223524304098593</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>53.24</v>
+        <v>57.46</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1088151736260143</v>
+        <v>0.1174402681545977</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-27.4</v>
+        <v>-26.39</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1941,114 +1941,114 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EMHGl_EQ</t>
+          <t>GOOGL_US_EQ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>iShares J.P. Morgan USD EM Bond (Dist)</t>
+          <t>Alphabet (Class A)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IE00BDFGJ734</t>
+          <t>US02079K3059</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3.8455</v>
+        <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.742</v>
+        <v>355.99</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>538.37</v>
+        <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>523.88</v>
+        <v>532.48</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01193953383217375</v>
+        <v>0.01191634301111003</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-14.49</v>
+        <v>124.56</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.02691457547783123</v>
+        <v>0.3053539909786233</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
+        <v>-4.91</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOOGL_US_EQ</t>
+          <t>EMHGl_EQ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alphabet (Class A)</t>
+          <t>iShares J.P. Morgan USD EM Bond (Dist)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US02079K3059</t>
+          <t>IE00BDFGJ734</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>269.43</v>
+        <v>3.8455</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>350.83</v>
+        <v>3.7535</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>407.92</v>
+        <v>538.37</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>523.62</v>
+        <v>525.49</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01193360827900057</v>
+        <v>0.01175991415434986</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>115.7</v>
+        <v>-12.88</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2836340458913512</v>
+        <v>-0.02392406709140554</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-5.79</v>
+        <v>0</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>230.17</v>
+        <v>231.3</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>190.7</v>
+        <v>192.05</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004346165346635744</v>
+        <v>0.004297877244748501</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-5.82</v>
+        <v>-4.47</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.02961530633014451</v>
+        <v>-0.02274577651129656</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.27</v>
+        <v>0.16</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>271.45</v>
+        <v>269.94</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>128.48</v>
+        <v>128.04</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002928134891115681</v>
+        <v>0.002865400689495434</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>28.63</v>
+        <v>28.19</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2867300951427141</v>
+        <v>0.2823234852278418</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.85</v>
+        <v>1.07</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.81488812</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>121.66614911</v>
+        <v>38.28159448</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>127.51</v>
+        <v>42.88</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>119.73</v>
+        <v>108.23</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.14</v>
+        <v>122.34</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002874804912557068</v>
+        <v>0.002737840677545075</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>6.41</v>
+        <v>14.11</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.05353712519836298</v>
+        <v>0.1303705072530721</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.63</v>
+        <v>0.99</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.81488812</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>188.32884805</v>
+        <v>121.66614911</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>209.45</v>
+        <v>123</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>110.41</v>
+        <v>119.73</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>123.57</v>
+        <v>121.94</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002816233098499103</v>
+        <v>0.002728889097759084</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>13.16</v>
+        <v>2.21</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.119192102164659</v>
+        <v>0.01845819761129207</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.7</v>
+        <v>0.89</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45.93199509</v>
+        <v>188.32884805</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>49.4</v>
+        <v>203.72</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>121.97</v>
+        <v>120.45</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002779768155894923</v>
+        <v>0.002695544463056272</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>9.26</v>
+        <v>10.04</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.08215774997781919</v>
+        <v>0.09093379222896476</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.7</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.55804584</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>38.28159448</v>
+        <v>91.20399179</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>42.55</v>
+        <v>102.98</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>108.23</v>
+        <v>105.28</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>121.14</v>
+        <v>120</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002760851966919004</v>
+        <v>0.002685473935797033</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>12.91</v>
+        <v>14.72</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.11928300840802</v>
+        <v>0.1398176291793313</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.55804584</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>91.20399179</v>
+        <v>228.00445932</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>103.17</v>
+        <v>270.06</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.96</v>
+        <v>119.53</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002733959071748421</v>
+        <v>0.002674955829548494</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>14.68</v>
+        <v>19.68</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1394376899696049</v>
+        <v>0.1970956434651978</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.77</v>
+        <v>1.07</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>228.00445932</v>
+        <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>270.2</v>
+        <v>567.65</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.34</v>
+        <v>119.03</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002719828906489302</v>
+        <v>0.002663766354816007</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>19.49</v>
+        <v>13.28</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1951927891837757</v>
+        <v>0.1255791962174941</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>0.85</v>
+        <v>1.02</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>509.16500577</v>
+        <v>45.93199509</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>566.27</v>
+        <v>48.05</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>105.75</v>
+        <v>112.71</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.49</v>
+        <v>118.9</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002700456905730831</v>
+        <v>0.00266085709138556</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>12.74</v>
+        <v>6.19</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1204728132387707</v>
+        <v>0.05491970543873659</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.79</v>
+        <v>0.95</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2593,25 +2593,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>63.04</v>
+        <v>62.69</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.81</v>
+        <v>117.41</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002684959305124054</v>
+        <v>0.002627512456682747</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1029866117404737</v>
+        <v>0.09924164404082014</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.77</v>
+        <v>1.01</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>2.50421091</v>
@@ -2650,25 +2650,25 @@
         <v>235.02053179</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>251.36</v>
+        <v>250.12</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.14</v>
+        <v>116.81</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002669689610408553</v>
+        <v>0.002614085087003761</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07695136526615794</v>
+        <v>0.07391744047071802</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.76</v>
+        <v>0.99</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.62445608</v>
@@ -2707,25 +2707,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>372.37</v>
+        <v>365.4</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.74</v>
+        <v>114.81</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002660573374757508</v>
+        <v>0.002569327188073811</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>7.58</v>
+        <v>5.65</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.0694393550751191</v>
+        <v>0.05175888603884207</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.74</v>
+        <v>0.99</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.42010405</v>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>88.20999999999999</v>
+        <v>56.39</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.15</v>
+        <v>114.17</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002601545748916992</v>
+        <v>0.002555004660416227</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>12.62</v>
+        <v>6.53</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1242982369742933</v>
+        <v>0.06066518023039762</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>53.65641702</v>
+        <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>56.5</v>
+        <v>87.44</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>114.15</v>
+        <v>113.4</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002601545748916992</v>
+        <v>0.002537772869328196</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>6.51</v>
+        <v>11.87</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.060479375696767</v>
+        <v>0.1169112577563282</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.77</v>
+        <v>1.06</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2878,25 +2878,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.63</v>
+        <v>113.39</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002544113464315407</v>
+        <v>0.002537549079833546</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>21.97</v>
+        <v>23.73</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.2450368057104617</v>
+        <v>0.2646665179567254</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.59010207</v>
@@ -2935,25 +2935,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>206.02</v>
+        <v>210.24</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>107.62</v>
+        <v>110.07</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002452723201913681</v>
+        <v>0.002463250967609828</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-11.14</v>
+        <v>-8.69</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.09380262714718761</v>
+        <v>-0.07317278544964634</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.63</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>324.07677699</v>
+        <v>306.99401668</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>340.97</v>
+        <v>351.91</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>101.39</v>
+        <v>92.83</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>107.52</v>
+        <v>107.56</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002450444143000919</v>
+        <v>0.00240707980445274</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>6.13</v>
+        <v>14.73</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.06045961140151888</v>
+        <v>0.1586771517828288</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
         <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.61</v>
+        <v>12.59</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>107.28</v>
+        <v>107.35</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002444974401610292</v>
+        <v>0.002402380225065095</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.01064531323598681</v>
+        <v>0.01130475741874705</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.78</v>
+        <v>1.02</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>11.40066159</v>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>306.99401668</v>
+        <v>54.82621761</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>349.36</v>
+        <v>51.83</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>92.83</v>
+        <v>112.48</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>106.55</v>
+        <v>107.23</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002428337271547135</v>
+        <v>0.002399694751129298</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>13.72</v>
+        <v>-5.25</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1477970483679845</v>
+        <v>-0.04667496443812233</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.42255419</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>104.90344487</v>
+        <v>324.07677699</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>122.48</v>
+        <v>339.2</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>89.53</v>
+        <v>101.39</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>105.42</v>
+        <v>107.19</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002402583905832932</v>
+        <v>0.002398799593150699</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>15.89</v>
+        <v>5.8</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1774824081313526</v>
+        <v>0.0572048525495611</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.42255419</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>148.63893521</v>
+        <v>104.90344487</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>174.49</v>
+        <v>124.04</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>88.44</v>
+        <v>89.53</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>104.71</v>
+        <v>106.99</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002386402587552327</v>
+        <v>0.002394323803257704</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>16.27</v>
+        <v>17.46</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1839665309814563</v>
+        <v>0.1950184295766782</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.76</v>
+        <v>0.95</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.80409618</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>54.82621761</v>
+        <v>148.63893521</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>50.72</v>
+        <v>177.19</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>112.48</v>
+        <v>88.44</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>104.71</v>
+        <v>106.56</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002386402587552327</v>
+        <v>0.002384700854987765</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>-7.77</v>
+        <v>18.12</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>-0.06907894736842105</v>
+        <v>0.2048846675712347</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.71</v>
+        <v>0.95</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.80409618</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>249.91595261</v>
+        <v>176.50746647</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>269.42</v>
+        <v>207.86</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>95.94</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>104.31</v>
+        <v>106.48</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002377286351901283</v>
+        <v>0.002382910539030567</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>17.02</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.0872420262664165</v>
+        <v>0.1902526268723452</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.1285649</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>176.50746647</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>203.38</v>
+        <v>1090.27</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>103.96</v>
+        <v>104.83</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002369309645706618</v>
+        <v>0.002345985272413358</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>14.5</v>
+        <v>5.94</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1620836127878381</v>
+        <v>0.06006674082313682</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.1285649</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3448,25 +3448,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>318.25</v>
+        <v>320.58</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>103.51</v>
+        <v>104.49</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002359053880599192</v>
+        <v>0.002338376429595266</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>-0.53</v>
+        <v>0.45</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>-0.005094194540561323</v>
+        <v>0.004325259515570934</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.8</v>
+        <v>1.03</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.43583007</v>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>74.99726962</v>
+        <v>194.45976548</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>79.39</v>
+        <v>227.33</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>103.21</v>
+        <v>104.08</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002352216703860908</v>
+        <v>0.002329201060314626</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>6.53</v>
+        <v>15.99</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.0675424079437319</v>
+        <v>0.1815189011238506</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>249.91595261</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>1072.44</v>
+        <v>267.52</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>102.89</v>
+        <v>103.8</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002344923715340072</v>
+        <v>0.002322934954464433</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4</v>
+        <v>7.86</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.04044898371928405</v>
+        <v>0.0819262038774234</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.84</v>
+        <v>1.03</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.90543241</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>221.99877812</v>
+        <v>137.713206</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>248.2</v>
+        <v>151.72</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>102.81</v>
+        <v>102.74</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002343100468209864</v>
+        <v>0.002299213268031559</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>11.63</v>
+        <v>10.47</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1275499012941435</v>
+        <v>0.1134713341281023</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.78</v>
+        <v>0.99</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.90543241</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.50675322</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>194.45976548</v>
+        <v>257.81779936</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>225</v>
+        <v>269.98</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.79</v>
+        <v>102.32</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002342644656427311</v>
+        <v>0.00228981410925627</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>14.7</v>
+        <v>5.64</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1668747871495062</v>
+        <v>0.05833678113363673</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.50675322</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>113.12478542</v>
+        <v>74.99726962</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>116.5</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>98.72</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.54</v>
+        <v>102.18</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002336947009145408</v>
+        <v>0.002286681056331173</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>3.82</v>
+        <v>5.5</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.03869529983792545</v>
+        <v>0.05688870500620603</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.85</v>
+        <v>1.03</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>137.713206</v>
+        <v>113.12478542</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>151.23</v>
+        <v>115.18</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>92.27</v>
+        <v>98.72</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>102.18</v>
+        <v>101.6</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002328742397059467</v>
+        <v>0.002273701265641487</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>9.91</v>
+        <v>2.88</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1074021892272678</v>
+        <v>0.02917341977309562</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.78</v>
+        <v>1.07</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.5550481</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>257.81779936</v>
+        <v>221.99877812</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>269.09</v>
+        <v>242.23</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>101.76</v>
+        <v>100.55</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.00231917034962587</v>
+        <v>0.002250203368703263</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>5.08</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.05254447662391394</v>
+        <v>0.1027637639833297</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.82</v>
+        <v>0.97</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.5550481</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.37810738</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>147.21071381</v>
+        <v>341.38450299</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>146.25</v>
+        <v>355.25</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.01</v>
+        <v>100.46</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002279286818652548</v>
+        <v>0.002248189263251415</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.16</v>
+        <v>4.95</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.001602403605408112</v>
+        <v>0.05182703381844833</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.37810738</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>341.38450299</v>
+        <v>147.21071381</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>353</v>
+        <v>146.12</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>99.61</v>
+        <v>100.14</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002270170583001503</v>
+        <v>0.002241027999422624</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>4.1</v>
+        <v>0.29</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.04292744215265416</v>
+        <v>0.002904356534802203</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.82</v>
+        <v>1.04</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.10445851</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>96.717382</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>98.14</v>
+        <v>1277.79</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>98.94</v>
+        <v>99.83</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002254900888286002</v>
+        <v>0.002234090525088481</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>2.26</v>
+        <v>10.94</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.02337608605709557</v>
+        <v>0.1230734615817302</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.83</v>
+        <v>0.96</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.10445851</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.11796351</v>
+        <v>13.30225117</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>127.23134407</v>
+        <v>10.85229847</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>117.97</v>
+        <v>9.99</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>105.36</v>
+        <v>106.96</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>98.42</v>
+        <v>99.39</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002243049781939644</v>
+        <v>0.002224243787323892</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-6.94</v>
+        <v>-7.57</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.0658694001518603</v>
+        <v>-0.07077412116679133</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.79</v>
+        <v>1.01</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.11796351</v>
+        <v>13.30225117</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>10.85229847</v>
+        <v>96.717382</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>9.9</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98.28</v>
+        <v>98.86</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002239859099461778</v>
+        <v>0.002212382944107455</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-8.68</v>
+        <v>2.18</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.08115183246073299</v>
+        <v>0.02254861398427803</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.77</v>
+        <v>1.04</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1252.5</v>
+        <v>117.03</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>88.89</v>
+        <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>97.64</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002225273122420106</v>
+        <v>0.00218978020514783</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>8.75</v>
+        <v>-7.51</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.09843626954663066</v>
+        <v>-0.07127942293090357</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.76</v>
+        <v>1.02</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,55 +4240,55 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>105.04894536</v>
+        <v>62.95787236</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>22.76</v>
+        <v>56.9</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>96.67</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002203166250966321</v>
+        <v>0.002167401255682855</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-356.29</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.7865815966089722</v>
+        <v>-0.08761186999528969</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-6.79</v>
+        <v>1.01</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0</v>
+        <v>2.27580753</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,55 +4297,55 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>62.95787236</v>
+        <v>105.04894536</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>56.91</v>
+        <v>22.34</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>96.65000000000001</v>
+        <v>95.09</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002202710439183769</v>
+        <v>0.002128014304624498</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-9.5</v>
+        <v>-357.87</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.08949599623174752</v>
+        <v>-0.7900697633345108</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.77</v>
+        <v>-5.82</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>76.24181082</v>
+        <v>154.44822659</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>68.05</v>
+        <v>129.81</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>104.98</v>
+        <v>111.44</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>94.41</v>
+        <v>94.47</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002151659519537916</v>
+        <v>0.002114139355956214</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-10.57</v>
+        <v>-16.97</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.1006858449228425</v>
+        <v>-0.1522792534099067</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.93456659</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>154.44822659</v>
+        <v>127.79185697</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>129.88</v>
+        <v>135.05</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>111.44</v>
+        <v>88.38</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>94.31999999999999</v>
+        <v>94.39</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002149608366516431</v>
+        <v>0.002112349039999016</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-17.12</v>
+        <v>6.01</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1536252692031587</v>
+        <v>0.06800181036433582</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.93456659</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>106.82</v>
+        <v>107.39</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>93.51000000000001</v>
+        <v>94.22</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002131147989323065</v>
+        <v>0.00210854461858997</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-16.94</v>
+        <v>-16.23</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.1533725667722952</v>
+        <v>-0.1469443186962426</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.72</v>
+        <v>0.97</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.17308322</v>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.85908491</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>127.79185697</v>
+        <v>76.24181082</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>132.09</v>
+        <v>67.62</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>88.38</v>
+        <v>104.98</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>92.12</v>
+        <v>94.02</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002099469070435683</v>
+        <v>0.002104068828696975</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3.74</v>
+        <v>-10.96</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.04231726634985291</v>
+        <v>-0.1044008382549057</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.85908491</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4588,25 +4588,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>104.52</v>
+        <v>106</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>90.91</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002071892457591272</v>
+        <v>0.002067814930563715</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-1.86</v>
+        <v>-0.37</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.0200495849951493</v>
+        <v>-0.003988358305486688</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.79</v>
+        <v>1</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>1.16558147</v>
@@ -4645,25 +4645,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>192.7</v>
+        <v>191.8</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>89.37</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002036794950334749</v>
+        <v>0.001995083344802545</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-18.45</v>
+        <v>-18.67</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.171118530884808</v>
+        <v>-0.1731589686514562</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>0.6214908</v>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>56</v>
+        <v>55.92</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.19</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001759205574760425</v>
+        <v>0.00172855005667469</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33.34</v>
+        <v>-33.29</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.301637564462137</v>
+        <v>-0.3011851985886185</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.74</v>
+        <v>0.97</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>104.5</v>
+        <v>104.63</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49.3</v>
+        <v>49.47</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001123576043991307</v>
+        <v>0.001107086630032327</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.02987257154794234</v>
+        <v>0.03342385627741801</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>248.96</v>
+        <v>248.28</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001026260228416401</v>
+        <v>0.001007052725923887</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-7.08</v>
+        <v>-7.11</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1358664363845711</v>
+        <v>-0.1364421416234888</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.44</v>
+        <v>0.55</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4865,7 +4865,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20 20:58:09</t>
+          <t>2026-09-21 22:05:55</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44110.22</v>
+        <v>44929.43</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43912.95</v>
+        <v>44717.68</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37746.75</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6166.2</v>
+        <v>6970.93</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1633571102147867</v>
+        <v>0.1846762966348096</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>232.46</v>
+        <v>246.94</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>110.3</v>
+        <v>111.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7059.2</v>
+        <v>7155.2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1013.43</v>
+        <v>1109.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.95</v>
+        <v>15.706</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4335.5</v>
+        <v>4554.74</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>904.79</v>
+        <v>1124.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,76 +5088,76 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1512.6</v>
+        <v>1533.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2668.12</v>
+        <v>2705.52</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1472.16</v>
+        <v>1509.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LCLN_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>115</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>26.11</v>
+        <v>616.5</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2240.77</v>
+        <v>2305.36</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1925.81</v>
+        <v>1898.55</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>314.96</v>
+        <v>406.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>LCLN_US_EQ</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="D6" t="n">
-        <v>557.98</v>
+        <v>24.68</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2082</v>
+        <v>2122.65</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1898.55</v>
+        <v>1925.81</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>183.45</v>
+        <v>196.84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,22 +5169,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D7" t="n">
-        <v>109.47</v>
+        <v>111.53</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2026.5</v>
+        <v>2069.12</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>379.93</v>
+        <v>422.55</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5196,22 +5196,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>222.53</v>
+        <v>227.19</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1814.45</v>
+        <v>1856.47</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>561.77</v>
+        <v>603.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5223,22 +5223,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>243.39</v>
+        <v>257.62</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1743.68</v>
+        <v>1849.64</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-252.38</v>
+        <v>-146.42</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>151.79</v>
+        <v>158.02</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1425.26</v>
+        <v>1486.98</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-446.58</v>
+        <v>-384.86</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,22 +5277,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.46</v>
+        <v>119.5</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1417.65</v>
+        <v>1421.21</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>73.86</v>
+        <v>77.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5304,22 +5304,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>41.55</v>
+        <v>41.75</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1318.86</v>
+        <v>1330.74</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>90.52</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>443.3</v>
+        <v>445.1</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1224.36</v>
+        <v>1229.62</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>309.87</v>
+        <v>315.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,22 +5358,22 @@
         <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>699.4</v>
+        <v>709</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1119.04</v>
+        <v>1134.4</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>365.58</v>
+        <v>380.94</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5385,22 +5385,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D15" t="n">
-        <v>108.95</v>
+        <v>110</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1105.15</v>
+        <v>1115.8</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>497.96</v>
+        <v>508.61</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,22 +5412,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>330.62</v>
+        <v>338.29</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1081.03</v>
+        <v>1108.51</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>439.04</v>
+        <v>466.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5439,22 +5439,22 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>27.762</v>
+        <v>28.302</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1077.32</v>
+        <v>1100.67</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-18.46</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>334.8</v>
+        <v>338.93</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>764.51</v>
+        <v>775.63</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>273.46</v>
+        <v>284.58</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>493.99</v>
+        <v>501.8</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>687.54</v>
+        <v>699.9299999999999</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>153.16</v>
+        <v>165.55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,76 +5520,76 @@
         <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>1015.5</v>
+        <v>1020.5</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>660.08</v>
+        <v>663.33</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-2.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>20</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>43.25</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>645.52</v>
+        <v>640.85</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>867.58</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-222.06</v>
+        <v>91.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>93.79000000000001</v>
+        <v>39.89</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>643.65</v>
+        <v>596.66</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>867.58</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>94.47</v>
+        <v>-270.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,76 +5601,76 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>312</v>
+        <v>313.74</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>542.51</v>
+        <v>546.73</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>53.24</v>
+        <v>57.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EMHGl_EQ</t>
+          <t>GOOGL_US_EQ</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3.742</v>
+        <v>355.99</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>523.88</v>
+        <v>532.48</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>538.37</v>
+        <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-14.49</v>
+        <v>124.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GOOGL_US_EQ</t>
+          <t>EMHGl_EQ</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="D25" t="n">
-        <v>350.83</v>
+        <v>3.7535</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>523.62</v>
+        <v>525.49</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>407.92</v>
+        <v>538.37</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>115.7</v>
+        <v>-12.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>230.17</v>
+        <v>231.3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>190.7</v>
+        <v>192.05</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-5.82</v>
+        <v>-4.47</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,211 +5709,211 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>271.45</v>
+        <v>269.94</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>128.48</v>
+        <v>128.04</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>28.63</v>
+        <v>28.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.81488812</v>
       </c>
       <c r="D28" t="n">
-        <v>127.51</v>
+        <v>42.88</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.14</v>
+        <v>122.34</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>119.73</v>
+        <v>108.23</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6.41</v>
+        <v>14.11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="D29" t="n">
-        <v>209.45</v>
+        <v>123</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>123.57</v>
+        <v>121.94</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>110.41</v>
+        <v>119.73</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>13.16</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7905852</v>
       </c>
       <c r="D30" t="n">
-        <v>49.4</v>
+        <v>203.72</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>121.97</v>
+        <v>120.45</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>112.71</v>
+        <v>110.41</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>9.26</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.55804584</v>
       </c>
       <c r="D31" t="n">
-        <v>42.55</v>
+        <v>102.98</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>121.14</v>
+        <v>120</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>108.23</v>
+        <v>105.28</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>12.91</v>
+        <v>14.72</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.59183053</v>
       </c>
       <c r="D32" t="n">
-        <v>103.17</v>
+        <v>270.06</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.96</v>
+        <v>119.53</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14.68</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>270.2</v>
+        <v>567.65</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.34</v>
+        <v>119.03</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>19.49</v>
+        <v>13.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="D34" t="n">
-        <v>566.27</v>
+        <v>48.05</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.49</v>
+        <v>118.9</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>105.75</v>
+        <v>112.71</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.74</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5925,22 +5925,22 @@
         <v>2.50421091</v>
       </c>
       <c r="D35" t="n">
-        <v>63.04</v>
+        <v>62.69</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.81</v>
+        <v>117.41</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>11</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5952,22 +5952,22 @@
         <v>0.62445608</v>
       </c>
       <c r="D36" t="n">
-        <v>251.36</v>
+        <v>250.12</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.14</v>
+        <v>116.81</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5979,76 +5979,76 @@
         <v>0.42010405</v>
       </c>
       <c r="D37" t="n">
-        <v>372.37</v>
+        <v>365.4</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.74</v>
+        <v>114.81</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>7.58</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D38" t="n">
-        <v>88.20999999999999</v>
+        <v>56.39</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.15</v>
+        <v>114.17</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>12.62</v>
+        <v>6.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>2.70722512</v>
+        <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>56.5</v>
+        <v>87.44</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>114.15</v>
+        <v>113.4</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>107.64</v>
+        <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6.51</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6060,22 +6060,22 @@
         <v>1.59010207</v>
       </c>
       <c r="D40" t="n">
-        <v>94.06999999999999</v>
+        <v>95.34999999999999</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.63</v>
+        <v>113.39</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>21.97</v>
+        <v>23.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6087,49 +6087,49 @@
         <v>0.7</v>
       </c>
       <c r="D41" t="n">
-        <v>206.02</v>
+        <v>210.24</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>107.62</v>
+        <v>110.07</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-11.14</v>
+        <v>-8.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="D42" t="n">
-        <v>340.97</v>
+        <v>351.91</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>107.52</v>
+        <v>107.56</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>101.39</v>
+        <v>92.83</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>6.13</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6141,184 +6141,184 @@
         <v>11.40066159</v>
       </c>
       <c r="D43" t="n">
-        <v>12.61</v>
+        <v>12.59</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>107.28</v>
+        <v>107.35</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="D44" t="n">
-        <v>349.36</v>
+        <v>51.83</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>106.55</v>
+        <v>107.23</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>92.83</v>
+        <v>112.48</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13.72</v>
+        <v>-5.25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.42255419</v>
       </c>
       <c r="D45" t="n">
-        <v>122.48</v>
+        <v>339.2</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>105.42</v>
+        <v>107.19</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>89.53</v>
+        <v>101.39</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>15.89</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="D46" t="n">
-        <v>174.49</v>
+        <v>124.04</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>104.71</v>
+        <v>106.99</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>88.44</v>
+        <v>89.53</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>16.27</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.80409618</v>
       </c>
       <c r="D47" t="n">
-        <v>50.72</v>
+        <v>177.19</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>104.71</v>
+        <v>106.56</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>112.48</v>
+        <v>88.44</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-7.77</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.68495686</v>
       </c>
       <c r="D48" t="n">
-        <v>269.42</v>
+        <v>207.86</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104.31</v>
+        <v>106.48</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>95.94</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>8.369999999999999</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.1285649</v>
       </c>
       <c r="D49" t="n">
-        <v>203.38</v>
+        <v>1090.27</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>103.96</v>
+        <v>104.83</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>14.5</v>
+        <v>5.94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6330,481 +6330,481 @@
         <v>0.43583007</v>
       </c>
       <c r="D50" t="n">
-        <v>318.25</v>
+        <v>320.58</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>103.51</v>
+        <v>104.49</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-0.53</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="D51" t="n">
-        <v>79.39</v>
+        <v>227.33</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>103.21</v>
+        <v>104.08</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>6.53</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="D52" t="n">
-        <v>1072.44</v>
+        <v>267.52</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>102.89</v>
+        <v>103.8</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>4</v>
+        <v>7.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.90543241</v>
       </c>
       <c r="D53" t="n">
-        <v>248.2</v>
+        <v>151.72</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>102.81</v>
+        <v>102.74</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>11.63</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.50675322</v>
       </c>
       <c r="D54" t="n">
-        <v>225</v>
+        <v>269.98</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.79</v>
+        <v>102.32</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>14.7</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="D55" t="n">
-        <v>116.5</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.54</v>
+        <v>102.18</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>98.72</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>3.82</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.17949395</v>
       </c>
       <c r="D56" t="n">
-        <v>151.23</v>
+        <v>115.18</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>102.18</v>
+        <v>101.6</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>92.27</v>
+        <v>98.72</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>9.91</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.5550481</v>
       </c>
       <c r="D57" t="n">
-        <v>269.09</v>
+        <v>242.23</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>101.76</v>
+        <v>100.55</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>5.08</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.37810738</v>
       </c>
       <c r="D58" t="n">
-        <v>146.25</v>
+        <v>355.25</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.01</v>
+        <v>100.46</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>0.16</v>
+        <v>4.95</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D59" t="n">
-        <v>353</v>
+        <v>146.12</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>99.61</v>
+        <v>100.14</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>4.1</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.10445851</v>
       </c>
       <c r="D60" t="n">
-        <v>98.14</v>
+        <v>1277.79</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>98.94</v>
+        <v>99.83</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>2.26</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.11796351</v>
+        <v>13.30225117</v>
       </c>
       <c r="D61" t="n">
-        <v>117.97</v>
+        <v>9.99</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>98.42</v>
+        <v>99.39</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>105.36</v>
+        <v>106.96</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-6.94</v>
+        <v>-7.57</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.35094641</v>
       </c>
       <c r="D62" t="n">
-        <v>9.9</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>98.28</v>
+        <v>98.86</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-8.68</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>1252.5</v>
+        <v>117.03</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>97.64</v>
+        <v>97.84999999999999</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>88.89</v>
+        <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>8.75</v>
+        <v>-7.51</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="D64" t="n">
-        <v>22.76</v>
+        <v>56.9</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>96.67</v>
+        <v>96.84999999999999</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-356.29</v>
+        <v>-9.300000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>2.27580753</v>
+        <v>5.691347</v>
       </c>
       <c r="D65" t="n">
-        <v>56.91</v>
+        <v>22.34</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>96.65000000000001</v>
+        <v>95.09</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>106.15</v>
+        <v>452.96</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-9.5</v>
+        <v>-357.87</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="D66" t="n">
-        <v>68.05</v>
+        <v>129.81</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>94.41</v>
+        <v>94.47</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>104.98</v>
+        <v>111.44</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-10.57</v>
+        <v>-16.97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>0.93456659</v>
       </c>
       <c r="D67" t="n">
-        <v>129.88</v>
+        <v>135.05</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>94.31999999999999</v>
+        <v>94.39</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>111.44</v>
+        <v>88.38</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-17.12</v>
+        <v>6.01</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6816,49 +6816,49 @@
         <v>1.17308322</v>
       </c>
       <c r="D68" t="n">
-        <v>106.82</v>
+        <v>107.39</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>93.51000000000001</v>
+        <v>94.22</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-16.94</v>
+        <v>-16.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.85908491</v>
       </c>
       <c r="D69" t="n">
-        <v>132.09</v>
+        <v>67.62</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>92.12</v>
+        <v>94.02</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>88.38</v>
+        <v>104.98</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>3.74</v>
+        <v>-10.96</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6870,22 +6870,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D70" t="n">
-        <v>104.52</v>
+        <v>106</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>90.91</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-1.86</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>192.7</v>
+        <v>191.8</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>89.37</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-18.45</v>
+        <v>-18.67</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>56</v>
+        <v>55.92</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.19</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33.34</v>
+        <v>-33.29</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>104.5</v>
+        <v>104.63</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>49.3</v>
+        <v>49.47</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>248.96</v>
+        <v>248.28</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45.03</v>
+        <v>45</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-7.08</v>
+        <v>-7.11</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44929.43</v>
+        <v>44793.81</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44717.68</v>
+        <v>44582.03</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37746.75</v>
+        <v>37747.22</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6970.93</v>
+        <v>6834.81</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1846762966348096</v>
+        <v>0.1810679038085454</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>211.75</v>
+        <v>211.78</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>35.19</v>
+        <v>35.66</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:55</t>
+          <t>2026-09-22 21:32:10</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>111.8</v>
+        <v>112.56</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7155.2</v>
+        <v>7203.84</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.160125859211791</v>
+        <v>0.1617141905333589</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1109.43</v>
+        <v>1158.07</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.183505161459996</v>
+        <v>0.1915504559386149</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.706</v>
+        <v>15.958</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4554.74</v>
+        <v>4627.82</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1019302962861015</v>
+        <v>0.103886838857344</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1124.03</v>
+        <v>1197.11</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.3276377193059162</v>
+        <v>0.3489394323623973</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1533.8</v>
+        <v>1509.4</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2705.52</v>
+        <v>2662.48</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06054669535647989</v>
+        <v>0.05976823444319382</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1509.56</v>
+        <v>1466.52</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.262216127629687</v>
+        <v>1.226228301949898</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>509.97</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>616.5</v>
+        <v>621.33</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2305.36</v>
+        <v>2327.5</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05159153493857539</v>
+        <v>0.05224849225779484</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>406.81</v>
+        <v>428.95</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2142740512496379</v>
+        <v>0.2259355824181612</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>8.449999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>24.68</v>
+        <v>24.03</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2122.65</v>
+        <v>2070.37</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04750267708182976</v>
+        <v>0.04647635270280159</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>196.84</v>
+        <v>144.56</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.1022115369636672</v>
+        <v>0.07506451830658269</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>10.2</v>
+        <v>13.6</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>111.53</v>
+        <v>106.04</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>2069.12</v>
+        <v>1970.72</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04630473191696963</v>
+        <v>0.04423937643921867</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>422.55</v>
+        <v>324.15</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.2566243767346666</v>
+        <v>0.1968637835014606</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5.67</v>
+        <v>8.57</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>1.15856288</v>
@@ -1029,17 +1029,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US5738741041</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,55 +1048,55 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.9260596</v>
+        <v>9.6</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>150.09436705</v>
+        <v>278.55208333</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>227.19</v>
+        <v>263.03</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1252.68</v>
+        <v>1996.06</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1856.47</v>
+        <v>1891.79</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04154584831324264</v>
+        <v>0.04246752961047205</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>603.79</v>
+        <v>-104.27</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4819985950122936</v>
+        <v>-0.0522379086800998</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-26.19</v>
+        <v>7.37</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US5738741041</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1105,38 +1105,38 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.6</v>
+        <v>10.9260596</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>278.55208333</v>
+        <v>150.09436705</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>257.62</v>
+        <v>228.19</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1996.06</v>
+        <v>1252.68</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1849.64</v>
+        <v>1867.91</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04139300008839686</v>
+        <v>0.04193146344715685</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-146.42</v>
+        <v>615.23</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.07335450838151157</v>
+        <v>0.4911310151036178</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3.87</v>
+        <v>-24.04</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>158.02</v>
+        <v>155.44</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1486.98</v>
+        <v>1465.27</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03327705027542893</v>
+        <v>0.03289286713236479</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-384.86</v>
+        <v>-406.57</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2056051799299086</v>
+        <v>-0.2172033934524318</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-69.56999999999999</v>
+        <v>-66.41</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.5</v>
+        <v>119.52</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1421.21</v>
+        <v>1423.94</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.0318051867691175</v>
+        <v>0.03196507757918986</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>77.42</v>
+        <v>80.15000000000001</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.05761316872427984</v>
+        <v>0.05964473615669116</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>0.59</v>
+        <v>2.95</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>41.75</v>
+        <v>40.33</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1330.74</v>
+        <v>1287.76</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.02978056321102119</v>
+        <v>0.02890806375505817</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>102.4</v>
+        <v>59.42</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.08336454076232966</v>
+        <v>0.0483742286337659</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-47.41</v>
+        <v>-45.31</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>445.1</v>
+        <v>430.2</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1229.62</v>
+        <v>1188.85</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02751760384112289</v>
+        <v>0.02668769925700511</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>315.13</v>
+        <v>274.36</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3445964417325504</v>
+        <v>0.3000142155737078</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-0.89</v>
+        <v>-0.59</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>470.9125</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1134.4</v>
+        <v>1112</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02538668027306795</v>
+        <v>0.0249625449583965</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>380.94</v>
+        <v>358.54</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.5055875560746423</v>
+        <v>0.4758580415682319</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1428,57 +1428,57 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLOYl_EQ</t>
+          <t>KOIDl_EQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lloyds Banking Group</t>
+          <t>KraneShares Global Humanoid Robotics and Physical AI Index (Acc)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GB0008706128</t>
+          <t>IE000O6Z73N7</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1014.362806</v>
+        <v>52</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>59.85909543</v>
+        <v>28.53653846</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>110</v>
+        <v>28.505</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>607.1900000000001</v>
+        <v>1095.78</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1115.8</v>
+        <v>1110.51</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02497043181301941</v>
+        <v>0.02492909694401879</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>508.61</v>
+        <v>14.73</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.8376455475221923</v>
+        <v>0.01344247932979248</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
+        <v>15.96</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>338.29</v>
+        <v>336.01</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1108.51</v>
+        <v>1102.97</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02480728927141974</v>
+        <v>0.02475983652226852</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>466.52</v>
+        <v>460.98</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.7266779856384056</v>
+        <v>0.7180485677346999</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-26.38</v>
+        <v>-25.3</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1542,57 +1542,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>KOIDl_EQ</t>
+          <t>LLOYl_EQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KraneShares Global Humanoid Robotics and Physical AI Index (Acc)</t>
+          <t>Lloyds Banking Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>IE000O6Z73N7</t>
+          <t>GB0008706128</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>52</v>
+        <v>1014.362806</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>28.53653846</v>
+        <v>59.85909543</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>28.302</v>
+        <v>108.3</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>1095.78</v>
+        <v>607.1900000000001</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1100.67</v>
+        <v>1098.55</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02463183830761433</v>
+        <v>0.02466061489572525</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>4.89</v>
+        <v>491.36</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.004462574604391392</v>
+        <v>0.8092359887349923</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>14.01</v>
+        <v>0</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2024-08-08</t>
         </is>
       </c>
     </row>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>338.93</v>
+        <v>339.97</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>775.63</v>
+        <v>779.37</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01735778457351877</v>
+        <v>0.01749555635272076</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>284.58</v>
+        <v>288.32</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5795336523775583</v>
+        <v>0.5871499847266062</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-15.34</v>
+        <v>-14.51</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>501.8</v>
+        <v>497.93</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>699.9299999999999</v>
+        <v>695.75</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01566369809902014</v>
+        <v>0.01561842684784565</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>165.55</v>
+        <v>161.37</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.3097982708933718</v>
+        <v>0.3019761218608481</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-19.04</v>
+        <v>-18.13</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1020.5</v>
+        <v>1034</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>663.33</v>
+        <v>672.1</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01484462854860205</v>
+        <v>0.01508752380084379</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.65</v>
+        <v>9.42</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.0009808655761453493</v>
+        <v>0.01421500573429106</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>93.18000000000001</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>640.85</v>
+        <v>652.1</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.0143415497646294</v>
+        <v>0.0146385571649014</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>91.67</v>
+        <v>102.92</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1669215921919953</v>
+        <v>0.1874066790487636</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-18.22</v>
+        <v>-17.29</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>57.84</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>39.89</v>
+        <v>39.38</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>596.66</v>
+        <v>590.0700000000001</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01335262398777214</v>
+        <v>0.0132460871435261</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-270.92</v>
+        <v>-277.51</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.3122709144977985</v>
+        <v>-0.3198667558034994</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-2.43</v>
+        <v>-0.91</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>313.74</v>
+        <v>305.89</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>546.73</v>
+        <v>533.98</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01223524304098593</v>
+        <v>0.01198696021302569</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>57.46</v>
+        <v>44.71</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1174402681545977</v>
+        <v>0.0913810370552047</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-26.39</v>
+        <v>-25.58</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>355.99</v>
+        <v>351.89</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>532.48</v>
+        <v>527.27</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01191634301111003</v>
+        <v>0.01183633190666702</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>124.56</v>
+        <v>119.35</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.3053539909786233</v>
+        <v>0.2925818787997647</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-4.91</v>
+        <v>-4.21</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,22 +2023,22 @@
         <v>3.8455</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3.7535</v>
+        <v>3.755</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>525.49</v>
+        <v>525.7</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01175991415434986</v>
+        <v>0.01180108802574554</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-12.88</v>
+        <v>-12.67</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02392406709140554</v>
+        <v>-0.02353400078013262</v>
       </c>
       <c r="M25" s="2" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>231.3</v>
+        <v>231.8</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>192.05</v>
+        <v>192.81</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004297877244748501</v>
+        <v>0.004328262853802545</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-4.47</v>
+        <v>-3.71</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.02274577651129656</v>
+        <v>-0.01887848565031549</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.16</v>
+        <v>0.51</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>269.94</v>
+        <v>269.64</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>128.04</v>
+        <v>128.12</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002865400689495434</v>
+        <v>0.002876080269846907</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>28.19</v>
+        <v>28.27</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2823234852278418</v>
+        <v>0.2831246870305458</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.55804584</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>38.28159448</v>
+        <v>91.20399179</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>42.88</v>
+        <v>103.75</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>108.23</v>
+        <v>105.28</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>122.34</v>
+        <v>121.11</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002737840677545075</v>
+        <v>0.002718717463949101</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>14.11</v>
+        <v>15.83</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.1303705072530721</v>
+        <v>0.1503609422492401</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.99</v>
+        <v>1.19</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.55804584</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.81488812</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>121.66614911</v>
+        <v>38.28159448</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>123</v>
+        <v>42.31</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>119.73</v>
+        <v>108.23</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>121.94</v>
+        <v>120.93</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002728889097759084</v>
+        <v>0.00271467676422562</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2.21</v>
+        <v>12.7</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.01845819761129207</v>
+        <v>0.1173426961101358</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.89</v>
+        <v>1.19</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.81488812</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>188.32884805</v>
+        <v>235.02053179</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>203.72</v>
+        <v>258</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>110.41</v>
+        <v>108.77</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>120.45</v>
+        <v>120.7</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002695544463056272</v>
+        <v>0.002709513647912283</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>10.04</v>
+        <v>11.93</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.09093379222896476</v>
+        <v>0.1096809782109037</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.18</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>91.20399179</v>
+        <v>188.32884805</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>102.98</v>
+        <v>203</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>105.28</v>
+        <v>110.41</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120</v>
+        <v>120.24</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002685473935797033</v>
+        <v>0.002699187415285608</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>14.72</v>
+        <v>9.83</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1398176291793313</v>
+        <v>0.08903179059867766</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.59183053</v>
+        <v>1.32559468</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>228.00445932</v>
+        <v>121.66614911</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>270.06</v>
+        <v>120.7</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.53</v>
+        <v>119.87</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002674955829548494</v>
+        <v>0.002690881532520673</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>19.68</v>
+        <v>0.14</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1970956434651978</v>
+        <v>0.001169297586235697</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.59183053</v>
+        <v>1.32559468</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>509.16500577</v>
+        <v>45.93199509</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>567.65</v>
+        <v>47.9</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>105.75</v>
+        <v>112.71</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.03</v>
+        <v>118.73</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002663766354816007</v>
+        <v>0.002665290434271958</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.28</v>
+        <v>6.02</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1255791962174941</v>
+        <v>0.05341140981279389</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.50421091</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45.93199509</v>
+        <v>57.56703616</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>48.05</v>
+        <v>63.04</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>112.71</v>
+        <v>106.81</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.9</v>
+        <v>118.27</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.00266085709138556</v>
+        <v>0.002654964201645283</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>6.19</v>
+        <v>11.46</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.05491970543873659</v>
+        <v>0.1072933245950754</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.95</v>
+        <v>1.19</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.50421091</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.59183053</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>57.56703616</v>
+        <v>228.00445932</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>62.69</v>
+        <v>266.57</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>106.81</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.41</v>
+        <v>118.2</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002627512456682747</v>
+        <v>0.002653392818419485</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>10.6</v>
+        <v>18.35</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.09924164404082014</v>
+        <v>0.1837756634952429</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.59183053</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.28038062</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>235.02053179</v>
+        <v>509.16500577</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>250.12</v>
+        <v>556.04</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>108.77</v>
+        <v>105.75</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.81</v>
+        <v>116.8</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002614085087003761</v>
+        <v>0.002621965153903518</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>11.05</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07391744047071802</v>
+        <v>0.1044917257683215</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.99</v>
+        <v>1.2</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.28038062</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.73400968</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>350.55601106</v>
+        <v>79.10567143</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>365.4</v>
+        <v>88.61</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>109.16</v>
+        <v>101.53</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>114.81</v>
+        <v>115.11</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002569327188073811</v>
+        <v>0.002584027473166386</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5.65</v>
+        <v>13.58</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.05175888603884207</v>
+        <v>0.1337535703732887</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.99</v>
+        <v>1.23</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.73400968</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.42010405</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>53.65641702</v>
+        <v>350.55601106</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>56.39</v>
+        <v>363.85</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>107.64</v>
+        <v>109.16</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.17</v>
+        <v>114.52</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002555004660416227</v>
+        <v>0.002570782957406086</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>6.53</v>
+        <v>5.36</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.06066518023039762</v>
+        <v>0.0491022352510077</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.42010405</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>87.44</v>
+        <v>56.07</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.4</v>
+        <v>113.72</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002537772869328196</v>
+        <v>0.00255282429196839</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>11.87</v>
+        <v>6.08</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1169112577563282</v>
+        <v>0.05648457822370866</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2878,25 +2878,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>95.34999999999999</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.39</v>
+        <v>112.03</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002537549079833546</v>
+        <v>0.002514886611231259</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>23.73</v>
+        <v>22.37</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.2646665179567254</v>
+        <v>0.249498103948249</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.95</v>
+        <v>1.11</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.59010207</v>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.7</v>
+        <v>2.76637723</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>225.62857143</v>
+        <v>54.82621761</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>210.24</v>
+        <v>52.67</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>118.76</v>
+        <v>112.48</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.07</v>
+        <v>109.16</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002463250967609828</v>
+        <v>0.002450459898973527</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-8.69</v>
+        <v>-3.32</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.07317278544964634</v>
+        <v>-0.02951635846372688</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.63</v>
+        <v>1.15</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0</v>
+        <v>2.76637723</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>306.99401668</v>
+        <v>12.56856884</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>351.91</v>
+        <v>12.77</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>107.56</v>
+        <v>109.07</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.00240707980445274</v>
+        <v>0.002448439549111787</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>14.73</v>
+        <v>2.92</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1586771517828288</v>
+        <v>0.0275082430522845</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,55 +3043,55 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.7</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>12.56856884</v>
+        <v>225.62857143</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>12.59</v>
+        <v>205.93</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>106.15</v>
+        <v>118.76</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>107.35</v>
+        <v>108</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002402380225065095</v>
+        <v>0.002424419834088869</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.2</v>
+        <v>-10.76</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.01130475741874705</v>
+        <v>-0.0906028965981812</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>1.02</v>
+        <v>-0.43</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.43583007</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>54.82621761</v>
+        <v>322.35040597</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>51.83</v>
+        <v>327.7</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>112.48</v>
+        <v>104.04</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.23</v>
+        <v>107</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002399694751129298</v>
+        <v>0.00240197150229175</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>-5.25</v>
+        <v>2.96</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>-0.04667496443812233</v>
+        <v>0.02845059592464437</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.95</v>
+        <v>1.21</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.43583007</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>339.2</v>
+        <v>336.05</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>107.19</v>
+        <v>106.39</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002398799593150699</v>
+        <v>0.002388278019895507</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.0572048525495611</v>
+        <v>0.04931452805996647</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>0.42255419</v>
@@ -3220,25 +3220,25 @@
         <v>104.90344487</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>124.04</v>
+        <v>122.65</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>106.99</v>
+        <v>105.98</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002394323803257704</v>
+        <v>0.002379074203858688</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>17.46</v>
+        <v>16.45</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1950184295766782</v>
+        <v>0.1837372947615324</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.95</v>
+        <v>1.12</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>1.1533463</v>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.50675322</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>148.63893521</v>
+        <v>257.81779936</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>177.19</v>
+        <v>277</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>88.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>106.56</v>
+        <v>105.17</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002384700854987765</v>
+        <v>0.002360891055103022</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>18.12</v>
+        <v>8.49</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.2048846675712347</v>
+        <v>0.08781547372776169</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.95</v>
+        <v>1.21</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.50675322</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.51881442</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>176.50746647</v>
+        <v>249.91595261</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>207.86</v>
+        <v>270.47</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>106.48</v>
+        <v>105.13</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002382910539030567</v>
+        <v>0.002359993121831137</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>17.02</v>
+        <v>9.19</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1902526268723452</v>
+        <v>0.09578903481342506</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.96</v>
+        <v>1.2</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.51881442</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.80409618</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>148.63893521</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>1090.27</v>
+        <v>174.41</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>98.89</v>
+        <v>88.44</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>104.83</v>
+        <v>105.07</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002345985272413358</v>
+        <v>0.00235864622192331</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>5.94</v>
+        <v>16.63</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.06006674082313682</v>
+        <v>0.1880370872908186</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.80409618</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.68495686</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>322.35040597</v>
+        <v>176.50746647</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>320.58</v>
+        <v>204.23</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>104.04</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>104.49</v>
+        <v>104.8</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002338376429595266</v>
+        <v>0.002352585172338088</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.45</v>
+        <v>15.34</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.004325259515570934</v>
+        <v>0.1714732841493405</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.68495686</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.90543241</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>194.45976548</v>
+        <v>137.713206</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>227.33</v>
+        <v>154.19</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>88.09</v>
+        <v>92.27</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>104.08</v>
+        <v>104.59</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002329201060314626</v>
+        <v>0.002347871022660693</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>15.99</v>
+        <v>12.32</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1815189011238506</v>
+        <v>0.1335211878183592</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.90543241</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.40867246</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>249.91595261</v>
+        <v>306.99401668</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>267.52</v>
+        <v>340.7</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>95.94</v>
+        <v>92.83</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>103.8</v>
+        <v>104.31</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002322934954464433</v>
+        <v>0.0023415854897575</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>7.86</v>
+        <v>11.48</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.0819262038774234</v>
+        <v>0.1236669180221911</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.40867246</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.1285649</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>137.713206</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>151.72</v>
+        <v>1068.48</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>92.27</v>
+        <v>98.89</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>102.74</v>
+        <v>102.92</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002299213268031559</v>
+        <v>0.002310382308559504</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>10.47</v>
+        <v>4.03</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1134713341281023</v>
+        <v>0.04075235109717869</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.99</v>
+        <v>1.24</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.1285649</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.74206342</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>257.81779936</v>
+        <v>74.99726962</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>269.98</v>
+        <v>78.42</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.32</v>
+        <v>102.35</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.00228981410925627</v>
+        <v>0.002297586759435146</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.05833678113363673</v>
+        <v>0.05864708316094331</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1.03</v>
+        <v>1.2</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.74206342</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>74.99726962</v>
+        <v>194.45976548</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>78.43000000000001</v>
+        <v>222.16</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>102.18</v>
+        <v>101.89</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002286681056331173</v>
+        <v>0.002287260526808471</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>5.5</v>
+        <v>13.8</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.05688870500620603</v>
+        <v>0.1566579634464752</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>113.12478542</v>
+        <v>147.21071381</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>115.18</v>
+        <v>148</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>98.72</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.6</v>
+        <v>101.61</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002273701265641487</v>
+        <v>0.002280974993905278</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>2.88</v>
+        <v>1.76</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.02917341977309562</v>
+        <v>0.01762643965948923</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3847,25 +3847,25 @@
         <v>221.99877812</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>242.23</v>
+        <v>244</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>100.55</v>
+        <v>101.47</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002250203368703263</v>
+        <v>0.002277832227453681</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>10.29</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1027637639833297</v>
+        <v>0.1128536959859618</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.97</v>
+        <v>1.14</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>0.5550481</v>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.17949395</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>341.38450299</v>
+        <v>113.12478542</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>355.25</v>
+        <v>114.6</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>100.46</v>
+        <v>101.27</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002248189263251415</v>
+        <v>0.002273342561094257</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>4.95</v>
+        <v>2.55</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.05182703381844833</v>
+        <v>0.02583063209076175</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1.03</v>
+        <v>1.25</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.17949395</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>13.30225117</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>147.21071381</v>
+        <v>10.85229847</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>146.12</v>
+        <v>10.11</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>106.96</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>100.14</v>
+        <v>100.76</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002241027999422624</v>
+        <v>0.002261893911877727</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.29</v>
+        <v>-6.2</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.002904356534802203</v>
+        <v>-0.05796559461480928</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>13.30225117</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.35094641</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>96.717382</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1277.79</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>88.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>99.83</v>
+        <v>100.35</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002234090525088481</v>
+        <v>0.002252690095840908</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>10.94</v>
+        <v>3.67</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1230734615817302</v>
+        <v>0.03796028134050475</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.96</v>
+        <v>1.21</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.35094641</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>10.85229847</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>9.99</v>
+        <v>1265.69</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>106.96</v>
+        <v>88.89</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>99.39</v>
+        <v>99.05</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002224243787323892</v>
+        <v>0.002223507264504653</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-7.57</v>
+        <v>10.16</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.07077412116679133</v>
+        <v>0.1142985712678592</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.11796351</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>96.717382</v>
+        <v>127.23134407</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>97.84999999999999</v>
+        <v>116.56</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>105.36</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>98.86</v>
+        <v>97.63</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002212382944107455</v>
+        <v>0.002191630633352743</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.18</v>
+        <v>-7.73</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.02254861398427803</v>
+        <v>-0.07336750189825361</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.11796351</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>127.23134407</v>
+        <v>341.38450299</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>117.03</v>
+        <v>343.5</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>105.36</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>97.84999999999999</v>
+        <v>97.31</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.00218978020514783</v>
+        <v>0.002184447167177665</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-7.51</v>
+        <v>1.8</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.07127942293090357</v>
+        <v>0.01884619411579939</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17308322</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>62.95787236</v>
+        <v>126.99866255</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>56.9</v>
+        <v>110.08</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>106.15</v>
+        <v>110.45</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>96.84999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002167401255682855</v>
+        <v>0.002171876101371279</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-13.7</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.08761186999528969</v>
+        <v>-0.1240380262562245</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17308322</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,38 +4297,38 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>105.04894536</v>
+        <v>62.95787236</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>22.34</v>
+        <v>56.67</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>95.09</v>
+        <v>96.62</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002128014304624498</v>
+        <v>0.002168957818237653</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-357.87</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.7900697633345108</v>
+        <v>-0.08977861516721619</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-5.82</v>
+        <v>1.19</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0</v>
+        <v>2.27580753</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4360,25 +4360,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>129.81</v>
+        <v>131.29</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>94.47</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002114139355956214</v>
+        <v>0.002148529836302275</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-16.97</v>
+        <v>-15.73</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.1522792534099067</v>
+        <v>-0.1411521895190237</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.96</v>
+        <v>1.15</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>0.97307689</v>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>127.79185697</v>
+        <v>107.56862839</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>135.05</v>
+        <v>107.77</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>94.39</v>
+        <v>94.11</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002112349039999016</v>
+        <v>0.002112612505426884</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>6.01</v>
+        <v>1.34</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.06800181036433582</v>
+        <v>0.01444432467392476</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.85908491</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>126.99866255</v>
+        <v>76.24181082</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>107.39</v>
+        <v>67.05</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>110.45</v>
+        <v>104.98</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>94.22</v>
+        <v>93.39</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.00210854461858997</v>
+        <v>0.002096449706532958</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-16.23</v>
+        <v>-11.59</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.1469443186962426</v>
+        <v>-0.1104019813297771</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.97</v>
+        <v>1.21</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.85908491</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.93456659</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>76.24181082</v>
+        <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>67.62</v>
+        <v>132.75</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>104.98</v>
+        <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>94.02</v>
+        <v>92.95</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002104068828696975</v>
+        <v>0.002086572440542226</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-10.96</v>
+        <v>4.57</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1044008382549057</v>
+        <v>0.05170853134193257</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.93456659</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,38 +4582,38 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>5.691347</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>107.56862839</v>
+        <v>105.04894536</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>106</v>
+        <v>21.77</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>92.77</v>
+        <v>452.96</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002067814930563715</v>
+        <v>0.002083878640726572</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-0.37</v>
+        <v>-360.13</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.003988358305486688</v>
+        <v>-0.7950591663723067</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1</v>
+        <v>-5.03</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
@@ -4645,25 +4645,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>191.8</v>
+        <v>196.21</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>89.15000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.001995083344802545</v>
+        <v>0.002050879592984806</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-18.67</v>
+        <v>-16.46</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1731589686514562</v>
+        <v>-0.1526618438137637</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1</v>
+        <v>1.19</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>0.6214908</v>
@@ -4702,25 +4702,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>55.92</v>
+        <v>55.79</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>77.23999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.00172855005667469</v>
+        <v>0.001733011214737599</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-33.29</v>
+        <v>-33.33</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.3011851985886185</v>
+        <v>-0.3015470912874332</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.97</v>
+        <v>1.17</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4759,25 +4759,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>104.63</v>
+        <v>103.92</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49.47</v>
+        <v>49.22</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001107086630032327</v>
+        <v>0.001104906891054205</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.03342385627741801</v>
+        <v>0.02820137873407145</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.51</v>
+        <v>0.59</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.63221571</v>
@@ -4816,25 +4816,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>248.28</v>
+        <v>250.8</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45</v>
+        <v>45.54</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001007052725923887</v>
+        <v>0.001022297030040806</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>-7.11</v>
+        <v>-6.57</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>-0.1364421416234888</v>
+        <v>-0.1260794473229706</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.24236298</v>
@@ -4926,34 +4926,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21 22:05:55</t>
+          <t>2026-09-22 21:32:10</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44929.43</v>
+        <v>44793.81</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44717.68</v>
+        <v>44582.03</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37746.75</v>
+        <v>37747.22</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6970.93</v>
+        <v>6834.81</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1846762966348096</v>
+        <v>0.1810679038085454</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>246.94</v>
+        <v>247.44</v>
       </c>
       <c r="J2" t="n">
         <v>73</v>
@@ -5022,7 +5022,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5034,22 +5034,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>111.8</v>
+        <v>112.56</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7155.2</v>
+        <v>7203.84</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1109.43</v>
+        <v>1158.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5061,22 +5061,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>15.706</v>
+        <v>15.958</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4554.74</v>
+        <v>4627.82</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1124.03</v>
+        <v>1197.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5088,22 +5088,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1533.8</v>
+        <v>1509.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2705.52</v>
+        <v>2662.48</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1509.56</v>
+        <v>1466.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5115,22 +5115,22 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>616.5</v>
+        <v>621.33</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2305.36</v>
+        <v>2327.5</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>406.81</v>
+        <v>428.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5142,22 +5142,22 @@
         <v>115</v>
       </c>
       <c r="D6" t="n">
-        <v>24.68</v>
+        <v>24.03</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2122.65</v>
+        <v>2070.37</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>196.84</v>
+        <v>144.56</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5169,76 +5169,76 @@
         <v>24.80610988</v>
       </c>
       <c r="D7" t="n">
-        <v>111.53</v>
+        <v>106.04</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>2069.12</v>
+        <v>1970.72</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>422.55</v>
+        <v>324.15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.9260596</v>
+        <v>9.6</v>
       </c>
       <c r="D8" t="n">
-        <v>227.19</v>
+        <v>263.03</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1856.47</v>
+        <v>1891.79</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1252.68</v>
+        <v>1996.06</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>603.79</v>
+        <v>-104.27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.6</v>
+        <v>10.9260596</v>
       </c>
       <c r="D9" t="n">
-        <v>257.62</v>
+        <v>228.19</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1849.64</v>
+        <v>1867.91</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1996.06</v>
+        <v>1252.68</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-146.42</v>
+        <v>615.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5250,22 +5250,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>158.02</v>
+        <v>155.44</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1486.98</v>
+        <v>1465.27</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-384.86</v>
+        <v>-406.57</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5277,22 +5277,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.5</v>
+        <v>119.52</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1421.21</v>
+        <v>1423.94</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>77.42</v>
+        <v>80.15000000000001</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5304,22 +5304,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>41.75</v>
+        <v>40.33</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1330.74</v>
+        <v>1287.76</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>102.4</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5331,22 +5331,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>445.1</v>
+        <v>430.2</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1229.62</v>
+        <v>1188.85</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>315.13</v>
+        <v>274.36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5358,49 +5358,49 @@
         <v>160</v>
       </c>
       <c r="D14" t="n">
-        <v>709</v>
+        <v>695</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1134.4</v>
+        <v>1112</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>380.94</v>
+        <v>358.54</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LLOYl_EQ</t>
+          <t>KOIDl_EQ</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1014.362806</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>110</v>
+        <v>28.505</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1115.8</v>
+        <v>1110.51</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>607.1900000000001</v>
+        <v>1095.78</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>508.61</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5412,49 +5412,49 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>338.29</v>
+        <v>336.01</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1108.51</v>
+        <v>1102.97</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>466.52</v>
+        <v>460.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>KOIDl_EQ</t>
+          <t>LLOYl_EQ</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>52</v>
+        <v>1014.362806</v>
       </c>
       <c r="D17" t="n">
-        <v>28.302</v>
+        <v>108.3</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1100.67</v>
+        <v>1098.55</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>1095.78</v>
+        <v>607.1900000000001</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4.89</v>
+        <v>491.36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5466,22 +5466,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D18" t="n">
-        <v>338.93</v>
+        <v>339.97</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>775.63</v>
+        <v>779.37</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>284.58</v>
+        <v>288.32</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5493,22 +5493,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>501.8</v>
+        <v>497.93</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>699.9299999999999</v>
+        <v>695.75</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>165.55</v>
+        <v>161.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5520,22 +5520,22 @@
         <v>65</v>
       </c>
       <c r="D20" t="n">
-        <v>1020.5</v>
+        <v>1034</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>663.33</v>
+        <v>672.1</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>0.65</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5547,22 +5547,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>93.18000000000001</v>
+        <v>94.65000000000001</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>640.85</v>
+        <v>652.1</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>91.67</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5574,22 +5574,22 @@
         <v>20</v>
       </c>
       <c r="D22" t="n">
-        <v>39.89</v>
+        <v>39.38</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>596.66</v>
+        <v>590.0700000000001</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-270.92</v>
+        <v>-277.51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5601,22 +5601,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>313.74</v>
+        <v>305.89</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>546.73</v>
+        <v>533.98</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>57.46</v>
+        <v>44.71</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5628,22 +5628,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>355.99</v>
+        <v>351.89</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>532.48</v>
+        <v>527.27</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>124.56</v>
+        <v>119.35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5655,22 +5655,22 @@
         <v>140</v>
       </c>
       <c r="D25" t="n">
-        <v>3.7535</v>
+        <v>3.755</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>525.49</v>
+        <v>525.7</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-12.88</v>
+        <v>-12.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5682,22 +5682,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>231.3</v>
+        <v>231.8</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>192.05</v>
+        <v>192.81</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-4.47</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5709,346 +5709,346 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>269.94</v>
+        <v>269.64</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>128.04</v>
+        <v>128.12</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>28.19</v>
+        <v>28.27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.55804584</v>
       </c>
       <c r="D28" t="n">
-        <v>42.88</v>
+        <v>103.75</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>122.34</v>
+        <v>121.11</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>108.23</v>
+        <v>105.28</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>14.11</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.81488812</v>
       </c>
       <c r="D29" t="n">
-        <v>123</v>
+        <v>42.31</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>121.94</v>
+        <v>120.93</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>119.73</v>
+        <v>108.23</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>2.21</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="D30" t="n">
-        <v>203.72</v>
+        <v>258</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>120.45</v>
+        <v>120.7</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>110.41</v>
+        <v>108.77</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>10.04</v>
+        <v>11.93</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="D31" t="n">
-        <v>102.98</v>
+        <v>203</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120</v>
+        <v>120.24</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>105.28</v>
+        <v>110.41</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>14.72</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.59183053</v>
+        <v>1.32559468</v>
       </c>
       <c r="D32" t="n">
-        <v>270.06</v>
+        <v>120.7</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.53</v>
+        <v>119.87</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>119.73</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>19.68</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="D33" t="n">
-        <v>567.65</v>
+        <v>47.9</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.03</v>
+        <v>118.73</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>105.75</v>
+        <v>112.71</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.28</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.50421091</v>
       </c>
       <c r="D34" t="n">
-        <v>48.05</v>
+        <v>63.04</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.9</v>
+        <v>118.27</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>112.71</v>
+        <v>106.81</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6.19</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.59183053</v>
       </c>
       <c r="D35" t="n">
-        <v>62.69</v>
+        <v>266.57</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.41</v>
+        <v>118.2</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>106.81</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10.6</v>
+        <v>18.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.28038062</v>
       </c>
       <c r="D36" t="n">
-        <v>250.12</v>
+        <v>556.04</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.81</v>
+        <v>116.8</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>108.77</v>
+        <v>105.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.039999999999999</v>
+        <v>11.05</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.73400968</v>
       </c>
       <c r="D37" t="n">
-        <v>365.4</v>
+        <v>88.61</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>114.81</v>
+        <v>115.11</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>109.16</v>
+        <v>101.53</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5.65</v>
+        <v>13.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.42010405</v>
       </c>
       <c r="D38" t="n">
-        <v>56.39</v>
+        <v>363.85</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.17</v>
+        <v>114.52</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>107.64</v>
+        <v>109.16</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>6.53</v>
+        <v>5.36</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D39" t="n">
-        <v>87.44</v>
+        <v>56.07</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.4</v>
+        <v>113.72</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>11.87</v>
+        <v>6.08</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6060,130 +6060,130 @@
         <v>1.59010207</v>
       </c>
       <c r="D40" t="n">
-        <v>95.34999999999999</v>
+        <v>94.04000000000001</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.39</v>
+        <v>112.03</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>23.73</v>
+        <v>22.37</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.7</v>
+        <v>2.76637723</v>
       </c>
       <c r="D41" t="n">
-        <v>210.24</v>
+        <v>52.67</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.07</v>
+        <v>109.16</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>118.76</v>
+        <v>112.48</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-8.69</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="D42" t="n">
-        <v>351.91</v>
+        <v>12.77</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>107.56</v>
+        <v>109.07</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>14.73</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.7</v>
       </c>
       <c r="D43" t="n">
-        <v>12.59</v>
+        <v>205.93</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>107.35</v>
+        <v>108</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>106.15</v>
+        <v>118.76</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1.2</v>
+        <v>-10.76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.43583007</v>
       </c>
       <c r="D44" t="n">
-        <v>51.83</v>
+        <v>327.7</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.23</v>
+        <v>107</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>112.48</v>
+        <v>104.04</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-5.25</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6195,22 +6195,22 @@
         <v>0.42255419</v>
       </c>
       <c r="D45" t="n">
-        <v>339.2</v>
+        <v>336.05</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>107.19</v>
+        <v>106.39</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>5.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6222,292 +6222,292 @@
         <v>1.1533463</v>
       </c>
       <c r="D46" t="n">
-        <v>124.04</v>
+        <v>122.65</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>106.99</v>
+        <v>105.98</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>17.46</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.50675322</v>
       </c>
       <c r="D47" t="n">
-        <v>177.19</v>
+        <v>277</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>106.56</v>
+        <v>105.17</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>88.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>18.12</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.51881442</v>
       </c>
       <c r="D48" t="n">
-        <v>207.86</v>
+        <v>270.47</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>106.48</v>
+        <v>105.13</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>17.02</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.80409618</v>
       </c>
       <c r="D49" t="n">
-        <v>1090.27</v>
+        <v>174.41</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>104.83</v>
+        <v>105.07</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>98.89</v>
+        <v>88.44</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>5.94</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.68495686</v>
       </c>
       <c r="D50" t="n">
-        <v>320.58</v>
+        <v>204.23</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>104.49</v>
+        <v>104.8</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>104.04</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.45</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.90543241</v>
       </c>
       <c r="D51" t="n">
-        <v>227.33</v>
+        <v>154.19</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>104.08</v>
+        <v>104.59</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>88.09</v>
+        <v>92.27</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15.99</v>
+        <v>12.32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.40867246</v>
       </c>
       <c r="D52" t="n">
-        <v>267.52</v>
+        <v>340.7</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>103.8</v>
+        <v>104.31</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>95.94</v>
+        <v>92.83</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>7.86</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.1285649</v>
       </c>
       <c r="D53" t="n">
-        <v>151.72</v>
+        <v>1068.48</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>102.74</v>
+        <v>102.92</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>92.27</v>
+        <v>98.89</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>10.47</v>
+        <v>4.03</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.74206342</v>
       </c>
       <c r="D54" t="n">
-        <v>269.98</v>
+        <v>78.42</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>102.32</v>
+        <v>102.35</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="D55" t="n">
-        <v>78.43000000000001</v>
+        <v>222.16</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>102.18</v>
+        <v>101.89</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>5.5</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D56" t="n">
-        <v>115.18</v>
+        <v>148</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>101.6</v>
+        <v>101.61</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>98.72</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>2.88</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6519,238 +6519,238 @@
         <v>0.5550481</v>
       </c>
       <c r="D57" t="n">
-        <v>242.23</v>
+        <v>244</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>100.55</v>
+        <v>101.47</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.17949395</v>
       </c>
       <c r="D58" t="n">
-        <v>355.25</v>
+        <v>114.6</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>100.46</v>
+        <v>101.27</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>4.95</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>13.30225117</v>
       </c>
       <c r="D59" t="n">
-        <v>146.12</v>
+        <v>10.11</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>100.14</v>
+        <v>100.76</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>106.96</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>0.29</v>
+        <v>-6.2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.35094641</v>
       </c>
       <c r="D60" t="n">
-        <v>1277.79</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>99.83</v>
+        <v>100.35</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>88.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>10.94</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="D61" t="n">
-        <v>9.99</v>
+        <v>1265.69</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>99.39</v>
+        <v>99.05</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>106.96</v>
+        <v>88.89</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-7.57</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.11796351</v>
       </c>
       <c r="D62" t="n">
-        <v>97.84999999999999</v>
+        <v>116.56</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>98.86</v>
+        <v>97.63</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>105.36</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2.18</v>
+        <v>-7.73</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="D63" t="n">
-        <v>117.03</v>
+        <v>343.5</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>97.84999999999999</v>
+        <v>97.31</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>105.36</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-7.51</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17308322</v>
       </c>
       <c r="D64" t="n">
-        <v>56.9</v>
+        <v>110.08</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>96.84999999999999</v>
+        <v>96.75</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>106.15</v>
+        <v>110.45</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-9.300000000000001</v>
+        <v>-13.7</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>5.691347</v>
+        <v>2.27580753</v>
       </c>
       <c r="D65" t="n">
-        <v>22.34</v>
+        <v>56.67</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>95.09</v>
+        <v>96.62</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>452.96</v>
+        <v>106.15</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-357.87</v>
+        <v>-9.529999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6762,130 +6762,130 @@
         <v>0.97307689</v>
       </c>
       <c r="D66" t="n">
-        <v>129.81</v>
+        <v>131.29</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>94.47</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-16.97</v>
+        <v>-15.73</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.16558147</v>
       </c>
       <c r="D67" t="n">
-        <v>135.05</v>
+        <v>107.77</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>94.39</v>
+        <v>94.11</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>88.38</v>
+        <v>92.77</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>6.01</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.85908491</v>
       </c>
       <c r="D68" t="n">
-        <v>107.39</v>
+        <v>67.05</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>94.22</v>
+        <v>93.39</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>110.45</v>
+        <v>104.98</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-16.23</v>
+        <v>-11.59</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>67.62</v>
+        <v>132.75</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>94.02</v>
+        <v>92.95</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>104.98</v>
+        <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-10.96</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1.16558147</v>
+        <v>5.691347</v>
       </c>
       <c r="D70" t="n">
-        <v>106</v>
+        <v>21.77</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>92.40000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>92.77</v>
+        <v>452.96</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-0.37</v>
+        <v>-360.13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6897,22 +6897,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D71" t="n">
-        <v>191.8</v>
+        <v>196.21</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>89.15000000000001</v>
+        <v>91.36</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-18.67</v>
+        <v>-16.46</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6924,22 +6924,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D72" t="n">
-        <v>55.92</v>
+        <v>55.79</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>77.23999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-33.29</v>
+        <v>-33.33</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6951,22 +6951,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D73" t="n">
-        <v>104.63</v>
+        <v>103.92</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>49.47</v>
+        <v>49.22</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6978,16 +6978,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D74" t="n">
-        <v>248.28</v>
+        <v>250.8</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45</v>
+        <v>45.54</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>-7.11</v>
+        <v>-6.57</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44793.81</v>
+        <v>44682.4</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44582.03</v>
+        <v>44470.6</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6834.81</v>
+        <v>6723.38</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1810679038085454</v>
+        <v>0.1781158983363543</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>211.78</v>
+        <v>211.8</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-22 21:32:10</t>
+          <t>2026-09-23 21:38:04</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>112.56</v>
+        <v>112.66</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7203.84</v>
+        <v>7210.24</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1617141905333589</v>
+        <v>0.1622649543220229</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1158.07</v>
+        <v>1164.47</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1915504559386149</v>
+        <v>0.1926090473173806</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.958</v>
+        <v>15.914</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4627.82</v>
+        <v>4615.06</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.103886838857344</v>
+        <v>0.1038609671929637</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1197.11</v>
+        <v>1184.35</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.3489394323623973</v>
+        <v>0.3452200856382498</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1509.4</v>
+        <v>1514.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2662.48</v>
+        <v>2671.65</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.05976823444319382</v>
+        <v>0.06012492860354612</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1466.52</v>
+        <v>1475.69</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.226228301949898</v>
+        <v>1.233895782467641</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>509.97</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>621.33</v>
+        <v>614.52</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2327.5</v>
+        <v>2318.56</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05224849225779484</v>
+        <v>0.05217871145660468</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>428.95</v>
+        <v>420.01</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2259355824181612</v>
+        <v>0.2212267256590556</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>11.8</v>
+        <v>25.55</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>24.03</v>
+        <v>23.95</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2070.37</v>
+        <v>2078.33</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04647635270280159</v>
+        <v>0.04677238517942395</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>144.56</v>
+        <v>152.52</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.07506451830658269</v>
+        <v>0.079197844024073</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>13.6</v>
+        <v>27.56</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>106.04</v>
+        <v>106.38</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1970.72</v>
+        <v>1991.27</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04423937643921867</v>
+        <v>0.04481311795346819</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>324.15</v>
+        <v>344.7</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.1968637835014606</v>
+        <v>0.20934427324681</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8.57</v>
+        <v>20.48</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>1.15856288</v>
@@ -1054,25 +1054,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>263.03</v>
+        <v>260.38</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1891.79</v>
+        <v>1886.21</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04246752961047205</v>
+        <v>0.04244876446439269</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-104.27</v>
+        <v>-109.85</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.0522379086800998</v>
+        <v>-0.05503341582918349</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>7.37</v>
+        <v>21.79</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>228.19</v>
+        <v>225.06</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1867.91</v>
+        <v>1855.56</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04193146344715685</v>
+        <v>0.04175899257746937</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>615.23</v>
+        <v>602.88</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.4911310151036178</v>
+        <v>0.4812721525050292</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-24.04</v>
+        <v>-15.19</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>155.44</v>
+        <v>151.62</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1465.27</v>
+        <v>1439.55</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03289286713236479</v>
+        <v>0.03239677389300051</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-406.57</v>
+        <v>-432.29</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2172033934524318</v>
+        <v>-0.2309438840926575</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-66.41</v>
+        <v>-53.41</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.52</v>
+        <v>119.5</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1423.94</v>
+        <v>1433.95</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03196507757918986</v>
+        <v>0.03227074705558548</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>80.15000000000001</v>
+        <v>90.16</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.05964473615669116</v>
+        <v>0.0670938167421993</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.95</v>
+        <v>12.64</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40.33</v>
+        <v>39.64</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1287.76</v>
+        <v>1267.66</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.02890806375505817</v>
+        <v>0.02852842512813104</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>59.42</v>
+        <v>39.32</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.0483742286337659</v>
+        <v>0.03201068108178518</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-45.31</v>
+        <v>-43.51</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>430.2</v>
+        <v>413.1</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1188.85</v>
+        <v>1143.65</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02668769925700511</v>
+        <v>0.02573760582316004</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>274.36</v>
+        <v>229.16</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3000142155737078</v>
+        <v>0.250587759297532</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-0.59</v>
+        <v>1.06</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1371,57 +1371,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RBSl_EQ</t>
+          <t>SNOW_US_EQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NatWest</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GB00BM8PJY71</t>
+          <t>US8334451098</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>160</v>
+        <v>4.3814255</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>470.9125</v>
+        <v>187.8703632</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>695</v>
+        <v>335.24</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>753.46</v>
+        <v>641.99</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1112</v>
+        <v>1108.37</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0249625449583965</v>
+        <v>0.02494363674744536</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>358.54</v>
+        <v>466.38</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.4758580415682319</v>
+        <v>0.726459913705821</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
+        <v>-20.85</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-11-21</t>
         </is>
       </c>
     </row>
@@ -1453,25 +1453,25 @@
         <v>28.53653846</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>28.505</v>
+        <v>28.21</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>1095.78</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1110.51</v>
+        <v>1106.93</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02492909694401879</v>
+        <v>0.02491122984639579</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>14.73</v>
+        <v>11.15</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.01344247932979248</v>
+        <v>0.01017540017156729</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>15.96</v>
+        <v>23.96</v>
       </c>
       <c r="N15" s="4" t="n">
         <v>0</v>
@@ -1485,57 +1485,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SNOW_US_EQ</t>
+          <t>RBSl_EQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>NatWest</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US8334451098</t>
+          <t>GB00BM8PJY71</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>4.3814255</v>
+        <v>160</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>187.8703632</v>
+        <v>470.9125</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>336.01</v>
+        <v>682.4</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>641.99</v>
+        <v>753.46</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1102.97</v>
+        <v>1091.84</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02475983652226852</v>
+        <v>0.02457163252914708</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>460.98</v>
+        <v>338.38</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.7180485677346999</v>
+        <v>0.4491014785124625</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-25.3</v>
+        <v>0</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
@@ -1567,22 +1567,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>108.3</v>
+        <v>107.55</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1098.55</v>
+        <v>1090.95</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02466061489572525</v>
+        <v>0.02455160326391505</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>491.36</v>
+        <v>483.76</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.8092359887349923</v>
+        <v>0.7967193135591824</v>
       </c>
       <c r="M17" s="2" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>339.97</v>
+        <v>336.95</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>779.37</v>
+        <v>778.01</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01749555635272076</v>
+        <v>0.01750895353165456</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>288.32</v>
+        <v>286.96</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.5871499847266062</v>
+        <v>0.5843804093269523</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-14.51</v>
+        <v>-11.08</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>497.93</v>
+        <v>499.98</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>695.75</v>
+        <v>703.64</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01561842684784565</v>
+        <v>0.01583527212119821</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>161.37</v>
+        <v>169.26</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.3019761218608481</v>
+        <v>0.3167408959916164</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-18.13</v>
+        <v>-14.42</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,22 +1738,22 @@
         <v>1019.5</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1034</v>
+        <v>1031.5</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>672.1</v>
+        <v>670.48</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01508752380084379</v>
+        <v>0.01508901320536208</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>9.42</v>
+        <v>7.8</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.01421500573429106</v>
+        <v>0.01177038691374419</v>
       </c>
       <c r="M20" s="2" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>94.65000000000001</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>652.1</v>
+        <v>666.16</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.0146385571649014</v>
+        <v>0.01499179250221334</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>102.92</v>
+        <v>116.98</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1874066790487636</v>
+        <v>0.2130084853782002</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-17.29</v>
+        <v>-13.46</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>57.84</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>39.38</v>
+        <v>38.26</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>590.0700000000001</v>
+        <v>577.41</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.0132460871435261</v>
+        <v>0.01299449217710911</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-277.51</v>
+        <v>-290.17</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.3198667558034994</v>
+        <v>-0.33445907005694</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-0.91</v>
+        <v>5.33</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>305.89</v>
+        <v>302.52</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>533.98</v>
+        <v>531.9</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01198696021302569</v>
+        <v>0.01197029907518806</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>44.71</v>
+        <v>42.63</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.0913810370552047</v>
+        <v>0.08712980562879392</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-25.58</v>
+        <v>-22.25</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1941,114 +1941,114 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GOOGL_US_EQ</t>
+          <t>EMHGl_EQ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alphabet (Class A)</t>
+          <t>iShares J.P. Morgan USD EM Bond (Dist)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US02079K3059</t>
+          <t>IE00BDFGJ734</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2</v>
+        <v>140</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>269.43</v>
+        <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>351.89</v>
+        <v>3.7185</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>407.92</v>
+        <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>527.27</v>
+        <v>520.59</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01183633190666702</v>
+        <v>0.0117157698731945</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>119.35</v>
+        <v>-17.78</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2925818787997647</v>
+        <v>-0.03302561435444026</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-4.21</v>
+        <v>0</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EMHGl_EQ</t>
+          <t>GOOGL_US_EQ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>iShares J.P. Morgan USD EM Bond (Dist)</t>
+          <t>Alphabet (Class A)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IE00BDFGJ734</t>
+          <t>US02079K3059</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>3.8455</v>
+        <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>3.755</v>
+        <v>338.7</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>538.37</v>
+        <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>525.7</v>
+        <v>511.16</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01180108802574554</v>
+        <v>0.01150354968090455</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-12.67</v>
+        <v>103.24</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02353400078013262</v>
+        <v>0.2530888409492057</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
+        <v>-1.3</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
     </row>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>231.8</v>
+        <v>232.99</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>192.81</v>
+        <v>195.19</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004328262853802545</v>
+        <v>0.004392710427685576</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-3.71</v>
+        <v>-1.33</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.01887848565031549</v>
+        <v>-0.006767759006716874</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.51</v>
+        <v>1.92</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>269.64</v>
+        <v>263.92</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>128.12</v>
+        <v>126.31</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002876080269846907</v>
+        <v>0.002842580327480737</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>28.27</v>
+        <v>26.46</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2831246870305458</v>
+        <v>0.2649974962443666</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>91.20399179</v>
+        <v>188.32884805</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>103.75</v>
+        <v>205.66</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>105.28</v>
+        <v>110.41</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>121.11</v>
+        <v>122.69</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002718717463949101</v>
+        <v>0.00276111297900888</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>15.83</v>
+        <v>12.28</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.1503609422492401</v>
+        <v>0.111221809618694</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1.19</v>
+        <v>1.94</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7905852</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2251,25 +2251,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>42.31</v>
+        <v>42.54</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>120.93</v>
+        <v>122.46</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.00271467676422562</v>
+        <v>0.002755936876757905</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>12.7</v>
+        <v>14.23</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1173426961101358</v>
+        <v>0.1314792571375774</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1.19</v>
+        <v>1.97</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>3.81488812</v>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.55804584</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>235.02053179</v>
+        <v>91.20399179</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>258</v>
+        <v>103.9</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>108.77</v>
+        <v>105.28</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>120.7</v>
+        <v>122.15</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002709513647912283</v>
+        <v>0.002748960391115288</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>11.93</v>
+        <v>16.87</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1096809782109037</v>
+        <v>0.1602393617021277</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1.18</v>
+        <v>1.94</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.55804584</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>188.32884805</v>
+        <v>228.00445932</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>203</v>
+        <v>268.1</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>110.41</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120.24</v>
+        <v>119.73</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002699187415285608</v>
+        <v>0.002694498793518079</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>9.83</v>
+        <v>19.88</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.08903179059867766</v>
+        <v>0.1990986479719579</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1.14</v>
+        <v>1.97</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2422,25 +2422,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>120.7</v>
+        <v>119.5</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.87</v>
+        <v>119.53</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002690881532520673</v>
+        <v>0.002689997835038972</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.001169297586235697</v>
+        <v>-0.001670425123193853</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1.1</v>
+        <v>1.97</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>1.32559468</v>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.62445608</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45.93199509</v>
+        <v>235.02053179</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>47.9</v>
+        <v>253</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>112.71</v>
+        <v>108.77</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>118.73</v>
+        <v>119.22</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002665290434271958</v>
+        <v>0.002683021349396354</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>6.02</v>
+        <v>10.45</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.05341140981279389</v>
+        <v>0.09607428518893077</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>1.14</v>
+        <v>1.98</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.62445608</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>57.56703616</v>
+        <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>63.04</v>
+        <v>560.35</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>106.81</v>
+        <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.27</v>
+        <v>118.55</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002654964201645283</v>
+        <v>0.002667943138491342</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>11.46</v>
+        <v>12.8</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1072933245950754</v>
+        <v>0.1210401891252955</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1.19</v>
+        <v>1.97</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>3.30858696</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>228.00445932</v>
+        <v>45.93199509</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>266.57</v>
+        <v>47.41</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>112.71</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.2</v>
+        <v>118.37</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002653392818419485</v>
+        <v>0.002663892275860144</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>18.35</v>
+        <v>5.66</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1837756634952429</v>
+        <v>0.05021737201667998</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>1.25</v>
+        <v>1.97</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>3.30858696</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.42010405</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>509.16500577</v>
+        <v>350.55601106</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>556.04</v>
+        <v>366.36</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>105.75</v>
+        <v>109.16</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.8</v>
+        <v>116.14</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002621965153903518</v>
+        <v>0.002613706588818089</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>11.05</v>
+        <v>6.98</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1044917257683215</v>
+        <v>0.06394283620373764</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.42010405</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.50421091</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>79.10567143</v>
+        <v>57.56703616</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>88.61</v>
+        <v>61.35</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>101.53</v>
+        <v>106.81</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>115.11</v>
+        <v>115.93</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002584027473166386</v>
+        <v>0.002608980582415025</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>13.58</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1337535703732887</v>
+        <v>0.08538526355210185</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>1.23</v>
+        <v>1.97</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.50421091</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.73400968</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>350.55601106</v>
+        <v>79.10567143</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>363.85</v>
+        <v>88.12</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>109.16</v>
+        <v>101.53</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.52</v>
+        <v>115.3</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002570782957406086</v>
+        <v>0.002594802563205835</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5.36</v>
+        <v>13.77</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.0491022352510077</v>
+        <v>0.1356249384418398</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.73400968</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2821,25 +2821,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>56.07</v>
+        <v>55.72</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.72</v>
+        <v>113.83</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.00255282429196839</v>
+        <v>0.00256172051838439</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>6.08</v>
+        <v>6.19</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.05648457822370866</v>
+        <v>0.05750650315867707</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>1.18</v>
+        <v>1.97</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>2.70722512</v>
@@ -2878,25 +2878,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>94.04000000000001</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.03</v>
+        <v>110.7</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002514886611231259</v>
+        <v>0.002491280518186348</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>22.37</v>
+        <v>21.04</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.249498103948249</v>
+        <v>0.2346642873076065</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1.11</v>
+        <v>1.77</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>1.59010207</v>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.7</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>54.82621761</v>
+        <v>225.62857143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>52.67</v>
+        <v>207.88</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>112.48</v>
+        <v>118.76</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>109.16</v>
+        <v>109.81</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002450459898973527</v>
+        <v>0.002471251252954317</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-3.32</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.02951635846372688</v>
+        <v>-0.07536207477265071</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>1.15</v>
+        <v>0.43</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>12.56856884</v>
+        <v>54.82621761</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>12.77</v>
+        <v>51.92</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>106.15</v>
+        <v>112.48</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.07</v>
+        <v>108.38</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002448439549111787</v>
+        <v>0.002439069399828693</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.92</v>
+        <v>-4.1</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.0275082430522845</v>
+        <v>-0.03645092460881934</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,38 +3043,38 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.7</v>
+        <v>11.40066159</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>225.62857143</v>
+        <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>205.93</v>
+        <v>12.57</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>118.76</v>
+        <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108</v>
+        <v>108.14</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002424419834088869</v>
+        <v>0.002433668249653764</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>-10.76</v>
+        <v>1.99</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>-0.0906028965981812</v>
+        <v>0.01874705605275553</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.43</v>
+        <v>1.98</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0</v>
+        <v>11.40066159</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3106,25 +3106,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>327.7</v>
+        <v>326.46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107</v>
+        <v>107.36</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.00240197150229175</v>
+        <v>0.002416114511585242</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>2.96</v>
+        <v>3.32</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.02845059592464437</v>
+        <v>0.03191080353710111</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1.21</v>
+        <v>1.97</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>0.43583007</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.51881442</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>324.07677699</v>
+        <v>249.91595261</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>336.05</v>
+        <v>273.42</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>101.39</v>
+        <v>95.94</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>106.39</v>
+        <v>107.04</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002388278019895507</v>
+        <v>0.002408912978018669</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>5</v>
+        <v>11.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.04931452805996647</v>
+        <v>0.115697310819262</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.51881442</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>104.90344487</v>
+        <v>257.81779936</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>122.65</v>
+        <v>279.9</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>105.98</v>
+        <v>107.03</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002379074203858688</v>
+        <v>0.002408687930094714</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>16.45</v>
+        <v>10.35</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1837372947615324</v>
+        <v>0.1070541994207695</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1.12</v>
+        <v>1.91</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.50675322</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.42255419</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>257.81779936</v>
+        <v>324.07677699</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>277</v>
+        <v>335.21</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>105.17</v>
+        <v>106.88</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002360891055103022</v>
+        <v>0.002405312211235382</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>8.49</v>
+        <v>5.49</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.08781547372776169</v>
+        <v>0.05414735180984318</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1.21</v>
+        <v>1.94</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.42255419</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.90543241</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>249.91595261</v>
+        <v>137.713206</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>270.47</v>
+        <v>154.1</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>95.94</v>
+        <v>92.27</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>105.13</v>
+        <v>105.29</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002359993121831137</v>
+        <v>0.002369529591326473</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>9.19</v>
+        <v>13.02</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.09578903481342506</v>
+        <v>0.1411076189444023</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>1.2</v>
+        <v>1.82</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.90543241</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>148.63893521</v>
+        <v>104.90344487</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>174.41</v>
+        <v>120.47</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>88.44</v>
+        <v>89.53</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>105.07</v>
+        <v>104.85</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.00235864622192331</v>
+        <v>0.002359627482672435</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>16.63</v>
+        <v>15.32</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1880370872908186</v>
+        <v>0.1711158270970624</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1.1</v>
+        <v>1.77</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.1533463</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.40867246</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>176.50746647</v>
+        <v>306.99401668</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>204.23</v>
+        <v>337.9</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>92.83</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>104.8</v>
+        <v>104.2</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002352585172338088</v>
+        <v>0.002344999367615334</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>15.34</v>
+        <v>11.37</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1714732841493405</v>
+        <v>0.1224819562641387</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1.11</v>
+        <v>1.84</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.40867246</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.5550481</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>137.713206</v>
+        <v>221.99877812</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>154.19</v>
+        <v>248</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>92.27</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>104.59</v>
+        <v>103.87</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002347871022660693</v>
+        <v>0.002337572786124805</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>12.32</v>
+        <v>12.69</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1335211878183592</v>
+        <v>0.1391752577319587</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>1.14</v>
+        <v>1.8</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.5550481</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>306.99401668</v>
+        <v>148.63893521</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>340.7</v>
+        <v>170.5</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>92.83</v>
+        <v>88.44</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>104.31</v>
+        <v>103.45</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.0023415854897575</v>
+        <v>0.002328120773318678</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>11.48</v>
+        <v>15.01</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1236669180221911</v>
+        <v>0.1697195838986884</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.68495686</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>176.50746647</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1068.48</v>
+        <v>199.55</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>98.89</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>102.92</v>
+        <v>103.14</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002310382308559504</v>
+        <v>0.00232114428767606</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>4.03</v>
+        <v>13.68</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.04075235109717869</v>
+        <v>0.1529175050301811</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.68495686</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.17949395</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>74.99726962</v>
+        <v>113.12478542</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>78.42</v>
+        <v>115.25</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>98.72</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>102.35</v>
+        <v>102.58</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002297586759435146</v>
+        <v>0.002308541603934558</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.67</v>
+        <v>3.86</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.05864708316094331</v>
+        <v>0.03910048622366288</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.17949395</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.1285649</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>194.45976548</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>222.16</v>
+        <v>1057.2</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>88.09</v>
+        <v>98.89</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>101.89</v>
+        <v>102.56</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002287260526808471</v>
+        <v>0.002308091508086647</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>13.8</v>
+        <v>3.67</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1566579634464752</v>
+        <v>0.03711194256244311</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1.1</v>
+        <v>1.95</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.1285649</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.61215748</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>147.21071381</v>
+        <v>194.45976548</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>148</v>
+        <v>221.27</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>101.61</v>
+        <v>102.21</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002280974993905278</v>
+        <v>0.002300214830748208</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.76</v>
+        <v>14.12</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.01762643965948923</v>
+        <v>0.1602906118742195</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1.22</v>
+        <v>1.74</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.61215748</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>221.99877812</v>
+        <v>147.21071381</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>244</v>
+        <v>147.38</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>101.47</v>
+        <v>101.91</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002277832227453681</v>
+        <v>0.002293463393029545</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>10.29</v>
+        <v>2.06</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1128536959859618</v>
+        <v>0.02063094641962945</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1.14</v>
+        <v>1.94</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>113.12478542</v>
+        <v>74.99726962</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>114.6</v>
+        <v>77.15000000000001</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>98.72</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>101.27</v>
+        <v>101.42</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002273342561094257</v>
+        <v>0.00228243604475573</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2.55</v>
+        <v>4.74</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.02583063209076175</v>
+        <v>0.04902772031443939</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1.25</v>
+        <v>1.91</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>10.85229847</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>10.11</v>
+        <v>1272.47</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>106.96</v>
+        <v>88.89</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>100.76</v>
+        <v>100.3</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002261893911877727</v>
+        <v>0.002257230677272725</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-6.2</v>
+        <v>11.41</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.05796559461480928</v>
+        <v>0.1283608954888064</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1.2</v>
+        <v>1.76</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.10445851</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4018,25 +4018,25 @@
         <v>96.717382</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>100.35</v>
+        <v>99.89</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002252690095840908</v>
+        <v>0.002248003712390553</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3.67</v>
+        <v>3.21</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.03796028134050475</v>
+        <v>0.03320231692180389</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1.21</v>
+        <v>1.91</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.35094641</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>13.30225117</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>10.85229847</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1265.69</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>88.89</v>
+        <v>106.96</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>99.05</v>
+        <v>99.88</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002223507264504653</v>
+        <v>0.002247778664466598</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>10.16</v>
+        <v>-7.08</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1142985712678592</v>
+        <v>-0.0661929693343306</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>13.30225117</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>127.23134407</v>
+        <v>341.38450299</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>116.56</v>
+        <v>343.82</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>105.36</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>97.63</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002191630633352743</v>
+        <v>0.002207720134002535</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-7.73</v>
+        <v>2.59</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.07336750189825361</v>
+        <v>0.0271175793110669</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1.21</v>
+        <v>1.9</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.37810738</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.17308322</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>341.38450299</v>
+        <v>126.99866255</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>343.5</v>
+        <v>110.39</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>110.45</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>97.31</v>
+        <v>97.72</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002184447167177665</v>
+        <v>0.00219916831289223</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>1.8</v>
+        <v>-12.73</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.01884619411579939</v>
+        <v>-0.1152557718424626</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1.2</v>
+        <v>1.97</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.17308322</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1.17308322<